--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PamelaSilvaTeixeira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6942C9-BBE3-4D6F-BA7E-2EF338C69F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A358F550-7A5A-42B0-8489-B38D1302F070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="551" xr2:uid="{9E8F4E85-D2FF-4383-A72B-5CAFDCCC5644}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="238">
   <si>
     <t>Origem</t>
   </si>
@@ -470,9 +470,6 @@
     <t>MINERIO</t>
   </si>
   <si>
-    <t>640,00</t>
-  </si>
-  <si>
     <t>repom</t>
   </si>
   <si>
@@ -527,9 +524,6 @@
     <t>170,00</t>
   </si>
   <si>
-    <t>Truck, Bitruck, Bitrem 7 eixos</t>
-  </si>
-  <si>
     <t>Barro Alto - GO</t>
   </si>
   <si>
@@ -602,156 +596,166 @@
     <t>milho</t>
   </si>
   <si>
+    <t>Hidrolândia - GO</t>
+  </si>
+  <si>
+    <t>55,00</t>
+  </si>
+  <si>
+    <t>Palmeiras de Goiás - GO</t>
+  </si>
+  <si>
+    <t>Jataí - GO</t>
+  </si>
+  <si>
+    <t>31,00</t>
+  </si>
+  <si>
+    <t>Avelinópolis - GO</t>
+  </si>
+  <si>
+    <t>Edéia - GO</t>
+  </si>
+  <si>
+    <t>Rio Verde - GO</t>
+  </si>
+  <si>
+    <t>Quirinópolis - GO</t>
+  </si>
+  <si>
+    <t>85,00</t>
+  </si>
+  <si>
+    <t>Montividiu - GO</t>
+  </si>
+  <si>
+    <t>65,00</t>
+  </si>
+  <si>
+    <t>80,00</t>
+  </si>
+  <si>
+    <t>Araguari - MG</t>
+  </si>
+  <si>
+    <t>135,00</t>
+  </si>
+  <si>
+    <t>Bonfinópolis de Minas - MG</t>
+  </si>
+  <si>
+    <t>Montes Claros - MG</t>
+  </si>
+  <si>
+    <t>157,00</t>
+  </si>
+  <si>
+    <t>Diversos</t>
+  </si>
+  <si>
+    <t>Cajati - SP</t>
+  </si>
+  <si>
+    <t>Carreta LS, Vanderléia, Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>Botucatu - SP</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
+  </si>
+  <si>
+    <t>Anhembi - SP</t>
+  </si>
+  <si>
+    <t>97,00</t>
+  </si>
+  <si>
+    <t>Primavera - PA</t>
+  </si>
+  <si>
+    <t>PARA MOTORISTAS CATIVOS NA REGIÃO - PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Toco, Truck</t>
+  </si>
+  <si>
+    <t>Marzagão - GO</t>
+  </si>
+  <si>
+    <t>70,00</t>
+  </si>
+  <si>
+    <t>Cezarina - GO</t>
+  </si>
+  <si>
+    <t>30,00</t>
+  </si>
+  <si>
+    <t>Rio Branco do Sul - PR</t>
+  </si>
+  <si>
+    <t>Carreta LS, Vanderléia</t>
+  </si>
+  <si>
+    <t>72,00</t>
+  </si>
+  <si>
+    <t>Itaperuçu - PR</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>Vidal Ramos - SC</t>
+  </si>
+  <si>
+    <t>150,00</t>
+  </si>
+  <si>
+    <t>650,00</t>
+  </si>
+  <si>
+    <t>60,00</t>
+  </si>
+  <si>
+    <t>São Pedro - SP</t>
+  </si>
+  <si>
+    <t>Cajamar - SP</t>
+  </si>
+  <si>
+    <t>Areia</t>
+  </si>
+  <si>
+    <t>115,00</t>
+  </si>
+  <si>
+    <t>Joinville - SC</t>
+  </si>
+  <si>
+    <t>São José - SC</t>
+  </si>
+  <si>
+    <t>Tubos e Conexões</t>
+  </si>
+  <si>
+    <t>Sider, Baú</t>
+  </si>
+  <si>
+    <t>1.150,00</t>
+  </si>
+  <si>
+    <t>precisa de MOPP ativo</t>
+  </si>
+  <si>
+    <t>Castro - PR</t>
+  </si>
+  <si>
+    <t>Chapadão do Sul - MS</t>
+  </si>
+  <si>
     <t>57,00</t>
-  </si>
-  <si>
-    <t>Hidrolândia - GO</t>
-  </si>
-  <si>
-    <t>55,00</t>
-  </si>
-  <si>
-    <t>Palmeiras de Goiás - GO</t>
-  </si>
-  <si>
-    <t>61,00</t>
-  </si>
-  <si>
-    <t>Nazário - GO</t>
-  </si>
-  <si>
-    <t>Jataí - GO</t>
-  </si>
-  <si>
-    <t>58,00</t>
-  </si>
-  <si>
-    <t>31,00</t>
-  </si>
-  <si>
-    <t>Avelinópolis - GO</t>
-  </si>
-  <si>
-    <t>Edéia - GO</t>
-  </si>
-  <si>
-    <t>Rio Verde - GO</t>
-  </si>
-  <si>
-    <t>Quirinópolis - GO</t>
-  </si>
-  <si>
-    <t>85,00</t>
-  </si>
-  <si>
-    <t>Montividiu - GO</t>
-  </si>
-  <si>
-    <t>35,00</t>
-  </si>
-  <si>
-    <t>65,00</t>
-  </si>
-  <si>
-    <t>80,00</t>
-  </si>
-  <si>
-    <t>Araguari - MG</t>
-  </si>
-  <si>
-    <t>135,00</t>
-  </si>
-  <si>
-    <t>Bonfinópolis de Minas - MG</t>
-  </si>
-  <si>
-    <t>Montes Claros - MG</t>
-  </si>
-  <si>
-    <t>157,00</t>
-  </si>
-  <si>
-    <t>Diversos</t>
-  </si>
-  <si>
-    <t>Cajati - SP</t>
-  </si>
-  <si>
-    <t>Itajaí - SC</t>
-  </si>
-  <si>
-    <t>125,00</t>
-  </si>
-  <si>
-    <t>Carreta LS, Vanderléia, Bitrem 7 eixos</t>
-  </si>
-  <si>
-    <t>Botucatu - SP</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
-  </si>
-  <si>
-    <t>Anhembi - SP</t>
-  </si>
-  <si>
-    <t>97,00</t>
-  </si>
-  <si>
-    <t>Primavera - PA</t>
-  </si>
-  <si>
-    <t>PARA MOTORISTAS CATIVOS NA REGIÃO - PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Toco, Truck</t>
-  </si>
-  <si>
-    <t>CALCARIO</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Bitrem 9 eixos</t>
-  </si>
-  <si>
-    <t>CALCARIO A GRANEL CARGA PARA RODO CAÇAMBA
-DESCARGA BEIRA DE PISTA</t>
-  </si>
-  <si>
-    <t>CALCARIO ITAPEVA SP X ANHEMBI CARGA PARA CAÇAMBA -
-CALCARIO GRANEL</t>
-  </si>
-  <si>
-    <t>Bitrem 9 eixos</t>
-  </si>
-  <si>
-    <t>Vicentinópolis - GO</t>
-  </si>
-  <si>
-    <t>49,00</t>
-  </si>
-  <si>
-    <t>Marzagão - GO</t>
-  </si>
-  <si>
-    <t>70,00</t>
-  </si>
-  <si>
-    <t>Cezarina - GO</t>
-  </si>
-  <si>
-    <t>30,00</t>
-  </si>
-  <si>
-    <t>Rio Branco do Sul - PR</t>
-  </si>
-  <si>
-    <t>Carreta LS, Vanderléia</t>
-  </si>
-  <si>
-    <t>72,00</t>
-  </si>
-  <si>
-    <t>Itaperuçu - PR</t>
   </si>
 </sst>
 </file>
@@ -1151,10 +1155,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}">
-  <dimension ref="A1:J113"/>
-  <sheetFormatPr defaultColWidth="24.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J111"/>
+  <sheetFormatPr defaultColWidth="12.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="9" max="10" width="24.26953125" style="3"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="255.6328125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1191,13 +1204,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1206,24 +1219,27 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>190</v>
+        <v>220</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1232,24 +1248,27 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>227</v>
+        <v>228</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1258,24 +1277,27 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>188</v>
+        <v>222</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1284,24 +1306,27 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>222</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -1310,24 +1335,27 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>217</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>186</v>
+        <v>218</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1336,24 +1364,27 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>206</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>229</v>
+        <v>218</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C8" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1362,24 +1393,27 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>202</v>
+        <v>218</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1388,24 +1422,27 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>193</v>
+        <v>196</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1414,24 +1451,27 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>206</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>194</v>
+        <v>196</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1440,24 +1480,27 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>206</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>231</v>
+        <v>111</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>198</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -1466,50 +1509,56 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>199</v>
+        <v>112</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="B13" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>231</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>188</v>
+        <v>233</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
@@ -1518,24 +1567,27 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>188</v>
+        <v>166</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>232</v>
+        <v>114</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -1544,13 +1596,13 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>233</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>117</v>
@@ -1558,13 +1610,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
-        <v>232</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -1573,13 +1625,13 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>234</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>117</v>
@@ -1590,7 +1642,7 @@
         <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
@@ -1602,13 +1654,13 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>117</v>
@@ -1616,13 +1668,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -1631,27 +1683,30 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>234</v>
+        <v>168</v>
+      </c>
+      <c r="I18" s="3">
+        <v>28000</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -1660,27 +1715,30 @@
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>208</v>
+        <v>168</v>
+      </c>
+      <c r="I19" s="3">
+        <v>28000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -1689,27 +1747,27 @@
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -1718,27 +1776,30 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" t="s">
         <v>169</v>
       </c>
-      <c r="G21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" t="s">
-        <v>212</v>
+      <c r="I21" s="3">
+        <v>28000</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="B22" t="s">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -1747,27 +1808,30 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>213</v>
+        <v>22</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>212</v>
+        <v>168</v>
+      </c>
+      <c r="I22" s="3">
+        <v>28000</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B23" t="s">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -1776,27 +1840,30 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
         <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>203</v>
+        <v>169</v>
+      </c>
+      <c r="I23" s="3">
+        <v>28000</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B24" t="s">
-        <v>216</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -1805,27 +1872,30 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>215</v>
+        <v>22</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>203</v>
+        <v>168</v>
+      </c>
+      <c r="I24" s="3">
+        <v>28000</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -1840,18 +1910,21 @@
         <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>164</v>
+        <v>170</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -1860,27 +1933,27 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>167</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -1889,13 +1962,13 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>215</v>
+        <v>22</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>21</v>
@@ -1903,13 +1976,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -1918,13 +1991,13 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>21</v>
@@ -1932,13 +2005,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -1947,27 +2020,27 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -1976,27 +2049,27 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -2005,27 +2078,27 @@
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2034,30 +2107,27 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
       </c>
       <c r="H32" t="s">
-        <v>170</v>
-      </c>
-      <c r="I32" s="3">
-        <v>28000</v>
+        <v>176</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -2066,30 +2136,27 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>169</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
         <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>170</v>
-      </c>
-      <c r="I33" s="3">
-        <v>28000</v>
+        <v>176</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -2098,27 +2165,27 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -2127,30 +2194,27 @@
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>171</v>
-      </c>
-      <c r="I35" s="3">
-        <v>28000</v>
+        <v>177</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -2159,30 +2223,27 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="G36" t="s">
         <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>170</v>
-      </c>
-      <c r="I36" s="3">
-        <v>28000</v>
+        <v>178</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -2191,30 +2252,27 @@
         <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="H37" t="s">
-        <v>171</v>
-      </c>
-      <c r="I37" s="3">
-        <v>28000</v>
+        <v>135</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -2223,30 +2281,30 @@
         <v>11</v>
       </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G38" t="s">
         <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="I38" s="3">
-        <v>28000</v>
+        <v>52</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -2255,27 +2313,27 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="G39" t="s">
         <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2284,27 +2342,27 @@
         <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
         <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -2313,27 +2371,27 @@
         <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G41" t="s">
         <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -2342,27 +2400,27 @@
         <v>11</v>
       </c>
       <c r="F42" t="s">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="G42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H42" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>197</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -2371,27 +2429,27 @@
         <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H43" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -2400,27 +2458,27 @@
         <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H44" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>176</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
@@ -2429,27 +2487,27 @@
         <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="G45" t="s">
         <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -2458,85 +2516,85 @@
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="G46" t="s">
         <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="C47" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="E47" t="s">
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G47" t="s">
         <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>178</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>21</v>
+        <v>208</v>
+      </c>
+      <c r="I47" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="E48" t="s">
         <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="G48" t="s">
         <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>179</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>21</v>
+        <v>155</v>
+      </c>
+      <c r="I48" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -2545,27 +2603,24 @@
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G49" t="s">
         <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>179</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -2574,27 +2629,27 @@
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>98</v>
+        <v>163</v>
       </c>
       <c r="G50" t="s">
         <v>14</v>
       </c>
       <c r="H50" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -2603,13 +2658,13 @@
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>21</v>
@@ -2617,13 +2672,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="B52" t="s">
         <v>36</v>
       </c>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -2632,30 +2687,27 @@
         <v>11</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
         <v>14</v>
       </c>
       <c r="H52" t="s">
-        <v>135</v>
-      </c>
-      <c r="I52" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>136</v>
+        <v>235</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>236</v>
       </c>
       <c r="C53" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2664,27 +2716,21 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="G53" t="s">
         <v>14</v>
-      </c>
-      <c r="H53" t="s">
-        <v>100</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>194</v>
       </c>
       <c r="B54" t="s">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -2696,24 +2742,21 @@
         <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H54" t="s">
-        <v>142</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -2722,27 +2765,24 @@
         <v>11</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H55" t="s">
-        <v>146</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>147</v>
+        <v>212</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -2751,27 +2791,24 @@
         <v>11</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s">
-        <v>150</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>138</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>183</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
@@ -2780,27 +2817,24 @@
         <v>11</v>
       </c>
       <c r="F57" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>182</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>106</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>187</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -2809,59 +2843,53 @@
         <v>11</v>
       </c>
       <c r="F58" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H58" t="s">
-        <v>182</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>106</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>151</v>
+        <v>214</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="E59" t="s">
         <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H59" t="s">
-        <v>217</v>
-      </c>
-      <c r="I59" s="3">
-        <v>49</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
         <v>11</v>
@@ -2870,24 +2898,21 @@
         <v>28</v>
       </c>
       <c r="G60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H60" t="s">
-        <v>156</v>
-      </c>
-      <c r="I60" s="3">
-        <v>49</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="C61" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -2896,24 +2921,24 @@
         <v>11</v>
       </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H61" t="s">
-        <v>112</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
@@ -2922,45 +2947,39 @@
         <v>11</v>
       </c>
       <c r="F62" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H62" t="s">
-        <v>160</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D63" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G63" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
@@ -2968,7 +2987,7 @@
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
         <v>40</v>
@@ -2980,13 +2999,13 @@
         <v>11</v>
       </c>
       <c r="F64" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G64" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
@@ -3006,13 +3025,13 @@
         <v>11</v>
       </c>
       <c r="F65" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G65" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
@@ -3032,21 +3051,21 @@
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C67" t="s">
         <v>40</v>
@@ -3058,13 +3077,13 @@
         <v>11</v>
       </c>
       <c r="F67" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G67" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
@@ -3072,7 +3091,7 @@
         <v>48</v>
       </c>
       <c r="B68" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C68" t="s">
         <v>40</v>
@@ -3098,7 +3117,7 @@
         <v>48</v>
       </c>
       <c r="B69" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C69" t="s">
         <v>40</v>
@@ -3124,7 +3143,7 @@
         <v>48</v>
       </c>
       <c r="B70" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C70" t="s">
         <v>40</v>
@@ -3147,10 +3166,10 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C71" t="s">
         <v>40</v>
@@ -3168,15 +3187,15 @@
         <v>42</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B72" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C72" t="s">
         <v>40</v>
@@ -3191,36 +3210,36 @@
         <v>50</v>
       </c>
       <c r="G72" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B73" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C73" t="s">
         <v>40</v>
       </c>
       <c r="D73" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
       </c>
       <c r="F73" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G73" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
@@ -3240,7 +3259,7 @@
         <v>11</v>
       </c>
       <c r="F74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G74" t="s">
         <v>42</v>
@@ -3251,16 +3270,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C75" t="s">
         <v>40</v>
       </c>
       <c r="D75" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E75" t="s">
         <v>11</v>
@@ -3269,18 +3288,18 @@
         <v>60</v>
       </c>
       <c r="G75" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="B76" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C76" t="s">
         <v>40</v>
@@ -3292,21 +3311,21 @@
         <v>11</v>
       </c>
       <c r="F76" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G76" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B77" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
         <v>40</v>
@@ -3324,7 +3343,7 @@
         <v>42</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
@@ -3335,7 +3354,7 @@
         <v>44</v>
       </c>
       <c r="C78" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D78" t="s">
         <v>41</v>
@@ -3350,18 +3369,18 @@
         <v>42</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>44</v>
+        <v>209</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>209</v>
       </c>
       <c r="C79" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D79" t="s">
         <v>41</v>
@@ -3370,21 +3389,21 @@
         <v>11</v>
       </c>
       <c r="F79" t="s">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="G79" t="s">
         <v>42</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="B80" t="s">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="C80" t="s">
         <v>40</v>
@@ -3396,21 +3415,21 @@
         <v>11</v>
       </c>
       <c r="F80" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G80" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>219</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="B81" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="C81" t="s">
         <v>40</v>
@@ -3422,39 +3441,39 @@
         <v>11</v>
       </c>
       <c r="F81" t="s">
-        <v>220</v>
+        <v>65</v>
       </c>
       <c r="G81" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
         <v>40</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E82" t="s">
         <v>11</v>
       </c>
       <c r="F82" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
@@ -3474,7 +3493,7 @@
         <v>11</v>
       </c>
       <c r="F83" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G83" t="s">
         <v>75</v>
@@ -3485,10 +3504,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C84" t="s">
         <v>40</v>
@@ -3500,10 +3519,10 @@
         <v>11</v>
       </c>
       <c r="F84" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="J84" s="3" t="s">
         <v>76</v>
@@ -3511,10 +3530,10 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="B85" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="C85" t="s">
         <v>40</v>
@@ -3526,13 +3545,13 @@
         <v>11</v>
       </c>
       <c r="F85" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="G85" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
@@ -3552,7 +3571,7 @@
         <v>11</v>
       </c>
       <c r="F86" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G86" t="s">
         <v>75</v>
@@ -3578,7 +3597,7 @@
         <v>11</v>
       </c>
       <c r="F87" t="s">
-        <v>233</v>
+        <v>60</v>
       </c>
       <c r="G87" t="s">
         <v>75</v>
@@ -3589,25 +3608,25 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C88" t="s">
         <v>40</v>
       </c>
       <c r="D88" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
       </c>
       <c r="F88" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="J88" s="3" t="s">
         <v>64</v>
@@ -3630,7 +3649,7 @@
         <v>11</v>
       </c>
       <c r="F89" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="G89" t="s">
         <v>67</v>
@@ -4196,93 +4215,32 @@
         <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="D111" t="s">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="E111" t="s">
         <v>11</v>
       </c>
       <c r="F111" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="G111" t="s">
         <v>14</v>
       </c>
       <c r="H111" t="s">
-        <v>168</v>
-      </c>
-      <c r="I111" s="3">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>108</v>
-      </c>
-      <c r="B112" t="s">
-        <v>216</v>
-      </c>
-      <c r="C112" t="s">
-        <v>221</v>
-      </c>
-      <c r="D112" t="s">
-        <v>209</v>
-      </c>
-      <c r="E112" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" t="s">
-        <v>222</v>
-      </c>
-      <c r="G112" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112" t="s">
-        <v>203</v>
-      </c>
-      <c r="J112" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>108</v>
-      </c>
-      <c r="B113" t="s">
-        <v>109</v>
-      </c>
-      <c r="C113" t="s">
-        <v>221</v>
-      </c>
-      <c r="D113" t="s">
-        <v>154</v>
-      </c>
-      <c r="E113" t="s">
-        <v>11</v>
-      </c>
-      <c r="F113" t="s">
-        <v>225</v>
-      </c>
-      <c r="G113" t="s">
-        <v>14</v>
-      </c>
-      <c r="H113" t="s">
-        <v>111</v>
-      </c>
-      <c r="I113" s="3">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J113" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
+  <autoFilter ref="A1:J111" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PamelaSilvaTeixeira\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tr.alienigenaV5-main\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A358F550-7A5A-42B0-8489-B38D1302F070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B92DF0D5-E987-4DFF-9AFB-84A78CFD1C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="551" xr2:uid="{9E8F4E85-D2FF-4383-A72B-5CAFDCCC5644}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="551" xr2:uid="{9E8F4E85-D2FF-4383-A72B-5CAFDCCC5644}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$118</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="251">
   <si>
     <t>Origem</t>
   </si>
@@ -362,12 +362,6 @@
     <t>Salto de Pirapora - SP</t>
   </si>
   <si>
-    <t>VALOR PAGO NO CARTÃO REPOM OU PAGUEBEM / PEDAGIO PAGO NA TAG</t>
-  </si>
-  <si>
-    <t>Carreta LS, Vanderléia, Rodotrem</t>
-  </si>
-  <si>
     <t>Itapeva - SP</t>
   </si>
   <si>
@@ -542,9 +536,6 @@
     <t>Apenas 7 eixos acima 38 ton</t>
   </si>
   <si>
-    <t>75,00</t>
-  </si>
-  <si>
     <t>Carreta 4º eixo</t>
   </si>
   <si>
@@ -584,9 +575,6 @@
     <t>calcario/ clínquer</t>
   </si>
   <si>
-    <t>180,00</t>
-  </si>
-  <si>
     <t>Mineiros - GO</t>
   </si>
   <si>
@@ -608,9 +596,6 @@
     <t>Jataí - GO</t>
   </si>
   <si>
-    <t>31,00</t>
-  </si>
-  <si>
     <t>Avelinópolis - GO</t>
   </si>
   <si>
@@ -716,9 +701,6 @@
     <t>650,00</t>
   </si>
   <si>
-    <t>60,00</t>
-  </si>
-  <si>
     <t>São Pedro - SP</t>
   </si>
   <si>
@@ -756,6 +738,63 @@
   </si>
   <si>
     <t>57,00</t>
+  </si>
+  <si>
+    <t>Santa Filomena - PI</t>
+  </si>
+  <si>
+    <t>175,00</t>
+  </si>
+  <si>
+    <t>210,00</t>
+  </si>
+  <si>
+    <t>só aceita rodocaçambas com lona fácil. Caso não tenham, o veículo não passa na vistoria dos guardas</t>
+  </si>
+  <si>
+    <t>Goiatuba - GO</t>
+  </si>
+  <si>
+    <t>73,00</t>
+  </si>
+  <si>
+    <t>Itaberaí - GO</t>
+  </si>
+  <si>
+    <t>87,00</t>
+  </si>
+  <si>
+    <t>35,00</t>
+  </si>
+  <si>
+    <t>62,00</t>
+  </si>
+  <si>
+    <t>Penápolis - SP</t>
+  </si>
+  <si>
+    <t>Ureia granel</t>
+  </si>
+  <si>
+    <t>Alfenas - MG</t>
+  </si>
+  <si>
+    <t>PARA MOTORISTAS CATIVOS - NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Inocência - MS</t>
+  </si>
+  <si>
+    <t>7.500,00</t>
+  </si>
+  <si>
+    <t>Costa Rica - MS</t>
+  </si>
+  <si>
+    <t>Três Lagoas - MS</t>
+  </si>
+  <si>
+    <t>Paranaíba - MS</t>
   </si>
 </sst>
 </file>
@@ -1155,22 +1194,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}">
-  <dimension ref="A1:J111"/>
-  <sheetFormatPr defaultColWidth="12.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J118"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="255.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="255.6640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1202,15 +1241,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>232</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1225,21 +1264,21 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1248,28 +1287,28 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" t="s">
         <v>221</v>
       </c>
-      <c r="C4" t="s">
-        <v>152</v>
-      </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
@@ -1277,7 +1316,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>167</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
@@ -1286,18 +1325,18 @@
         <v>222</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1306,27 +1345,27 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B6" t="s">
         <v>216</v>
       </c>
       <c r="C6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -1335,27 +1374,27 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
         <v>217</v>
       </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>218</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1364,27 +1403,27 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1393,57 +1432,57 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>201</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s">
+        <v>213</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" t="s">
         <v>108</v>
       </c>
-      <c r="B9" t="s">
-        <v>205</v>
-      </c>
-      <c r="C9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>206</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>196</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B10" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" t="s">
-        <v>110</v>
-      </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -1451,28 +1490,28 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C11" t="s">
         <v>108</v>
       </c>
-      <c r="B11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" t="s">
-        <v>110</v>
-      </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
@@ -1480,27 +1519,27 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -1509,85 +1548,85 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>201</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>229</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>231</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>202</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
         <v>18</v>
       </c>
-      <c r="G13" t="s">
-        <v>232</v>
-      </c>
-      <c r="H13" t="s">
-        <v>233</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="G14" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14" t="s">
+        <v>227</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
         <v>113</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>166</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" t="s">
-        <v>115</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -1602,21 +1641,21 @@
         <v>14</v>
       </c>
       <c r="H15" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>116</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="B16" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="C16" t="s">
         <v>118</v>
-      </c>
-      <c r="B16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" t="s">
-        <v>120</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -1631,21 +1670,21 @@
         <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" t="s">
         <v>113</v>
-      </c>
-      <c r="B17" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" t="s">
-        <v>115</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -1660,18 +1699,18 @@
         <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -1683,24 +1722,24 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I18" s="3">
         <v>28000</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
         <v>105</v>
@@ -1715,30 +1754,30 @@
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I19" s="3">
         <v>28000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
         <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -1753,18 +1792,18 @@
         <v>14</v>
       </c>
       <c r="H20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>125</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="B21" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>127</v>
-      </c>
-      <c r="B21" t="s">
-        <v>128</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
@@ -1782,21 +1821,21 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I21" s="3">
         <v>28000</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
@@ -1814,18 +1853,18 @@
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I22" s="3">
         <v>28000</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
         <v>105</v>
@@ -1846,18 +1885,18 @@
         <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I23" s="3">
         <v>28000</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
         <v>105</v>
@@ -1878,24 +1917,24 @@
         <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I24" s="3">
         <v>28000</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>131</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -1910,21 +1949,21 @@
         <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -1933,27 +1972,27 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -1968,21 +2007,21 @@
         <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -1991,27 +2030,27 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -2026,21 +2065,21 @@
         <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -2055,21 +2094,21 @@
         <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -2084,21 +2123,21 @@
         <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2107,27 +2146,27 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
       </c>
       <c r="H32" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -2142,21 +2181,21 @@
         <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B34" t="s">
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -2165,27 +2204,27 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B35" t="s">
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -2200,21 +2239,21 @@
         <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
         <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -2229,21 +2268,21 @@
         <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -2258,21 +2297,21 @@
         <v>42</v>
       </c>
       <c r="H37" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B38" t="s">
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -2287,7 +2326,7 @@
         <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I38" s="3">
         <v>52</v>
@@ -2296,15 +2335,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -2313,7 +2352,7 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G39" t="s">
         <v>14</v>
@@ -2322,18 +2361,18 @@
         <v>100</v>
       </c>
       <c r="J39" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="C40" t="s">
         <v>139</v>
-      </c>
-      <c r="B40" t="s">
-        <v>140</v>
-      </c>
-      <c r="C40" t="s">
-        <v>141</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2348,21 +2387,21 @@
         <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -2377,21 +2416,21 @@
         <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -2406,21 +2445,21 @@
         <v>13</v>
       </c>
       <c r="H42" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>144</v>
+      </c>
+      <c r="B43" t="s">
+        <v>192</v>
+      </c>
+      <c r="C43" t="s">
         <v>146</v>
-      </c>
-      <c r="B43" t="s">
-        <v>197</v>
-      </c>
-      <c r="C43" t="s">
-        <v>148</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -2435,21 +2474,21 @@
         <v>13</v>
       </c>
       <c r="H43" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" t="s">
         <v>146</v>
-      </c>
-      <c r="B44" t="s">
-        <v>147</v>
-      </c>
-      <c r="C44" t="s">
-        <v>148</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -2464,82 +2503,82 @@
         <v>13</v>
       </c>
       <c r="H44" t="s">
+        <v>147</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>148</v>
+      </c>
+      <c r="B45" t="s">
         <v>149</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>19</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" t="s">
+        <v>151</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s">
+        <v>203</v>
+      </c>
+      <c r="I45" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>153</v>
+      </c>
+      <c r="I46" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" t="s">
         <v>105</v>
       </c>
-      <c r="C45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" t="s">
-        <v>104</v>
-      </c>
-      <c r="G45" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" t="s">
-        <v>180</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>105</v>
-      </c>
-      <c r="C46" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" t="s">
-        <v>107</v>
-      </c>
-      <c r="G46" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" t="s">
-        <v>180</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>150</v>
-      </c>
-      <c r="B47" t="s">
-        <v>151</v>
-      </c>
       <c r="C47" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D47" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
         <v>11</v>
@@ -2551,50 +2590,47 @@
         <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>208</v>
-      </c>
-      <c r="I47" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s">
+        <v>161</v>
+      </c>
+      <c r="G48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" t="s">
+        <v>162</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" t="s">
         <v>27</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>23</v>
-      </c>
-      <c r="D48" t="s">
-        <v>153</v>
-      </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" t="s">
-        <v>28</v>
-      </c>
-      <c r="G48" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" t="s">
-        <v>155</v>
-      </c>
-      <c r="I48" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>160</v>
-      </c>
-      <c r="B49" t="s">
-        <v>105</v>
-      </c>
-      <c r="C49" t="s">
-        <v>161</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -2609,18 +2645,21 @@
         <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>160</v>
+        <v>33</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -2629,27 +2668,27 @@
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>163</v>
+        <v>34</v>
       </c>
       <c r="G50" t="s">
         <v>14</v>
       </c>
       <c r="H50" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C51" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -2658,27 +2697,27 @@
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
         <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>159</v>
+        <v>37</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -2687,27 +2726,21 @@
         <v>11</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G52" t="s">
         <v>14</v>
       </c>
-      <c r="H52" t="s">
-        <v>37</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B53" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2716,18 +2749,21 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G53" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B54" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="C54" t="s">
         <v>31</v>
@@ -2739,24 +2775,24 @@
         <v>11</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
         <v>13</v>
       </c>
       <c r="H54" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C55" t="s">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -2765,24 +2801,24 @@
         <v>11</v>
       </c>
       <c r="F55" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G55" t="s">
         <v>13</v>
       </c>
       <c r="H55" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="B56" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C56" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -2794,47 +2830,47 @@
         <v>28</v>
       </c>
       <c r="G56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H56" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>207</v>
+      </c>
+      <c r="B57" t="s">
+        <v>180</v>
+      </c>
+      <c r="C57" t="s">
+        <v>179</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" t="s">
+        <v>28</v>
+      </c>
+      <c r="G57" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>183</v>
+      </c>
+      <c r="B58" t="s">
         <v>187</v>
       </c>
-      <c r="B57" t="s">
-        <v>192</v>
-      </c>
-      <c r="C57" t="s">
-        <v>183</v>
-      </c>
-      <c r="D57" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" t="s">
-        <v>13</v>
-      </c>
-      <c r="H57" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>187</v>
-      </c>
-      <c r="B58" t="s">
-        <v>182</v>
-      </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -2849,15 +2885,15 @@
         <v>13</v>
       </c>
       <c r="H58" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="B59" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
@@ -2869,21 +2905,21 @@
         <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
       </c>
       <c r="H59" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="B60" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C60" t="s">
         <v>31</v>
@@ -2901,15 +2937,15 @@
         <v>13</v>
       </c>
       <c r="H60" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="B61" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C61" t="s">
         <v>31</v>
@@ -2927,15 +2963,15 @@
         <v>13</v>
       </c>
       <c r="H61" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>79</v>
-      </c>
-      <c r="B62" t="s">
-        <v>79</v>
       </c>
       <c r="C62" t="s">
         <v>31</v>
@@ -2947,99 +2983,93 @@
         <v>11</v>
       </c>
       <c r="F62" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
       </c>
       <c r="H62" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
       </c>
       <c r="F63" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G63" t="s">
-        <v>62</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="H63" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>242</v>
       </c>
       <c r="C64" t="s">
-        <v>40</v>
+        <v>243</v>
       </c>
       <c r="D64" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
         <v>11</v>
       </c>
       <c r="F64" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>67</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>242</v>
       </c>
       <c r="C65" t="s">
-        <v>40</v>
+        <v>243</v>
       </c>
       <c r="D65" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
         <v>11</v>
       </c>
       <c r="F65" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G65" t="s">
-        <v>62</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C66" t="s">
         <v>40</v>
@@ -3051,21 +3081,21 @@
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G66" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C67" t="s">
         <v>40</v>
@@ -3077,21 +3107,21 @@
         <v>11</v>
       </c>
       <c r="F67" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G67" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C68" t="s">
         <v>40</v>
@@ -3103,21 +3133,21 @@
         <v>11</v>
       </c>
       <c r="F68" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G68" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C69" t="s">
         <v>40</v>
@@ -3129,21 +3159,21 @@
         <v>11</v>
       </c>
       <c r="F69" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>48</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C70" t="s">
         <v>40</v>
@@ -3164,12 +3194,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B71" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C71" t="s">
         <v>40</v>
@@ -3187,15 +3217,15 @@
         <v>42</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C72" t="s">
         <v>40</v>
@@ -3210,56 +3240,56 @@
         <v>50</v>
       </c>
       <c r="G72" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C73" t="s">
         <v>40</v>
       </c>
       <c r="D73" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
       </c>
       <c r="F73" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G73" t="s">
         <v>42</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C74" t="s">
         <v>40</v>
       </c>
       <c r="D74" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E74" t="s">
         <v>11</v>
       </c>
       <c r="F74" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G74" t="s">
         <v>42</v>
@@ -3268,12 +3298,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B75" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C75" t="s">
         <v>40</v>
@@ -3285,76 +3315,76 @@
         <v>11</v>
       </c>
       <c r="F75" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G75" t="s">
         <v>62</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C76" t="s">
         <v>40</v>
       </c>
       <c r="D76" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
       </c>
       <c r="F76" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="G76" t="s">
         <v>42</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C77" t="s">
         <v>40</v>
       </c>
       <c r="D77" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E77" t="s">
         <v>11</v>
       </c>
       <c r="F77" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="G77" t="s">
         <v>42</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C78" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D78" t="s">
         <v>41</v>
@@ -3363,21 +3393,21 @@
         <v>11</v>
       </c>
       <c r="F78" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="G78" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>209</v>
+        <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>209</v>
+        <v>39</v>
       </c>
       <c r="C79" t="s">
         <v>40</v>
@@ -3389,21 +3419,21 @@
         <v>11</v>
       </c>
       <c r="F79" t="s">
-        <v>206</v>
+        <v>18</v>
       </c>
       <c r="G79" t="s">
         <v>42</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="C80" t="s">
         <v>40</v>
@@ -3415,24 +3445,24 @@
         <v>11</v>
       </c>
       <c r="F80" t="s">
-        <v>211</v>
+        <v>18</v>
       </c>
       <c r="G80" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D81" t="s">
         <v>41</v>
@@ -3441,99 +3471,99 @@
         <v>11</v>
       </c>
       <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>42</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>204</v>
+      </c>
+      <c r="B82" t="s">
+        <v>204</v>
+      </c>
+      <c r="C82" t="s">
+        <v>40</v>
+      </c>
+      <c r="D82" t="s">
+        <v>41</v>
+      </c>
+      <c r="E82" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" t="s">
+        <v>201</v>
+      </c>
+      <c r="G82" t="s">
+        <v>42</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>73</v>
+      </c>
+      <c r="B83" t="s">
+        <v>73</v>
+      </c>
+      <c r="C83" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" t="s">
+        <v>41</v>
+      </c>
+      <c r="E83" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" t="s">
+        <v>206</v>
+      </c>
+      <c r="G83" t="s">
+        <v>67</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>26</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>40</v>
+      </c>
+      <c r="D84" t="s">
+        <v>41</v>
+      </c>
+      <c r="E84" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" t="s">
         <v>65</v>
       </c>
-      <c r="G81" t="s">
+      <c r="G84" t="s">
         <v>62</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="J84" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>29</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B85" t="s">
         <v>29</v>
-      </c>
-      <c r="C82" t="s">
-        <v>40</v>
-      </c>
-      <c r="D82" t="s">
-        <v>58</v>
-      </c>
-      <c r="E82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" t="s">
-        <v>15</v>
-      </c>
-      <c r="G82" t="s">
-        <v>75</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>29</v>
-      </c>
-      <c r="B83" t="s">
-        <v>29</v>
-      </c>
-      <c r="C83" t="s">
-        <v>40</v>
-      </c>
-      <c r="D83" t="s">
-        <v>58</v>
-      </c>
-      <c r="E83" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" t="s">
-        <v>17</v>
-      </c>
-      <c r="G83" t="s">
-        <v>75</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>77</v>
-      </c>
-      <c r="B84" t="s">
-        <v>77</v>
-      </c>
-      <c r="C84" t="s">
-        <v>40</v>
-      </c>
-      <c r="D84" t="s">
-        <v>58</v>
-      </c>
-      <c r="E84" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" t="s">
-        <v>15</v>
-      </c>
-      <c r="G84" t="s">
-        <v>67</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>30</v>
-      </c>
-      <c r="B85" t="s">
-        <v>30</v>
       </c>
       <c r="C85" t="s">
         <v>40</v>
@@ -3545,21 +3575,21 @@
         <v>11</v>
       </c>
       <c r="F85" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="G85" t="s">
         <v>75</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C86" t="s">
         <v>40</v>
@@ -3571,21 +3601,21 @@
         <v>11</v>
       </c>
       <c r="F86" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c r="G86" t="s">
         <v>75</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="C87" t="s">
         <v>40</v>
@@ -3597,99 +3627,99 @@
         <v>11</v>
       </c>
       <c r="F87" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
+        <v>67</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" t="s">
+        <v>30</v>
+      </c>
+      <c r="C88" t="s">
+        <v>40</v>
+      </c>
+      <c r="D88" t="s">
+        <v>58</v>
+      </c>
+      <c r="E88" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" t="s">
+        <v>201</v>
+      </c>
+      <c r="G88" t="s">
         <v>75</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>19</v>
-      </c>
-      <c r="B88" t="s">
-        <v>19</v>
-      </c>
-      <c r="C88" t="s">
-        <v>40</v>
-      </c>
-      <c r="D88" t="s">
-        <v>41</v>
-      </c>
-      <c r="E88" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" t="s">
-        <v>67</v>
       </c>
       <c r="J88" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C89" t="s">
         <v>40</v>
       </c>
       <c r="D89" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E89" t="s">
         <v>11</v>
       </c>
       <c r="F89" t="s">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="G89" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C90" t="s">
         <v>40</v>
       </c>
       <c r="D90" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G90" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>244</v>
       </c>
       <c r="C91" t="s">
         <v>40</v>
@@ -3701,21 +3731,21 @@
         <v>11</v>
       </c>
       <c r="F91" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G91" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>246</v>
       </c>
       <c r="C92" t="s">
         <v>40</v>
@@ -3732,16 +3762,19 @@
       <c r="G92" t="s">
         <v>42</v>
       </c>
+      <c r="H92" t="s">
+        <v>247</v>
+      </c>
       <c r="J92" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="C93" t="s">
         <v>40</v>
@@ -3753,21 +3786,24 @@
         <v>11</v>
       </c>
       <c r="F93" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="G93" t="s">
         <v>42</v>
       </c>
+      <c r="H93" t="s">
+        <v>247</v>
+      </c>
       <c r="J93" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="C94" t="s">
         <v>40</v>
@@ -3779,21 +3815,21 @@
         <v>11</v>
       </c>
       <c r="F94" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="G94" t="s">
         <v>42</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="C95" t="s">
         <v>40</v>
@@ -3805,21 +3841,24 @@
         <v>11</v>
       </c>
       <c r="F95" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="G95" t="s">
         <v>42</v>
       </c>
+      <c r="H95" t="s">
+        <v>247</v>
+      </c>
       <c r="J95" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B96" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="C96" t="s">
         <v>40</v>
@@ -3831,21 +3870,21 @@
         <v>11</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B97" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C97" t="s">
         <v>40</v>
@@ -3857,24 +3896,21 @@
         <v>11</v>
       </c>
       <c r="F97" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G97" t="s">
-        <v>62</v>
-      </c>
-      <c r="I97" s="3">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C98" t="s">
         <v>40</v>
@@ -3886,24 +3922,21 @@
         <v>11</v>
       </c>
       <c r="F98" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G98" t="s">
-        <v>62</v>
-      </c>
-      <c r="I98" s="3">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="J98" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="C99" t="s">
         <v>40</v>
@@ -3915,183 +3948,186 @@
         <v>11</v>
       </c>
       <c r="F99" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G99" t="s">
+        <v>62</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>79</v>
+      </c>
+      <c r="B100" t="s">
+        <v>103</v>
+      </c>
+      <c r="C100" t="s">
+        <v>40</v>
+      </c>
+      <c r="D100" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" t="s">
+        <v>104</v>
+      </c>
+      <c r="G100" t="s">
         <v>42</v>
       </c>
-      <c r="J99" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>85</v>
-      </c>
-      <c r="B100" t="s">
-        <v>86</v>
-      </c>
-      <c r="C100" t="s">
-        <v>40</v>
-      </c>
-      <c r="D100" t="s">
-        <v>58</v>
-      </c>
-      <c r="E100" t="s">
-        <v>11</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="J100" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>79</v>
+      </c>
+      <c r="B101" t="s">
+        <v>80</v>
+      </c>
+      <c r="C101" t="s">
+        <v>40</v>
+      </c>
+      <c r="D101" t="s">
+        <v>41</v>
+      </c>
+      <c r="E101" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" t="s">
+        <v>42</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" t="s">
+        <v>81</v>
+      </c>
+      <c r="C102" t="s">
+        <v>40</v>
+      </c>
+      <c r="D102" t="s">
+        <v>41</v>
+      </c>
+      <c r="E102" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" t="s">
+        <v>42</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>79</v>
+      </c>
+      <c r="B103" t="s">
+        <v>79</v>
+      </c>
+      <c r="C103" t="s">
+        <v>40</v>
+      </c>
+      <c r="D103" t="s">
+        <v>41</v>
+      </c>
+      <c r="E103" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" t="s">
         <v>65</v>
       </c>
-      <c r="G100" t="s">
-        <v>87</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>85</v>
-      </c>
-      <c r="B101" t="s">
-        <v>86</v>
-      </c>
-      <c r="C101" t="s">
-        <v>40</v>
-      </c>
-      <c r="D101" t="s">
-        <v>58</v>
-      </c>
-      <c r="E101" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" t="s">
-        <v>65</v>
-      </c>
-      <c r="G101" t="s">
-        <v>62</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>85</v>
-      </c>
-      <c r="B102" t="s">
-        <v>85</v>
-      </c>
-      <c r="C102" t="s">
-        <v>40</v>
-      </c>
-      <c r="D102" t="s">
-        <v>58</v>
-      </c>
-      <c r="E102" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" t="s">
-        <v>65</v>
-      </c>
-      <c r="G102" t="s">
-        <v>62</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>88</v>
-      </c>
-      <c r="B103" t="s">
-        <v>89</v>
-      </c>
-      <c r="C103" t="s">
-        <v>40</v>
-      </c>
-      <c r="D103" t="s">
-        <v>58</v>
-      </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s">
-        <v>102</v>
-      </c>
       <c r="G103" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="B104" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C104" t="s">
         <v>40</v>
       </c>
       <c r="D104" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E104" t="s">
         <v>11</v>
       </c>
       <c r="F104" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="G104" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="B105" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="C105" t="s">
         <v>40</v>
       </c>
       <c r="D105" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E105" t="s">
         <v>11</v>
       </c>
       <c r="F105" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="G105" t="s">
         <v>62</v>
       </c>
+      <c r="I105" s="3">
+        <v>14</v>
+      </c>
       <c r="J105" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="C106" t="s">
         <v>40</v>
       </c>
       <c r="D106" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E106" t="s">
         <v>11</v>
@@ -4102,16 +4138,19 @@
       <c r="G106" t="s">
         <v>62</v>
       </c>
+      <c r="I106" s="3">
+        <v>14</v>
+      </c>
       <c r="J106" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B107" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C107" t="s">
         <v>40</v>
@@ -4123,124 +4162,303 @@
         <v>11</v>
       </c>
       <c r="F107" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G107" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B108" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C108" t="s">
         <v>40</v>
       </c>
       <c r="D108" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
       </c>
       <c r="F108" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G108" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B109" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C109" t="s">
         <v>40</v>
       </c>
       <c r="D109" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E109" t="s">
         <v>11</v>
       </c>
       <c r="F109" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="G109" t="s">
         <v>62</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B110" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C110" t="s">
         <v>40</v>
       </c>
       <c r="D110" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E110" t="s">
         <v>11</v>
       </c>
       <c r="F110" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G110" t="s">
         <v>62</v>
       </c>
       <c r="J110" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>88</v>
+      </c>
+      <c r="B111" t="s">
+        <v>89</v>
+      </c>
+      <c r="C111" t="s">
+        <v>40</v>
+      </c>
+      <c r="D111" t="s">
+        <v>58</v>
+      </c>
+      <c r="E111" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" t="s">
+        <v>102</v>
+      </c>
+      <c r="G111" t="s">
+        <v>90</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>88</v>
+      </c>
+      <c r="B112" t="s">
+        <v>88</v>
+      </c>
+      <c r="C112" t="s">
+        <v>40</v>
+      </c>
+      <c r="D112" t="s">
+        <v>58</v>
+      </c>
+      <c r="E112" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" t="s">
+        <v>102</v>
+      </c>
+      <c r="G112" t="s">
+        <v>90</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>92</v>
+      </c>
+      <c r="B113" t="s">
+        <v>92</v>
+      </c>
+      <c r="C113" t="s">
+        <v>40</v>
+      </c>
+      <c r="D113" t="s">
+        <v>58</v>
+      </c>
+      <c r="E113" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" t="s">
+        <v>15</v>
+      </c>
+      <c r="G113" t="s">
+        <v>62</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>92</v>
+      </c>
+      <c r="B114" t="s">
+        <v>92</v>
+      </c>
+      <c r="C114" t="s">
+        <v>40</v>
+      </c>
+      <c r="D114" t="s">
+        <v>58</v>
+      </c>
+      <c r="E114" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" t="s">
+        <v>60</v>
+      </c>
+      <c r="G114" t="s">
+        <v>62</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>95</v>
+      </c>
+      <c r="B115" t="s">
+        <v>96</v>
+      </c>
+      <c r="C115" t="s">
+        <v>40</v>
+      </c>
+      <c r="D115" t="s">
+        <v>41</v>
+      </c>
+      <c r="E115" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" t="s">
+        <v>59</v>
+      </c>
+      <c r="G115" t="s">
+        <v>62</v>
+      </c>
+      <c r="J115" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>108</v>
-      </c>
-      <c r="B111" t="s">
-        <v>109</v>
-      </c>
-      <c r="C111" t="s">
-        <v>110</v>
-      </c>
-      <c r="D111" t="s">
-        <v>10</v>
-      </c>
-      <c r="E111" t="s">
-        <v>11</v>
-      </c>
-      <c r="F111" t="s">
-        <v>206</v>
-      </c>
-      <c r="G111" t="s">
-        <v>14</v>
-      </c>
-      <c r="H111" t="s">
-        <v>111</v>
-      </c>
-      <c r="J111" s="3" t="s">
-        <v>21</v>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>95</v>
+      </c>
+      <c r="B116" t="s">
+        <v>96</v>
+      </c>
+      <c r="C116" t="s">
+        <v>40</v>
+      </c>
+      <c r="D116" t="s">
+        <v>41</v>
+      </c>
+      <c r="E116" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" t="s">
+        <v>60</v>
+      </c>
+      <c r="G116" t="s">
+        <v>62</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>95</v>
+      </c>
+      <c r="B117" t="s">
+        <v>95</v>
+      </c>
+      <c r="C117" t="s">
+        <v>40</v>
+      </c>
+      <c r="D117" t="s">
+        <v>41</v>
+      </c>
+      <c r="E117" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" t="s">
+        <v>16</v>
+      </c>
+      <c r="G117" t="s">
+        <v>62</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>95</v>
+      </c>
+      <c r="B118" t="s">
+        <v>95</v>
+      </c>
+      <c r="C118" t="s">
+        <v>40</v>
+      </c>
+      <c r="D118" t="s">
+        <v>41</v>
+      </c>
+      <c r="E118" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" t="s">
+        <v>50</v>
+      </c>
+      <c r="G118" t="s">
+        <v>62</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J111" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
+  <autoFilter ref="A1:J118" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tr.alienigenaV5-main\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B92DF0D5-E987-4DFF-9AFB-84A78CFD1C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9BC6202-462C-40D9-9DDA-5E6030BF438D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="551" xr2:uid="{9E8F4E85-D2FF-4383-A72B-5CAFDCCC5644}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="234">
   <si>
     <t>Origem</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Carreta, Bitrem 7 eixos, Rodotrem</t>
-  </si>
-  <si>
     <t>Graneleiro, Caçamba</t>
   </si>
   <si>
@@ -149,18 +146,9 @@
     <t>Carreta LS, Rodotrem</t>
   </si>
   <si>
-    <t>Dias dÁvila - BA</t>
-  </si>
-  <si>
     <t>Laranjeiras - SE</t>
   </si>
   <si>
-    <t>88,00</t>
-  </si>
-  <si>
-    <t>PAGBEM</t>
-  </si>
-  <si>
     <t>São Gonçalo - RJ</t>
   </si>
   <si>
@@ -338,9 +326,6 @@
     <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Região de Gargalo, Vitória da Conquista e Ipiau</t>
   </si>
   <si>
-    <t>Carreta</t>
-  </si>
-  <si>
     <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI / Tem cargas todos os dias e não agregamos passantes.</t>
   </si>
   <si>
@@ -407,18 +392,6 @@
     <t>8.902,06</t>
   </si>
   <si>
-    <t>São João da Barra - RJ</t>
-  </si>
-  <si>
-    <t>Coque</t>
-  </si>
-  <si>
-    <t>13.630,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO PAGBEM / PEDÁGIO INCLUSO NO FRETE</t>
-  </si>
-  <si>
     <t>Itaguaí - RJ</t>
   </si>
   <si>
@@ -428,9 +401,6 @@
     <t>VALOR PAGO NO CARTÃO REPOM /</t>
   </si>
   <si>
-    <t>Vanderléia</t>
-  </si>
-  <si>
     <t>Trindade - PE</t>
   </si>
   <si>
@@ -449,9 +419,6 @@
     <t>Pitimbu - PB</t>
   </si>
   <si>
-    <t>Vanderléia, Bitrem 7 eixos, Rodotrem</t>
-  </si>
-  <si>
     <t>PAGBEM/REPOM</t>
   </si>
   <si>
@@ -479,15 +446,9 @@
     <t>Unaí - MG</t>
   </si>
   <si>
-    <t>Pará de Minas - MG</t>
-  </si>
-  <si>
     <t>SORGO</t>
   </si>
   <si>
-    <t>169,00</t>
-  </si>
-  <si>
     <t>Grajaú - MA</t>
   </si>
   <si>
@@ -512,9 +473,6 @@
     <t>CALCÁRIO</t>
   </si>
   <si>
-    <t>Calcario</t>
-  </si>
-  <si>
     <t>170,00</t>
   </si>
   <si>
@@ -536,9 +494,6 @@
     <t>Apenas 7 eixos acima 38 ton</t>
   </si>
   <si>
-    <t>Carreta 4º eixo</t>
-  </si>
-  <si>
     <t>130,00</t>
   </si>
   <si>
@@ -587,21 +542,9 @@
     <t>Hidrolândia - GO</t>
   </si>
   <si>
-    <t>55,00</t>
-  </si>
-  <si>
-    <t>Palmeiras de Goiás - GO</t>
-  </si>
-  <si>
     <t>Jataí - GO</t>
   </si>
   <si>
-    <t>Avelinópolis - GO</t>
-  </si>
-  <si>
-    <t>Edéia - GO</t>
-  </si>
-  <si>
     <t>Rio Verde - GO</t>
   </si>
   <si>
@@ -614,9 +557,6 @@
     <t>Montividiu - GO</t>
   </si>
   <si>
-    <t>65,00</t>
-  </si>
-  <si>
     <t>80,00</t>
   </si>
   <si>
@@ -635,18 +575,9 @@
     <t>157,00</t>
   </si>
   <si>
-    <t>Diversos</t>
-  </si>
-  <si>
     <t>Cajati - SP</t>
   </si>
   <si>
-    <t>Carreta LS, Vanderléia, Bitrem 7 eixos</t>
-  </si>
-  <si>
-    <t>Botucatu - SP</t>
-  </si>
-  <si>
     <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
   </si>
   <si>
@@ -671,12 +602,6 @@
     <t>70,00</t>
   </si>
   <si>
-    <t>Cezarina - GO</t>
-  </si>
-  <si>
-    <t>30,00</t>
-  </si>
-  <si>
     <t>Rio Branco do Sul - PR</t>
   </si>
   <si>
@@ -713,24 +638,6 @@
     <t>115,00</t>
   </si>
   <si>
-    <t>Joinville - SC</t>
-  </si>
-  <si>
-    <t>São José - SC</t>
-  </si>
-  <si>
-    <t>Tubos e Conexões</t>
-  </si>
-  <si>
-    <t>Sider, Baú</t>
-  </si>
-  <si>
-    <t>1.150,00</t>
-  </si>
-  <si>
-    <t>precisa de MOPP ativo</t>
-  </si>
-  <si>
     <t>Castro - PR</t>
   </si>
   <si>
@@ -767,15 +674,6 @@
     <t>35,00</t>
   </si>
   <si>
-    <t>62,00</t>
-  </si>
-  <si>
-    <t>Penápolis - SP</t>
-  </si>
-  <si>
-    <t>Ureia granel</t>
-  </si>
-  <si>
     <t>Alfenas - MG</t>
   </si>
   <si>
@@ -795,6 +693,57 @@
   </si>
   <si>
     <t>Paranaíba - MS</t>
+  </si>
+  <si>
+    <t>Edealina - GO</t>
+  </si>
+  <si>
+    <t>4.670,00</t>
+  </si>
+  <si>
+    <t>Aldeias Altas - MA</t>
+  </si>
+  <si>
+    <t>190,00</t>
+  </si>
+  <si>
+    <t>Carreta LS, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Itápolis - SP</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS</t>
+  </si>
+  <si>
+    <t>Vanderléia, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>230,00</t>
+  </si>
+  <si>
+    <t>Cabeceira Grande - MG</t>
+  </si>
+  <si>
+    <t>Rio Pomba - MG</t>
+  </si>
+  <si>
+    <t>235,00</t>
+  </si>
+  <si>
+    <t>70,71</t>
+  </si>
+  <si>
+    <t>Bariri - SP</t>
+  </si>
+  <si>
+    <t>40,00</t>
+  </si>
+  <si>
+    <t>Caruaru - PE</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1146,7 @@
   <dimension ref="A1:J118"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -1243,13 +1192,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1258,27 +1207,24 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>21</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1287,56 +1233,56 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" t="s">
         <v>219</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
         <v>220</v>
       </c>
-      <c r="C4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>222</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>198</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1345,27 +1291,27 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>164</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -1374,27 +1320,27 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>199</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1403,27 +1349,27 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1432,27 +1378,27 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="B9" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1461,27 +1407,27 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1490,27 +1436,27 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1519,27 +1465,27 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -1548,27 +1494,27 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>201</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -1577,56 +1523,56 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>224</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>225</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>226</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>227</v>
+        <v>104</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -1635,27 +1581,27 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -1664,16 +1610,16 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -1693,27 +1639,27 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -1722,30 +1668,27 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" t="s">
-        <v>165</v>
-      </c>
-      <c r="I18" s="3">
-        <v>28000</v>
+        <v>115</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -1754,30 +1697,30 @@
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="I19" s="3">
         <v>28000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -1786,27 +1729,30 @@
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>123</v>
+        <v>150</v>
+      </c>
+      <c r="I20" s="3">
+        <v>28000</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -1815,30 +1761,30 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="I21" s="3">
         <v>28000</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -1847,30 +1793,30 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="I22" s="3">
         <v>28000</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -1879,30 +1825,30 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="I23" s="3">
         <v>28000</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -1911,30 +1857,30 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="I24" s="3">
         <v>28000</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -1943,27 +1889,27 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" t="s">
+        <v>152</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s">
-        <v>167</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -1972,27 +1918,27 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -2001,27 +1947,27 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -2030,27 +1976,27 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="G28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -2059,27 +2005,27 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -2088,56 +2034,56 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>98</v>
+        <v>224</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H30" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
         <v>33</v>
       </c>
-      <c r="C31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>157</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="G31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" t="s">
-        <v>172</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2146,27 +2092,27 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="G32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H32" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -2175,27 +2121,27 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H33" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -2204,27 +2150,27 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="G34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H34" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -2233,27 +2179,27 @@
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H35" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -2262,27 +2208,27 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>224</v>
       </c>
       <c r="G36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H36" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -2291,27 +2237,27 @@
         <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G37" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H37" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -2320,30 +2266,30 @@
         <v>11</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H38" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="I38" s="3">
         <v>52</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -2352,27 +2298,27 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="G39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H39" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C40" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2381,27 +2327,27 @@
         <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H40" t="s">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>227</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>228</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -2410,27 +2356,27 @@
         <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H41" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -2439,27 +2385,27 @@
         <v>11</v>
       </c>
       <c r="F42" t="s">
+        <v>225</v>
+      </c>
+      <c r="G42" t="s">
         <v>12</v>
       </c>
-      <c r="G42" t="s">
-        <v>13</v>
-      </c>
       <c r="H42" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B43" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -2468,27 +2414,27 @@
         <v>11</v>
       </c>
       <c r="F43" t="s">
+        <v>225</v>
+      </c>
+      <c r="G43" t="s">
         <v>12</v>
       </c>
-      <c r="G43" t="s">
-        <v>13</v>
-      </c>
       <c r="H43" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>228</v>
       </c>
       <c r="C44" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -2497,85 +2443,85 @@
         <v>11</v>
       </c>
       <c r="F44" t="s">
+        <v>27</v>
+      </c>
+      <c r="G44" t="s">
         <v>12</v>
       </c>
-      <c r="G44" t="s">
-        <v>13</v>
-      </c>
       <c r="H44" t="s">
-        <v>147</v>
+        <v>226</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D45" t="s">
-        <v>151</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
         <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H45" t="s">
-        <v>203</v>
-      </c>
-      <c r="I45" s="3">
-        <v>49</v>
+        <v>176</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="D46" t="s">
-        <v>151</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>28</v>
+        <v>225</v>
       </c>
       <c r="G46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H46" t="s">
-        <v>153</v>
-      </c>
-      <c r="I46" s="3">
-        <v>49</v>
+        <v>176</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C47" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -2584,24 +2530,27 @@
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="G47" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H47" t="s">
-        <v>160</v>
+        <v>173</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C48" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2610,114 +2559,114 @@
         <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H48" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D49" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E49" t="s">
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" t="s">
-        <v>234</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>235</v>
+        <v>171</v>
+      </c>
+      <c r="I49" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="C50" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E50" t="s">
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H50" t="s">
-        <v>157</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>21</v>
+        <v>180</v>
+      </c>
+      <c r="I50" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E51" t="s">
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H51" t="s">
-        <v>37</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>38</v>
+        <v>140</v>
+      </c>
+      <c r="I51" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>229</v>
+        <v>144</v>
       </c>
       <c r="B52" t="s">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -2726,21 +2675,24 @@
         <v>11</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G52" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="B53" t="s">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2749,24 +2701,27 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="G53" t="s">
         <v>13</v>
       </c>
       <c r="H53" t="s">
-        <v>237</v>
+        <v>148</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>238</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -2775,24 +2730,27 @@
         <v>11</v>
       </c>
       <c r="F54" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G54" t="s">
         <v>13</v>
       </c>
       <c r="H54" t="s">
-        <v>239</v>
+        <v>230</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>186</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -2801,24 +2759,27 @@
         <v>11</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G55" t="s">
         <v>13</v>
       </c>
       <c r="H55" t="s">
-        <v>240</v>
+        <v>203</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B56" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="C56" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -2827,24 +2788,21 @@
         <v>11</v>
       </c>
       <c r="F56" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
         <v>13</v>
-      </c>
-      <c r="H56" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="C57" t="s">
-        <v>179</v>
+        <v>30</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
@@ -2853,24 +2811,24 @@
         <v>11</v>
       </c>
       <c r="F57" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B58" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C58" t="s">
-        <v>179</v>
+        <v>30</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -2879,24 +2837,24 @@
         <v>11</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H58" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
@@ -2905,24 +2863,24 @@
         <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H59" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="B60" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -2931,24 +2889,24 @@
         <v>11</v>
       </c>
       <c r="F60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H60" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="B61" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -2957,24 +2915,24 @@
         <v>11</v>
       </c>
       <c r="F61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
       </c>
       <c r="H61" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B62" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
@@ -2983,24 +2941,24 @@
         <v>11</v>
       </c>
       <c r="F62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H62" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D63" t="s">
         <v>10</v>
@@ -3009,24 +2967,24 @@
         <v>11</v>
       </c>
       <c r="F63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G63" t="s">
         <v>12</v>
       </c>
-      <c r="G63" t="s">
-        <v>13</v>
-      </c>
       <c r="H63" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B64" t="s">
-        <v>242</v>
+        <v>168</v>
       </c>
       <c r="C64" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="D64" t="s">
         <v>10</v>
@@ -3035,1426 +2993,1432 @@
         <v>11</v>
       </c>
       <c r="F64" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G64" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="H64" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>242</v>
+        <v>65</v>
       </c>
       <c r="C65" t="s">
-        <v>243</v>
+        <v>36</v>
       </c>
       <c r="D65" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E65" t="s">
         <v>11</v>
       </c>
       <c r="F65" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G65" t="s">
-        <v>13</v>
+        <v>58</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D66" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E66" t="s">
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="G66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D67" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E67" t="s">
         <v>11</v>
       </c>
       <c r="F67" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G67" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68" t="s">
+        <v>36</v>
+      </c>
+      <c r="D68" t="s">
+        <v>37</v>
+      </c>
+      <c r="E68" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" t="s">
+        <v>63</v>
+      </c>
+      <c r="J68" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B68" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" t="s">
-        <v>40</v>
-      </c>
-      <c r="D68" t="s">
-        <v>41</v>
-      </c>
-      <c r="E68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" t="s">
-        <v>65</v>
-      </c>
-      <c r="G68" t="s">
-        <v>62</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C69" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D69" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E69" t="s">
         <v>11</v>
       </c>
       <c r="F69" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G69" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" t="s">
         <v>48</v>
       </c>
-      <c r="B70" t="s">
-        <v>49</v>
-      </c>
       <c r="C70" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D70" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
       </c>
       <c r="F70" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G70" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C71" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E71" t="s">
         <v>11</v>
       </c>
       <c r="F71" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G71" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C72" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D72" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E72" t="s">
         <v>11</v>
       </c>
       <c r="F72" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G72" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C73" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D73" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
       </c>
       <c r="F73" t="s">
+        <v>46</v>
+      </c>
+      <c r="G73" t="s">
+        <v>38</v>
+      </c>
+      <c r="J73" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="G73" t="s">
-        <v>42</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C74" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D74" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E74" t="s">
         <v>11</v>
       </c>
       <c r="F74" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G74" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D75" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E75" t="s">
         <v>11</v>
       </c>
       <c r="F75" t="s">
+        <v>55</v>
+      </c>
+      <c r="G75" t="s">
+        <v>38</v>
+      </c>
+      <c r="J75" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="G75" t="s">
-        <v>62</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D76" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
       </c>
       <c r="F76" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G76" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B77" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C77" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D77" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" t="s">
+        <v>56</v>
+      </c>
+      <c r="G77" t="s">
         <v>58</v>
       </c>
-      <c r="E77" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" t="s">
-        <v>60</v>
-      </c>
-      <c r="G77" t="s">
-        <v>42</v>
-      </c>
       <c r="J77" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="B78" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C78" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D78" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E78" t="s">
         <v>11</v>
       </c>
       <c r="F78" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="G78" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B79" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C79" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D79" t="s">
+        <v>37</v>
+      </c>
+      <c r="E79" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" t="s">
+        <v>38</v>
+      </c>
+      <c r="J79" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E79" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" t="s">
-        <v>18</v>
-      </c>
-      <c r="G79" t="s">
-        <v>42</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C80" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D80" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E80" t="s">
         <v>11</v>
       </c>
       <c r="F80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="C81" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D81" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E81" t="s">
         <v>11</v>
       </c>
       <c r="F81" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="G81" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>47</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="B82" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="C82" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E82" t="s">
         <v>11</v>
       </c>
       <c r="F82" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="G82" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="C83" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D83" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E83" t="s">
         <v>11</v>
       </c>
       <c r="F83" t="s">
-        <v>206</v>
+        <v>61</v>
       </c>
       <c r="G83" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
       <c r="C84" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D84" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E84" t="s">
         <v>11</v>
       </c>
       <c r="F84" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G84" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D85" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E85" t="s">
         <v>11</v>
       </c>
       <c r="F85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C86" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D86" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E86" t="s">
         <v>11</v>
       </c>
       <c r="F86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G86" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B87" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C87" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D87" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E87" t="s">
         <v>11</v>
       </c>
       <c r="F87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D88" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
       </c>
       <c r="F88" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="G88" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D89" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E89" t="s">
         <v>11</v>
       </c>
       <c r="F89" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="G89" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C90" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D90" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
       </c>
       <c r="F90" t="s">
+        <v>56</v>
+      </c>
+      <c r="G90" t="s">
+        <v>71</v>
+      </c>
+      <c r="J90" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="G90" t="s">
-        <v>75</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B91" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="C91" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D91" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
       </c>
       <c r="F91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G91" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B92" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="C92" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D92" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E92" t="s">
         <v>11</v>
       </c>
       <c r="F92" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G92" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H92" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B93" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="C93" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E93" t="s">
         <v>11</v>
       </c>
       <c r="F93" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G93" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H93" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="C94" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E94" t="s">
         <v>11</v>
       </c>
       <c r="F94" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G94" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B95" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="C95" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D95" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E95" t="s">
         <v>11</v>
       </c>
       <c r="F95" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G95" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H95" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C96" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D96" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E96" t="s">
         <v>11</v>
       </c>
       <c r="F96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G96" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C97" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D97" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E97" t="s">
         <v>11</v>
       </c>
       <c r="F97" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G97" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B98" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C98" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D98" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E98" t="s">
         <v>11</v>
       </c>
       <c r="F98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B99" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E99" t="s">
         <v>11</v>
       </c>
       <c r="F99" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G99" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B100" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D100" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E100" t="s">
         <v>11</v>
       </c>
       <c r="F100" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G100" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B101" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C101" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E101" t="s">
         <v>11</v>
       </c>
       <c r="F101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G101" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B102" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C102" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D102" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E102" t="s">
         <v>11</v>
       </c>
       <c r="F102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G102" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C103" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E103" t="s">
         <v>11</v>
       </c>
       <c r="F103" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G103" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B104" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C104" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D104" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E104" t="s">
         <v>11</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G104" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D105" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E105" t="s">
         <v>11</v>
       </c>
       <c r="F105" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G105" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I105" s="3">
         <v>14</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C106" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D106" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E106" t="s">
         <v>11</v>
       </c>
       <c r="F106" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G106" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I106" s="3">
         <v>14</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B107" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C107" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D107" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E107" t="s">
         <v>11</v>
       </c>
       <c r="F107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G107" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B108" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C108" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D108" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
       </c>
       <c r="F108" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G108" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B109" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C109" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D109" t="s">
+        <v>54</v>
+      </c>
+      <c r="E109" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" t="s">
+        <v>61</v>
+      </c>
+      <c r="G109" t="s">
         <v>58</v>
       </c>
-      <c r="E109" t="s">
-        <v>11</v>
-      </c>
-      <c r="F109" t="s">
-        <v>65</v>
-      </c>
-      <c r="G109" t="s">
-        <v>62</v>
-      </c>
       <c r="J109" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B110" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C110" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D110" t="s">
+        <v>54</v>
+      </c>
+      <c r="E110" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" t="s">
+        <v>61</v>
+      </c>
+      <c r="G110" t="s">
         <v>58</v>
       </c>
-      <c r="E110" t="s">
-        <v>11</v>
-      </c>
-      <c r="F110" t="s">
-        <v>65</v>
-      </c>
-      <c r="G110" t="s">
-        <v>62</v>
-      </c>
       <c r="J110" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B111" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D111" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E111" t="s">
         <v>11</v>
       </c>
       <c r="F111" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G111" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B112" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C112" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D112" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E112" t="s">
         <v>11</v>
       </c>
       <c r="F112" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G112" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B113" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D113" t="s">
+        <v>54</v>
+      </c>
+      <c r="E113" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" t="s">
+        <v>14</v>
+      </c>
+      <c r="G113" t="s">
         <v>58</v>
       </c>
-      <c r="E113" t="s">
-        <v>11</v>
-      </c>
-      <c r="F113" t="s">
-        <v>15</v>
-      </c>
-      <c r="G113" t="s">
-        <v>62</v>
-      </c>
       <c r="J113" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B114" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D114" t="s">
+        <v>54</v>
+      </c>
+      <c r="E114" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" t="s">
+        <v>56</v>
+      </c>
+      <c r="G114" t="s">
         <v>58</v>
       </c>
-      <c r="E114" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" t="s">
-        <v>60</v>
-      </c>
-      <c r="G114" t="s">
-        <v>62</v>
-      </c>
       <c r="J114" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B115" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C115" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D115" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E115" t="s">
         <v>11</v>
       </c>
       <c r="F115" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G115" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B116" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C116" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D116" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E116" t="s">
         <v>11</v>
       </c>
       <c r="F116" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G116" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B117" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C117" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E117" t="s">
         <v>11</v>
       </c>
       <c r="F117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G117" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B118" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C118" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E118" t="s">
         <v>11</v>
       </c>
       <c r="F118" t="s">
+        <v>46</v>
+      </c>
+      <c r="G118" t="s">
+        <v>58</v>
+      </c>
+      <c r="J118" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="G118" t="s">
-        <v>62</v>
-      </c>
-      <c r="J118" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tr.alienigenaV5-main\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9BC6202-462C-40D9-9DDA-5E6030BF438D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6D289F3-ED23-4377-A366-8066841AFA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="551" xr2:uid="{9E8F4E85-D2FF-4383-A72B-5CAFDCCC5644}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$122</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="227">
   <si>
     <t>Origem</t>
   </si>
@@ -134,18 +134,12 @@
     <t>Corumbá - MS</t>
   </si>
   <si>
-    <t>MILHO</t>
-  </si>
-  <si>
     <t>São Gonçalo do Amarante - CE</t>
   </si>
   <si>
     <t>Sobral - CE</t>
   </si>
   <si>
-    <t>Carreta LS, Rodotrem</t>
-  </si>
-  <si>
     <t>Laranjeiras - SE</t>
   </si>
   <si>
@@ -161,21 +155,12 @@
     <t>Grade Baixa</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI. Possíveis destinos disponíveis:Região dos Lagos (Araruama/RJ com Saquarema/RJ na mesma rota e Cabo Frio/RJ com Arraial do Cabo/RJ na mesma rota)</t>
-  </si>
-  <si>
     <t>Rio de Janeiro - RJ</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI. Possíveis destinos disponíveis CD Santa Cruz: Rio de Janeiro-RJ, Itaguaí -RJ, Seropédica-RJ, Itatiaia-RJ.</t>
-  </si>
-  <si>
     <t>CIMENTO ENSACADO</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI. Possíveis destinos disponíveis CD RIO: Rio de Janeiro-RJ, Nova Iguaçu-RJ, Duque de Caxias-RJ, Mesquita-RJ )</t>
-  </si>
-  <si>
     <t>Campinas - SP</t>
   </si>
   <si>
@@ -185,9 +170,6 @@
     <t>Toco, Truck, Bitruck</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI- VEICULOS TOCO APENAS 10 TON</t>
-  </si>
-  <si>
     <t>Serra Negra - SP</t>
   </si>
   <si>
@@ -203,9 +185,6 @@
     <t>Guarulhos - SP</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
-  </si>
-  <si>
     <t>Saco</t>
   </si>
   <si>
@@ -245,18 +224,9 @@
     <t>Truck, Carreta LS</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
-  </si>
-  <si>
-    <t>DESTINOS DISPONIVEIS: No Extremo Sul do Estado do PI - PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
     <t>Petrolina - PE</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI / DESTINOS: regiões Metropolitana , PB e RN</t>
-  </si>
-  <si>
     <t>Graneleiro, Grade Baixa</t>
   </si>
   <si>
@@ -266,9 +236,6 @@
     <t>Nobres - MT</t>
   </si>
   <si>
-    <t>DESTINO INTRA MUNICIPAL / PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
     <t>Brasília - DF</t>
   </si>
   <si>
@@ -284,9 +251,6 @@
     <t>Luís Eduardo Magalhães - BA</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: Cocos/BA, Serra Dourada/BA, São Félix do Coribe/BA, Tabocas do Brejo Velho/BA, Correntina/BA, Mansidão/BA, Formosa do Rio Preto/BA, Santa Rita de Cassia/BA, Barreiras/BA e Morpará/BA</t>
-  </si>
-  <si>
     <t>Camaçari - BA</t>
   </si>
   <si>
@@ -305,36 +269,18 @@
     <t>Sider, Grade Baixa, Prancha</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: Simões Filho/BA, Lauro de Freitas/BA, Salvador/BA. - Não trabalhamos com motoristas passantes, prioridade em atuação local com disponibilidade para operar nas regiões mencionadas acima</t>
-  </si>
-  <si>
     <t>Feira de Santana - BA</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI. Veiculos Aceitos: TRUCK E CARRETA TOCO (28 TON)</t>
-  </si>
-  <si>
     <t>Itabuna - BA</t>
   </si>
   <si>
     <t>Vitória da Conquista - BA</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Região de Gargalo, Vitória da Conquista e Ipiau</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI / Tem cargas todos os dias e não agregamos passantes.</t>
-  </si>
-  <si>
     <t>50,00</t>
   </si>
   <si>
-    <t>APENAS MOTORISTAS CATIVOS - PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: Região do Litoral Norte de Camaçari, Catu/Ba Pojuca/Ba, Maragojipe/BA, Candeias/BA, São Francisco/BA, São Félix/BA, Cachoeira/BA - Não trabalhamos com motoristas passantes, prioridade em atuação local com disponibilidade para operar nas regiões mencionadas acima</t>
-  </si>
-  <si>
     <t>Toco</t>
   </si>
   <si>
@@ -467,15 +413,6 @@
     <t>168,00</t>
   </si>
   <si>
-    <t>Buriti Alegre - GO</t>
-  </si>
-  <si>
-    <t>CALCÁRIO</t>
-  </si>
-  <si>
-    <t>170,00</t>
-  </si>
-  <si>
     <t>Barro Alto - GO</t>
   </si>
   <si>
@@ -530,33 +467,6 @@
     <t>calcario/ clínquer</t>
   </si>
   <si>
-    <t>Mineiros - GO</t>
-  </si>
-  <si>
-    <t>Chapadão do Céu - GO</t>
-  </si>
-  <si>
-    <t>milho</t>
-  </si>
-  <si>
-    <t>Hidrolândia - GO</t>
-  </si>
-  <si>
-    <t>Jataí - GO</t>
-  </si>
-  <si>
-    <t>Rio Verde - GO</t>
-  </si>
-  <si>
-    <t>Quirinópolis - GO</t>
-  </si>
-  <si>
-    <t>85,00</t>
-  </si>
-  <si>
-    <t>Montividiu - GO</t>
-  </si>
-  <si>
     <t>80,00</t>
   </si>
   <si>
@@ -590,18 +500,9 @@
     <t>Primavera - PA</t>
   </si>
   <si>
-    <t>PARA MOTORISTAS CATIVOS NA REGIÃO - PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
     <t>Toco, Truck</t>
   </si>
   <si>
-    <t>Marzagão - GO</t>
-  </si>
-  <si>
-    <t>70,00</t>
-  </si>
-  <si>
     <t>Rio Branco do Sul - PR</t>
   </si>
   <si>
@@ -620,33 +521,9 @@
     <t>Vidal Ramos - SC</t>
   </si>
   <si>
-    <t>150,00</t>
-  </si>
-  <si>
     <t>650,00</t>
   </si>
   <si>
-    <t>São Pedro - SP</t>
-  </si>
-  <si>
-    <t>Cajamar - SP</t>
-  </si>
-  <si>
-    <t>Areia</t>
-  </si>
-  <si>
-    <t>115,00</t>
-  </si>
-  <si>
-    <t>Castro - PR</t>
-  </si>
-  <si>
-    <t>Chapadão do Sul - MS</t>
-  </si>
-  <si>
-    <t>57,00</t>
-  </si>
-  <si>
     <t>Santa Filomena - PI</t>
   </si>
   <si>
@@ -659,21 +536,6 @@
     <t>só aceita rodocaçambas com lona fácil. Caso não tenham, o veículo não passa na vistoria dos guardas</t>
   </si>
   <si>
-    <t>Goiatuba - GO</t>
-  </si>
-  <si>
-    <t>73,00</t>
-  </si>
-  <si>
-    <t>Itaberaí - GO</t>
-  </si>
-  <si>
-    <t>87,00</t>
-  </si>
-  <si>
-    <t>35,00</t>
-  </si>
-  <si>
     <t>Alfenas - MG</t>
   </si>
   <si>
@@ -707,18 +569,12 @@
     <t>190,00</t>
   </si>
   <si>
-    <t>Carreta LS, Carreta 4º eixo</t>
-  </si>
-  <si>
     <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
   </si>
   <si>
     <t>Itápolis - SP</t>
   </si>
   <si>
-    <t>Carreta, Carreta LS</t>
-  </si>
-  <si>
     <t>Vanderléia, Carreta 4º eixo</t>
   </si>
   <si>
@@ -737,13 +593,136 @@
     <t>70,71</t>
   </si>
   <si>
-    <t>Bariri - SP</t>
-  </si>
-  <si>
-    <t>40,00</t>
-  </si>
-  <si>
     <t>Caruaru - PE</t>
+  </si>
+  <si>
+    <t>Joinville - SC</t>
+  </si>
+  <si>
+    <t>Tubos e Conexões</t>
+  </si>
+  <si>
+    <t>Tubo</t>
+  </si>
+  <si>
+    <t>Truck, Carreta, Carreta LS, Vanderléia, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Sider, Baú, Grade Baixa</t>
+  </si>
+  <si>
+    <t>Vanderléia</t>
+  </si>
+  <si>
+    <t>155,00</t>
+  </si>
+  <si>
+    <t>Poço Fundo - MG</t>
+  </si>
+  <si>
+    <t>Big Bag</t>
+  </si>
+  <si>
+    <t>Graneleiro, Sider, Grade Baixa</t>
+  </si>
+  <si>
+    <t>195,00</t>
+  </si>
+  <si>
+    <t>Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Carreta</t>
+  </si>
+  <si>
+    <t>Primavera do Leste - MT</t>
+  </si>
+  <si>
+    <t>São João da Barra - RJ</t>
+  </si>
+  <si>
+    <t>Milho</t>
+  </si>
+  <si>
+    <t>510,00</t>
+  </si>
+  <si>
+    <t>Santos - SP</t>
+  </si>
+  <si>
+    <t>180,00</t>
+  </si>
+  <si>
+    <t>Nova Ponte - MG</t>
+  </si>
+  <si>
+    <t>Ponte Nova - MG</t>
+  </si>
+  <si>
+    <t>Brasilândia de Minas - MG</t>
+  </si>
+  <si>
+    <t>Penápolis - SP</t>
+  </si>
+  <si>
+    <t>Ureia granel</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>DESTINOS DISPONIVEIS: No Extremo Sul do Estado do PI - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI- VEICULOS TOCO APENAS 10 TON</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possíveis destinos disponíveis:Região dos Lagos (Araruama/RJ com Saquarema/RJ na mesma rota e Cabo Frio/RJ com Arraial do Cabo/RJ na mesma rota)</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possíveis destinos disponíveis CD Santa Cruz: Rio de Janeiro-RJ, Itaguaí -RJ, Seropédica-RJ, Itatiaia-RJ.</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possíveis destinos disponíveis CD RIO: Rio de Janeiro-RJ, Nova Iguaçu-RJ, Duque de Caxias-RJ, Mesquita-RJ )</t>
+  </si>
+  <si>
+    <t>PARA MOTORISTAS CATIVOS NA REGIÃO - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS: regiões Metropolitana , PB e RN</t>
+  </si>
+  <si>
+    <t>DESTINO INTRA MUNICIPAL / PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: Cocos/BA, Serra Dourada/BA, São Félix do Coribe/BA, Tabocas do Brejo Velho/BA, Correntina/BA, Mansidão/BA, Formosa do Rio Preto/BA, Santa Rita de Cassia/BA, Barreiras/BA e Morpará/BA</t>
+  </si>
+  <si>
+    <t>APENAS MOTORISTAS CATIVOS - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: Região do Litoral Norte de Camaçari, Catu/Ba Pojuca/Ba, Maragojipe/BA, Candeias/BA, São Francisco/BA, São Félix/BA, Cachoeira/BA - Não trabalhamos com motoristas passantes, prioridade em atuação local com disponibilidade para operar nas regiões mencionadas acima</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / Tem cargas todos os dias e não agregamos passantes.</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: Simões Filho/BA, Lauro de Freitas/BA, Salvador/BA. - Não trabalhamos com motoristas passantes, prioridade em atuação local com disponibilidade para operar nas regiões mencionadas acima</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Veiculos Aceitos: TRUCK E CARRETA TOCO (28 TON)</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Região de Gargalo, Vitória da Conquista e Ipiau</t>
+  </si>
+  <si>
+    <t>Ureia Granel</t>
   </si>
 </sst>
 </file>
@@ -1143,15 +1122,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}">
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="6" max="6" width="44.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
@@ -1192,39 +1171,39 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>186</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>187</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>218</v>
+        <v>188</v>
+      </c>
+      <c r="I2" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1233,27 +1212,27 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1268,7 +1247,7 @@
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>220</v>
+        <v>161</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>20</v>
@@ -1276,13 +1255,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1291,42 +1270,42 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" t="s">
         <v>194</v>
-      </c>
-      <c r="B6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>197</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>20</v>
@@ -1334,13 +1313,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1349,27 +1328,27 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1378,27 +1357,27 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1407,27 +1386,27 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="C10" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1436,27 +1415,27 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C11" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1465,27 +1444,27 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -1494,13 +1473,13 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>20</v>
@@ -1508,13 +1487,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -1523,13 +1502,13 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>171</v>
+        <v>86</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>20</v>
@@ -1537,13 +1516,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
@@ -1552,13 +1531,13 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>20</v>
@@ -1566,13 +1545,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -1581,27 +1560,27 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -1610,27 +1589,27 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -1639,27 +1618,27 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -1668,24 +1647,27 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18" t="s">
-        <v>115</v>
+        <v>129</v>
+      </c>
+      <c r="I18" s="3">
+        <v>28000</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
@@ -1697,27 +1679,27 @@
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="I19" s="3">
         <v>28000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -1729,27 +1711,27 @@
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>221</v>
+        <v>19</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="I20" s="3">
         <v>28000</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -1761,27 +1743,27 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I21" s="3">
         <v>28000</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -1793,27 +1775,27 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="I22" s="3">
         <v>28000</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -1825,30 +1807,30 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I23" s="3">
         <v>28000</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -1857,30 +1839,27 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>150</v>
-      </c>
-      <c r="I24" s="3">
-        <v>28000</v>
+        <v>87</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -1889,13 +1868,13 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>20</v>
@@ -1903,13 +1882,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -1918,13 +1897,13 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>20</v>
@@ -1932,13 +1911,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -1947,13 +1926,13 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>20</v>
@@ -1961,13 +1940,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -1976,13 +1955,13 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>20</v>
@@ -1990,13 +1969,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -2011,7 +1990,7 @@
         <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>20</v>
@@ -2019,13 +1998,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -2034,27 +2013,27 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -2063,13 +2042,13 @@
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>20</v>
@@ -2077,13 +2056,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2092,13 +2071,13 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>20</v>
@@ -2106,13 +2085,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -2121,13 +2100,13 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
       </c>
       <c r="H33" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>20</v>
@@ -2135,13 +2114,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -2150,13 +2129,13 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
       </c>
       <c r="H34" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>20</v>
@@ -2164,13 +2143,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -2185,7 +2164,7 @@
         <v>13</v>
       </c>
       <c r="H35" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>20</v>
@@ -2193,13 +2172,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -2208,27 +2187,27 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
       </c>
       <c r="H36" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -2237,13 +2216,13 @@
         <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H37" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>20</v>
@@ -2251,13 +2230,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -2266,13 +2245,13 @@
         <v>11</v>
       </c>
       <c r="F38" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G38" t="s">
         <v>13</v>
       </c>
       <c r="H38" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="I38" s="3">
         <v>52</v>
@@ -2283,13 +2262,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -2298,27 +2277,27 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
       </c>
       <c r="H39" t="s">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2327,27 +2306,27 @@
         <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>148</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
       </c>
       <c r="H40" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -2356,27 +2335,27 @@
         <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H41" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>227</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>228</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -2385,27 +2364,27 @@
         <v>11</v>
       </c>
       <c r="F42" t="s">
-        <v>225</v>
+        <v>19</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H42" t="s">
-        <v>229</v>
+        <v>114</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="C43" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -2414,27 +2393,27 @@
         <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>225</v>
+        <v>27</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
       </c>
       <c r="H43" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -2443,27 +2422,27 @@
         <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
@@ -2478,21 +2457,21 @@
         <v>12</v>
       </c>
       <c r="H45" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="B46" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -2501,27 +2480,27 @@
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
       </c>
       <c r="H46" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="B47" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -2530,27 +2509,27 @@
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>225</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
       </c>
       <c r="H47" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2559,114 +2538,114 @@
         <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
       </c>
       <c r="H48" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H49" t="s">
-        <v>171</v>
-      </c>
-      <c r="I49" s="3">
-        <v>49</v>
+        <v>181</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="D50" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="G50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H50" t="s">
-        <v>180</v>
-      </c>
-      <c r="I50" s="3">
-        <v>49</v>
+        <v>181</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="C51" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="G51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H51" t="s">
-        <v>140</v>
-      </c>
-      <c r="I51" s="3">
-        <v>49</v>
+        <v>178</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -2675,13 +2654,16 @@
         <v>11</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H52" t="s">
-        <v>146</v>
+        <v>178</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -2689,10 +2671,10 @@
         <v>144</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2701,27 +2683,27 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H53" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -2730,27 +2712,27 @@
         <v>11</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="G54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H54" t="s">
-        <v>230</v>
+        <v>146</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>204</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -2759,27 +2741,27 @@
         <v>11</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="G55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H55" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>204</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="B56" t="s">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="C56" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -2788,24 +2770,30 @@
         <v>11</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="H56" t="s">
+        <v>143</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>199</v>
+        <v>121</v>
       </c>
       <c r="B57" t="s">
-        <v>231</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D57" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="E57" t="s">
         <v>11</v>
@@ -2817,70 +2805,79 @@
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>143</v>
+        <v>141</v>
+      </c>
+      <c r="I57" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="B58" t="s">
-        <v>207</v>
+        <v>118</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="E58" t="s">
         <v>11</v>
       </c>
       <c r="F58" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H58" t="s">
-        <v>208</v>
+        <v>150</v>
+      </c>
+      <c r="I58" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="B59" t="s">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="E59" t="s">
         <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G59" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H59" t="s">
-        <v>209</v>
+        <v>122</v>
+      </c>
+      <c r="I59" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="B60" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C60" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -2889,24 +2886,24 @@
         <v>11</v>
       </c>
       <c r="F60" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G60" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H60" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>184</v>
+        <v>123</v>
       </c>
       <c r="B61" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="C61" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -2915,24 +2912,24 @@
         <v>11</v>
       </c>
       <c r="F61" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
       </c>
       <c r="H61" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="C62" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
@@ -2941,24 +2938,27 @@
         <v>11</v>
       </c>
       <c r="F62" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="G62" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H62" t="s">
-        <v>232</v>
+        <v>127</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>205</v>
+        <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>168</v>
+        <v>31</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D63" t="s">
         <v>10</v>
@@ -2967,24 +2967,27 @@
         <v>11</v>
       </c>
       <c r="F63" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H63" t="s">
-        <v>206</v>
+        <v>182</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D64" t="s">
         <v>10</v>
@@ -2993,417 +2996,414 @@
         <v>11</v>
       </c>
       <c r="F64" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H64" t="s">
-        <v>169</v>
+        <v>162</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>206</v>
       </c>
       <c r="C65" t="s">
-        <v>36</v>
+        <v>207</v>
       </c>
       <c r="D65" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
         <v>11</v>
       </c>
       <c r="F65" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>58</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>206</v>
       </c>
       <c r="C66" t="s">
-        <v>36</v>
+        <v>207</v>
       </c>
       <c r="D66" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G66" t="s">
-        <v>63</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C67" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E67" t="s">
         <v>11</v>
       </c>
       <c r="F67" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C68" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E68" t="s">
         <v>11</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="G68" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>68</v>
+        <v>208</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D69" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E69" t="s">
         <v>11</v>
       </c>
       <c r="F69" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G69" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C70" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
       </c>
       <c r="F70" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" t="s">
+        <v>41</v>
+      </c>
+      <c r="G71" t="s">
         <v>36</v>
       </c>
-      <c r="D71" t="s">
-        <v>37</v>
-      </c>
-      <c r="E71" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" t="s">
-        <v>46</v>
-      </c>
-      <c r="G71" t="s">
-        <v>38</v>
-      </c>
       <c r="J71" s="3" t="s">
-        <v>47</v>
+        <v>211</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C72" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" t="s">
+        <v>41</v>
+      </c>
+      <c r="G72" t="s">
         <v>36</v>
       </c>
-      <c r="D72" t="s">
-        <v>37</v>
-      </c>
-      <c r="E72" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" t="s">
-        <v>46</v>
-      </c>
-      <c r="G72" t="s">
-        <v>38</v>
-      </c>
       <c r="J72" s="3" t="s">
-        <v>47</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B73" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C73" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" t="s">
+        <v>41</v>
+      </c>
+      <c r="G73" t="s">
         <v>36</v>
       </c>
-      <c r="D73" t="s">
-        <v>37</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" t="s">
-        <v>46</v>
-      </c>
-      <c r="G73" t="s">
-        <v>38</v>
-      </c>
       <c r="J73" s="3" t="s">
-        <v>50</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B74" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C74" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" t="s">
+        <v>41</v>
+      </c>
+      <c r="G74" t="s">
         <v>36</v>
       </c>
-      <c r="D74" t="s">
-        <v>37</v>
-      </c>
-      <c r="E74" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" t="s">
-        <v>46</v>
-      </c>
-      <c r="G74" t="s">
-        <v>58</v>
-      </c>
       <c r="J74" s="3" t="s">
-        <v>53</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C75" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" t="s">
+        <v>41</v>
+      </c>
+      <c r="G75" t="s">
         <v>36</v>
       </c>
-      <c r="D75" t="s">
-        <v>54</v>
-      </c>
-      <c r="E75" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" t="s">
-        <v>55</v>
-      </c>
-      <c r="G75" t="s">
-        <v>38</v>
-      </c>
       <c r="J75" s="3" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C76" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
       </c>
       <c r="F76" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G76" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" t="s">
+        <v>47</v>
+      </c>
+      <c r="E77" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" t="s">
         <v>36</v>
       </c>
-      <c r="D77" t="s">
-        <v>37</v>
-      </c>
-      <c r="E77" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" t="s">
-        <v>56</v>
-      </c>
-      <c r="G77" t="s">
-        <v>58</v>
-      </c>
       <c r="J77" s="3" t="s">
-        <v>59</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C78" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" t="s">
+        <v>47</v>
+      </c>
+      <c r="E78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" t="s">
+        <v>49</v>
+      </c>
+      <c r="G78" t="s">
         <v>36</v>
       </c>
-      <c r="D78" t="s">
-        <v>37</v>
-      </c>
-      <c r="E78" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" t="s">
-        <v>17</v>
-      </c>
-      <c r="G78" t="s">
-        <v>38</v>
-      </c>
       <c r="J78" s="3" t="s">
-        <v>39</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B79" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C79" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D79" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
       </c>
       <c r="F79" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G79" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C80" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E80" t="s">
         <v>11</v>
@@ -3412,180 +3412,180 @@
         <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>43</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>37</v>
       </c>
       <c r="B81" t="s">
-        <v>181</v>
+        <v>37</v>
       </c>
       <c r="C81" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" t="s">
         <v>36</v>
       </c>
-      <c r="D81" t="s">
-        <v>37</v>
-      </c>
-      <c r="E81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" t="s">
-        <v>178</v>
-      </c>
-      <c r="G81" t="s">
-        <v>38</v>
-      </c>
       <c r="J81" s="3" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="B82" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="C82" t="s">
+        <v>38</v>
+      </c>
+      <c r="D82" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" t="s">
+        <v>17</v>
+      </c>
+      <c r="G82" t="s">
         <v>36</v>
       </c>
-      <c r="D82" t="s">
-        <v>37</v>
-      </c>
-      <c r="E82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" t="s">
-        <v>183</v>
-      </c>
-      <c r="G82" t="s">
-        <v>63</v>
-      </c>
       <c r="J82" s="3" t="s">
-        <v>50</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="C83" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" t="s">
+        <v>148</v>
+      </c>
+      <c r="G83" t="s">
         <v>36</v>
       </c>
-      <c r="D83" t="s">
-        <v>37</v>
-      </c>
-      <c r="E83" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" t="s">
-        <v>61</v>
-      </c>
-      <c r="G83" t="s">
-        <v>58</v>
-      </c>
       <c r="J83" s="3" t="s">
-        <v>70</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>233</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>233</v>
+        <v>60</v>
       </c>
       <c r="C84" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D84" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E84" t="s">
         <v>11</v>
       </c>
       <c r="F84" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="G84" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D85" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" t="s">
         <v>54</v>
       </c>
-      <c r="E85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="s">
-        <v>14</v>
-      </c>
       <c r="G85" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>72</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="B86" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="C86" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D86" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" t="s">
         <v>54</v>
       </c>
-      <c r="E86" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" t="s">
-        <v>16</v>
-      </c>
       <c r="G86" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>72</v>
+        <v>209</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="B87" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="C87" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D87" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E87" t="s">
         <v>11</v>
@@ -3594,62 +3594,62 @@
         <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D88" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
       </c>
       <c r="F88" t="s">
-        <v>178</v>
+        <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C89" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D89" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E89" t="s">
         <v>11</v>
       </c>
       <c r="F89" t="s">
-        <v>187</v>
+        <v>14</v>
       </c>
       <c r="G89" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
@@ -3660,77 +3660,74 @@
         <v>29</v>
       </c>
       <c r="C90" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D90" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
       </c>
       <c r="F90" t="s">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="G90" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B91" t="s">
-        <v>210</v>
+        <v>29</v>
       </c>
       <c r="C91" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D91" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
       </c>
       <c r="F91" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="G91" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>211</v>
+        <v>53</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B92" t="s">
-        <v>212</v>
+        <v>29</v>
       </c>
       <c r="C92" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D92" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E92" t="s">
         <v>11</v>
       </c>
       <c r="F92" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="G92" t="s">
-        <v>38</v>
-      </c>
-      <c r="H92" t="s">
-        <v>213</v>
+        <v>61</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>211</v>
+        <v>53</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
@@ -3738,28 +3735,25 @@
         <v>18</v>
       </c>
       <c r="B93" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="C93" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" t="s">
+        <v>24</v>
+      </c>
+      <c r="G93" t="s">
         <v>36</v>
       </c>
-      <c r="D93" t="s">
-        <v>37</v>
-      </c>
-      <c r="E93" t="s">
-        <v>11</v>
-      </c>
-      <c r="F93" t="s">
-        <v>99</v>
-      </c>
-      <c r="G93" t="s">
-        <v>38</v>
-      </c>
-      <c r="H93" t="s">
-        <v>213</v>
-      </c>
       <c r="J93" s="3" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
@@ -3767,25 +3761,28 @@
         <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>215</v>
+        <v>166</v>
       </c>
       <c r="C94" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" t="s">
+        <v>81</v>
+      </c>
+      <c r="G94" t="s">
         <v>36</v>
       </c>
-      <c r="D94" t="s">
-        <v>37</v>
-      </c>
-      <c r="E94" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" t="s">
-        <v>99</v>
-      </c>
-      <c r="G94" t="s">
-        <v>38</v>
+      <c r="H94" t="s">
+        <v>167</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
@@ -3793,28 +3790,28 @@
         <v>18</v>
       </c>
       <c r="B95" t="s">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="C95" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" t="s">
+        <v>81</v>
+      </c>
+      <c r="G95" t="s">
         <v>36</v>
       </c>
-      <c r="D95" t="s">
-        <v>37</v>
-      </c>
-      <c r="E95" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" t="s">
-        <v>99</v>
-      </c>
-      <c r="G95" t="s">
-        <v>38</v>
-      </c>
       <c r="H95" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
@@ -3822,25 +3819,25 @@
         <v>18</v>
       </c>
       <c r="B96" t="s">
-        <v>18</v>
+        <v>169</v>
       </c>
       <c r="C96" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" t="s">
+        <v>81</v>
+      </c>
+      <c r="G96" t="s">
         <v>36</v>
       </c>
-      <c r="D96" t="s">
-        <v>37</v>
-      </c>
-      <c r="E96" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96" t="s">
-        <v>14</v>
-      </c>
-      <c r="G96" t="s">
-        <v>63</v>
-      </c>
       <c r="J96" s="3" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
@@ -3848,581 +3845,688 @@
         <v>18</v>
       </c>
       <c r="B97" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="C97" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" t="s">
+        <v>81</v>
+      </c>
+      <c r="G97" t="s">
         <v>36</v>
       </c>
-      <c r="D97" t="s">
-        <v>37</v>
-      </c>
-      <c r="E97" t="s">
-        <v>11</v>
-      </c>
-      <c r="F97" t="s">
-        <v>61</v>
-      </c>
-      <c r="G97" t="s">
-        <v>63</v>
+      <c r="H97" t="s">
+        <v>167</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C98" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D98" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E98" t="s">
         <v>11</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B99" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C99" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D99" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E99" t="s">
         <v>11</v>
       </c>
       <c r="F99" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G99" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D100" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E100" t="s">
         <v>11</v>
       </c>
       <c r="F100" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>62</v>
+        <v>218</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="B101" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D101" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E101" t="s">
         <v>11</v>
       </c>
       <c r="F101" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="G101" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>62</v>
+        <v>218</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B102" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C102" t="s">
+        <v>34</v>
+      </c>
+      <c r="D102" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" t="s">
+        <v>81</v>
+      </c>
+      <c r="G102" t="s">
         <v>36</v>
       </c>
-      <c r="D102" t="s">
-        <v>37</v>
-      </c>
-      <c r="E102" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" t="s">
-        <v>21</v>
-      </c>
-      <c r="G102" t="s">
-        <v>38</v>
-      </c>
       <c r="J102" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B103" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C103" t="s">
+        <v>34</v>
+      </c>
+      <c r="D103" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" t="s">
+        <v>21</v>
+      </c>
+      <c r="G103" t="s">
         <v>36</v>
       </c>
-      <c r="D103" t="s">
-        <v>37</v>
-      </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s">
-        <v>61</v>
-      </c>
-      <c r="G103" t="s">
-        <v>38</v>
-      </c>
       <c r="J103" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B104" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C104" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" t="s">
+        <v>21</v>
+      </c>
+      <c r="G104" t="s">
         <v>36</v>
       </c>
-      <c r="D104" t="s">
-        <v>37</v>
-      </c>
-      <c r="E104" t="s">
-        <v>11</v>
-      </c>
-      <c r="F104" t="s">
-        <v>19</v>
-      </c>
-      <c r="G104" t="s">
-        <v>38</v>
-      </c>
       <c r="J104" s="3" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B105" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C105" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" t="s">
+        <v>54</v>
+      </c>
+      <c r="G105" t="s">
         <v>36</v>
       </c>
-      <c r="D105" t="s">
-        <v>37</v>
-      </c>
-      <c r="E105" t="s">
-        <v>11</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="J105" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="G105" t="s">
-        <v>58</v>
-      </c>
-      <c r="I105" s="3">
-        <v>14</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B106" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C106" t="s">
+        <v>34</v>
+      </c>
+      <c r="D106" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" t="s">
+        <v>19</v>
+      </c>
+      <c r="G106" t="s">
         <v>36</v>
       </c>
-      <c r="D106" t="s">
-        <v>37</v>
-      </c>
-      <c r="E106" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" t="s">
-        <v>56</v>
-      </c>
-      <c r="G106" t="s">
-        <v>58</v>
-      </c>
-      <c r="I106" s="3">
-        <v>14</v>
-      </c>
       <c r="J106" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B107" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C107" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D107" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E107" t="s">
         <v>11</v>
       </c>
       <c r="F107" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G107" t="s">
-        <v>38</v>
+        <v>51</v>
+      </c>
+      <c r="I107" s="3">
+        <v>14</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>80</v>
+        <v>209</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B108" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="C108" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D108" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
       </c>
       <c r="F108" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G108" t="s">
-        <v>83</v>
+        <v>51</v>
+      </c>
+      <c r="I108" s="3">
+        <v>14</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B109" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C109" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" t="s">
+        <v>24</v>
+      </c>
+      <c r="G109" t="s">
         <v>36</v>
       </c>
-      <c r="D109" t="s">
-        <v>54</v>
-      </c>
-      <c r="E109" t="s">
-        <v>11</v>
-      </c>
-      <c r="F109" t="s">
-        <v>61</v>
-      </c>
-      <c r="G109" t="s">
-        <v>58</v>
-      </c>
       <c r="J109" s="3" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B110" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C110" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D110" t="s">
+        <v>47</v>
+      </c>
+      <c r="E110" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" t="s">
         <v>54</v>
       </c>
-      <c r="E110" t="s">
-        <v>11</v>
-      </c>
-      <c r="F110" t="s">
-        <v>61</v>
-      </c>
       <c r="G110" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>96</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B111" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C111" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D111" t="s">
+        <v>47</v>
+      </c>
+      <c r="E111" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" t="s">
         <v>54</v>
       </c>
-      <c r="E111" t="s">
-        <v>11</v>
-      </c>
-      <c r="F111" t="s">
-        <v>97</v>
-      </c>
       <c r="G111" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B112" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C112" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D112" t="s">
+        <v>47</v>
+      </c>
+      <c r="E112" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" t="s">
         <v>54</v>
       </c>
-      <c r="E112" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" t="s">
-        <v>97</v>
-      </c>
       <c r="G112" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>87</v>
+        <v>220</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B113" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C113" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D113" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E113" t="s">
         <v>11</v>
       </c>
       <c r="F113" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="G113" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>89</v>
+        <v>221</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B114" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C114" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D114" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E114" t="s">
         <v>11</v>
       </c>
       <c r="F114" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G114" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>90</v>
+        <v>222</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B115" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C115" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D115" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E115" t="s">
         <v>11</v>
       </c>
       <c r="F115" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>50</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B116" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C116" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D116" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E116" t="s">
         <v>11</v>
       </c>
       <c r="F116" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G116" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>50</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B117" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C117" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D117" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E117" t="s">
         <v>11</v>
       </c>
       <c r="F117" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="G117" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>93</v>
+        <v>209</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B118" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C118" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D118" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E118" t="s">
         <v>11</v>
       </c>
       <c r="F118" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G118" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>50</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>76</v>
+      </c>
+      <c r="B119" t="s">
+        <v>76</v>
+      </c>
+      <c r="C119" t="s">
+        <v>34</v>
+      </c>
+      <c r="D119" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" t="s">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s">
+        <v>51</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>76</v>
+      </c>
+      <c r="B120" t="s">
+        <v>76</v>
+      </c>
+      <c r="C120" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" t="s">
+        <v>41</v>
+      </c>
+      <c r="G120" t="s">
+        <v>51</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>69</v>
+      </c>
+      <c r="B121" t="s">
+        <v>206</v>
+      </c>
+      <c r="C121" t="s">
+        <v>226</v>
+      </c>
+      <c r="D121" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" t="s">
+        <v>19</v>
+      </c>
+      <c r="G121" t="s">
+        <v>12</v>
+      </c>
+      <c r="I121" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>32</v>
+      </c>
+      <c r="B122" t="s">
+        <v>206</v>
+      </c>
+      <c r="C122" t="s">
+        <v>226</v>
+      </c>
+      <c r="D122" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" t="s">
+        <v>19</v>
+      </c>
+      <c r="G122" t="s">
+        <v>12</v>
+      </c>
+      <c r="I122" s="3">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J118" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
+  <autoFilter ref="A1:J122" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tr.alienigenaV5-main\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6D289F3-ED23-4377-A366-8066841AFA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{883037DA-9842-47F7-AF2D-CC8EC2E7B76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="551" xr2:uid="{9E8F4E85-D2FF-4383-A72B-5CAFDCCC5644}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="218">
   <si>
     <t>Origem</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Laranjeiras - SE</t>
   </si>
   <si>
-    <t>São Gonçalo - RJ</t>
-  </si>
-  <si>
     <t>CIMENTO</t>
   </si>
   <si>
@@ -155,12 +152,6 @@
     <t>Grade Baixa</t>
   </si>
   <si>
-    <t>Rio de Janeiro - RJ</t>
-  </si>
-  <si>
-    <t>CIMENTO ENSACADO</t>
-  </si>
-  <si>
     <t>Campinas - SP</t>
   </si>
   <si>
@@ -653,21 +644,9 @@
     <t>180,00</t>
   </si>
   <si>
-    <t>Nova Ponte - MG</t>
-  </si>
-  <si>
-    <t>Ponte Nova - MG</t>
-  </si>
-  <si>
     <t>Brasilândia de Minas - MG</t>
   </si>
   <si>
-    <t>Penápolis - SP</t>
-  </si>
-  <si>
-    <t>Ureia granel</t>
-  </si>
-  <si>
     <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
   </si>
   <si>
@@ -683,15 +662,6 @@
     <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
   </si>
   <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possíveis destinos disponíveis:Região dos Lagos (Araruama/RJ com Saquarema/RJ na mesma rota e Cabo Frio/RJ com Arraial do Cabo/RJ na mesma rota)</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possíveis destinos disponíveis CD Santa Cruz: Rio de Janeiro-RJ, Itaguaí -RJ, Seropédica-RJ, Itatiaia-RJ.</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possíveis destinos disponíveis CD RIO: Rio de Janeiro-RJ, Nova Iguaçu-RJ, Duque de Caxias-RJ, Mesquita-RJ )</t>
-  </si>
-  <si>
     <t>PARA MOTORISTAS CATIVOS NA REGIÃO - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
   </si>
   <si>
@@ -722,7 +692,10 @@
     <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Região de Gargalo, Vitória da Conquista e Ipiau</t>
   </si>
   <si>
-    <t>Ureia Granel</t>
+    <t>Diversos</t>
+  </si>
+  <si>
+    <t>Truck, Carreta, Carreta 4º eixo</t>
   </si>
 </sst>
 </file>
@@ -1122,19 +1095,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}">
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="255.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="112" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1171,39 +1144,42 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I2" s="3">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1218,7 +1194,7 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>20</v>
@@ -1226,13 +1202,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1241,85 +1217,85 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>192</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="G6" t="s">
-        <v>193</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1328,27 +1304,27 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1357,27 +1333,27 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B9" t="s">
         <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1386,27 +1362,27 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1415,27 +1391,27 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>175</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1450,7 +1426,7 @@
         <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>20</v>
@@ -1458,13 +1434,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -1479,7 +1455,7 @@
         <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>20</v>
@@ -1487,28 +1463,28 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
         <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" t="s">
-        <v>86</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>20</v>
@@ -1516,71 +1492,59 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>182</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>216</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>20</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>216</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>217</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" t="s">
-        <v>91</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -1595,50 +1559,50 @@
         <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" t="s">
-        <v>97</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -1647,27 +1611,24 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18" t="s">
-        <v>129</v>
-      </c>
-      <c r="I18" s="3">
-        <v>28000</v>
+        <v>94</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
@@ -1679,27 +1640,27 @@
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I19" s="3">
         <v>28000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -1711,27 +1672,27 @@
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I20" s="3">
         <v>28000</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -1743,27 +1704,27 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I21" s="3">
         <v>28000</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -1775,27 +1736,27 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I22" s="3">
         <v>28000</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -1807,30 +1768,30 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I23" s="3">
         <v>28000</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -1839,27 +1800,30 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>87</v>
+        <v>126</v>
+      </c>
+      <c r="I24" s="3">
+        <v>28000</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -1868,13 +1832,13 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>20</v>
@@ -1882,13 +1846,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -1897,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>20</v>
@@ -1911,13 +1875,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -1926,13 +1890,13 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>20</v>
@@ -1940,13 +1904,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -1955,13 +1919,13 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>20</v>
@@ -1969,13 +1933,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -1984,13 +1948,13 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>186</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>20</v>
@@ -1998,13 +1962,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
         <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -2013,27 +1977,27 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>196</v>
+        <v>24</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -2042,27 +2006,27 @@
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2071,13 +2035,13 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>20</v>
@@ -2085,13 +2049,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -2100,13 +2064,13 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
       </c>
       <c r="H33" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>20</v>
@@ -2114,13 +2078,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -2129,13 +2093,13 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
       </c>
       <c r="H34" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>20</v>
@@ -2143,13 +2107,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -2158,13 +2122,13 @@
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>186</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
       </c>
       <c r="H35" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>20</v>
@@ -2172,13 +2136,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -2187,27 +2151,27 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>196</v>
+        <v>24</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
       </c>
       <c r="H36" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -2216,27 +2180,27 @@
         <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>193</v>
       </c>
       <c r="G37" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="H37" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -2248,13 +2212,10 @@
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>105</v>
-      </c>
-      <c r="I38" s="3">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>20</v>
@@ -2262,13 +2223,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -2277,27 +2238,30 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
       </c>
       <c r="H39" t="s">
-        <v>78</v>
+        <v>102</v>
+      </c>
+      <c r="I39" s="3">
+        <v>52</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>197</v>
+        <v>103</v>
       </c>
       <c r="B40" t="s">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2306,27 +2270,27 @@
         <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
       </c>
       <c r="H40" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="C41" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -2335,27 +2299,27 @@
         <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
       </c>
       <c r="H41" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -2370,21 +2334,21 @@
         <v>13</v>
       </c>
       <c r="H42" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -2393,27 +2357,27 @@
         <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H43" t="s">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -2422,27 +2386,27 @@
         <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B45" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
@@ -2451,27 +2415,27 @@
         <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="G45" t="s">
         <v>12</v>
       </c>
       <c r="H45" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="B46" t="s">
-        <v>203</v>
+        <v>142</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -2480,27 +2444,27 @@
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
       </c>
       <c r="H46" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B47" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -2509,27 +2473,27 @@
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
       </c>
       <c r="H47" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2538,27 +2502,27 @@
         <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
       </c>
       <c r="H48" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B49" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -2567,27 +2531,27 @@
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="G49" t="s">
         <v>12</v>
       </c>
       <c r="H49" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -2596,27 +2560,27 @@
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G50" t="s">
         <v>12</v>
       </c>
       <c r="H50" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -2625,27 +2589,27 @@
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
       </c>
       <c r="H51" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B52" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C52" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -2660,21 +2624,21 @@
         <v>12</v>
       </c>
       <c r="H52" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C53" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2683,27 +2647,27 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
       </c>
       <c r="H53" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -2712,27 +2676,27 @@
         <v>11</v>
       </c>
       <c r="F54" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G54" t="s">
         <v>12</v>
       </c>
       <c r="H54" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B55" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -2741,59 +2705,59 @@
         <v>11</v>
       </c>
       <c r="F55" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
       </c>
       <c r="H55" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" t="s">
         <v>115</v>
       </c>
-      <c r="B56" t="s">
-        <v>142</v>
-      </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="E56" t="s">
         <v>11</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H56" t="s">
-        <v>143</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>107</v>
+        <v>138</v>
+      </c>
+      <c r="I56" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E57" t="s">
         <v>11</v>
@@ -2805,7 +2769,7 @@
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I57" s="3">
         <v>49</v>
@@ -2813,28 +2777,28 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>118</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
         <v>117</v>
       </c>
-      <c r="B58" t="s">
-        <v>118</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="E58" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" t="s">
+        <v>27</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s">
         <v>119</v>
-      </c>
-      <c r="D58" t="s">
-        <v>120</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" t="s">
-        <v>150</v>
       </c>
       <c r="I58" s="3">
         <v>49</v>
@@ -2842,42 +2806,39 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>120</v>
+      </c>
+      <c r="B59" t="s">
+        <v>168</v>
+      </c>
+      <c r="C59" t="s">
         <v>121</v>
       </c>
-      <c r="B59" t="s">
-        <v>26</v>
-      </c>
-      <c r="C59" t="s">
-        <v>22</v>
-      </c>
       <c r="D59" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="E59" t="s">
         <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
       </c>
       <c r="H59" t="s">
-        <v>122</v>
-      </c>
-      <c r="I59" s="3">
-        <v>49</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B60" t="s">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -2892,44 +2853,47 @@
         <v>13</v>
       </c>
       <c r="H60" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" t="s">
+        <v>121</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" t="s">
         <v>123</v>
       </c>
-      <c r="B61" t="s">
-        <v>82</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="G61" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" t="s">
         <v>124</v>
       </c>
-      <c r="D61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" t="s">
-        <v>19</v>
-      </c>
-      <c r="G61" t="s">
-        <v>13</v>
-      </c>
-      <c r="H61" t="s">
+      <c r="J61" s="3" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
@@ -2938,16 +2902,16 @@
         <v>11</v>
       </c>
       <c r="F62" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
       </c>
       <c r="H62" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -2955,7 +2919,7 @@
         <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
         <v>22</v>
@@ -2973,761 +2937,773 @@
         <v>13</v>
       </c>
       <c r="H63" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C64" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D64" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E64" t="s">
         <v>11</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>163</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B65" t="s">
-        <v>206</v>
+        <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>33</v>
       </c>
       <c r="D65" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E65" t="s">
         <v>11</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G65" t="s">
-        <v>12</v>
+        <v>53</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B66" t="s">
-        <v>206</v>
+        <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>207</v>
+        <v>33</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E66" t="s">
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G66" t="s">
-        <v>12</v>
+        <v>48</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C67" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" t="s">
         <v>34</v>
       </c>
-      <c r="D67" t="s">
-        <v>35</v>
-      </c>
       <c r="E67" t="s">
         <v>11</v>
       </c>
       <c r="F67" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>44</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C68" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" t="s">
         <v>34</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" t="s">
+        <v>38</v>
+      </c>
+      <c r="G68" t="s">
         <v>35</v>
       </c>
-      <c r="E68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" t="s">
-        <v>59</v>
-      </c>
-      <c r="G68" t="s">
-        <v>56</v>
-      </c>
       <c r="J68" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
+        <v>33</v>
+      </c>
+      <c r="D69" t="s">
         <v>34</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" t="s">
+        <v>38</v>
+      </c>
+      <c r="G69" t="s">
         <v>35</v>
       </c>
-      <c r="E69" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" t="s">
-        <v>54</v>
-      </c>
-      <c r="G69" t="s">
-        <v>51</v>
-      </c>
       <c r="J69" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" t="s">
         <v>34</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" t="s">
+        <v>38</v>
+      </c>
+      <c r="G70" t="s">
         <v>35</v>
       </c>
-      <c r="E70" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" t="s">
-        <v>14</v>
-      </c>
-      <c r="G70" t="s">
-        <v>56</v>
-      </c>
       <c r="J70" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C71" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" t="s">
         <v>34</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" t="s">
+        <v>38</v>
+      </c>
+      <c r="G71" t="s">
         <v>35</v>
       </c>
-      <c r="E71" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" t="s">
-        <v>41</v>
-      </c>
-      <c r="G71" t="s">
-        <v>36</v>
-      </c>
       <c r="J71" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B72" t="s">
         <v>42</v>
       </c>
       <c r="C72" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" t="s">
         <v>34</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" t="s">
+        <v>38</v>
+      </c>
+      <c r="G72" t="s">
         <v>35</v>
       </c>
-      <c r="E72" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" t="s">
-        <v>41</v>
-      </c>
-      <c r="G72" t="s">
-        <v>36</v>
-      </c>
       <c r="J72" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B73" t="s">
         <v>43</v>
       </c>
       <c r="C73" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" t="s">
         <v>34</v>
       </c>
-      <c r="D73" t="s">
-        <v>35</v>
-      </c>
       <c r="E73" t="s">
         <v>11</v>
       </c>
       <c r="F73" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G73" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D74" t="s">
+        <v>44</v>
+      </c>
+      <c r="E74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" t="s">
+        <v>45</v>
+      </c>
+      <c r="G74" t="s">
         <v>35</v>
       </c>
-      <c r="E74" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" t="s">
-        <v>41</v>
-      </c>
-      <c r="G74" t="s">
-        <v>36</v>
-      </c>
       <c r="J74" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D75" t="s">
+        <v>44</v>
+      </c>
+      <c r="E75" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" t="s">
+        <v>46</v>
+      </c>
+      <c r="G75" t="s">
         <v>35</v>
       </c>
-      <c r="E75" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" t="s">
-        <v>41</v>
-      </c>
-      <c r="G75" t="s">
-        <v>36</v>
-      </c>
       <c r="J75" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>47</v>
+      </c>
+      <c r="B76" t="s">
+        <v>47</v>
+      </c>
+      <c r="C76" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76" t="s">
+        <v>34</v>
+      </c>
+      <c r="E76" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" t="s">
         <v>46</v>
       </c>
-      <c r="B76" t="s">
-        <v>46</v>
-      </c>
-      <c r="C76" t="s">
-        <v>34</v>
-      </c>
-      <c r="D76" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" t="s">
-        <v>41</v>
-      </c>
       <c r="G76" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>212</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="C77" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" t="s">
         <v>34</v>
       </c>
-      <c r="D77" t="s">
-        <v>47</v>
-      </c>
       <c r="E77" t="s">
         <v>11</v>
       </c>
       <c r="F77" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
       <c r="G77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C78" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" t="s">
         <v>34</v>
       </c>
-      <c r="D78" t="s">
-        <v>47</v>
-      </c>
       <c r="E78" t="s">
         <v>11</v>
       </c>
       <c r="F78" t="s">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="G78" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C79" t="s">
+        <v>33</v>
+      </c>
+      <c r="D79" t="s">
         <v>34</v>
       </c>
-      <c r="D79" t="s">
-        <v>35</v>
-      </c>
       <c r="E79" t="s">
         <v>11</v>
       </c>
       <c r="F79" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G79" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>52</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="B80" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="C80" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" t="s">
         <v>34</v>
       </c>
-      <c r="D80" t="s">
-        <v>35</v>
-      </c>
       <c r="E80" t="s">
         <v>11</v>
       </c>
       <c r="F80" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G80" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B81" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D81" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E81" t="s">
         <v>11</v>
       </c>
       <c r="F81" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B82" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C82" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D82" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E82" t="s">
         <v>11</v>
       </c>
       <c r="F82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>215</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="C83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D83" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E83" t="s">
         <v>11</v>
       </c>
       <c r="F83" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="G83" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>216</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D84" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E84" t="s">
         <v>11</v>
       </c>
       <c r="F84" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G84" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>209</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D85" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E85" t="s">
         <v>11</v>
       </c>
       <c r="F85" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="G85" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>217</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>183</v>
+        <v>29</v>
       </c>
       <c r="B86" t="s">
-        <v>183</v>
+        <v>29</v>
       </c>
       <c r="C86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E86" t="s">
         <v>11</v>
       </c>
       <c r="F86" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G86" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>209</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B87" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
       <c r="C87" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" t="s">
         <v>34</v>
       </c>
-      <c r="D87" t="s">
-        <v>47</v>
-      </c>
       <c r="E87" t="s">
         <v>11</v>
       </c>
       <c r="F87" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G87" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>62</v>
+        <v>162</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B88" t="s">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="C88" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" t="s">
         <v>34</v>
       </c>
-      <c r="D88" t="s">
-        <v>47</v>
-      </c>
       <c r="E88" t="s">
         <v>11</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="G88" t="s">
-        <v>61</v>
+        <v>35</v>
+      </c>
+      <c r="H88" t="s">
+        <v>164</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>62</v>
+        <v>162</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="B89" t="s">
-        <v>63</v>
+        <v>165</v>
       </c>
       <c r="C89" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" t="s">
         <v>34</v>
       </c>
-      <c r="D89" t="s">
-        <v>47</v>
-      </c>
       <c r="E89" t="s">
         <v>11</v>
       </c>
       <c r="F89" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="G89" t="s">
-        <v>56</v>
+        <v>35</v>
+      </c>
+      <c r="H89" t="s">
+        <v>164</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>62</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B90" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
       <c r="C90" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" t="s">
         <v>34</v>
       </c>
-      <c r="D90" t="s">
-        <v>47</v>
-      </c>
       <c r="E90" t="s">
         <v>11</v>
       </c>
       <c r="F90" t="s">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="G90" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="C91" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" t="s">
         <v>34</v>
       </c>
-      <c r="D91" t="s">
-        <v>47</v>
-      </c>
       <c r="E91" t="s">
         <v>11</v>
       </c>
       <c r="F91" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="G91" t="s">
-        <v>61</v>
+        <v>35</v>
+      </c>
+      <c r="H91" t="s">
+        <v>164</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C92" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" t="s">
         <v>34</v>
       </c>
-      <c r="D92" t="s">
-        <v>47</v>
-      </c>
       <c r="E92" t="s">
         <v>11</v>
       </c>
       <c r="F92" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
@@ -3735,204 +3711,195 @@
         <v>18</v>
       </c>
       <c r="B93" t="s">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="C93" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" t="s">
         <v>34</v>
       </c>
-      <c r="D93" t="s">
-        <v>35</v>
-      </c>
       <c r="E93" t="s">
         <v>11</v>
       </c>
       <c r="F93" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G93" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B94" t="s">
-        <v>166</v>
+        <v>26</v>
       </c>
       <c r="C94" t="s">
+        <v>33</v>
+      </c>
+      <c r="D94" t="s">
         <v>34</v>
       </c>
-      <c r="D94" t="s">
-        <v>35</v>
-      </c>
       <c r="E94" t="s">
         <v>11</v>
       </c>
       <c r="F94" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>36</v>
-      </c>
-      <c r="H94" t="s">
-        <v>167</v>
+        <v>53</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B95" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="C95" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" t="s">
         <v>34</v>
       </c>
-      <c r="D95" t="s">
-        <v>35</v>
-      </c>
       <c r="E95" t="s">
         <v>11</v>
       </c>
       <c r="F95" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="G95" t="s">
-        <v>36</v>
-      </c>
-      <c r="H95" t="s">
-        <v>167</v>
+        <v>48</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="B96" t="s">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="C96" t="s">
+        <v>33</v>
+      </c>
+      <c r="D96" t="s">
         <v>34</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" t="s">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s">
         <v>35</v>
       </c>
-      <c r="E96" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96" t="s">
-        <v>81</v>
-      </c>
-      <c r="G96" t="s">
-        <v>36</v>
-      </c>
       <c r="J96" s="3" t="s">
-        <v>165</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="B97" t="s">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="C97" t="s">
+        <v>33</v>
+      </c>
+      <c r="D97" t="s">
         <v>34</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" t="s">
+        <v>21</v>
+      </c>
+      <c r="G97" t="s">
         <v>35</v>
       </c>
-      <c r="E97" t="s">
-        <v>11</v>
-      </c>
-      <c r="F97" t="s">
-        <v>81</v>
-      </c>
-      <c r="G97" t="s">
-        <v>36</v>
-      </c>
-      <c r="H97" t="s">
-        <v>167</v>
-      </c>
       <c r="J97" s="3" t="s">
-        <v>165</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="B98" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C98" t="s">
+        <v>33</v>
+      </c>
+      <c r="D98" t="s">
         <v>34</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" t="s">
+        <v>21</v>
+      </c>
+      <c r="G98" t="s">
         <v>35</v>
       </c>
-      <c r="E98" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" t="s">
-        <v>14</v>
-      </c>
-      <c r="G98" t="s">
-        <v>56</v>
-      </c>
       <c r="J98" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="C99" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" t="s">
         <v>34</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" t="s">
+        <v>51</v>
+      </c>
+      <c r="G99" t="s">
         <v>35</v>
       </c>
-      <c r="E99" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" t="s">
-        <v>54</v>
-      </c>
-      <c r="G99" t="s">
-        <v>56</v>
-      </c>
       <c r="J99" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B100" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C100" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" t="s">
         <v>34</v>
-      </c>
-      <c r="D100" t="s">
-        <v>35</v>
       </c>
       <c r="E100" t="s">
         <v>11</v>
@@ -3941,592 +3908,410 @@
         <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>218</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B101" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C101" t="s">
+        <v>33</v>
+      </c>
+      <c r="D101" t="s">
         <v>34</v>
       </c>
-      <c r="D101" t="s">
-        <v>35</v>
-      </c>
       <c r="E101" t="s">
         <v>11</v>
       </c>
       <c r="F101" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G101" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="I101" s="3">
+        <v>14</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="B102" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="C102" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" t="s">
         <v>34</v>
       </c>
-      <c r="D102" t="s">
-        <v>35</v>
-      </c>
       <c r="E102" t="s">
         <v>11</v>
       </c>
       <c r="F102" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G102" t="s">
-        <v>36</v>
+        <v>48</v>
+      </c>
+      <c r="I102" s="3">
+        <v>14</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>55</v>
+        <v>202</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B103" t="s">
         <v>65</v>
       </c>
       <c r="C103" t="s">
+        <v>33</v>
+      </c>
+      <c r="D103" t="s">
         <v>34</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" t="s">
+        <v>24</v>
+      </c>
+      <c r="G103" t="s">
         <v>35</v>
       </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s">
-        <v>21</v>
-      </c>
-      <c r="G103" t="s">
-        <v>36</v>
-      </c>
       <c r="J103" s="3" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B104" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D104" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E104" t="s">
         <v>11</v>
       </c>
       <c r="F104" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="G104" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>55</v>
+        <v>202</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B105" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D105" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E105" t="s">
         <v>11</v>
       </c>
       <c r="F105" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G105" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D106" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E106" t="s">
         <v>11</v>
       </c>
       <c r="F106" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G106" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>67</v>
+        <v>210</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B107" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="C107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D107" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E107" t="s">
         <v>11</v>
       </c>
       <c r="F107" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="G107" t="s">
-        <v>51</v>
-      </c>
-      <c r="I107" s="3">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B108" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D108" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
       </c>
       <c r="F108" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="G108" t="s">
-        <v>51</v>
-      </c>
-      <c r="I108" s="3">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B109" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D109" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E109" t="s">
         <v>11</v>
       </c>
       <c r="F109" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D110" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E110" t="s">
         <v>11</v>
       </c>
       <c r="F110" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G110" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B111" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C111" t="s">
+        <v>33</v>
+      </c>
+      <c r="D111" t="s">
         <v>34</v>
       </c>
-      <c r="D111" t="s">
-        <v>47</v>
-      </c>
       <c r="E111" t="s">
         <v>11</v>
       </c>
       <c r="F111" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G111" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B112" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C112" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" t="s">
         <v>34</v>
       </c>
-      <c r="D112" t="s">
-        <v>47</v>
-      </c>
       <c r="E112" t="s">
         <v>11</v>
       </c>
       <c r="F112" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G112" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B113" t="s">
         <v>73</v>
       </c>
       <c r="C113" t="s">
+        <v>33</v>
+      </c>
+      <c r="D113" t="s">
         <v>34</v>
       </c>
-      <c r="D113" t="s">
-        <v>47</v>
-      </c>
       <c r="E113" t="s">
         <v>11</v>
       </c>
       <c r="F113" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B114" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C114" t="s">
+        <v>33</v>
+      </c>
+      <c r="D114" t="s">
         <v>34</v>
       </c>
-      <c r="D114" t="s">
-        <v>47</v>
-      </c>
       <c r="E114" t="s">
         <v>11</v>
       </c>
       <c r="F114" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="G114" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="B115" t="s">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="C115" t="s">
-        <v>34</v>
+        <v>182</v>
       </c>
       <c r="D115" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="E115" t="s">
         <v>11</v>
       </c>
       <c r="F115" t="s">
+        <v>184</v>
+      </c>
+      <c r="G115" t="s">
+        <v>185</v>
+      </c>
+      <c r="I115" s="3">
         <v>14</v>
       </c>
-      <c r="G115" t="s">
-        <v>51</v>
-      </c>
-      <c r="J115" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>75</v>
-      </c>
-      <c r="B116" t="s">
-        <v>75</v>
-      </c>
-      <c r="C116" t="s">
-        <v>34</v>
-      </c>
-      <c r="D116" t="s">
-        <v>47</v>
-      </c>
-      <c r="E116" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" t="s">
-        <v>49</v>
-      </c>
-      <c r="G116" t="s">
-        <v>51</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>76</v>
-      </c>
-      <c r="B117" t="s">
-        <v>77</v>
-      </c>
-      <c r="C117" t="s">
-        <v>34</v>
-      </c>
-      <c r="D117" t="s">
-        <v>35</v>
-      </c>
-      <c r="E117" t="s">
-        <v>11</v>
-      </c>
-      <c r="F117" t="s">
-        <v>48</v>
-      </c>
-      <c r="G117" t="s">
-        <v>51</v>
-      </c>
-      <c r="J117" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>76</v>
-      </c>
-      <c r="B118" t="s">
-        <v>77</v>
-      </c>
-      <c r="C118" t="s">
-        <v>34</v>
-      </c>
-      <c r="D118" t="s">
-        <v>35</v>
-      </c>
-      <c r="E118" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" t="s">
-        <v>49</v>
-      </c>
-      <c r="G118" t="s">
-        <v>51</v>
-      </c>
-      <c r="J118" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>76</v>
-      </c>
-      <c r="B119" t="s">
-        <v>76</v>
-      </c>
-      <c r="C119" t="s">
-        <v>34</v>
-      </c>
-      <c r="D119" t="s">
-        <v>35</v>
-      </c>
-      <c r="E119" t="s">
-        <v>11</v>
-      </c>
-      <c r="F119" t="s">
-        <v>15</v>
-      </c>
-      <c r="G119" t="s">
-        <v>51</v>
-      </c>
-      <c r="J119" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>76</v>
-      </c>
-      <c r="B120" t="s">
-        <v>76</v>
-      </c>
-      <c r="C120" t="s">
-        <v>34</v>
-      </c>
-      <c r="D120" t="s">
-        <v>35</v>
-      </c>
-      <c r="E120" t="s">
-        <v>11</v>
-      </c>
-      <c r="F120" t="s">
-        <v>41</v>
-      </c>
-      <c r="G120" t="s">
-        <v>51</v>
-      </c>
-      <c r="J120" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>69</v>
-      </c>
-      <c r="B121" t="s">
-        <v>206</v>
-      </c>
-      <c r="C121" t="s">
-        <v>226</v>
-      </c>
-      <c r="D121" t="s">
-        <v>10</v>
-      </c>
-      <c r="E121" t="s">
-        <v>11</v>
-      </c>
-      <c r="F121" t="s">
-        <v>19</v>
-      </c>
-      <c r="G121" t="s">
-        <v>12</v>
-      </c>
-      <c r="I121" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>32</v>
-      </c>
-      <c r="B122" t="s">
-        <v>206</v>
-      </c>
-      <c r="C122" t="s">
-        <v>226</v>
-      </c>
-      <c r="D122" t="s">
-        <v>10</v>
-      </c>
-      <c r="E122" t="s">
-        <v>11</v>
-      </c>
-      <c r="F122" t="s">
-        <v>19</v>
-      </c>
-      <c r="G122" t="s">
-        <v>12</v>
-      </c>
-      <c r="I122" s="3">
-        <v>48</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J122" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
+  <autoFilter ref="A1:J115" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tr.alienigenaV5-main\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{883037DA-9842-47F7-AF2D-CC8EC2E7B76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD2F5F5D-2821-4C84-AF0B-6682B0C718BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="551" xr2:uid="{9E8F4E85-D2FF-4383-A72B-5CAFDCCC5644}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$114</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="212">
   <si>
     <t>Origem</t>
   </si>
@@ -266,9 +266,6 @@
     <t>Itabuna - BA</t>
   </si>
   <si>
-    <t>Vitória da Conquista - BA</t>
-  </si>
-  <si>
     <t>50,00</t>
   </si>
   <si>
@@ -410,18 +407,6 @@
     <t>BAUXITA</t>
   </si>
   <si>
-    <t>14.131,00</t>
-  </si>
-  <si>
-    <t>Vanderléia, Bitrem 7 eixos, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>10.718,00</t>
-  </si>
-  <si>
-    <t>Apenas 7 eixos acima 38 ton</t>
-  </si>
-  <si>
     <t>130,00</t>
   </si>
   <si>
@@ -503,9 +488,6 @@
     <t>72,00</t>
   </si>
   <si>
-    <t>Itaperuçu - PR</t>
-  </si>
-  <si>
     <t>100,00</t>
   </si>
   <si>
@@ -557,9 +539,6 @@
     <t>Aldeias Altas - MA</t>
   </si>
   <si>
-    <t>190,00</t>
-  </si>
-  <si>
     <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
   </si>
   <si>
@@ -593,12 +572,6 @@
     <t>Tubos e Conexões</t>
   </si>
   <si>
-    <t>Tubo</t>
-  </si>
-  <si>
-    <t>Truck, Carreta, Carreta LS, Vanderléia, Carreta 4º eixo</t>
-  </si>
-  <si>
     <t>Sider, Baú, Grade Baixa</t>
   </si>
   <si>
@@ -696,6 +669,15 @@
   </si>
   <si>
     <t>Truck, Carreta, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Ponte Nova - MG</t>
+  </si>
+  <si>
+    <t>Guarapuava - PR</t>
+  </si>
+  <si>
+    <t>Ourinhos - SP</t>
   </si>
 </sst>
 </file>
@@ -1095,19 +1077,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}">
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="112" style="3" customWidth="1"/>
+    <col min="10" max="10" width="255.6640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1144,13 +1126,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1165,7 +1147,7 @@
         <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>20</v>
@@ -1173,13 +1155,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1194,7 +1176,7 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>20</v>
@@ -1202,13 +1184,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1217,30 +1199,30 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1249,10 +1231,10 @@
         <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>20</v>
@@ -1260,13 +1242,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -1275,27 +1257,27 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1304,27 +1286,27 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1333,27 +1315,27 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1362,27 +1344,27 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1397,7 +1379,7 @@
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>20</v>
@@ -1405,13 +1387,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
       </c>
-      <c r="B11" t="s">
-        <v>146</v>
-      </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1426,7 +1408,7 @@
         <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>20</v>
@@ -1434,13 +1416,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -1449,7 +1431,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -1463,88 +1445,88 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>20</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>151</v>
+        <v>208</v>
       </c>
       <c r="G14" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>216</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>185</v>
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -1559,21 +1541,21 @@
         <v>13</v>
       </c>
       <c r="H16" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -1582,7 +1564,7 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1591,18 +1573,18 @@
         <v>93</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -1611,24 +1593,27 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>121</v>
+      </c>
+      <c r="I18" s="3">
+        <v>28000</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
@@ -1640,27 +1625,27 @@
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I19" s="3">
         <v>28000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
         <v>95</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -1672,27 +1657,27 @@
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I20" s="3">
         <v>28000</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" t="s">
         <v>95</v>
-      </c>
-      <c r="B21" t="s">
-        <v>96</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -1704,27 +1689,27 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I21" s="3">
         <v>28000</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -1736,27 +1721,27 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I22" s="3">
         <v>28000</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -1768,30 +1753,30 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I23" s="3">
         <v>28000</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -1800,30 +1785,27 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>126</v>
-      </c>
-      <c r="I24" s="3">
-        <v>28000</v>
+        <v>83</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -1832,13 +1814,13 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>20</v>
@@ -1846,13 +1828,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -1861,13 +1843,13 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>20</v>
@@ -1875,13 +1857,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -1890,13 +1872,13 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>20</v>
@@ -1904,13 +1886,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -1919,13 +1901,13 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>20</v>
@@ -1933,13 +1915,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -1948,13 +1930,13 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>20</v>
@@ -1962,13 +1944,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
         <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -1977,28 +1959,28 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>184</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" t="s">
         <v>98</v>
       </c>
-      <c r="B31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>99</v>
-      </c>
       <c r="D31" t="s">
         <v>10</v>
       </c>
@@ -2006,27 +1988,27 @@
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>132</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2035,13 +2017,13 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>20</v>
@@ -2049,13 +2031,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -2064,13 +2046,13 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>20</v>
@@ -2078,13 +2060,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -2093,13 +2075,13 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
       </c>
       <c r="H34" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>20</v>
@@ -2107,13 +2089,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -2122,13 +2104,13 @@
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
       </c>
       <c r="H35" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>20</v>
@@ -2136,13 +2118,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -2151,27 +2133,27 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>184</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
       </c>
       <c r="H36" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -2180,27 +2162,27 @@
         <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>193</v>
+        <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>132</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
         <v>100</v>
-      </c>
-      <c r="B38" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" t="s">
-        <v>101</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -2212,10 +2194,13 @@
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H38" t="s">
-        <v>102</v>
+        <v>101</v>
+      </c>
+      <c r="I38" s="3">
+        <v>52</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>20</v>
@@ -2223,13 +2208,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -2238,30 +2223,27 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
       </c>
       <c r="H39" t="s">
-        <v>102</v>
-      </c>
-      <c r="I39" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2270,27 +2252,27 @@
         <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
       </c>
       <c r="H40" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -2299,27 +2281,27 @@
         <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>145</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
       </c>
       <c r="H41" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -2334,21 +2316,21 @@
         <v>13</v>
       </c>
       <c r="H42" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="C43" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -2357,28 +2339,28 @@
         <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H43" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s">
+        <v>189</v>
+      </c>
+      <c r="C44" t="s">
         <v>112</v>
       </c>
-      <c r="B44" t="s">
-        <v>198</v>
-      </c>
-      <c r="C44" t="s">
-        <v>113</v>
-      </c>
       <c r="D44" t="s">
         <v>10</v>
       </c>
@@ -2386,28 +2368,28 @@
         <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" t="s">
         <v>112</v>
       </c>
-      <c r="B45" t="s">
-        <v>198</v>
-      </c>
-      <c r="C45" t="s">
-        <v>113</v>
-      </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
@@ -2415,27 +2397,27 @@
         <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="G45" t="s">
         <v>12</v>
       </c>
       <c r="H45" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -2444,27 +2426,27 @@
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
       </c>
       <c r="H46" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -2473,27 +2455,27 @@
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
       </c>
       <c r="H47" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="C48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2502,27 +2484,27 @@
         <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
       </c>
       <c r="H48" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -2531,28 +2513,28 @@
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="G49" t="s">
         <v>12</v>
       </c>
       <c r="H49" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>169</v>
+      </c>
+      <c r="B50" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" t="s">
         <v>112</v>
       </c>
-      <c r="B50" t="s">
-        <v>177</v>
-      </c>
-      <c r="C50" t="s">
-        <v>113</v>
-      </c>
       <c r="D50" t="s">
         <v>10</v>
       </c>
@@ -2560,28 +2542,28 @@
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G50" t="s">
         <v>12</v>
       </c>
       <c r="H50" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" t="s">
         <v>112</v>
       </c>
-      <c r="B51" t="s">
-        <v>177</v>
-      </c>
-      <c r="C51" t="s">
-        <v>113</v>
-      </c>
       <c r="D51" t="s">
         <v>10</v>
       </c>
@@ -2589,27 +2571,27 @@
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
       </c>
       <c r="H51" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="C52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -2624,21 +2606,21 @@
         <v>12</v>
       </c>
       <c r="H52" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2647,28 +2629,28 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
       </c>
       <c r="H53" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" t="s">
         <v>112</v>
       </c>
-      <c r="B54" t="s">
-        <v>139</v>
-      </c>
-      <c r="C54" t="s">
-        <v>113</v>
-      </c>
       <c r="D54" t="s">
         <v>10</v>
       </c>
@@ -2676,28 +2658,28 @@
         <v>11</v>
       </c>
       <c r="F54" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G54" t="s">
         <v>12</v>
       </c>
       <c r="H54" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" t="s">
+        <v>134</v>
+      </c>
+      <c r="C55" t="s">
         <v>112</v>
       </c>
-      <c r="B55" t="s">
-        <v>139</v>
-      </c>
-      <c r="C55" t="s">
-        <v>113</v>
-      </c>
       <c r="D55" t="s">
         <v>10</v>
       </c>
@@ -2705,59 +2687,59 @@
         <v>11</v>
       </c>
       <c r="F55" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
       </c>
       <c r="H55" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>11</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>138</v>
-      </c>
-      <c r="I56" s="3">
-        <v>49</v>
+        <v>135</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57" t="s">
         <v>114</v>
       </c>
-      <c r="B57" t="s">
-        <v>115</v>
-      </c>
       <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
         <v>116</v>
-      </c>
-      <c r="D57" t="s">
-        <v>117</v>
       </c>
       <c r="E57" t="s">
         <v>11</v>
@@ -2769,7 +2751,7 @@
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="I57" s="3">
         <v>49</v>
@@ -2777,28 +2759,28 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="C58" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="D58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E58" t="s">
         <v>11</v>
       </c>
       <c r="F58" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G58" t="s">
         <v>13</v>
       </c>
       <c r="H58" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="I58" s="3">
         <v>49</v>
@@ -2806,40 +2788,43 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="E59" t="s">
         <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
       </c>
       <c r="H59" t="s">
-        <v>169</v>
+        <v>118</v>
+      </c>
+      <c r="I59" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C60" t="s">
         <v>120</v>
       </c>
-      <c r="B60" t="s">
-        <v>79</v>
-      </c>
-      <c r="C60" t="s">
-        <v>121</v>
-      </c>
       <c r="D60" t="s">
         <v>10</v>
       </c>
@@ -2847,24 +2832,24 @@
         <v>11</v>
       </c>
       <c r="F60" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="G60" t="s">
         <v>13</v>
       </c>
       <c r="H60" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -2873,16 +2858,16 @@
         <v>11</v>
       </c>
       <c r="F61" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
       </c>
       <c r="H61" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -2890,7 +2875,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C62" t="s">
         <v>22</v>
@@ -2908,47 +2893,41 @@
         <v>13</v>
       </c>
       <c r="H62" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="C63" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D63" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
       </c>
       <c r="F63" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s">
-        <v>13</v>
-      </c>
-      <c r="H63" t="s">
-        <v>159</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>160</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="B64" t="s">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="C64" t="s">
         <v>33</v>
@@ -2960,13 +2939,10 @@
         <v>11</v>
       </c>
       <c r="F64" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s">
-        <v>48</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
@@ -2974,7 +2950,7 @@
         <v>54</v>
       </c>
       <c r="B65" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C65" t="s">
         <v>33</v>
@@ -2986,13 +2962,13 @@
         <v>11</v>
       </c>
       <c r="F65" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="G65" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>201</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
@@ -3012,13 +2988,13 @@
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G66" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
@@ -3038,21 +3014,21 @@
         <v>11</v>
       </c>
       <c r="F67" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="G67" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B68" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C68" t="s">
         <v>33</v>
@@ -3064,13 +3040,13 @@
         <v>11</v>
       </c>
       <c r="F68" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
@@ -3078,7 +3054,7 @@
         <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C69" t="s">
         <v>33</v>
@@ -3096,7 +3072,7 @@
         <v>35</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
@@ -3104,7 +3080,7 @@
         <v>36</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C70" t="s">
         <v>33</v>
@@ -3122,7 +3098,7 @@
         <v>35</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
@@ -3130,7 +3106,7 @@
         <v>36</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
         <v>33</v>
@@ -3148,15 +3124,15 @@
         <v>35</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C72" t="s">
         <v>33</v>
@@ -3174,15 +3150,15 @@
         <v>35</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C73" t="s">
         <v>33</v>
@@ -3197,36 +3173,36 @@
         <v>38</v>
       </c>
       <c r="G73" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C74" t="s">
         <v>33</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E74" t="s">
         <v>11</v>
       </c>
       <c r="F74" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G74" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
@@ -3246,27 +3222,27 @@
         <v>11</v>
       </c>
       <c r="F75" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G75" t="s">
         <v>35</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C76" t="s">
         <v>33</v>
       </c>
       <c r="D76" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
@@ -3275,18 +3251,18 @@
         <v>46</v>
       </c>
       <c r="G76" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="C77" t="s">
         <v>33</v>
@@ -3298,21 +3274,21 @@
         <v>11</v>
       </c>
       <c r="F77" t="s">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="G77" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>206</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="C78" t="s">
         <v>33</v>
@@ -3324,21 +3300,21 @@
         <v>11</v>
       </c>
       <c r="F78" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G78" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="B79" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C79" t="s">
         <v>33</v>
@@ -3350,21 +3326,21 @@
         <v>11</v>
       </c>
       <c r="F79" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="G79" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="C80" t="s">
         <v>33</v>
@@ -3382,33 +3358,33 @@
         <v>48</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="B81" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="C81" t="s">
         <v>33</v>
       </c>
       <c r="D81" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E81" t="s">
         <v>11</v>
       </c>
       <c r="F81" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="G81" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
@@ -3428,7 +3404,7 @@
         <v>11</v>
       </c>
       <c r="F82" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G82" t="s">
         <v>58</v>
@@ -3439,10 +3415,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B83" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C83" t="s">
         <v>33</v>
@@ -3454,10 +3430,10 @@
         <v>11</v>
       </c>
       <c r="F83" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>59</v>
@@ -3465,10 +3441,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C84" t="s">
         <v>33</v>
@@ -3480,13 +3456,13 @@
         <v>11</v>
       </c>
       <c r="F84" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
@@ -3506,7 +3482,7 @@
         <v>11</v>
       </c>
       <c r="F85" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="G85" t="s">
         <v>58</v>
@@ -3532,7 +3508,7 @@
         <v>11</v>
       </c>
       <c r="F86" t="s">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="G86" t="s">
         <v>58</v>
@@ -3543,28 +3519,28 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B87" t="s">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="C87" t="s">
         <v>33</v>
       </c>
       <c r="D87" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E87" t="s">
         <v>11</v>
       </c>
       <c r="F87" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G87" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>162</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
@@ -3572,7 +3548,7 @@
         <v>18</v>
       </c>
       <c r="B88" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C88" t="s">
         <v>33</v>
@@ -3584,16 +3560,13 @@
         <v>11</v>
       </c>
       <c r="F88" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="G88" t="s">
         <v>35</v>
       </c>
-      <c r="H88" t="s">
-        <v>164</v>
-      </c>
       <c r="J88" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
@@ -3601,7 +3574,7 @@
         <v>18</v>
       </c>
       <c r="B89" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C89" t="s">
         <v>33</v>
@@ -3613,16 +3586,16 @@
         <v>11</v>
       </c>
       <c r="F89" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G89" t="s">
         <v>35</v>
       </c>
       <c r="H89" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
@@ -3630,7 +3603,7 @@
         <v>18</v>
       </c>
       <c r="B90" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C90" t="s">
         <v>33</v>
@@ -3642,13 +3615,16 @@
         <v>11</v>
       </c>
       <c r="F90" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G90" t="s">
         <v>35</v>
       </c>
+      <c r="H90" t="s">
+        <v>158</v>
+      </c>
       <c r="J90" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
@@ -3656,7 +3632,7 @@
         <v>18</v>
       </c>
       <c r="B91" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C91" t="s">
         <v>33</v>
@@ -3668,16 +3644,13 @@
         <v>11</v>
       </c>
       <c r="F91" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G91" t="s">
         <v>35</v>
       </c>
-      <c r="H91" t="s">
-        <v>164</v>
-      </c>
       <c r="J91" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
@@ -3685,7 +3658,7 @@
         <v>18</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="C92" t="s">
         <v>33</v>
@@ -3697,13 +3670,16 @@
         <v>11</v>
       </c>
       <c r="F92" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="G92" t="s">
-        <v>53</v>
+        <v>35</v>
+      </c>
+      <c r="H92" t="s">
+        <v>158</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
@@ -3723,7 +3699,7 @@
         <v>11</v>
       </c>
       <c r="F93" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G93" t="s">
         <v>53</v>
@@ -3734,10 +3710,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
         <v>33</v>
@@ -3749,13 +3725,13 @@
         <v>11</v>
       </c>
       <c r="F94" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G94" t="s">
         <v>53</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>208</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
@@ -3775,21 +3751,21 @@
         <v>11</v>
       </c>
       <c r="F95" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B96" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C96" t="s">
         <v>33</v>
@@ -3801,13 +3777,13 @@
         <v>11</v>
       </c>
       <c r="F96" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G96" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>52</v>
+        <v>199</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
@@ -3815,7 +3791,7 @@
         <v>61</v>
       </c>
       <c r="B97" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C97" t="s">
         <v>33</v>
@@ -3827,7 +3803,7 @@
         <v>11</v>
       </c>
       <c r="F97" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="G97" t="s">
         <v>35</v>
@@ -3841,7 +3817,7 @@
         <v>61</v>
       </c>
       <c r="B98" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C98" t="s">
         <v>33</v>
@@ -3867,7 +3843,7 @@
         <v>61</v>
       </c>
       <c r="B99" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C99" t="s">
         <v>33</v>
@@ -3879,7 +3855,7 @@
         <v>11</v>
       </c>
       <c r="F99" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G99" t="s">
         <v>35</v>
@@ -3890,10 +3866,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="B100" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C100" t="s">
         <v>33</v>
@@ -3905,13 +3881,13 @@
         <v>11</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G100" t="s">
         <v>35</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
@@ -3919,7 +3895,7 @@
         <v>31</v>
       </c>
       <c r="B101" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C101" t="s">
         <v>33</v>
@@ -3931,16 +3907,13 @@
         <v>11</v>
       </c>
       <c r="F101" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G101" t="s">
-        <v>48</v>
-      </c>
-      <c r="I101" s="3">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>202</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
@@ -3960,7 +3933,7 @@
         <v>11</v>
       </c>
       <c r="F102" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G102" t="s">
         <v>48</v>
@@ -3969,15 +3942,15 @@
         <v>14</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="B103" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="C103" t="s">
         <v>33</v>
@@ -3989,39 +3962,42 @@
         <v>11</v>
       </c>
       <c r="F103" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G103" t="s">
-        <v>35</v>
+        <v>48</v>
+      </c>
+      <c r="I103" s="3">
+        <v>14</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B104" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C104" t="s">
         <v>33</v>
       </c>
       <c r="D104" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E104" t="s">
         <v>11</v>
       </c>
       <c r="F104" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="G104" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
@@ -4044,10 +4020,10 @@
         <v>51</v>
       </c>
       <c r="G105" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>41</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
@@ -4055,7 +4031,7 @@
         <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C106" t="s">
         <v>33</v>
@@ -4073,15 +4049,15 @@
         <v>48</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B107" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C107" t="s">
         <v>33</v>
@@ -4093,13 +4069,13 @@
         <v>11</v>
       </c>
       <c r="F107" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="G107" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
@@ -4107,7 +4083,7 @@
         <v>69</v>
       </c>
       <c r="B108" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C108" t="s">
         <v>33</v>
@@ -4119,21 +4095,21 @@
         <v>11</v>
       </c>
       <c r="F108" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G108" t="s">
         <v>71</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B109" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C109" t="s">
         <v>33</v>
@@ -4145,13 +4121,13 @@
         <v>11</v>
       </c>
       <c r="F109" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="G109" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
@@ -4171,39 +4147,39 @@
         <v>11</v>
       </c>
       <c r="F110" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="G110" t="s">
         <v>48</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B111" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C111" t="s">
         <v>33</v>
       </c>
       <c r="D111" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E111" t="s">
         <v>11</v>
       </c>
       <c r="F111" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G111" t="s">
         <v>48</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
@@ -4211,7 +4187,7 @@
         <v>73</v>
       </c>
       <c r="B112" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C112" t="s">
         <v>33</v>
@@ -4223,13 +4199,13 @@
         <v>11</v>
       </c>
       <c r="F112" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="G112" t="s">
         <v>48</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
@@ -4249,69 +4225,46 @@
         <v>11</v>
       </c>
       <c r="F113" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G113" t="s">
         <v>48</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="B114" t="s">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="C114" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="D114" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E114" t="s">
         <v>11</v>
       </c>
       <c r="F114" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="G114" t="s">
-        <v>48</v>
+        <v>12</v>
+      </c>
+      <c r="H114" t="s">
+        <v>168</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>181</v>
-      </c>
-      <c r="B115" t="s">
-        <v>181</v>
-      </c>
-      <c r="C115" t="s">
-        <v>182</v>
-      </c>
-      <c r="D115" t="s">
-        <v>183</v>
-      </c>
-      <c r="E115" t="s">
-        <v>11</v>
-      </c>
-      <c r="F115" t="s">
-        <v>184</v>
-      </c>
-      <c r="G115" t="s">
-        <v>185</v>
-      </c>
-      <c r="I115" s="3">
-        <v>14</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J115" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
+  <autoFilter ref="A1:J114" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tr.alienigenaV5-main\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD2F5F5D-2821-4C84-AF0B-6682B0C718BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{613C5BD6-1F4A-4095-B105-7B47B2D3C525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="551" xr2:uid="{9E8F4E85-D2FF-4383-A72B-5CAFDCCC5644}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$141</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="271">
   <si>
     <t>Origem</t>
   </si>
@@ -134,550 +134,727 @@
     <t>Corumbá - MS</t>
   </si>
   <si>
+    <t>Sobral - CE</t>
+  </si>
+  <si>
+    <t>Laranjeiras - SE</t>
+  </si>
+  <si>
+    <t>CIMENTO</t>
+  </si>
+  <si>
+    <t>Pallet</t>
+  </si>
+  <si>
+    <t>Grade Baixa</t>
+  </si>
+  <si>
+    <t>Campinas - SP</t>
+  </si>
+  <si>
+    <t>Bragança Paulista - SP</t>
+  </si>
+  <si>
+    <t>Toco, Truck, Bitruck</t>
+  </si>
+  <si>
+    <t>Serra Negra - SP</t>
+  </si>
+  <si>
+    <t>Jundiaí - SP</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Diadema - SP</t>
+  </si>
+  <si>
+    <t>Guarulhos - SP</t>
+  </si>
+  <si>
+    <t>Saco</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>Truck, Carreta</t>
+  </si>
+  <si>
+    <t>Grade Baixa, Prancha</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Truck, Bitruck</t>
+  </si>
+  <si>
+    <t>Graneleiro, Grade Baixa, Prancha</t>
+  </si>
+  <si>
+    <t>Teresina - PI</t>
+  </si>
+  <si>
+    <t>Timon - MA</t>
+  </si>
+  <si>
+    <t>Truck, Carreta LS</t>
+  </si>
+  <si>
+    <t>Petrolina - PE</t>
+  </si>
+  <si>
+    <t>Graneleiro, Grade Baixa</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM / PEDÁGIO INCLUSO NO FRETE</t>
+  </si>
+  <si>
+    <t>Nobres - MT</t>
+  </si>
+  <si>
+    <t>Brasília - DF</t>
+  </si>
+  <si>
+    <t>RODOTREM (48 Ton)</t>
+  </si>
+  <si>
+    <t>Luís Eduardo Magalhães - BA</t>
+  </si>
+  <si>
+    <t>Feira de Santana - BA</t>
+  </si>
+  <si>
+    <t>Itabuna - BA</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Salto de Pirapora - SP</t>
+  </si>
+  <si>
+    <t>Itapeva - SP</t>
+  </si>
+  <si>
+    <t>calcário</t>
+  </si>
+  <si>
+    <t>Baraúna - RN</t>
+  </si>
+  <si>
+    <t>Nossa Senhora do Socorro - SE</t>
+  </si>
+  <si>
+    <t>Clínquer</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM</t>
+  </si>
+  <si>
+    <t>8.902,06</t>
+  </si>
+  <si>
+    <t>Trindade - PE</t>
+  </si>
+  <si>
+    <t>Gpisita</t>
+  </si>
+  <si>
+    <t>Ouricuri - PE</t>
+  </si>
+  <si>
+    <t>gesso</t>
+  </si>
+  <si>
+    <t>142,00</t>
+  </si>
+  <si>
+    <t>Pitimbu - PB</t>
+  </si>
+  <si>
+    <t>PAGBEM/REPOM</t>
+  </si>
+  <si>
+    <t>Unaí - MG</t>
+  </si>
+  <si>
+    <t>SORGO</t>
+  </si>
+  <si>
+    <t>Xambioá - TO</t>
+  </si>
+  <si>
+    <t>Gesso</t>
+  </si>
+  <si>
+    <t>Outro</t>
+  </si>
+  <si>
+    <t>Açailândia - MA</t>
+  </si>
+  <si>
+    <t>Barro Alto - GO</t>
+  </si>
+  <si>
+    <t>BAUXITA</t>
+  </si>
+  <si>
+    <t>7.002,79</t>
+  </si>
+  <si>
+    <t>6.136,82</t>
+  </si>
+  <si>
+    <t>5.575,13</t>
+  </si>
+  <si>
+    <t>5.095,98</t>
+  </si>
+  <si>
+    <t>Carreta toco 5 eixos</t>
+  </si>
+  <si>
+    <t>6.520,95</t>
+  </si>
+  <si>
+    <t>5.716,37</t>
+  </si>
+  <si>
+    <t>5.188,21</t>
+  </si>
+  <si>
+    <t>4.745,60</t>
+  </si>
+  <si>
+    <t>calcario/ clínquer</t>
+  </si>
+  <si>
+    <t>80,00</t>
+  </si>
+  <si>
+    <t>Araguari - MG</t>
+  </si>
+  <si>
+    <t>Bonfinópolis de Minas - MG</t>
+  </si>
+  <si>
+    <t>Montes Claros - MG</t>
+  </si>
+  <si>
+    <t>Cajati - SP</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
+  </si>
+  <si>
+    <t>Toco, Truck</t>
+  </si>
+  <si>
+    <t>Rio Branco do Sul - PR</t>
+  </si>
+  <si>
+    <t>Carreta LS, Vanderléia</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>Vidal Ramos - SC</t>
+  </si>
+  <si>
+    <t>Santa Filomena - PI</t>
+  </si>
+  <si>
+    <t>175,00</t>
+  </si>
+  <si>
+    <t>Edealina - GO</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Vanderléia, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Caruaru - PE</t>
+  </si>
+  <si>
+    <t>Vanderléia</t>
+  </si>
+  <si>
+    <t>Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Carreta</t>
+  </si>
+  <si>
+    <t>Milho</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>DESTINOS DISPONIVEIS: No Extremo Sul do Estado do PI - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI- VEICULOS TOCO APENAS 10 TON</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS: regiões Metropolitana , PB e RN</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
+  </si>
+  <si>
+    <t>Ourinhos - SP</t>
+  </si>
+  <si>
+    <t>Regente Feijó - SP</t>
+  </si>
+  <si>
+    <t>PAGBEM</t>
+  </si>
+  <si>
+    <t>162,00</t>
+  </si>
+  <si>
+    <t>170,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO REPOM</t>
+  </si>
+  <si>
+    <t>Juazeiro do Norte - CE</t>
+  </si>
+  <si>
+    <t>Crateús - CE</t>
+  </si>
+  <si>
+    <t>Cantagalo - RJ</t>
+  </si>
+  <si>
+    <t>Volta Redonda - RJ</t>
+  </si>
+  <si>
+    <t>São Gonçalo - RJ</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro - RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: Cocos/BA, Serra Dourada/BA, São Félix do Coribe/BA, Tabocas do Brejo Velho/BA, Correntina/BA, Mansidão/BA, Formosa do Rio Preto/BA, Santa Rita de Cassia/BA, Barreiras/BA e Morpará/BA</t>
+  </si>
+  <si>
+    <t>Sorgo</t>
+  </si>
+  <si>
+    <t>160,00</t>
+  </si>
+  <si>
+    <t>Cabeceiras - GO</t>
+  </si>
+  <si>
+    <t>135,00</t>
+  </si>
+  <si>
+    <t>Pará de Minas - MG</t>
+  </si>
+  <si>
+    <t>Truck, Bitruck, Carreta</t>
+  </si>
+  <si>
+    <t>Vitória da Conquista - BA</t>
+  </si>
+  <si>
+    <t>Duque de Caxias - RJ</t>
+  </si>
+  <si>
+    <t>coque</t>
+  </si>
+  <si>
+    <t>São João da Barra - RJ</t>
+  </si>
+  <si>
+    <t>8.700,00</t>
+  </si>
+  <si>
+    <t>10.400,00</t>
+  </si>
+  <si>
+    <t>155,00</t>
+  </si>
+  <si>
+    <t>Jucurutu - RN</t>
+  </si>
+  <si>
+    <t>5.520,00</t>
+  </si>
+  <si>
+    <t>13.630,00</t>
+  </si>
+  <si>
+    <t>Embu das Artes - SP</t>
+  </si>
+  <si>
+    <t>Buri - SP</t>
+  </si>
+  <si>
+    <t>Minério de Ferro</t>
+  </si>
+  <si>
+    <t>3.840,00</t>
+  </si>
+  <si>
+    <t>4.400,00</t>
+  </si>
+  <si>
+    <t>Carreta, Bitrem 7 eixos, Rodotrem</t>
+  </si>
+  <si>
+    <t>Barra do Corda - MA</t>
+  </si>
+  <si>
+    <t>Calcário</t>
+  </si>
+  <si>
+    <t>12.678,00</t>
+  </si>
+  <si>
+    <t>14.562,00</t>
+  </si>
+  <si>
+    <t>Graneleiro, Sider</t>
+  </si>
+  <si>
+    <t>Imbituba - SC</t>
+  </si>
+  <si>
+    <t>172,00</t>
+  </si>
+  <si>
+    <t>CLINQUER</t>
+  </si>
+  <si>
+    <t>140,00</t>
+  </si>
+  <si>
+    <t>Brotas - SP</t>
+  </si>
+  <si>
+    <t>95,00</t>
+  </si>
+  <si>
+    <t>48,00</t>
+  </si>
+  <si>
+    <t>Grajaú - MA</t>
+  </si>
+  <si>
+    <t>Belém - PA</t>
+  </si>
+  <si>
+    <t>210,00</t>
+  </si>
+  <si>
+    <t>Pacatuba - SE</t>
+  </si>
+  <si>
+    <t>Machadinho DOeste - RO</t>
+  </si>
+  <si>
+    <t>270,00</t>
+  </si>
+  <si>
+    <t>repom</t>
+  </si>
+  <si>
+    <t>Goiatuba - GO</t>
+  </si>
+  <si>
+    <t>130,00</t>
+  </si>
+  <si>
+    <t>Juína - MT</t>
+  </si>
+  <si>
+    <t>165,00</t>
+  </si>
+  <si>
+    <t>230,00</t>
+  </si>
+  <si>
+    <t>Cubatão - SP</t>
+  </si>
+  <si>
+    <t>São José dos Campos - SP</t>
+  </si>
+  <si>
+    <t>Barueri - SP</t>
+  </si>
+  <si>
+    <t>Imperatriz - MA</t>
+  </si>
+  <si>
+    <t>Pinheiro Machado - RS</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO PALLETS, CINTA, LONA E EPI. POSSIVEIS DESTINOS DISPONIVEIS: Arroio Grande/RS, Bagé/RS, Canguçu/RS, Cristal/RS, Dom Pedrito/RS, Jaguarão/RS, Pelotas/RS, Rio Grande/RS, Santana da Boa Vista/RS, SantAna do Livramento/RS, São Gabriel/RS, São José do Norte/RS e São Lourenço do Sul/RS</t>
+  </si>
+  <si>
+    <t>Porto Velho - RO</t>
+  </si>
+  <si>
+    <t>320,00</t>
+  </si>
+  <si>
+    <t>Aripuanã - MT</t>
+  </si>
+  <si>
+    <t>Três Marias - MG</t>
+  </si>
+  <si>
+    <t>MINERIO</t>
+  </si>
+  <si>
+    <t>568,00</t>
+  </si>
+  <si>
+    <t>CAÇAMBA LAVADA, SIRENE DE RÉ, LONA FACIL, TECNIL e INCINOMETRO</t>
+  </si>
+  <si>
+    <t>Goianira - GO</t>
+  </si>
+  <si>
+    <t>295,00</t>
+  </si>
+  <si>
+    <t>4.200,00</t>
+  </si>
+  <si>
+    <t>5.250,00</t>
+  </si>
+  <si>
+    <t>Guiratinga - MT</t>
+  </si>
+  <si>
+    <t>Rondonópolis - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS</t>
+  </si>
+  <si>
+    <t>Itaituba - PA</t>
+  </si>
+  <si>
+    <t>Querência - MT</t>
+  </si>
+  <si>
+    <t>Dom Aquino - MT</t>
+  </si>
+  <si>
+    <t>Rio Verde - GO</t>
+  </si>
+  <si>
+    <t>Confresa - MT</t>
+  </si>
+  <si>
+    <t>Barcarena - PA</t>
+  </si>
+  <si>
+    <t>São José do Xingu - MT</t>
+  </si>
+  <si>
+    <t>Balsas - MA</t>
+  </si>
+  <si>
+    <t>ARM AGRICOLA</t>
+  </si>
+  <si>
+    <t>Colinas do Tocantins - TO</t>
+  </si>
+  <si>
+    <t>Sorriso - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA CARAMURU - (ARM CARAMURU)</t>
+  </si>
+  <si>
+    <t>DESCARGA BERTUOL - (ARM COOAVIL)</t>
+  </si>
+  <si>
+    <t>Nova Ubiratã - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (ARM VEDANA)</t>
+  </si>
+  <si>
+    <t>Sinop - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA MASTER - (ARM INPASA)</t>
+  </si>
+  <si>
+    <t>Tabaporã - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA BERTOLINI - (ARM SAO THIAGO)</t>
+  </si>
+  <si>
+    <t>Feliz Natal - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA BERTOLINI - (ARM NAVARRO)</t>
+  </si>
+  <si>
+    <t>Cláudia - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (ARMZ COFCO)</t>
+  </si>
+  <si>
+    <t>União do Sul - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (FAZ RIO VERDE)</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (ARM TIGRE)</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (REAL AGRO)</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (FAZENDA FIORESE)</t>
+  </si>
+  <si>
+    <t>Guarantã do Norte - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA UNITAPAJOS - (ARMAZEM PLENITUDE)</t>
+  </si>
+  <si>
+    <t>Alta Floresta - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA UNITAPAJOS - (VERDE AGRICOLA)</t>
+  </si>
+  <si>
+    <t>DESCARGA UNITAPAJOS - (FAZENDA VENEZZI</t>
+  </si>
+  <si>
+    <t>Nova Santa Helena - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA UNITAPAJOS - (GO AGRO)</t>
+  </si>
+  <si>
+    <t>Novo Mundo - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA CARGILL - (FAZENDA NOVA GUARITA)</t>
+  </si>
+  <si>
+    <t>Nova Guarita - MT</t>
+  </si>
+  <si>
+    <t>Peixoto de Azevedo - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA BERTOLINE - (FAZENDA VITORIA)</t>
+  </si>
+  <si>
+    <t>Matupá - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA BERTOLINE - (BUNGUE)</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (FAZENDA CHAPADAO)</t>
+  </si>
+  <si>
+    <t>Nova Canaã do Norte - MT</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (FAZENDA EXPOENTE)</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (FAZENDA ZILLI)</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (COFCO NOVO MUNDO)</t>
+  </si>
+  <si>
+    <t>DESCARGA HIDROVIAS - (FAZENDA VITORIA)</t>
+  </si>
+  <si>
+    <t>Diamantino - MT</t>
+  </si>
+  <si>
+    <t>70,00</t>
+  </si>
+  <si>
     <t>São Gonçalo do Amarante - CE</t>
   </si>
   <si>
-    <t>Sobral - CE</t>
-  </si>
-  <si>
-    <t>Laranjeiras - SE</t>
-  </si>
-  <si>
-    <t>CIMENTO</t>
-  </si>
-  <si>
-    <t>Pallet</t>
-  </si>
-  <si>
-    <t>Grade Baixa</t>
-  </si>
-  <si>
-    <t>Campinas - SP</t>
-  </si>
-  <si>
-    <t>Bragança Paulista - SP</t>
-  </si>
-  <si>
-    <t>Toco, Truck, Bitruck</t>
-  </si>
-  <si>
-    <t>Serra Negra - SP</t>
-  </si>
-  <si>
-    <t>Jundiaí - SP</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Diadema - SP</t>
-  </si>
-  <si>
-    <t>Guarulhos - SP</t>
-  </si>
-  <si>
-    <t>Saco</t>
-  </si>
-  <si>
-    <t>Carreta LS, Bitrem 7 eixos</t>
-  </si>
-  <si>
-    <t>Truck, Carreta</t>
-  </si>
-  <si>
-    <t>Caxias do Sul - RS</t>
-  </si>
-  <si>
-    <t>Grade Baixa, Prancha</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI - VEICULOS: CARRETA TOCO (27 ou 28t) e TRUCK - PARA AGREGAR</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Truck, Bitruck</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM</t>
-  </si>
-  <si>
-    <t>Graneleiro, Grade Baixa, Prancha</t>
-  </si>
-  <si>
-    <t>Teresina - PI</t>
-  </si>
-  <si>
-    <t>Timon - MA</t>
-  </si>
-  <si>
-    <t>Truck, Carreta LS</t>
-  </si>
-  <si>
-    <t>Petrolina - PE</t>
-  </si>
-  <si>
-    <t>Graneleiro, Grade Baixa</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM / PEDÁGIO INCLUSO NO FRETE</t>
-  </si>
-  <si>
-    <t>Nobres - MT</t>
-  </si>
-  <si>
-    <t>Brasília - DF</t>
-  </si>
-  <si>
-    <t>Pirenópolis - GO</t>
-  </si>
-  <si>
-    <t>Anápolis - GO</t>
-  </si>
-  <si>
-    <t>RODOTREM (48 Ton)</t>
-  </si>
-  <si>
-    <t>Luís Eduardo Magalhães - BA</t>
-  </si>
-  <si>
-    <t>Camaçari - BA</t>
-  </si>
-  <si>
-    <t>Conde - BA</t>
-  </si>
-  <si>
-    <t>Graneleiro, Sider</t>
-  </si>
-  <si>
-    <t>Simões Filho - BA</t>
-  </si>
-  <si>
-    <t>Salvador - BA</t>
-  </si>
-  <si>
-    <t>Sider, Grade Baixa, Prancha</t>
-  </si>
-  <si>
-    <t>Feira de Santana - BA</t>
-  </si>
-  <si>
-    <t>Itabuna - BA</t>
-  </si>
-  <si>
-    <t>50,00</t>
-  </si>
-  <si>
-    <t>Toco</t>
-  </si>
-  <si>
-    <t>Goiânia - GO</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>Salto de Pirapora - SP</t>
-  </si>
-  <si>
-    <t>Itapeva - SP</t>
-  </si>
-  <si>
-    <t>Brotas - SP</t>
-  </si>
-  <si>
-    <t>calcário</t>
-  </si>
-  <si>
-    <t>90,00</t>
-  </si>
-  <si>
-    <t>140,00</t>
-  </si>
-  <si>
-    <t>Baraúna - RN</t>
-  </si>
-  <si>
-    <t>Nossa Senhora do Socorro - SE</t>
-  </si>
-  <si>
-    <t>Clínquer</t>
-  </si>
-  <si>
-    <t>10.162,50</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO PAGBEM</t>
-  </si>
-  <si>
-    <t>Currais Novos - RN</t>
-  </si>
-  <si>
-    <t>Pacatuba - SE</t>
-  </si>
-  <si>
-    <t>Minério</t>
-  </si>
-  <si>
-    <t>9.120,00</t>
-  </si>
-  <si>
-    <t>8.902,06</t>
-  </si>
-  <si>
-    <t>Itaguaí - RJ</t>
-  </si>
-  <si>
-    <t>Votorantim - SP</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO REPOM /</t>
-  </si>
-  <si>
-    <t>Trindade - PE</t>
-  </si>
-  <si>
-    <t>Gpisita</t>
-  </si>
-  <si>
-    <t>Ouricuri - PE</t>
-  </si>
-  <si>
-    <t>gesso</t>
-  </si>
-  <si>
-    <t>142,00</t>
-  </si>
-  <si>
-    <t>Pitimbu - PB</t>
-  </si>
-  <si>
-    <t>PAGBEM/REPOM</t>
-  </si>
-  <si>
-    <t>Aripuanã - MT</t>
-  </si>
-  <si>
-    <t>Juiz de Fora - MG</t>
-  </si>
-  <si>
-    <t>MINERIO</t>
-  </si>
-  <si>
-    <t>repom</t>
-  </si>
-  <si>
-    <t>Porto Velho - RO</t>
-  </si>
-  <si>
-    <t>CLINQUER</t>
-  </si>
-  <si>
-    <t>320,00</t>
-  </si>
-  <si>
-    <t>Unaí - MG</t>
-  </si>
-  <si>
-    <t>SORGO</t>
-  </si>
-  <si>
-    <t>Grajaú - MA</t>
-  </si>
-  <si>
-    <t>Xambioá - TO</t>
-  </si>
-  <si>
-    <t>Gesso</t>
-  </si>
-  <si>
-    <t>Outro</t>
-  </si>
-  <si>
-    <t>Açailândia - MA</t>
-  </si>
-  <si>
-    <t>168,00</t>
-  </si>
-  <si>
-    <t>Barro Alto - GO</t>
-  </si>
-  <si>
-    <t>BAUXITA</t>
-  </si>
-  <si>
-    <t>130,00</t>
-  </si>
-  <si>
-    <t>106,00</t>
-  </si>
-  <si>
-    <t>7.002,79</t>
-  </si>
-  <si>
-    <t>6.136,82</t>
-  </si>
-  <si>
-    <t>5.575,13</t>
-  </si>
-  <si>
-    <t>5.095,98</t>
-  </si>
-  <si>
-    <t>Carreta toco 5 eixos</t>
-  </si>
-  <si>
-    <t>6.520,95</t>
-  </si>
-  <si>
-    <t>5.716,37</t>
-  </si>
-  <si>
-    <t>5.188,21</t>
-  </si>
-  <si>
-    <t>4.745,60</t>
-  </si>
-  <si>
-    <t>calcario/ clínquer</t>
-  </si>
-  <si>
-    <t>80,00</t>
-  </si>
-  <si>
-    <t>Araguari - MG</t>
-  </si>
-  <si>
-    <t>135,00</t>
-  </si>
-  <si>
-    <t>Bonfinópolis de Minas - MG</t>
-  </si>
-  <si>
-    <t>Montes Claros - MG</t>
-  </si>
-  <si>
-    <t>157,00</t>
-  </si>
-  <si>
-    <t>Cajati - SP</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
-  </si>
-  <si>
-    <t>Anhembi - SP</t>
-  </si>
-  <si>
-    <t>97,00</t>
-  </si>
-  <si>
-    <t>Primavera - PA</t>
-  </si>
-  <si>
-    <t>Toco, Truck</t>
-  </si>
-  <si>
-    <t>Rio Branco do Sul - PR</t>
-  </si>
-  <si>
-    <t>Carreta LS, Vanderléia</t>
-  </si>
-  <si>
-    <t>72,00</t>
-  </si>
-  <si>
-    <t>100,00</t>
-  </si>
-  <si>
-    <t>Vidal Ramos - SC</t>
-  </si>
-  <si>
-    <t>650,00</t>
-  </si>
-  <si>
-    <t>Santa Filomena - PI</t>
-  </si>
-  <si>
-    <t>175,00</t>
-  </si>
-  <si>
-    <t>210,00</t>
+    <t>70,71</t>
   </si>
   <si>
     <t>só aceita rodocaçambas com lona fácil. Caso não tenham, o veículo não passa na vistoria dos guardas</t>
   </si>
   <si>
-    <t>Alfenas - MG</t>
-  </si>
-  <si>
-    <t>PARA MOTORISTAS CATIVOS - NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Inocência - MS</t>
-  </si>
-  <si>
-    <t>7.500,00</t>
-  </si>
-  <si>
-    <t>Costa Rica - MS</t>
-  </si>
-  <si>
-    <t>Três Lagoas - MS</t>
-  </si>
-  <si>
-    <t>Paranaíba - MS</t>
-  </si>
-  <si>
-    <t>Edealina - GO</t>
-  </si>
-  <si>
-    <t>4.670,00</t>
-  </si>
-  <si>
-    <t>Aldeias Altas - MA</t>
-  </si>
-  <si>
-    <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>Itápolis - SP</t>
-  </si>
-  <si>
-    <t>Vanderléia, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>230,00</t>
-  </si>
-  <si>
-    <t>Cabeceira Grande - MG</t>
-  </si>
-  <si>
-    <t>Rio Pomba - MG</t>
-  </si>
-  <si>
-    <t>235,00</t>
-  </si>
-  <si>
-    <t>70,71</t>
-  </si>
-  <si>
-    <t>Caruaru - PE</t>
-  </si>
-  <si>
-    <t>Joinville - SC</t>
-  </si>
-  <si>
-    <t>Tubos e Conexões</t>
-  </si>
-  <si>
-    <t>Sider, Baú, Grade Baixa</t>
-  </si>
-  <si>
-    <t>Vanderléia</t>
-  </si>
-  <si>
-    <t>155,00</t>
-  </si>
-  <si>
-    <t>Poço Fundo - MG</t>
-  </si>
-  <si>
-    <t>Big Bag</t>
-  </si>
-  <si>
-    <t>Graneleiro, Sider, Grade Baixa</t>
-  </si>
-  <si>
-    <t>195,00</t>
-  </si>
-  <si>
-    <t>Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>Carreta</t>
-  </si>
-  <si>
-    <t>Primavera do Leste - MT</t>
-  </si>
-  <si>
-    <t>São João da Barra - RJ</t>
-  </si>
-  <si>
-    <t>Milho</t>
-  </si>
-  <si>
-    <t>510,00</t>
-  </si>
-  <si>
-    <t>Santos - SP</t>
-  </si>
-  <si>
-    <t>180,00</t>
-  </si>
-  <si>
-    <t>Brasilândia de Minas - MG</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>DESTINOS DISPONIVEIS: No Extremo Sul do Estado do PI - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI- VEICULOS TOCO APENAS 10 TON</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
-  </si>
-  <si>
-    <t>PARA MOTORISTAS CATIVOS NA REGIÃO - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS: regiões Metropolitana , PB e RN</t>
-  </si>
-  <si>
-    <t>DESTINO INTRA MUNICIPAL / PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: Cocos/BA, Serra Dourada/BA, São Félix do Coribe/BA, Tabocas do Brejo Velho/BA, Correntina/BA, Mansidão/BA, Formosa do Rio Preto/BA, Santa Rita de Cassia/BA, Barreiras/BA e Morpará/BA</t>
-  </si>
-  <si>
-    <t>APENAS MOTORISTAS CATIVOS - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: Região do Litoral Norte de Camaçari, Catu/Ba Pojuca/Ba, Maragojipe/BA, Candeias/BA, São Francisco/BA, São Félix/BA, Cachoeira/BA - Não trabalhamos com motoristas passantes, prioridade em atuação local com disponibilidade para operar nas regiões mencionadas acima</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / Tem cargas todos os dias e não agregamos passantes.</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: Simões Filho/BA, Lauro de Freitas/BA, Salvador/BA. - Não trabalhamos com motoristas passantes, prioridade em atuação local com disponibilidade para operar nas regiões mencionadas acima</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Veiculos Aceitos: TRUCK E CARRETA TOCO (28 TON)</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Região de Gargalo, Vitória da Conquista e Ipiau</t>
-  </si>
-  <si>
-    <t>Diversos</t>
-  </si>
-  <si>
-    <t>Truck, Carreta, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>Ponte Nova - MG</t>
-  </si>
-  <si>
-    <t>Guarapuava - PR</t>
-  </si>
-  <si>
-    <t>Ourinhos - SP</t>
+    <t>Coque</t>
+  </si>
+  <si>
+    <t>Carreta LS, Rodotrem</t>
+  </si>
+  <si>
+    <t>190,00</t>
+  </si>
+  <si>
+    <t>Campo Grande - MS</t>
+  </si>
+  <si>
+    <t>pneu picado</t>
+  </si>
+  <si>
+    <t>305,00</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Arame/MA, Buriticupu/MA, Carolina/MA, Cidelândia/MA, Estreito/MA, Formosa da Serra/MA, Grajaú/MA, Imperatriz/MA, Itinga do Maranhão /MA, Porto Franco/MA, Riachão/MA, São Pedro da Água Branca /MA, São Pedro dos Crentes/MA, Vila Nova dos Martírios/MA</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI. POSSIVEIS DESTINOS DISPONIVEIS em 62 Cidades no Estado do CE e nos demais estados destinos para Conceição/PB, Salgueiro/PE, São José do Belmonte/PE, Santa Inês/PB, Cajazeiras/PB, Diamante/PB, Araripina/PE, Serra Grande/PB, Nazarezinho/PB, Itaporanga/PB, Sousa/PB, Uiraúna/PB, Fronteiras/PI, Piancó/PB, Areia Branca/RN, Catolé do Rocha/PB, Patos/PB, São Bento/PB e Mossoró/RN</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI. - POSSIVEIS DESTINOS DISPONIVEIS - Mombaça/CE, Poranga/CE, Pedra Branca/CE, Tauá/CE, Nova Russas/CE, Independência/CE e Tamboril/CE</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possiveis Destinos Disponiveis: Araruama/RJ, Campos dos Goytacazes/RJ, Itaperuna/RJ, Saquarema//RJ, Serra/ES</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Paraty/RJ, Resende/RJ e Volta Redonda/RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Armação dos Búzios/RJ, Arraial do Cabo/RJ, Cabo Frio/RJ, Campos dos Goytacazes/RJ, Guapimirim/RJ, Itaboraí/RJ, Magé/RJ, Maricá/RJ, Niterói/RJ e São Gonçalo/RJ</t>
+  </si>
+  <si>
+    <t>CIMENTO ENSACADO</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD SANTA CRUZ - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Duque de Caxias/RJ, Nova Iguaçu/RJ, Paraty/RJ, Petrópolis/RJ, Queimados/RJ e Rio de Janeiro/RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD PARADA DE LUCAS - Possiveis Destinos Disponiveis Duque de Caxias/RJ, Mangaratiba/RJ, Mesquita/RJ, Nova Iguaçu/RJ, Petrópolis/RJ e Rio de Janeiro/RJ</t>
   </si>
 </sst>
 </file>
@@ -1077,12 +1254,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}">
-  <dimension ref="A1:J114"/>
-  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J141"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34.88671875" bestFit="1" customWidth="1"/>
@@ -1126,13 +1303,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1147,21 +1324,21 @@
         <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1176,21 +1353,18 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>253</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1199,56 +1373,50 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>177</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>178</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>88</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="G5" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>182</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>253</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -1257,27 +1425,27 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>88</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1286,27 +1454,27 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>146</v>
+        <v>257</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>258</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>259</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>260</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1315,27 +1483,27 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>261</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>147</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1344,27 +1512,27 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1373,27 +1541,27 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1402,13 +1570,13 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>20</v>
@@ -1416,13 +1584,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -1431,13 +1599,13 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>20</v>
@@ -1445,59 +1613,71 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>207</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="G13" t="s">
-        <v>176</v>
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>176</v>
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -1506,27 +1686,27 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -1535,27 +1715,27 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -1564,27 +1744,27 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -1593,30 +1773,27 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" s="3">
-        <v>28000</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -1625,30 +1802,27 @@
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>121</v>
-      </c>
-      <c r="I19" s="3">
-        <v>28000</v>
+        <v>182</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -1657,30 +1831,27 @@
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>122</v>
-      </c>
-      <c r="I20" s="3">
-        <v>28000</v>
+        <v>70</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -1689,30 +1860,27 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>121</v>
-      </c>
-      <c r="I21" s="3">
-        <v>28000</v>
+        <v>182</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -1721,30 +1889,27 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>122</v>
-      </c>
-      <c r="I22" s="3">
-        <v>28000</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -1753,30 +1918,27 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="3">
-        <v>28000</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -1785,27 +1947,27 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -1814,27 +1976,27 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -1843,27 +2005,27 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -1872,27 +2034,27 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -1901,27 +2063,27 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -1930,27 +2092,27 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -1959,27 +2121,27 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>184</v>
+        <v>19</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30" t="s">
+        <v>148</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -1988,13 +2150,13 @@
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>20</v>
@@ -2002,13 +2164,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2017,13 +2179,13 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>183</v>
+        <v>24</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>20</v>
@@ -2031,13 +2193,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -2046,27 +2208,27 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
       </c>
       <c r="H33" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -2075,13 +2237,13 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>177</v>
+        <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H34" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>20</v>
@@ -2089,13 +2251,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -2104,13 +2266,16 @@
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
       </c>
       <c r="H35" t="s">
-        <v>130</v>
+        <v>127</v>
+      </c>
+      <c r="I35" s="3">
+        <v>52</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>20</v>
@@ -2118,13 +2283,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -2133,27 +2298,27 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
+        <v>19</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
       </c>
       <c r="H36" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -2162,13 +2327,13 @@
         <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H37" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>20</v>
@@ -2176,13 +2341,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -2191,16 +2356,13 @@
         <v>11</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G38" t="s">
         <v>13</v>
       </c>
       <c r="H38" t="s">
-        <v>101</v>
-      </c>
-      <c r="I38" s="3">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>20</v>
@@ -2208,13 +2370,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -2223,27 +2385,27 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
       </c>
       <c r="H39" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="B40" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2252,27 +2414,27 @@
         <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
       </c>
       <c r="H40" t="s">
-        <v>188</v>
+        <v>88</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -2281,27 +2443,27 @@
         <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
       </c>
       <c r="H41" t="s">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -2316,21 +2478,21 @@
         <v>13</v>
       </c>
       <c r="H42" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -2339,27 +2501,27 @@
         <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H43" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -2368,27 +2530,27 @@
         <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H44" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
@@ -2397,27 +2559,27 @@
         <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>168</v>
+        <v>93</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -2426,27 +2588,27 @@
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H46" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>191</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -2458,24 +2620,24 @@
         <v>27</v>
       </c>
       <c r="G47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H47" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>191</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2484,27 +2646,27 @@
         <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>103</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C49" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -2513,27 +2675,27 @@
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H49" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>103</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="B50" t="s">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -2542,27 +2704,27 @@
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="G50" t="s">
         <v>12</v>
       </c>
       <c r="H50" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="B51" t="s">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -2571,56 +2733,56 @@
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
       </c>
       <c r="H51" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" t="s">
         <v>111</v>
-      </c>
-      <c r="B52" t="s">
-        <v>170</v>
-      </c>
-      <c r="C52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" t="s">
-        <v>27</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
       </c>
       <c r="H52" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2635,21 +2797,21 @@
         <v>12</v>
       </c>
       <c r="H53" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="C54" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -2658,7 +2820,7 @@
         <v>11</v>
       </c>
       <c r="F54" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
         <v>12</v>
@@ -2667,47 +2829,47 @@
         <v>138</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>98</v>
+      </c>
+      <c r="B55" t="s">
+        <v>99</v>
+      </c>
+      <c r="C55" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" t="s">
         <v>111</v>
-      </c>
-      <c r="B55" t="s">
-        <v>134</v>
-      </c>
-      <c r="C55" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="s">
-        <v>167</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
       </c>
       <c r="H55" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="B56" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -2716,59 +2878,59 @@
         <v>11</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H56" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D57" t="s">
-        <v>116</v>
+        <v>10</v>
       </c>
       <c r="E57" t="s">
         <v>11</v>
       </c>
       <c r="F57" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G57" t="s">
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>133</v>
-      </c>
-      <c r="I57" s="3">
-        <v>49</v>
+        <v>138</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="E58" t="s">
         <v>11</v>
@@ -2780,7 +2942,7 @@
         <v>13</v>
       </c>
       <c r="H58" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="I58" s="3">
         <v>49</v>
@@ -2788,28 +2950,28 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="E59" t="s">
         <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
       </c>
       <c r="H59" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="I59" s="3">
         <v>49</v>
@@ -2817,39 +2979,42 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="B60" t="s">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E60" t="s">
         <v>11</v>
       </c>
       <c r="F60" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="G60" t="s">
         <v>13</v>
       </c>
       <c r="H60" t="s">
-        <v>163</v>
+        <v>138</v>
+      </c>
+      <c r="I60" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>196</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -2864,21 +3029,18 @@
         <v>13</v>
       </c>
       <c r="H61" t="s">
-        <v>172</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
@@ -2887,865 +3049,859 @@
         <v>11</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
       </c>
       <c r="H62" t="s">
-        <v>153</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="C63" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D63" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
       </c>
       <c r="F63" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>58</v>
+        <v>13</v>
+      </c>
+      <c r="H63" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B64" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="C64" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="D64" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
         <v>11</v>
       </c>
       <c r="F64" t="s">
+        <v>111</v>
+      </c>
+      <c r="G64" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" t="s">
+        <v>140</v>
+      </c>
+      <c r="J64" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="G64" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="C65" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="D65" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
         <v>11</v>
       </c>
       <c r="F65" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>48</v>
+        <v>12</v>
+      </c>
+      <c r="H65" t="s">
+        <v>140</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C66" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="D66" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="G66" t="s">
-        <v>53</v>
+        <v>12</v>
+      </c>
+      <c r="H66" t="s">
+        <v>128</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>192</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C67" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="D67" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
         <v>11</v>
       </c>
       <c r="F67" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>48</v>
+        <v>12</v>
+      </c>
+      <c r="H67" t="s">
+        <v>128</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>193</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>54</v>
+        <v>200</v>
       </c>
       <c r="B68" t="s">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="C68" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D68" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
         <v>11</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G68" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="B69" t="s">
-        <v>37</v>
+        <v>205</v>
       </c>
       <c r="C69" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D69" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
         <v>11</v>
       </c>
       <c r="F69" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G69" t="s">
-        <v>35</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>195</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="B70" t="s">
-        <v>39</v>
+        <v>206</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D70" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
       </c>
       <c r="F70" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G70" t="s">
-        <v>35</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>195</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>36</v>
+        <v>207</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="C71" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D71" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
         <v>11</v>
       </c>
       <c r="F71" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G71" t="s">
-        <v>35</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>195</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>36</v>
+        <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="C72" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D72" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
         <v>11</v>
       </c>
       <c r="F72" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G72" t="s">
-        <v>35</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>195</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>42</v>
+        <v>207</v>
       </c>
       <c r="B73" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="C73" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D73" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
       </c>
       <c r="F73" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G73" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>212</v>
       </c>
       <c r="C74" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D74" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E74" t="s">
         <v>11</v>
       </c>
       <c r="F74" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G74" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="C75" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D75" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
         <v>11</v>
       </c>
       <c r="F75" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="G75" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="C76" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D76" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
       </c>
       <c r="F76" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="G76" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>216</v>
       </c>
       <c r="B77" t="s">
-        <v>47</v>
+        <v>203</v>
       </c>
       <c r="C77" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D77" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
         <v>11</v>
       </c>
       <c r="F77" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="G77" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>49</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>143</v>
+        <v>218</v>
       </c>
       <c r="B78" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="C78" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D78" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>11</v>
       </c>
       <c r="F78" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="G78" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>57</v>
+        <v>220</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
       <c r="C79" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D79" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
       </c>
       <c r="F79" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="G79" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>203</v>
       </c>
       <c r="C80" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D80" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
         <v>11</v>
       </c>
       <c r="F80" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="G80" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="C81" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D81" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E81" t="s">
         <v>11</v>
       </c>
       <c r="F81" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="G81" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
       <c r="B82" t="s">
-        <v>28</v>
+        <v>203</v>
       </c>
       <c r="C82" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D82" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
         <v>11</v>
       </c>
       <c r="F82" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G82" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>59</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>28</v>
+        <v>224</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>203</v>
       </c>
       <c r="C83" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D83" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E83" t="s">
         <v>11</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G83" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>59</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>60</v>
+        <v>226</v>
       </c>
       <c r="B84" t="s">
-        <v>60</v>
+        <v>203</v>
       </c>
       <c r="C84" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D84" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
         <v>11</v>
       </c>
       <c r="F84" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G84" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>222</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>203</v>
       </c>
       <c r="C85" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D85" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>11</v>
       </c>
       <c r="F85" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="G85" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>50</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>29</v>
+        <v>231</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>203</v>
       </c>
       <c r="C86" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E86" t="s">
         <v>11</v>
       </c>
       <c r="F86" t="s">
-        <v>146</v>
+        <v>19</v>
       </c>
       <c r="G86" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>50</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>29</v>
+        <v>233</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>203</v>
       </c>
       <c r="C87" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D87" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E87" t="s">
         <v>11</v>
       </c>
       <c r="F87" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G87" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>18</v>
+        <v>231</v>
       </c>
       <c r="B88" t="s">
-        <v>155</v>
+        <v>203</v>
       </c>
       <c r="C88" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D88" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
       </c>
       <c r="F88" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G88" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>156</v>
+        <v>235</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="B89" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="C89" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D89" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E89" t="s">
         <v>11</v>
       </c>
       <c r="F89" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="G89" t="s">
-        <v>35</v>
-      </c>
-      <c r="H89" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>156</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>18</v>
+        <v>238</v>
       </c>
       <c r="B90" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="C90" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D90" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
       </c>
       <c r="F90" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="G90" t="s">
-        <v>35</v>
-      </c>
-      <c r="H90" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>156</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="B91" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="C91" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D91" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
       </c>
       <c r="F91" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="G91" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="B92" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="C92" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D92" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
         <v>11</v>
       </c>
       <c r="F92" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="G92" t="s">
-        <v>35</v>
-      </c>
-      <c r="H92" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="B93" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="C93" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E93" t="s">
         <v>11</v>
       </c>
       <c r="F93" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G93" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>50</v>
+        <v>242</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>18</v>
+        <v>243</v>
       </c>
       <c r="B94" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="C94" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D94" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
         <v>11</v>
       </c>
       <c r="F94" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>50</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>26</v>
+        <v>241</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>203</v>
       </c>
       <c r="C95" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D95" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E95" t="s">
         <v>11</v>
@@ -3754,517 +3910,1201 @@
         <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>203</v>
       </c>
       <c r="C96" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D96" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>11</v>
       </c>
       <c r="F96" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G96" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>199</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>61</v>
+        <v>240</v>
       </c>
       <c r="B97" t="s">
-        <v>76</v>
+        <v>203</v>
       </c>
       <c r="C97" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D97" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
         <v>11</v>
       </c>
       <c r="F97" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="G97" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>52</v>
+        <v>248</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>61</v>
+        <v>238</v>
       </c>
       <c r="B98" t="s">
-        <v>62</v>
+        <v>203</v>
       </c>
       <c r="C98" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D98" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
         <v>11</v>
       </c>
       <c r="F98" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>52</v>
+        <v>249</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="B99" t="s">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="C99" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D99" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
         <v>11</v>
       </c>
       <c r="F99" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G99" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>52</v>
+        <v>250</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>183</v>
       </c>
       <c r="B100" t="s">
-        <v>61</v>
+        <v>183</v>
       </c>
       <c r="C100" t="s">
+        <v>32</v>
+      </c>
+      <c r="D100" t="s">
         <v>33</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" t="s">
         <v>34</v>
       </c>
-      <c r="E100" t="s">
-        <v>11</v>
-      </c>
-      <c r="F100" t="s">
-        <v>51</v>
-      </c>
-      <c r="G100" t="s">
-        <v>35</v>
-      </c>
       <c r="J100" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="B101" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="C101" t="s">
+        <v>32</v>
+      </c>
+      <c r="D101" t="s">
         <v>33</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" t="s">
         <v>34</v>
       </c>
-      <c r="E101" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" t="s">
-        <v>19</v>
-      </c>
-      <c r="G101" t="s">
-        <v>35</v>
-      </c>
       <c r="J101" s="3" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="B102" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="C102" t="s">
+        <v>32</v>
+      </c>
+      <c r="D102" t="s">
         <v>33</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" t="s">
+        <v>21</v>
+      </c>
+      <c r="G102" t="s">
         <v>34</v>
       </c>
-      <c r="E102" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" t="s">
-        <v>45</v>
-      </c>
-      <c r="G102" t="s">
-        <v>48</v>
-      </c>
-      <c r="I102" s="3">
-        <v>14</v>
-      </c>
       <c r="J102" s="3" t="s">
-        <v>193</v>
+        <v>47</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="B103" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="C103" t="s">
+        <v>32</v>
+      </c>
+      <c r="D103" t="s">
         <v>33</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" t="s">
+        <v>52</v>
+      </c>
+      <c r="G103" t="s">
         <v>34</v>
       </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s">
-        <v>46</v>
-      </c>
-      <c r="G103" t="s">
-        <v>48</v>
-      </c>
-      <c r="I103" s="3">
-        <v>14</v>
-      </c>
       <c r="J103" s="3" t="s">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B104" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C104" t="s">
+        <v>32</v>
+      </c>
+      <c r="D104" t="s">
         <v>33</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" t="s">
+        <v>15</v>
+      </c>
+      <c r="G104" t="s">
         <v>34</v>
       </c>
-      <c r="E104" t="s">
-        <v>11</v>
-      </c>
-      <c r="F104" t="s">
-        <v>24</v>
-      </c>
-      <c r="G104" t="s">
-        <v>35</v>
-      </c>
       <c r="J104" s="3" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="B105" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="C105" t="s">
+        <v>32</v>
+      </c>
+      <c r="D105" t="s">
         <v>33</v>
       </c>
-      <c r="D105" t="s">
-        <v>44</v>
-      </c>
       <c r="E105" t="s">
         <v>11</v>
       </c>
       <c r="F105" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="G105" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="B106" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="C106" t="s">
+        <v>32</v>
+      </c>
+      <c r="D106" t="s">
         <v>33</v>
       </c>
-      <c r="D106" t="s">
-        <v>44</v>
-      </c>
       <c r="E106" t="s">
         <v>11</v>
       </c>
       <c r="F106" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="G106" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>41</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>66</v>
+        <v>187</v>
       </c>
       <c r="B107" t="s">
-        <v>66</v>
+        <v>187</v>
       </c>
       <c r="C107" t="s">
+        <v>32</v>
+      </c>
+      <c r="D107" t="s">
         <v>33</v>
       </c>
-      <c r="D107" t="s">
-        <v>44</v>
-      </c>
       <c r="E107" t="s">
         <v>11</v>
       </c>
       <c r="F107" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G107" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="B108" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="C108" t="s">
+        <v>32</v>
+      </c>
+      <c r="D108" t="s">
         <v>33</v>
       </c>
-      <c r="D108" t="s">
-        <v>44</v>
-      </c>
       <c r="E108" t="s">
         <v>11</v>
       </c>
       <c r="F108" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="G108" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>202</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="B109" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="C109" t="s">
+        <v>32</v>
+      </c>
+      <c r="D109" t="s">
         <v>33</v>
       </c>
-      <c r="D109" t="s">
-        <v>44</v>
-      </c>
       <c r="E109" t="s">
         <v>11</v>
       </c>
       <c r="F109" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="G109" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>203</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="B110" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="C110" t="s">
+        <v>32</v>
+      </c>
+      <c r="D110" t="s">
         <v>33</v>
       </c>
-      <c r="D110" t="s">
-        <v>44</v>
-      </c>
       <c r="E110" t="s">
         <v>11</v>
       </c>
       <c r="F110" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="G110" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>204</v>
+        <v>267</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="B111" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="C111" t="s">
+        <v>268</v>
+      </c>
+      <c r="D111" t="s">
         <v>33</v>
       </c>
-      <c r="D111" t="s">
-        <v>44</v>
-      </c>
       <c r="E111" t="s">
         <v>11</v>
       </c>
       <c r="F111" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G111" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>205</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="B112" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="C112" t="s">
+        <v>32</v>
+      </c>
+      <c r="D112" t="s">
         <v>33</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" t="s">
+        <v>48</v>
+      </c>
+      <c r="G112" t="s">
         <v>34</v>
       </c>
-      <c r="E112" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" t="s">
-        <v>15</v>
-      </c>
-      <c r="G112" t="s">
-        <v>48</v>
-      </c>
       <c r="J112" s="3" t="s">
-        <v>206</v>
+        <v>270</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="C113" t="s">
+        <v>32</v>
+      </c>
+      <c r="D113" t="s">
         <v>33</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" t="s">
+        <v>101</v>
+      </c>
+      <c r="G113" t="s">
         <v>34</v>
       </c>
-      <c r="E113" t="s">
-        <v>11</v>
-      </c>
-      <c r="F113" t="s">
-        <v>38</v>
-      </c>
-      <c r="G113" t="s">
-        <v>48</v>
-      </c>
       <c r="J113" s="3" t="s">
-        <v>193</v>
+        <v>47</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="C114" t="s">
+        <v>32</v>
+      </c>
+      <c r="D114" t="s">
+        <v>33</v>
+      </c>
+      <c r="E114" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" t="s">
+        <v>101</v>
+      </c>
+      <c r="G114" t="s">
+        <v>34</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>103</v>
+      </c>
+      <c r="B115" t="s">
+        <v>125</v>
+      </c>
+      <c r="C115" t="s">
+        <v>32</v>
+      </c>
+      <c r="D115" t="s">
+        <v>33</v>
+      </c>
+      <c r="E115" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" t="s">
+        <v>101</v>
+      </c>
+      <c r="G115" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>103</v>
+      </c>
+      <c r="B116" t="s">
+        <v>125</v>
+      </c>
+      <c r="C116" t="s">
+        <v>32</v>
+      </c>
+      <c r="D116" t="s">
+        <v>33</v>
+      </c>
+      <c r="E116" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" t="s">
+        <v>101</v>
+      </c>
+      <c r="G116" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>103</v>
+      </c>
+      <c r="B117" t="s">
+        <v>124</v>
+      </c>
+      <c r="C117" t="s">
+        <v>32</v>
+      </c>
+      <c r="D117" t="s">
+        <v>33</v>
+      </c>
+      <c r="E117" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" t="s">
+        <v>62</v>
+      </c>
+      <c r="G117" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>50</v>
+      </c>
+      <c r="B118" t="s">
+        <v>51</v>
+      </c>
+      <c r="C118" t="s">
+        <v>32</v>
+      </c>
+      <c r="D118" t="s">
+        <v>33</v>
+      </c>
+      <c r="E118" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" t="s">
+        <v>17</v>
+      </c>
+      <c r="G118" t="s">
+        <v>46</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>50</v>
+      </c>
+      <c r="B119" t="s">
+        <v>50</v>
+      </c>
+      <c r="C119" t="s">
+        <v>32</v>
+      </c>
+      <c r="D119" t="s">
+        <v>33</v>
+      </c>
+      <c r="E119" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" t="s">
+        <v>52</v>
+      </c>
+      <c r="G119" t="s">
+        <v>49</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>50</v>
+      </c>
+      <c r="B120" t="s">
+        <v>50</v>
+      </c>
+      <c r="C120" t="s">
+        <v>32</v>
+      </c>
+      <c r="D120" t="s">
+        <v>33</v>
+      </c>
+      <c r="E120" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" t="s">
+        <v>48</v>
+      </c>
+      <c r="G120" t="s">
+        <v>46</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>50</v>
+      </c>
+      <c r="B121" t="s">
+        <v>50</v>
+      </c>
+      <c r="C121" t="s">
+        <v>32</v>
+      </c>
+      <c r="D121" t="s">
+        <v>33</v>
+      </c>
+      <c r="E121" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" t="s">
+        <v>14</v>
+      </c>
+      <c r="G121" t="s">
+        <v>49</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>35</v>
+      </c>
+      <c r="B122" t="s">
+        <v>36</v>
+      </c>
+      <c r="C122" t="s">
+        <v>32</v>
+      </c>
+      <c r="D122" t="s">
+        <v>33</v>
+      </c>
+      <c r="E122" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" t="s">
+        <v>37</v>
+      </c>
+      <c r="G122" t="s">
+        <v>34</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>35</v>
+      </c>
+      <c r="B123" t="s">
+        <v>38</v>
+      </c>
+      <c r="C123" t="s">
+        <v>32</v>
+      </c>
+      <c r="D123" t="s">
+        <v>33</v>
+      </c>
+      <c r="E123" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" t="s">
+        <v>37</v>
+      </c>
+      <c r="G123" t="s">
+        <v>34</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>35</v>
+      </c>
+      <c r="B124" t="s">
+        <v>39</v>
+      </c>
+      <c r="C124" t="s">
+        <v>32</v>
+      </c>
+      <c r="D124" t="s">
+        <v>33</v>
+      </c>
+      <c r="E124" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" t="s">
+        <v>37</v>
+      </c>
+      <c r="G124" t="s">
+        <v>34</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>35</v>
+      </c>
+      <c r="B125" t="s">
+        <v>35</v>
+      </c>
+      <c r="C125" t="s">
+        <v>32</v>
+      </c>
+      <c r="D125" t="s">
+        <v>33</v>
+      </c>
+      <c r="E125" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" t="s">
+        <v>37</v>
+      </c>
+      <c r="G125" t="s">
+        <v>34</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>41</v>
+      </c>
+      <c r="B126" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126" t="s">
+        <v>32</v>
+      </c>
+      <c r="D126" t="s">
+        <v>33</v>
+      </c>
+      <c r="E126" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" t="s">
+        <v>37</v>
+      </c>
+      <c r="G126" t="s">
+        <v>34</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>42</v>
+      </c>
+      <c r="B127" t="s">
+        <v>42</v>
+      </c>
+      <c r="C127" t="s">
+        <v>32</v>
+      </c>
+      <c r="D127" t="s">
+        <v>33</v>
+      </c>
+      <c r="E127" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" t="s">
+        <v>37</v>
+      </c>
+      <c r="G127" t="s">
+        <v>46</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>31</v>
+      </c>
+      <c r="B128" t="s">
+        <v>31</v>
+      </c>
+      <c r="C128" t="s">
+        <v>32</v>
+      </c>
+      <c r="D128" t="s">
+        <v>43</v>
+      </c>
+      <c r="E128" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" t="s">
+        <v>15</v>
+      </c>
+      <c r="G128" t="s">
+        <v>34</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>53</v>
+      </c>
+      <c r="B129" t="s">
+        <v>53</v>
+      </c>
+      <c r="C129" t="s">
+        <v>32</v>
+      </c>
+      <c r="D129" t="s">
+        <v>33</v>
+      </c>
+      <c r="E129" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" t="s">
+        <v>102</v>
+      </c>
+      <c r="G129" t="s">
+        <v>49</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B130" t="s">
+        <v>25</v>
+      </c>
+      <c r="C130" t="s">
+        <v>32</v>
+      </c>
+      <c r="D130" t="s">
+        <v>33</v>
+      </c>
+      <c r="E130" t="s">
+        <v>11</v>
+      </c>
+      <c r="F130" t="s">
+        <v>48</v>
+      </c>
+      <c r="G130" t="s">
+        <v>46</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>112</v>
       </c>
-      <c r="D114" t="s">
-        <v>10</v>
-      </c>
-      <c r="E114" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" t="s">
-        <v>167</v>
-      </c>
-      <c r="G114" t="s">
-        <v>12</v>
-      </c>
-      <c r="H114" t="s">
-        <v>168</v>
-      </c>
-      <c r="J114" s="3" t="s">
-        <v>103</v>
+      <c r="B131" t="s">
+        <v>112</v>
+      </c>
+      <c r="C131" t="s">
+        <v>32</v>
+      </c>
+      <c r="D131" t="s">
+        <v>33</v>
+      </c>
+      <c r="E131" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" t="s">
+        <v>142</v>
+      </c>
+      <c r="G131" t="s">
+        <v>46</v>
+      </c>
+      <c r="J131" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>28</v>
+      </c>
+      <c r="B132" t="s">
+        <v>28</v>
+      </c>
+      <c r="C132" t="s">
+        <v>32</v>
+      </c>
+      <c r="D132" t="s">
+        <v>43</v>
+      </c>
+      <c r="E132" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132" t="s">
+        <v>54</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>28</v>
+      </c>
+      <c r="B133" t="s">
+        <v>28</v>
+      </c>
+      <c r="C133" t="s">
+        <v>32</v>
+      </c>
+      <c r="D133" t="s">
+        <v>43</v>
+      </c>
+      <c r="E133" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" t="s">
+        <v>16</v>
+      </c>
+      <c r="G133" t="s">
+        <v>54</v>
+      </c>
+      <c r="J133" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>56</v>
+      </c>
+      <c r="B134" t="s">
+        <v>56</v>
+      </c>
+      <c r="C134" t="s">
+        <v>32</v>
+      </c>
+      <c r="D134" t="s">
+        <v>43</v>
+      </c>
+      <c r="E134" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" t="s">
+        <v>49</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>29</v>
+      </c>
+      <c r="B135" t="s">
+        <v>29</v>
+      </c>
+      <c r="C135" t="s">
+        <v>32</v>
+      </c>
+      <c r="D135" t="s">
+        <v>43</v>
+      </c>
+      <c r="E135" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135" t="s">
+        <v>101</v>
+      </c>
+      <c r="G135" t="s">
+        <v>54</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>29</v>
+      </c>
+      <c r="B136" t="s">
+        <v>29</v>
+      </c>
+      <c r="C136" t="s">
+        <v>32</v>
+      </c>
+      <c r="D136" t="s">
+        <v>43</v>
+      </c>
+      <c r="E136" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" t="s">
+        <v>104</v>
+      </c>
+      <c r="G136" t="s">
+        <v>54</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>29</v>
+      </c>
+      <c r="B137" t="s">
+        <v>29</v>
+      </c>
+      <c r="C137" t="s">
+        <v>32</v>
+      </c>
+      <c r="D137" t="s">
+        <v>43</v>
+      </c>
+      <c r="E137" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" t="s">
+        <v>45</v>
+      </c>
+      <c r="G137" t="s">
+        <v>54</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>30</v>
+      </c>
+      <c r="B138" t="s">
+        <v>50</v>
+      </c>
+      <c r="C138" t="s">
+        <v>32</v>
+      </c>
+      <c r="D138" t="s">
+        <v>33</v>
+      </c>
+      <c r="E138" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" t="s">
+        <v>19</v>
+      </c>
+      <c r="G138" t="s">
+        <v>34</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>60</v>
+      </c>
+      <c r="B139" t="s">
+        <v>60</v>
+      </c>
+      <c r="C139" t="s">
+        <v>32</v>
+      </c>
+      <c r="D139" t="s">
+        <v>43</v>
+      </c>
+      <c r="E139" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" t="s">
+        <v>158</v>
+      </c>
+      <c r="G139" t="s">
+        <v>46</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>61</v>
+      </c>
+      <c r="B140" t="s">
+        <v>143</v>
+      </c>
+      <c r="C140" t="s">
+        <v>32</v>
+      </c>
+      <c r="D140" t="s">
+        <v>33</v>
+      </c>
+      <c r="E140" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" t="s">
+        <v>44</v>
+      </c>
+      <c r="G140" t="s">
+        <v>46</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>61</v>
+      </c>
+      <c r="B141" t="s">
+        <v>143</v>
+      </c>
+      <c r="C141" t="s">
+        <v>32</v>
+      </c>
+      <c r="D141" t="s">
+        <v>33</v>
+      </c>
+      <c r="E141" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" t="s">
+        <v>45</v>
+      </c>
+      <c r="G141" t="s">
+        <v>46</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J114" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
+  <autoFilter ref="A1:J141" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -1,27 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tr.alienigenaV5-main\scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transportadoramovc-my.sharepoint.com/personal/camilla_rio_motz_com_br/Documents/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB135A83-6C4F-46C3-B4B3-51D5985F3F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F491E60-C656-4813-891D-1542DE83645F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="551" xr2:uid="{9E8F4E85-D2FF-4383-A72B-5CAFDCCC5644}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E5C93A47-8C6F-4362-A297-19B613721B24}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$147</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -31,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="269">
   <si>
     <t>Origem</t>
   </si>
@@ -63,34 +74,520 @@
     <t>Obs.</t>
   </si>
   <si>
+    <t>Sobral - CE</t>
+  </si>
+  <si>
+    <t>São Luís - MA</t>
+  </si>
+  <si>
+    <t>Escória</t>
+  </si>
+  <si>
     <t>Granel</t>
   </si>
   <si>
     <t>Não</t>
   </si>
   <si>
+    <t>Rodotrem</t>
+  </si>
+  <si>
+    <t>Caçamba</t>
+  </si>
+  <si>
+    <t>190,00</t>
+  </si>
+  <si>
+    <t>REPOM</t>
+  </si>
+  <si>
+    <t>São Gonçalo do Amarante - CE</t>
+  </si>
+  <si>
+    <t>só aceita rodocaçambas com lona fácil. Caso não tenham, o veículo não passa na vistoria dos guardas</t>
+  </si>
+  <si>
+    <t>Xambioá - TO</t>
+  </si>
+  <si>
+    <t>Urbano Santos - MA</t>
+  </si>
+  <si>
+    <t>Calcário</t>
+  </si>
+  <si>
+    <t>200,00</t>
+  </si>
+  <si>
+    <t>Santa Filomena - PI</t>
+  </si>
+  <si>
+    <t>calcário</t>
+  </si>
+  <si>
+    <t>175,00</t>
+  </si>
+  <si>
+    <t>Cajati - SP</t>
+  </si>
+  <si>
+    <t>Rio Branco do Sul - PR</t>
+  </si>
+  <si>
+    <t>Gesso</t>
+  </si>
+  <si>
+    <t>74,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM</t>
+  </si>
+  <si>
+    <t>Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>77,00</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>Itapeva - SP</t>
+  </si>
+  <si>
+    <t>Ipaussu - SP</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
+  </si>
+  <si>
+    <t>75,00</t>
+  </si>
+  <si>
+    <t>Laranjeiras - SE</t>
+  </si>
+  <si>
+    <t>Paulista - PE</t>
+  </si>
+  <si>
+    <t>Clinquer</t>
+  </si>
+  <si>
+    <t>185,00</t>
+  </si>
+  <si>
+    <t>Joinville - SC</t>
+  </si>
+  <si>
+    <t>Cascavel - PR</t>
+  </si>
+  <si>
+    <t>Tubos e Conexões</t>
+  </si>
+  <si>
+    <t>Outro</t>
+  </si>
+  <si>
+    <t>Truck</t>
+  </si>
+  <si>
+    <t>Sider</t>
+  </si>
+  <si>
+    <t>3.500,00</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Vanderléia</t>
+  </si>
+  <si>
+    <t>4.800,00</t>
+  </si>
+  <si>
+    <t>Jucurutu - RN</t>
+  </si>
+  <si>
+    <t>Pitimbu - PB</t>
+  </si>
+  <si>
+    <t>Minério de Ferro</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>110,00</t>
+  </si>
+  <si>
+    <t>Baraúna - RN</t>
+  </si>
+  <si>
+    <t>Pacatuba - SE</t>
+  </si>
+  <si>
+    <t>Clínquer</t>
+  </si>
+  <si>
+    <t>Carreta LS, Vanderléia</t>
+  </si>
+  <si>
+    <t>240,00</t>
+  </si>
+  <si>
+    <t>Nossa Senhora do Socorro - SE</t>
+  </si>
+  <si>
+    <t>8.902,06</t>
+  </si>
+  <si>
+    <t>230,00</t>
+  </si>
+  <si>
+    <t>São João da Barra - RJ</t>
+  </si>
+  <si>
+    <t>Edealina - GO</t>
+  </si>
+  <si>
+    <t>coque</t>
+  </si>
+  <si>
+    <t>17.625,00</t>
+  </si>
+  <si>
+    <t>PAGBEM</t>
+  </si>
+  <si>
+    <t>Itaguaí - RJ</t>
+  </si>
+  <si>
+    <t>Votorantim - SP</t>
+  </si>
+  <si>
+    <t>107,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO REPOM /</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>130,00</t>
+  </si>
+  <si>
+    <t>Salto de Pirapora - SP</t>
+  </si>
+  <si>
+    <t>Brasília - DF</t>
+  </si>
+  <si>
+    <t>325,00</t>
+  </si>
+  <si>
+    <t>295,00</t>
+  </si>
+  <si>
+    <t>Duque de Caxias - RJ</t>
+  </si>
+  <si>
+    <t>Cantagalo - RJ</t>
+  </si>
+  <si>
+    <t>106,00</t>
+  </si>
+  <si>
+    <t>Itaú de Minas - MG</t>
+  </si>
+  <si>
+    <t>260,00</t>
+  </si>
+  <si>
+    <t>231,00</t>
+  </si>
+  <si>
+    <t>Castro - PR</t>
+  </si>
+  <si>
+    <t>Cajamar - SP</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>4.600,00</t>
+  </si>
+  <si>
+    <t>Ouricuri - PE</t>
+  </si>
+  <si>
+    <t>gesso</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Rodotrem</t>
+  </si>
+  <si>
+    <t>Grade Baixa</t>
+  </si>
+  <si>
+    <t>142,00</t>
+  </si>
+  <si>
+    <t>162,00</t>
+  </si>
+  <si>
+    <t>Trindade - PE</t>
+  </si>
+  <si>
+    <t>Gpisita</t>
+  </si>
+  <si>
+    <t>180,00</t>
+  </si>
+  <si>
+    <t>Vanderléia</t>
+  </si>
+  <si>
+    <t>Carreta LS</t>
+  </si>
+  <si>
+    <t>Carreta</t>
+  </si>
+  <si>
+    <t>Carreta toco 5 eixos</t>
+  </si>
+  <si>
+    <t>5.188,21</t>
+  </si>
+  <si>
+    <t>4.745,60</t>
+  </si>
+  <si>
+    <t>6.520,95</t>
+  </si>
+  <si>
+    <t>5.716,37</t>
+  </si>
+  <si>
+    <t>Belém - PA</t>
+  </si>
+  <si>
+    <t>Primavera - PA</t>
+  </si>
+  <si>
+    <t>Carvão</t>
+  </si>
+  <si>
+    <t>3.400,00</t>
+  </si>
+  <si>
+    <t>Pagbem</t>
+  </si>
+  <si>
+    <t>Barcarena - PA</t>
+  </si>
+  <si>
+    <t>Carvão Mineral</t>
+  </si>
+  <si>
+    <t>3.840,00</t>
+  </si>
+  <si>
+    <t>Aripuanã - MT</t>
+  </si>
+  <si>
+    <t>Juiz de Fora - MG</t>
+  </si>
+  <si>
+    <t>MINERIO</t>
+  </si>
+  <si>
+    <t>650,00</t>
+  </si>
+  <si>
+    <t>PASSAR NA GR,SIRENE DE RÉ,LONA FACIL,TECNIL,INCINOMETRO</t>
+  </si>
+  <si>
+    <t>Nobres - MT</t>
+  </si>
+  <si>
+    <t>Porto Velho - RO</t>
+  </si>
+  <si>
     <t>Graneleiro, Caçamba</t>
   </si>
   <si>
-    <t>Caçamba</t>
-  </si>
-  <si>
-    <t>Truck</t>
-  </si>
-  <si>
-    <t>Rodotrem</t>
-  </si>
-  <si>
-    <t>Escória</t>
-  </si>
-  <si>
-    <t>São Luís - MA</t>
+    <t>320,00</t>
+  </si>
+  <si>
+    <t>repom</t>
+  </si>
+  <si>
+    <t>Campo Grande - MS</t>
+  </si>
+  <si>
+    <t>pneu picado</t>
+  </si>
+  <si>
+    <t>305,00</t>
+  </si>
+  <si>
+    <t>PAGBEM/REPOM</t>
+  </si>
+  <si>
+    <t>Chapada Gaúcha - MG</t>
+  </si>
+  <si>
+    <t>Uberaba - MG</t>
+  </si>
+  <si>
+    <t>SOJA</t>
+  </si>
+  <si>
+    <t>Vanderléia, Carreta 4º eixo</t>
   </si>
   <si>
     <t>Carreta LS, Bitrem 7 eixos, Rodotrem</t>
   </si>
   <si>
-    <t>Sobral - CE</t>
+    <t>Unaí - MG</t>
+  </si>
+  <si>
+    <t>170,00</t>
+  </si>
+  <si>
+    <t>140,00</t>
+  </si>
+  <si>
+    <t>Bonfinópolis de Minas - MG</t>
+  </si>
+  <si>
+    <t>Araguari - MG</t>
+  </si>
+  <si>
+    <t>SORGO</t>
+  </si>
+  <si>
+    <t>165,00</t>
+  </si>
+  <si>
+    <t>Patos de Minas - MG</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>135,00</t>
+  </si>
+  <si>
+    <t>Janaúba - MG</t>
+  </si>
+  <si>
+    <t>Milho</t>
+  </si>
+  <si>
+    <t>Montes Claros - MG</t>
+  </si>
+  <si>
+    <t>Borda da Mata - MG</t>
+  </si>
+  <si>
+    <t>115,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO REPOM</t>
+  </si>
+  <si>
+    <t>Grajaú - MA</t>
+  </si>
+  <si>
+    <t>Goianira - GO</t>
+  </si>
+  <si>
+    <t>385,00</t>
+  </si>
+  <si>
+    <t>Acreúna - GO</t>
+  </si>
+  <si>
+    <t>Cabeceiras - GO</t>
+  </si>
+  <si>
+    <t>Sorgo</t>
+  </si>
+  <si>
+    <t>150,00</t>
+  </si>
+  <si>
+    <t>Barro Alto - GO</t>
+  </si>
+  <si>
+    <t>BAUXITA</t>
+  </si>
+  <si>
+    <t>12.700,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM</t>
+  </si>
+  <si>
+    <t>Cuiabá - MT</t>
+  </si>
+  <si>
+    <t>9.930,00</t>
+  </si>
+  <si>
+    <t>17.750,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM / Só vamos carregar se aceitar carregar com os 5% (a partir de 48,5 )</t>
+  </si>
+  <si>
+    <t>Paracatu - MG</t>
+  </si>
+  <si>
+    <t>125,00</t>
+  </si>
+  <si>
+    <t>Paranaguá - PR</t>
+  </si>
+  <si>
+    <t>Lençóis Paulista - SP</t>
+  </si>
+  <si>
+    <t>Fertilizantes</t>
+  </si>
+  <si>
+    <t>Graneleiro</t>
+  </si>
+  <si>
+    <t>Volumes em Bigbag</t>
+  </si>
+  <si>
+    <t>Tatuí - SP</t>
+  </si>
+  <si>
+    <t>Angatuba - SP</t>
+  </si>
+  <si>
+    <t>Cajuru - SP</t>
+  </si>
+  <si>
+    <t>Volumes em Bigbag / 40 Ton</t>
+  </si>
+  <si>
+    <t>Frutal - MG</t>
+  </si>
+  <si>
+    <t>Borebi - SP</t>
+  </si>
+  <si>
+    <t>Pardinho - SP</t>
+  </si>
+  <si>
+    <t>Pinheiro Machado - RS</t>
   </si>
   <si>
     <t>CIMENTO</t>
@@ -99,55 +596,259 @@
     <t>Pallet</t>
   </si>
   <si>
-    <t>Grade Baixa</t>
+    <t>Truck, Bitruck</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI.</t>
+  </si>
+  <si>
+    <t>Aparecida de Goiânia - GO</t>
+  </si>
+  <si>
+    <t>Leopoldo de Bulhões - GO</t>
+  </si>
+  <si>
+    <t>CARGA FRACIONADA (3 A 5 entregas) COM VAGA PARA FICAR FIXO NA UNIDADE COM DESTINOS AS REGIÕES DE: Anápolis/GO, Heitoraí/GO, Inhumas/GO, Itaberaí/GO, Jaraguá/GO e Leopoldo de Bulhões/GO - PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Jaraguá - GO</t>
+  </si>
+  <si>
+    <t>Itaberaí - GO</t>
+  </si>
+  <si>
+    <t>Inhumas - GO</t>
+  </si>
+  <si>
+    <t>Heitoraí - GO</t>
+  </si>
+  <si>
+    <t>Anápolis - GO</t>
+  </si>
+  <si>
+    <t>Goiânia - GO</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM</t>
+  </si>
+  <si>
+    <t>Alfenas - MG</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Cubatão - SP</t>
+  </si>
+  <si>
+    <t>São José dos Campos - SP</t>
+  </si>
+  <si>
+    <t>Barueri - SP</t>
+  </si>
+  <si>
+    <t>Luís Eduardo Magalhães - BA</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: Cocos/BA, Serra Dourada/BA, São Félix do Coribe/BA, Tabocas do Brejo Velho/BA, Correntina/BA, Mansidão/BA, Formosa do Rio Preto/BA, Santa Rita de Cassia/BA, Barreiras/BA e Morpará/BA</t>
+  </si>
+  <si>
+    <t>Crateús - CE</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI. - POSSIVEIS DESTINOS DISPONIVEIS - Mombaça/CE, Poranga/CE, Pedra Branca/CE, Tauá/CE, Nova Russas/CE, Independência/CE e Tamboril/CE</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possiveis Destinos Disponiveis: Araruama/RJ, Campos dos Goytacazes/RJ, Itaperuna/RJ, Saquarema//RJ, Serra/ES</t>
+  </si>
+  <si>
+    <t>Volta Redonda - RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Paraty/RJ, Resende/RJ e Volta Redonda/RJ</t>
+  </si>
+  <si>
+    <t>São Gonçalo - RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Armação dos Búzios/RJ, Arraial do Cabo/RJ, Cabo Frio/RJ, Campos dos Goytacazes/RJ, Guapimirim/RJ, Itaboraí/RJ, Magé/RJ, Maricá/RJ, Niterói/RJ e São Gonçalo/RJ</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro - RJ</t>
+  </si>
+  <si>
+    <t>CIMENTO ENSACADO</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD SANTA CRUZ - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Duque de Caxias/RJ, Nova Iguaçu/RJ, Paraty/RJ, Petrópolis/RJ, Queimados/RJ e Rio de Janeiro/RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD PARADA DE LUCAS - Possiveis Destinos Disponiveis Duque de Caxias/RJ, Mangaratiba/RJ, Mesquita/RJ, Nova Iguaçu/RJ, Petrópolis/RJ e Rio de Janeiro/RJ</t>
+  </si>
+  <si>
+    <t>Vidal Ramos - SC</t>
+  </si>
+  <si>
+    <t>Blumenau - SC</t>
+  </si>
+  <si>
+    <t>Grade Baixa, Prancha</t>
+  </si>
+  <si>
+    <t>53,50</t>
+  </si>
+  <si>
+    <t>Buri - SP</t>
+  </si>
+  <si>
+    <t>116,00</t>
+  </si>
+  <si>
+    <t>120,00</t>
+  </si>
+  <si>
+    <t>Embu das Artes - SP</t>
+  </si>
+  <si>
+    <t>105,00</t>
+  </si>
+  <si>
+    <t>113,00</t>
+  </si>
+  <si>
+    <t>117,00</t>
+  </si>
+  <si>
+    <t>Regente Feijó - SP</t>
+  </si>
+  <si>
+    <t>Graneleiro, Sider</t>
+  </si>
+  <si>
+    <t>160,00</t>
+  </si>
+  <si>
+    <t>168,00</t>
+  </si>
+  <si>
+    <t>Ourinhos - SP</t>
+  </si>
+  <si>
+    <t>Graneleiro, Grade Baixa</t>
+  </si>
+  <si>
+    <t>129,00</t>
+  </si>
+  <si>
+    <t>134,00</t>
   </si>
   <si>
     <t>Teresina - PI</t>
   </si>
   <si>
+    <t>Truck, Carreta LS</t>
+  </si>
+  <si>
+    <t>Graneleiro, Grade Baixa, Prancha</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>DESTINOS DISPONIVEIS: No Extremo Sul do Estado do PI - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Campinas - SP</t>
+  </si>
+  <si>
+    <t>Bragança Paulista - SP</t>
+  </si>
+  <si>
+    <t>Toco, Truck, Bitruck</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI- VEICULOS TOCO APENAS 10 TON</t>
+  </si>
+  <si>
+    <t>Serra Negra - SP</t>
+  </si>
+  <si>
+    <t>Jundiaí - SP</t>
+  </si>
+  <si>
+    <t>Diadema - SP</t>
+  </si>
+  <si>
+    <t>Guarulhos - SP</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
+  </si>
+  <si>
+    <t>Saco</t>
+  </si>
+  <si>
+    <t>Petrolina - PE</t>
+  </si>
+  <si>
+    <t>Caruaru - PE</t>
+  </si>
+  <si>
+    <t>Truck, Bitruck, Carreta</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM / PEDÁGIO INCLUSO NO FRETE</t>
+  </si>
+  <si>
+    <t>Bitruck, Carreta LS</t>
+  </si>
+  <si>
+    <t>Corumbá - MS</t>
+  </si>
+  <si>
+    <t>Truck, Carreta</t>
+  </si>
+  <si>
     <t>RODOTREM (48 Ton)</t>
   </si>
   <si>
-    <t>Bitrem 7 eixos, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>Carreta LS, Vanderléia</t>
-  </si>
-  <si>
-    <t>170,00</t>
-  </si>
-  <si>
-    <t>Crateús - CE</t>
-  </si>
-  <si>
-    <t>São Gonçalo do Amarante - CE</t>
-  </si>
-  <si>
-    <t>70,71</t>
-  </si>
-  <si>
-    <t>só aceita rodocaçambas com lona fácil. Caso não tenham, o veículo não passa na vistoria dos guardas</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI. - POSSIVEIS DESTINOS DISPONIVEIS - Mombaça/CE, Poranga/CE, Pedra Branca/CE, Tauá/CE, Nova Russas/CE, Independência/CE e Tamboril/CE</t>
-  </si>
-  <si>
-    <t>Vanderléia, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>PAGBEM/REPOM</t>
-  </si>
-  <si>
-    <t>Araguari - MG</t>
-  </si>
-  <si>
-    <t>Cabeceiras - GO</t>
-  </si>
-  <si>
-    <t>Sorgo</t>
-  </si>
-  <si>
-    <t>150,00</t>
+    <t>Feira de Santana - BA</t>
+  </si>
+  <si>
+    <t>Carreta, Bitrem 7 eixos, Rodotrem</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
+  </si>
+  <si>
+    <t>Itabuna - BA</t>
+  </si>
+  <si>
+    <t>Vitória da Conquista - BA</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER 07 PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>Tubo</t>
+  </si>
+  <si>
+    <t>Querência - MT</t>
+  </si>
+  <si>
+    <t>São Simão - GO</t>
+  </si>
+  <si>
+    <t>Soja</t>
+  </si>
+  <si>
+    <t>Bitrem 9 eixos, Rodotrem</t>
   </si>
 </sst>
 </file>
@@ -203,19 +904,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{2D6B0D08-A4F0-40C2-B248-C58A4DB0EC02}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{B8ECB8C7-189A-4853-8704-7C158215864E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -546,23 +1241,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A090B303-E5A5-440F-8977-F555609CC44A}">
+  <dimension ref="A1:J147"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="255.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="29.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="31.7265625" customWidth="1"/>
+    <col min="7" max="7" width="20.7265625" customWidth="1"/>
+    <col min="10" max="10" width="229.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,232 +1277,4079 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" t="s">
+        <v>95</v>
+      </c>
+      <c r="J6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>120</v>
+      </c>
+      <c r="J10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" t="s">
+        <v>116</v>
+      </c>
+      <c r="J15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" t="s">
+        <v>161</v>
+      </c>
+      <c r="J16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="s">
+        <v>165</v>
+      </c>
+      <c r="J18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" t="s">
+        <v>182</v>
+      </c>
+      <c r="D19" t="s">
+        <v>183</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" t="s">
+        <v>95</v>
+      </c>
+      <c r="J19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s">
+        <v>112</v>
+      </c>
+      <c r="J20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" t="s">
+        <v>142</v>
+      </c>
+      <c r="J21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>134</v>
+      </c>
+      <c r="G22" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" t="s">
+        <v>142</v>
+      </c>
+      <c r="J22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" t="s">
+        <v>142</v>
+      </c>
+      <c r="J23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" t="s">
+        <v>134</v>
+      </c>
+      <c r="G24" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" t="s">
+        <v>142</v>
+      </c>
+      <c r="J24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" t="s">
+        <v>183</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s">
+        <v>95</v>
+      </c>
+      <c r="J26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>134</v>
+      </c>
+      <c r="G28" t="s">
+        <v>124</v>
+      </c>
+      <c r="H28" t="s">
+        <v>158</v>
+      </c>
+      <c r="J28" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>156</v>
+      </c>
+      <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>135</v>
+      </c>
+      <c r="G29" t="s">
+        <v>124</v>
+      </c>
+      <c r="H29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>239</v>
+      </c>
+      <c r="B33" t="s">
+        <v>240</v>
+      </c>
+      <c r="C33" t="s">
+        <v>182</v>
+      </c>
+      <c r="D33" t="s">
+        <v>183</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
+        <v>241</v>
+      </c>
+      <c r="G33" t="s">
+        <v>95</v>
+      </c>
+      <c r="J33" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>239</v>
+      </c>
+      <c r="B34" t="s">
+        <v>243</v>
+      </c>
+      <c r="C34" t="s">
+        <v>182</v>
+      </c>
+      <c r="D34" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" t="s">
+        <v>241</v>
+      </c>
+      <c r="G34" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>239</v>
+      </c>
+      <c r="B35" t="s">
+        <v>244</v>
+      </c>
+      <c r="C35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>241</v>
+      </c>
+      <c r="G35" t="s">
+        <v>95</v>
+      </c>
+      <c r="J35" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>239</v>
+      </c>
+      <c r="B36" t="s">
+        <v>239</v>
+      </c>
+      <c r="C36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>241</v>
+      </c>
+      <c r="G36" t="s">
+        <v>95</v>
+      </c>
+      <c r="J36" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s">
+        <v>129</v>
+      </c>
+      <c r="J37" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
+        <v>182</v>
+      </c>
+      <c r="D38" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s">
+        <v>184</v>
+      </c>
+      <c r="G38" t="s">
+        <v>95</v>
+      </c>
+      <c r="J38" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>250</v>
+      </c>
+      <c r="B39" t="s">
+        <v>250</v>
+      </c>
+      <c r="C39" t="s">
+        <v>182</v>
+      </c>
+      <c r="D39" t="s">
+        <v>183</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>251</v>
+      </c>
+      <c r="G39" t="s">
+        <v>216</v>
+      </c>
+      <c r="J39" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s">
+        <v>90</v>
+      </c>
+      <c r="G40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" t="s">
+        <v>91</v>
+      </c>
+      <c r="J40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" t="s">
+        <v>133</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" t="s">
+        <v>124</v>
+      </c>
+      <c r="H41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s">
+        <v>135</v>
+      </c>
+      <c r="G42" t="s">
+        <v>124</v>
+      </c>
+      <c r="H42" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B43" t="s">
+        <v>254</v>
+      </c>
+      <c r="C43" t="s">
+        <v>182</v>
+      </c>
+      <c r="D43" t="s">
+        <v>248</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G43" t="s">
+        <v>230</v>
+      </c>
+      <c r="J43" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>254</v>
+      </c>
+      <c r="B44" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" t="s">
+        <v>182</v>
+      </c>
+      <c r="D44" t="s">
+        <v>248</v>
+      </c>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" t="s">
+        <v>62</v>
+      </c>
+      <c r="G44" t="s">
+        <v>230</v>
+      </c>
+      <c r="J44" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>254</v>
+      </c>
+      <c r="B45" t="s">
+        <v>254</v>
+      </c>
+      <c r="C45" t="s">
+        <v>182</v>
+      </c>
+      <c r="D45" t="s">
+        <v>248</v>
+      </c>
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
+        <v>255</v>
+      </c>
+      <c r="G45" t="s">
+        <v>230</v>
+      </c>
+      <c r="J45" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>203</v>
+      </c>
+      <c r="B46" t="s">
+        <v>203</v>
+      </c>
+      <c r="C46" t="s">
+        <v>182</v>
+      </c>
+      <c r="D46" t="s">
+        <v>183</v>
+      </c>
+      <c r="E46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" t="s">
+        <v>48</v>
+      </c>
+      <c r="G46" t="s">
+        <v>95</v>
+      </c>
+      <c r="J46" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>198</v>
+      </c>
+      <c r="B47" t="s">
+        <v>198</v>
+      </c>
+      <c r="C47" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" t="s">
+        <v>183</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" t="s">
+        <v>48</v>
+      </c>
+      <c r="G47" t="s">
+        <v>95</v>
+      </c>
+      <c r="J47" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>163</v>
+      </c>
+      <c r="B48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48" t="s">
+        <v>182</v>
+      </c>
+      <c r="D48" t="s">
+        <v>248</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s">
+        <v>94</v>
+      </c>
+      <c r="G48" t="s">
+        <v>230</v>
+      </c>
+      <c r="J48" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>163</v>
+      </c>
+      <c r="B49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" t="s">
+        <v>182</v>
+      </c>
+      <c r="D49" t="s">
+        <v>248</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
+        <v>253</v>
+      </c>
+      <c r="G49" t="s">
+        <v>230</v>
+      </c>
+      <c r="J49" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>245</v>
+      </c>
+      <c r="B50" t="s">
+        <v>245</v>
+      </c>
+      <c r="C50" t="s">
+        <v>182</v>
+      </c>
+      <c r="D50" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" t="s">
+        <v>241</v>
+      </c>
+      <c r="G50" t="s">
+        <v>95</v>
+      </c>
+      <c r="J50" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
+        <v>83</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>84</v>
+      </c>
+      <c r="J51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>257</v>
+      </c>
+      <c r="B52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C52" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" t="s">
+        <v>248</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s">
+        <v>258</v>
+      </c>
+      <c r="G52" t="s">
+        <v>216</v>
+      </c>
+      <c r="J52" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" t="s">
+        <v>134</v>
+      </c>
+      <c r="G53" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" t="s">
+        <v>154</v>
+      </c>
+      <c r="J53" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" t="s">
+        <v>135</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" t="s">
+        <v>154</v>
+      </c>
+      <c r="J54" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>152</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" t="s">
+        <v>47</v>
+      </c>
+      <c r="E55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H55" t="s">
+        <v>63</v>
+      </c>
+      <c r="I55">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>246</v>
+      </c>
+      <c r="B56" t="s">
+        <v>246</v>
+      </c>
+      <c r="C56" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" t="s">
+        <v>183</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>241</v>
+      </c>
+      <c r="G56" t="s">
+        <v>216</v>
+      </c>
+      <c r="J56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>260</v>
+      </c>
+      <c r="B57" t="s">
+        <v>261</v>
+      </c>
+      <c r="C57" t="s">
+        <v>182</v>
+      </c>
+      <c r="D57" t="s">
+        <v>183</v>
+      </c>
+      <c r="E57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" t="s">
+        <v>48</v>
+      </c>
+      <c r="G57" t="s">
+        <v>216</v>
+      </c>
+      <c r="J57" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>260</v>
+      </c>
+      <c r="B58" t="s">
+        <v>260</v>
+      </c>
+      <c r="C58" t="s">
+        <v>182</v>
+      </c>
+      <c r="D58" t="s">
+        <v>183</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" t="s">
+        <v>263</v>
+      </c>
+      <c r="G58" t="s">
+        <v>216</v>
+      </c>
+      <c r="J58" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>260</v>
+      </c>
+      <c r="B59" t="s">
+        <v>260</v>
+      </c>
+      <c r="C59" t="s">
+        <v>182</v>
+      </c>
+      <c r="D59" t="s">
+        <v>183</v>
+      </c>
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" t="s">
+        <v>255</v>
+      </c>
+      <c r="G59" t="s">
+        <v>216</v>
+      </c>
+      <c r="J59" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" t="s">
+        <v>74</v>
+      </c>
+      <c r="I60">
+        <v>28000</v>
+      </c>
+      <c r="J60" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61" t="s">
+        <v>76</v>
+      </c>
+      <c r="G61" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" t="s">
+        <v>77</v>
+      </c>
+      <c r="I61">
+        <v>28000</v>
+      </c>
+      <c r="J61" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" t="s">
+        <v>74</v>
+      </c>
+      <c r="I62">
+        <v>28000</v>
+      </c>
+      <c r="J62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" t="s">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" t="s">
+        <v>77</v>
+      </c>
+      <c r="I63">
+        <v>28000</v>
+      </c>
+      <c r="J63" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>36</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B64" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" t="s">
+        <v>38</v>
+      </c>
+      <c r="G64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>85</v>
+      </c>
+      <c r="B65" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s">
+        <v>14</v>
+      </c>
+      <c r="F65" t="s">
+        <v>102</v>
+      </c>
+      <c r="G65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" t="s">
+        <v>150</v>
+      </c>
+      <c r="J65" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" t="s">
+        <v>78</v>
+      </c>
+      <c r="C66" t="s">
+        <v>42</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" t="s">
+        <v>135</v>
+      </c>
+      <c r="G66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" t="s">
+        <v>142</v>
+      </c>
+      <c r="J66" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>85</v>
+      </c>
+      <c r="B67" t="s">
+        <v>196</v>
+      </c>
+      <c r="C67" t="s">
+        <v>182</v>
+      </c>
+      <c r="D67" t="s">
+        <v>183</v>
+      </c>
+      <c r="E67" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" t="s">
+        <v>102</v>
+      </c>
+      <c r="G67" t="s">
+        <v>95</v>
+      </c>
+      <c r="J67" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" t="s">
+        <v>47</v>
+      </c>
+      <c r="E68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" t="s">
+        <v>48</v>
+      </c>
+      <c r="G68" t="s">
+        <v>49</v>
+      </c>
+      <c r="H68" t="s">
+        <v>50</v>
+      </c>
+      <c r="J68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" t="s">
+        <v>45</v>
+      </c>
+      <c r="C69" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" t="s">
+        <v>47</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" t="s">
+        <v>49</v>
+      </c>
+      <c r="H69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" t="s">
+        <v>264</v>
+      </c>
+      <c r="E70" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" t="s">
+        <v>48</v>
+      </c>
+      <c r="G70" t="s">
+        <v>49</v>
+      </c>
+      <c r="H70" t="s">
+        <v>50</v>
+      </c>
+      <c r="I70">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>54</v>
+      </c>
+      <c r="B71" t="s">
+        <v>55</v>
+      </c>
+      <c r="C71" t="s">
+        <v>56</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" t="s">
+        <v>58</v>
+      </c>
+      <c r="J71" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>54</v>
+      </c>
+      <c r="B72" t="s">
+        <v>55</v>
+      </c>
+      <c r="C72" t="s">
+        <v>56</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" t="s">
+        <v>58</v>
+      </c>
+      <c r="J72" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" t="s">
+        <v>43</v>
+      </c>
+      <c r="J73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" t="s">
+        <v>42</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" t="s">
+        <v>51</v>
+      </c>
+      <c r="G74" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" t="s">
+        <v>43</v>
+      </c>
+      <c r="J74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" t="s">
+        <v>40</v>
+      </c>
+      <c r="C75" t="s">
+        <v>182</v>
+      </c>
+      <c r="D75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E75" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="G75" t="s">
+        <v>95</v>
+      </c>
+      <c r="J75" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>201</v>
+      </c>
+      <c r="B76" t="s">
+        <v>201</v>
+      </c>
+      <c r="C76" t="s">
+        <v>182</v>
+      </c>
+      <c r="D76" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" t="s">
+        <v>35</v>
+      </c>
+      <c r="G76" t="s">
+        <v>95</v>
+      </c>
+      <c r="J76" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>122</v>
+      </c>
+      <c r="B77" t="s">
+        <v>123</v>
+      </c>
+      <c r="C77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>124</v>
+      </c>
+      <c r="H77" t="s">
+        <v>125</v>
+      </c>
+      <c r="J77" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" t="s">
+        <v>122</v>
+      </c>
+      <c r="C78" t="s">
+        <v>182</v>
+      </c>
+      <c r="D78" t="s">
+        <v>248</v>
+      </c>
+      <c r="E78" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" t="s">
+        <v>94</v>
+      </c>
+      <c r="G78" t="s">
+        <v>235</v>
+      </c>
+      <c r="J78" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" t="s">
+        <v>93</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" t="s">
+        <v>94</v>
+      </c>
+      <c r="G79" t="s">
+        <v>95</v>
+      </c>
+      <c r="H79" t="s">
+        <v>96</v>
+      </c>
+      <c r="J79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" t="s">
+        <v>40</v>
+      </c>
+      <c r="C80" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80" t="s">
+        <v>94</v>
+      </c>
+      <c r="G80" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" t="s">
+        <v>97</v>
+      </c>
+      <c r="I80">
+        <v>52</v>
+      </c>
+      <c r="J80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>169</v>
+      </c>
+      <c r="B81" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" t="s">
+        <v>171</v>
+      </c>
+      <c r="D81" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" t="s">
+        <v>135</v>
+      </c>
+      <c r="G81" t="s">
+        <v>172</v>
+      </c>
+      <c r="J81" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>169</v>
+      </c>
+      <c r="B82" t="s">
+        <v>174</v>
+      </c>
+      <c r="C82" t="s">
+        <v>171</v>
+      </c>
+      <c r="D82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" t="s">
+        <v>102</v>
+      </c>
+      <c r="G82" t="s">
+        <v>172</v>
+      </c>
+      <c r="J82" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>169</v>
+      </c>
+      <c r="B83" t="s">
+        <v>175</v>
+      </c>
+      <c r="C83" t="s">
+        <v>171</v>
+      </c>
+      <c r="D83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s">
+        <v>14</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s">
+        <v>172</v>
+      </c>
+      <c r="J83" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>169</v>
+      </c>
+      <c r="B84" t="s">
+        <v>176</v>
+      </c>
+      <c r="C84" t="s">
+        <v>171</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" t="s">
+        <v>33</v>
+      </c>
+      <c r="G84" t="s">
+        <v>172</v>
+      </c>
+      <c r="J84" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" t="s">
+        <v>178</v>
+      </c>
+      <c r="C85" t="s">
+        <v>171</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
+        <v>172</v>
+      </c>
+      <c r="J85" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" t="s">
+        <v>171</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>14</v>
+      </c>
+      <c r="F86" t="s">
+        <v>135</v>
+      </c>
+      <c r="G86" t="s">
+        <v>172</v>
+      </c>
+      <c r="J86" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>169</v>
+      </c>
+      <c r="B87" t="s">
+        <v>180</v>
+      </c>
+      <c r="C87" t="s">
+        <v>171</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>14</v>
+      </c>
+      <c r="F87" t="s">
+        <v>135</v>
+      </c>
+      <c r="G87" t="s">
+        <v>172</v>
+      </c>
+      <c r="J87" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>143</v>
+      </c>
+      <c r="B88" t="s">
+        <v>140</v>
+      </c>
+      <c r="C88" t="s">
+        <v>141</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" t="s">
+        <v>134</v>
+      </c>
+      <c r="G88" t="s">
+        <v>124</v>
+      </c>
+      <c r="H88" t="s">
+        <v>144</v>
+      </c>
+      <c r="J88" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>143</v>
+      </c>
+      <c r="B89" t="s">
+        <v>140</v>
+      </c>
+      <c r="C89" t="s">
+        <v>141</v>
+      </c>
+      <c r="D89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89" t="s">
+        <v>135</v>
+      </c>
+      <c r="G89" t="s">
+        <v>124</v>
+      </c>
+      <c r="H89" t="s">
+        <v>144</v>
+      </c>
+      <c r="J89" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>249</v>
+      </c>
+      <c r="B90" t="s">
+        <v>249</v>
+      </c>
+      <c r="C90" t="s">
+        <v>182</v>
+      </c>
+      <c r="D90" t="s">
+        <v>183</v>
+      </c>
+      <c r="E90" t="s">
+        <v>14</v>
+      </c>
+      <c r="F90" t="s">
+        <v>241</v>
+      </c>
+      <c r="G90" t="s">
+        <v>235</v>
+      </c>
+      <c r="J90" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" t="s">
+        <v>181</v>
+      </c>
+      <c r="C91" t="s">
+        <v>182</v>
+      </c>
+      <c r="D91" t="s">
+        <v>183</v>
+      </c>
+      <c r="E91" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" t="s">
+        <v>184</v>
+      </c>
+      <c r="G91" t="s">
+        <v>95</v>
+      </c>
+      <c r="J91" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>265</v>
+      </c>
+      <c r="B92" t="s">
+        <v>266</v>
+      </c>
+      <c r="C92" t="s">
+        <v>267</v>
+      </c>
+      <c r="D92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" t="s">
+        <v>268</v>
+      </c>
+      <c r="G92" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>29</v>
+      </c>
+      <c r="B93" t="s">
+        <v>218</v>
+      </c>
+      <c r="C93" t="s">
+        <v>182</v>
+      </c>
+      <c r="D93" t="s">
+        <v>183</v>
+      </c>
+      <c r="E93" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" t="s">
+        <v>95</v>
+      </c>
+      <c r="H93" t="s">
+        <v>219</v>
+      </c>
+      <c r="J93" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>29</v>
+      </c>
+      <c r="B94" t="s">
+        <v>218</v>
+      </c>
+      <c r="C94" t="s">
+        <v>182</v>
+      </c>
+      <c r="D94" t="s">
+        <v>183</v>
+      </c>
+      <c r="E94" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" t="s">
+        <v>76</v>
+      </c>
+      <c r="G94" t="s">
+        <v>95</v>
+      </c>
+      <c r="H94" t="s">
+        <v>220</v>
+      </c>
+      <c r="J94" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>29</v>
+      </c>
+      <c r="B95" t="s">
+        <v>221</v>
+      </c>
+      <c r="C95" t="s">
+        <v>182</v>
+      </c>
+      <c r="D95" t="s">
+        <v>183</v>
+      </c>
+      <c r="E95" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95" t="s">
+        <v>15</v>
+      </c>
+      <c r="G95" t="s">
+        <v>95</v>
+      </c>
+      <c r="H95" t="s">
+        <v>222</v>
+      </c>
+      <c r="J95" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>29</v>
+      </c>
+      <c r="B96" t="s">
+        <v>221</v>
+      </c>
+      <c r="C96" t="s">
+        <v>182</v>
+      </c>
+      <c r="D96" t="s">
+        <v>183</v>
+      </c>
+      <c r="E96" t="s">
+        <v>14</v>
+      </c>
+      <c r="F96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G96" t="s">
+        <v>95</v>
+      </c>
+      <c r="H96" t="s">
+        <v>223</v>
+      </c>
+      <c r="J96" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>29</v>
+      </c>
+      <c r="B97" t="s">
+        <v>221</v>
+      </c>
+      <c r="C97" t="s">
+        <v>182</v>
+      </c>
+      <c r="D97" t="s">
+        <v>183</v>
+      </c>
+      <c r="E97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F97" t="s">
+        <v>76</v>
+      </c>
+      <c r="G97" t="s">
+        <v>95</v>
+      </c>
+      <c r="H97" t="s">
+        <v>224</v>
+      </c>
+      <c r="J97" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>29</v>
+      </c>
+      <c r="B98" t="s">
+        <v>225</v>
+      </c>
+      <c r="C98" t="s">
+        <v>182</v>
+      </c>
+      <c r="D98" t="s">
+        <v>183</v>
+      </c>
+      <c r="E98" t="s">
+        <v>14</v>
+      </c>
+      <c r="F98" t="s">
+        <v>15</v>
+      </c>
+      <c r="G98" t="s">
+        <v>226</v>
+      </c>
+      <c r="H98" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>29</v>
+      </c>
+      <c r="B99" t="s">
+        <v>225</v>
+      </c>
+      <c r="C99" t="s">
+        <v>182</v>
+      </c>
+      <c r="D99" t="s">
+        <v>183</v>
+      </c>
+      <c r="E99" t="s">
+        <v>14</v>
+      </c>
+      <c r="F99" t="s">
+        <v>15</v>
+      </c>
+      <c r="G99" t="s">
+        <v>216</v>
+      </c>
+      <c r="H99" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>29</v>
+      </c>
+      <c r="B100" t="s">
+        <v>225</v>
+      </c>
+      <c r="C100" t="s">
+        <v>182</v>
+      </c>
+      <c r="D100" t="s">
+        <v>183</v>
+      </c>
+      <c r="E100" t="s">
+        <v>14</v>
+      </c>
+      <c r="F100" t="s">
+        <v>33</v>
+      </c>
+      <c r="G100" t="s">
+        <v>226</v>
+      </c>
+      <c r="H100" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>29</v>
+      </c>
+      <c r="B101" t="s">
+        <v>225</v>
+      </c>
+      <c r="C101" t="s">
+        <v>182</v>
+      </c>
+      <c r="D101" t="s">
+        <v>183</v>
+      </c>
+      <c r="E101" t="s">
+        <v>14</v>
+      </c>
+      <c r="F101" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101" t="s">
+        <v>216</v>
+      </c>
+      <c r="H101" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>29</v>
+      </c>
+      <c r="B102" t="s">
+        <v>225</v>
+      </c>
+      <c r="C102" t="s">
+        <v>182</v>
+      </c>
+      <c r="D102" t="s">
+        <v>183</v>
+      </c>
+      <c r="E102" t="s">
+        <v>14</v>
+      </c>
+      <c r="F102" t="s">
+        <v>76</v>
+      </c>
+      <c r="G102" t="s">
+        <v>226</v>
+      </c>
+      <c r="H102" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>29</v>
+      </c>
+      <c r="B103" t="s">
+        <v>225</v>
+      </c>
+      <c r="C103" t="s">
+        <v>182</v>
+      </c>
+      <c r="D103" t="s">
+        <v>183</v>
+      </c>
+      <c r="E103" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" t="s">
+        <v>76</v>
+      </c>
+      <c r="G103" t="s">
+        <v>216</v>
+      </c>
+      <c r="H103" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>29</v>
+      </c>
+      <c r="B104" t="s">
+        <v>229</v>
+      </c>
+      <c r="C104" t="s">
+        <v>182</v>
+      </c>
+      <c r="D104" t="s">
+        <v>183</v>
+      </c>
+      <c r="E104" t="s">
+        <v>14</v>
+      </c>
+      <c r="F104" t="s">
+        <v>15</v>
+      </c>
+      <c r="G104" t="s">
+        <v>230</v>
+      </c>
+      <c r="H104" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>29</v>
+      </c>
+      <c r="B105" t="s">
+        <v>229</v>
+      </c>
+      <c r="C105" t="s">
+        <v>182</v>
+      </c>
+      <c r="D105" t="s">
+        <v>183</v>
+      </c>
+      <c r="E105" t="s">
+        <v>14</v>
+      </c>
+      <c r="F105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G105" t="s">
+        <v>230</v>
+      </c>
+      <c r="H105" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>29</v>
+      </c>
+      <c r="B106" t="s">
+        <v>229</v>
+      </c>
+      <c r="C106" t="s">
+        <v>182</v>
+      </c>
+      <c r="D106" t="s">
+        <v>183</v>
+      </c>
+      <c r="E106" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" t="s">
+        <v>76</v>
+      </c>
+      <c r="G106" t="s">
+        <v>230</v>
+      </c>
+      <c r="H106" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>210</v>
+      </c>
+      <c r="B107" t="s">
+        <v>210</v>
+      </c>
+      <c r="C107" t="s">
+        <v>211</v>
+      </c>
+      <c r="D107" t="s">
+        <v>183</v>
+      </c>
+      <c r="E107" t="s">
+        <v>14</v>
+      </c>
+      <c r="F107" t="s">
+        <v>184</v>
+      </c>
+      <c r="G107" t="s">
+        <v>95</v>
+      </c>
+      <c r="J107" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>210</v>
+      </c>
+      <c r="B108" t="s">
+        <v>210</v>
+      </c>
+      <c r="C108" t="s">
+        <v>182</v>
+      </c>
+      <c r="D108" t="s">
+        <v>183</v>
+      </c>
+      <c r="E108" t="s">
+        <v>14</v>
+      </c>
+      <c r="F108" t="s">
+        <v>184</v>
+      </c>
+      <c r="G108" t="s">
+        <v>95</v>
+      </c>
+      <c r="J108" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>208</v>
+      </c>
+      <c r="B109" t="s">
+        <v>208</v>
+      </c>
+      <c r="C109" t="s">
+        <v>182</v>
+      </c>
+      <c r="D109" t="s">
+        <v>183</v>
+      </c>
+      <c r="E109" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109" t="s">
+        <v>184</v>
+      </c>
+      <c r="G109" t="s">
+        <v>95</v>
+      </c>
+      <c r="J109" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>19</v>
+      </c>
+      <c r="B110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" t="s">
+        <v>14</v>
+      </c>
+      <c r="F110" t="s">
+        <v>15</v>
+      </c>
+      <c r="G110" t="s">
+        <v>16</v>
+      </c>
+      <c r="H110" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>67</v>
+      </c>
+      <c r="B111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C111" t="s">
+        <v>69</v>
+      </c>
+      <c r="D111" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111" t="s">
+        <v>15</v>
+      </c>
+      <c r="G111" t="s">
+        <v>16</v>
+      </c>
+      <c r="H111" t="s">
+        <v>70</v>
+      </c>
+      <c r="J111" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>67</v>
+      </c>
+      <c r="B112" t="s">
+        <v>79</v>
+      </c>
+      <c r="C112" t="s">
+        <v>69</v>
+      </c>
+      <c r="D112" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" t="s">
+        <v>14</v>
+      </c>
+      <c r="F112" t="s">
+        <v>57</v>
+      </c>
+      <c r="G112" t="s">
+        <v>16</v>
+      </c>
+      <c r="H112" t="s">
+        <v>80</v>
+      </c>
+      <c r="J112" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>67</v>
+      </c>
+      <c r="B113" t="s">
+        <v>79</v>
+      </c>
+      <c r="C113" t="s">
+        <v>69</v>
+      </c>
+      <c r="D113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>14</v>
+      </c>
+      <c r="F113" t="s">
+        <v>15</v>
+      </c>
+      <c r="G113" t="s">
+        <v>16</v>
+      </c>
+      <c r="H113" t="s">
+        <v>81</v>
+      </c>
+      <c r="J113" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>67</v>
+      </c>
+      <c r="B114" t="s">
+        <v>85</v>
+      </c>
+      <c r="C114" t="s">
+        <v>69</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>14</v>
+      </c>
+      <c r="F114" t="s">
+        <v>57</v>
+      </c>
+      <c r="G114" t="s">
+        <v>16</v>
+      </c>
+      <c r="H114" t="s">
+        <v>86</v>
+      </c>
+      <c r="J114" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>67</v>
+      </c>
+      <c r="B115" t="s">
+        <v>85</v>
+      </c>
+      <c r="C115" t="s">
+        <v>69</v>
+      </c>
+      <c r="D115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" t="s">
+        <v>14</v>
+      </c>
+      <c r="F115" t="s">
+        <v>15</v>
+      </c>
+      <c r="G115" t="s">
+        <v>16</v>
+      </c>
+      <c r="H115" t="s">
+        <v>87</v>
+      </c>
+      <c r="J115" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>199</v>
+      </c>
+      <c r="B116" t="s">
+        <v>199</v>
+      </c>
+      <c r="C116" t="s">
+        <v>182</v>
+      </c>
+      <c r="D116" t="s">
+        <v>183</v>
+      </c>
+      <c r="E116" t="s">
+        <v>14</v>
+      </c>
+      <c r="F116" t="s">
+        <v>48</v>
+      </c>
+      <c r="G116" t="s">
+        <v>95</v>
+      </c>
+      <c r="J116" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B117" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C117" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" t="s">
+        <v>14</v>
+      </c>
+      <c r="F117" t="s">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="J117" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>10</v>
+      </c>
+      <c r="B118" t="s">
+        <v>233</v>
+      </c>
+      <c r="C118" t="s">
+        <v>182</v>
+      </c>
+      <c r="D118" t="s">
+        <v>183</v>
+      </c>
+      <c r="E118" t="s">
+        <v>14</v>
+      </c>
+      <c r="F118" t="s">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>95</v>
+      </c>
+      <c r="J118" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>233</v>
+      </c>
+      <c r="B119" t="s">
+        <v>233</v>
+      </c>
+      <c r="C119" t="s">
+        <v>182</v>
+      </c>
+      <c r="D119" t="s">
+        <v>183</v>
+      </c>
+      <c r="E119" t="s">
+        <v>14</v>
+      </c>
+      <c r="F119" t="s">
+        <v>234</v>
+      </c>
+      <c r="G119" t="s">
+        <v>235</v>
+      </c>
+      <c r="J119" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>233</v>
+      </c>
+      <c r="B120" t="s">
+        <v>233</v>
+      </c>
+      <c r="C120" t="s">
+        <v>182</v>
+      </c>
+      <c r="D120" t="s">
+        <v>183</v>
+      </c>
+      <c r="E120" t="s">
+        <v>14</v>
+      </c>
+      <c r="F120" t="s">
+        <v>184</v>
+      </c>
+      <c r="G120" t="s">
+        <v>216</v>
+      </c>
+      <c r="J120" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>233</v>
+      </c>
+      <c r="B121" t="s">
+        <v>233</v>
+      </c>
+      <c r="C121" t="s">
+        <v>182</v>
+      </c>
+      <c r="D121" t="s">
+        <v>183</v>
+      </c>
+      <c r="E121" t="s">
+        <v>14</v>
+      </c>
+      <c r="F121" t="s">
+        <v>94</v>
+      </c>
+      <c r="G121" t="s">
+        <v>235</v>
+      </c>
+      <c r="J121" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>98</v>
+      </c>
+      <c r="B122" t="s">
+        <v>40</v>
+      </c>
+      <c r="C122" t="s">
+        <v>99</v>
+      </c>
+      <c r="D122" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" t="s">
+        <v>14</v>
+      </c>
+      <c r="F122" t="s">
+        <v>15</v>
+      </c>
+      <c r="G122" t="s">
+        <v>16</v>
+      </c>
+      <c r="H122" t="s">
+        <v>100</v>
+      </c>
+      <c r="J122" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>98</v>
+      </c>
+      <c r="B123" t="s">
+        <v>40</v>
+      </c>
+      <c r="C123" t="s">
+        <v>99</v>
+      </c>
+      <c r="D123" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" t="s">
+        <v>14</v>
+      </c>
+      <c r="F123" t="s">
         <v>33</v>
       </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G123" t="s">
+        <v>16</v>
+      </c>
+      <c r="H123" t="s">
+        <v>100</v>
+      </c>
+      <c r="J123" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>98</v>
+      </c>
+      <c r="B124" t="s">
+        <v>40</v>
+      </c>
+      <c r="C124" t="s">
+        <v>99</v>
+      </c>
+      <c r="D124" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" t="s">
+        <v>14</v>
+      </c>
+      <c r="F124" t="s">
+        <v>76</v>
+      </c>
+      <c r="G124" t="s">
+        <v>16</v>
+      </c>
+      <c r="H124" t="s">
+        <v>100</v>
+      </c>
+      <c r="J124" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>98</v>
+      </c>
+      <c r="B125" t="s">
+        <v>40</v>
+      </c>
+      <c r="C125" t="s">
+        <v>99</v>
+      </c>
+      <c r="D125" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" t="s">
+        <v>14</v>
+      </c>
+      <c r="F125" t="s">
+        <v>101</v>
+      </c>
+      <c r="G125" t="s">
+        <v>16</v>
+      </c>
+      <c r="H125" t="s">
+        <v>100</v>
+      </c>
+      <c r="J125" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>98</v>
+      </c>
+      <c r="B126" t="s">
+        <v>40</v>
+      </c>
+      <c r="C126" t="s">
+        <v>99</v>
+      </c>
+      <c r="D126" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" t="s">
+        <v>14</v>
+      </c>
+      <c r="F126" t="s">
+        <v>102</v>
+      </c>
+      <c r="G126" t="s">
+        <v>16</v>
+      </c>
+      <c r="H126" t="s">
+        <v>100</v>
+      </c>
+      <c r="J126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>98</v>
+      </c>
+      <c r="B127" t="s">
+        <v>40</v>
+      </c>
+      <c r="C127" t="s">
+        <v>99</v>
+      </c>
+      <c r="D127" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127" t="s">
+        <v>103</v>
+      </c>
+      <c r="G127" t="s">
+        <v>16</v>
+      </c>
+      <c r="H127" t="s">
+        <v>100</v>
+      </c>
+      <c r="J127" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>98</v>
+      </c>
+      <c r="B128" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C128" t="s">
+        <v>99</v>
+      </c>
+      <c r="D128" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" t="s">
+        <v>14</v>
+      </c>
+      <c r="F128" t="s">
+        <v>102</v>
+      </c>
+      <c r="G128" t="s">
+        <v>16</v>
+      </c>
+      <c r="H128" t="s">
+        <v>105</v>
+      </c>
+      <c r="J128" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>98</v>
+      </c>
+      <c r="B129" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" t="s">
+        <v>99</v>
+      </c>
+      <c r="D129" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" t="s">
+        <v>14</v>
+      </c>
+      <c r="F129" t="s">
+        <v>103</v>
+      </c>
+      <c r="G129" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H129" t="s">
+        <v>106</v>
+      </c>
+      <c r="J129" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>98</v>
+      </c>
+      <c r="B130" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C130" t="s">
+        <v>99</v>
+      </c>
+      <c r="D130" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" t="s">
+        <v>14</v>
+      </c>
+      <c r="F130" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="G130" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="H130" t="s">
+        <v>107</v>
+      </c>
+      <c r="J130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>98</v>
+      </c>
+      <c r="B131" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C131" t="s">
+        <v>99</v>
+      </c>
+      <c r="D131" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" t="s">
+        <v>14</v>
+      </c>
+      <c r="F131" t="s">
+        <v>33</v>
+      </c>
+      <c r="G131" t="s">
+        <v>16</v>
+      </c>
+      <c r="H131" t="s">
+        <v>108</v>
+      </c>
+      <c r="J131" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>98</v>
+      </c>
+      <c r="B132" t="s">
+        <v>10</v>
+      </c>
+      <c r="C132" t="s">
+        <v>99</v>
+      </c>
+      <c r="D132" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" t="s">
+        <v>14</v>
+      </c>
+      <c r="F132" t="s">
+        <v>76</v>
+      </c>
+      <c r="G132" t="s">
+        <v>16</v>
+      </c>
+      <c r="H132" t="s">
+        <v>108</v>
+      </c>
+      <c r="J132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>98</v>
+      </c>
+      <c r="B133" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" t="s">
+        <v>99</v>
+      </c>
+      <c r="D133" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" t="s">
+        <v>14</v>
+      </c>
+      <c r="F133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G133" t="s">
+        <v>16</v>
+      </c>
+      <c r="H133" t="s">
+        <v>105</v>
+      </c>
+      <c r="J133" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>136</v>
+      </c>
+      <c r="B134" t="s">
+        <v>132</v>
+      </c>
+      <c r="C134" t="s">
+        <v>133</v>
+      </c>
+      <c r="D134" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" t="s">
+        <v>14</v>
+      </c>
+      <c r="F134" t="s">
+        <v>134</v>
+      </c>
+      <c r="G134" t="s">
+        <v>124</v>
+      </c>
+      <c r="H134" t="s">
+        <v>137</v>
+      </c>
+      <c r="J134" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135" t="s">
+        <v>132</v>
+      </c>
+      <c r="C135" t="s">
+        <v>133</v>
+      </c>
+      <c r="D135" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" t="s">
+        <v>14</v>
+      </c>
+      <c r="F135" t="s">
+        <v>135</v>
+      </c>
+      <c r="G135" t="s">
+        <v>124</v>
+      </c>
+      <c r="H135" t="s">
+        <v>137</v>
+      </c>
+      <c r="J135" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" t="s">
+        <v>132</v>
+      </c>
+      <c r="C136" t="s">
+        <v>133</v>
+      </c>
+      <c r="D136" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" t="s">
+        <v>14</v>
+      </c>
+      <c r="F136" t="s">
+        <v>134</v>
+      </c>
+      <c r="G136" t="s">
+        <v>124</v>
+      </c>
+      <c r="H136" t="s">
+        <v>138</v>
+      </c>
+      <c r="J136" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>132</v>
+      </c>
+      <c r="C137" t="s">
+        <v>133</v>
+      </c>
+      <c r="D137" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" t="s">
+        <v>14</v>
+      </c>
+      <c r="F137" t="s">
+        <v>135</v>
+      </c>
+      <c r="G137" t="s">
+        <v>124</v>
+      </c>
+      <c r="H137" t="s">
+        <v>138</v>
+      </c>
+      <c r="J137" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" t="s">
+        <v>140</v>
+      </c>
+      <c r="C138" t="s">
+        <v>141</v>
+      </c>
+      <c r="D138" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" t="s">
+        <v>14</v>
+      </c>
+      <c r="F138" t="s">
+        <v>134</v>
+      </c>
+      <c r="G138" t="s">
+        <v>124</v>
+      </c>
+      <c r="H138" t="s">
+        <v>145</v>
+      </c>
+      <c r="J138" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>136</v>
+      </c>
+      <c r="B139" t="s">
+        <v>140</v>
+      </c>
+      <c r="C139" t="s">
+        <v>141</v>
+      </c>
+      <c r="D139" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" t="s">
+        <v>14</v>
+      </c>
+      <c r="F139" t="s">
+        <v>135</v>
+      </c>
+      <c r="G139" t="s">
+        <v>124</v>
+      </c>
+      <c r="H139" t="s">
+        <v>145</v>
+      </c>
+      <c r="J139" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>136</v>
+      </c>
+      <c r="B140" t="s">
+        <v>146</v>
+      </c>
+      <c r="C140" t="s">
+        <v>147</v>
+      </c>
+      <c r="D140" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" t="s">
+        <v>14</v>
+      </c>
+      <c r="F140" t="s">
+        <v>134</v>
+      </c>
+      <c r="G140" t="s">
+        <v>124</v>
+      </c>
+      <c r="H140" t="s">
+        <v>24</v>
+      </c>
+      <c r="J140" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>136</v>
+      </c>
+      <c r="B141" t="s">
+        <v>146</v>
+      </c>
+      <c r="C141" t="s">
+        <v>147</v>
+      </c>
+      <c r="D141" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" t="s">
+        <v>14</v>
+      </c>
+      <c r="F141" t="s">
+        <v>135</v>
+      </c>
+      <c r="G141" t="s">
+        <v>124</v>
+      </c>
+      <c r="H141" t="s">
+        <v>24</v>
+      </c>
+      <c r="J141" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>136</v>
+      </c>
+      <c r="B142" t="s">
+        <v>148</v>
+      </c>
+      <c r="C142" t="s">
+        <v>141</v>
+      </c>
+      <c r="D142" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" t="s">
+        <v>14</v>
+      </c>
+      <c r="F142" t="s">
+        <v>134</v>
+      </c>
+      <c r="G142" t="s">
+        <v>124</v>
+      </c>
+      <c r="H142" t="s">
+        <v>27</v>
+      </c>
+      <c r="J142" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>136</v>
+      </c>
+      <c r="B143" t="s">
+        <v>148</v>
+      </c>
+      <c r="C143" t="s">
+        <v>141</v>
+      </c>
+      <c r="D143" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" t="s">
+        <v>14</v>
+      </c>
+      <c r="F143" t="s">
+        <v>135</v>
+      </c>
+      <c r="G143" t="s">
+        <v>124</v>
+      </c>
+      <c r="H143" t="s">
+        <v>27</v>
+      </c>
+      <c r="J143" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>214</v>
+      </c>
+      <c r="B144" t="s">
+        <v>215</v>
+      </c>
+      <c r="C144" t="s">
+        <v>182</v>
+      </c>
+      <c r="D144" t="s">
+        <v>183</v>
+      </c>
+      <c r="E144" t="s">
+        <v>14</v>
+      </c>
+      <c r="F144" t="s">
+        <v>57</v>
+      </c>
+      <c r="G144" t="s">
+        <v>216</v>
+      </c>
+      <c r="H144" t="s">
+        <v>217</v>
+      </c>
+      <c r="J144" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>206</v>
+      </c>
+      <c r="B145" t="s">
+        <v>206</v>
+      </c>
+      <c r="C145" t="s">
+        <v>182</v>
+      </c>
+      <c r="D145" t="s">
+        <v>183</v>
+      </c>
+      <c r="E145" t="s">
+        <v>14</v>
+      </c>
+      <c r="F145" t="s">
+        <v>184</v>
+      </c>
+      <c r="G145" t="s">
+        <v>95</v>
+      </c>
+      <c r="J145" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>21</v>
+      </c>
+      <c r="B146" t="s">
+        <v>22</v>
+      </c>
+      <c r="C146" t="s">
+        <v>23</v>
+      </c>
+      <c r="D146" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" t="s">
+        <v>14</v>
+      </c>
+      <c r="F146" t="s">
+        <v>15</v>
+      </c>
+      <c r="G146" t="s">
+        <v>16</v>
+      </c>
+      <c r="H146" t="s">
+        <v>24</v>
+      </c>
+      <c r="J146" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>21</v>
+      </c>
+      <c r="B147" t="s">
         <v>25</v>
       </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C147" t="s">
+        <v>26</v>
+      </c>
+      <c r="D147" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" t="s">
+        <v>14</v>
+      </c>
+      <c r="F147" t="s">
+        <v>15</v>
+      </c>
+      <c r="G147" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="H147" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>24</v>
+      <c r="J147" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J9" xr:uid="{EAF16D4A-DA29-4FF0-AC3B-589258931E62}"/>
+  <autoFilter ref="A1:J147" xr:uid="{A090B303-E5A5-440F-8977-F555609CC44A}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J147">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transportadoramovc-my.sharepoint.com/personal/camilla_rio_motz_com_br/Documents/Documents/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PamelaSilvaTeixeira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F491E60-C656-4813-891D-1542DE83645F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D9E989-B6B4-4810-9BCA-7DB56618D5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E5C93A47-8C6F-4362-A297-19B613721B24}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F9C8F682-8F69-48C0-A164-B472E5744D19}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$132</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="242">
   <si>
     <t>Origem</t>
   </si>
@@ -77,540 +77,687 @@
     <t>Sobral - CE</t>
   </si>
   <si>
+    <t>Granel</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Rodotrem</t>
+  </si>
+  <si>
+    <t>Caçamba</t>
+  </si>
+  <si>
+    <t>REPOM</t>
+  </si>
+  <si>
+    <t>Xambioá - TO</t>
+  </si>
+  <si>
+    <t>Urbano Santos - MA</t>
+  </si>
+  <si>
+    <t>Calcário</t>
+  </si>
+  <si>
+    <t>200,00</t>
+  </si>
+  <si>
+    <t>Santa Filomena - PI</t>
+  </si>
+  <si>
+    <t>calcário</t>
+  </si>
+  <si>
+    <t>175,00</t>
+  </si>
+  <si>
+    <t>Cajati - SP</t>
+  </si>
+  <si>
+    <t>Rio Branco do Sul - PR</t>
+  </si>
+  <si>
+    <t>Gesso</t>
+  </si>
+  <si>
+    <t>74,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM</t>
+  </si>
+  <si>
+    <t>Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>77,00</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>Itapeva - SP</t>
+  </si>
+  <si>
+    <t>Ipaussu - SP</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
+  </si>
+  <si>
+    <t>75,00</t>
+  </si>
+  <si>
+    <t>Laranjeiras - SE</t>
+  </si>
+  <si>
+    <t>Paulista - PE</t>
+  </si>
+  <si>
+    <t>Clinquer</t>
+  </si>
+  <si>
+    <t>185,00</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Joinville - SC</t>
+  </si>
+  <si>
+    <t>Cascavel - PR</t>
+  </si>
+  <si>
+    <t>Tubos e Conexões</t>
+  </si>
+  <si>
+    <t>Outro</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Vanderléia</t>
+  </si>
+  <si>
+    <t>Sider</t>
+  </si>
+  <si>
+    <t>Jucurutu - RN</t>
+  </si>
+  <si>
+    <t>Pitimbu - PB</t>
+  </si>
+  <si>
+    <t>Minério de Ferro</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>110,00</t>
+  </si>
+  <si>
+    <t>Baraúna - RN</t>
+  </si>
+  <si>
+    <t>Pacatuba - SE</t>
+  </si>
+  <si>
+    <t>Clínquer</t>
+  </si>
+  <si>
+    <t>Carreta LS, Vanderléia</t>
+  </si>
+  <si>
+    <t>240,00</t>
+  </si>
+  <si>
+    <t>Nossa Senhora do Socorro - SE</t>
+  </si>
+  <si>
+    <t>8.902,06</t>
+  </si>
+  <si>
+    <t>230,00</t>
+  </si>
+  <si>
+    <t>São João da Barra - RJ</t>
+  </si>
+  <si>
+    <t>Edealina - GO</t>
+  </si>
+  <si>
+    <t>coque</t>
+  </si>
+  <si>
+    <t>17.625,00</t>
+  </si>
+  <si>
+    <t>PAGBEM</t>
+  </si>
+  <si>
+    <t>Itaguaí - RJ</t>
+  </si>
+  <si>
+    <t>Votorantim - SP</t>
+  </si>
+  <si>
+    <t>Escória</t>
+  </si>
+  <si>
+    <t>107,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO REPOM /</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>130,00</t>
+  </si>
+  <si>
+    <t>Salto de Pirapora - SP</t>
+  </si>
+  <si>
+    <t>Brasília - DF</t>
+  </si>
+  <si>
+    <t>325,00</t>
+  </si>
+  <si>
+    <t>295,00</t>
+  </si>
+  <si>
+    <t>Duque de Caxias - RJ</t>
+  </si>
+  <si>
+    <t>Cantagalo - RJ</t>
+  </si>
+  <si>
+    <t>106,00</t>
+  </si>
+  <si>
+    <t>Itaú de Minas - MG</t>
+  </si>
+  <si>
+    <t>260,00</t>
+  </si>
+  <si>
+    <t>Castro - PR</t>
+  </si>
+  <si>
+    <t>Cajamar - SP</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>4.600,00</t>
+  </si>
+  <si>
+    <t>Ouricuri - PE</t>
+  </si>
+  <si>
+    <t>gesso</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Rodotrem</t>
+  </si>
+  <si>
+    <t>Grade Baixa</t>
+  </si>
+  <si>
+    <t>142,00</t>
+  </si>
+  <si>
+    <t>162,00</t>
+  </si>
+  <si>
+    <t>Trindade - PE</t>
+  </si>
+  <si>
+    <t>Gpisita</t>
+  </si>
+  <si>
+    <t>180,00</t>
+  </si>
+  <si>
+    <t>Vanderléia</t>
+  </si>
+  <si>
+    <t>Carreta LS</t>
+  </si>
+  <si>
+    <t>Carreta</t>
+  </si>
+  <si>
+    <t>Carreta toco 5 eixos</t>
+  </si>
+  <si>
+    <t>5.188,21</t>
+  </si>
+  <si>
+    <t>4.745,60</t>
+  </si>
+  <si>
+    <t>6.520,95</t>
+  </si>
+  <si>
+    <t>5.716,37</t>
+  </si>
+  <si>
+    <t>Belém - PA</t>
+  </si>
+  <si>
+    <t>Primavera - PA</t>
+  </si>
+  <si>
+    <t>Carvão</t>
+  </si>
+  <si>
+    <t>3.400,00</t>
+  </si>
+  <si>
+    <t>Pagbem</t>
+  </si>
+  <si>
+    <t>Barcarena - PA</t>
+  </si>
+  <si>
+    <t>Carvão Mineral</t>
+  </si>
+  <si>
+    <t>3.840,00</t>
+  </si>
+  <si>
+    <t>Nobres - MT</t>
+  </si>
+  <si>
+    <t>Porto Velho - RO</t>
+  </si>
+  <si>
+    <t>Graneleiro, Caçamba</t>
+  </si>
+  <si>
+    <t>320,00</t>
+  </si>
+  <si>
+    <t>repom</t>
+  </si>
+  <si>
+    <t>PAGBEM/REPOM</t>
+  </si>
+  <si>
+    <t>Vanderléia, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos, Rodotrem</t>
+  </si>
+  <si>
+    <t>Unaí - MG</t>
+  </si>
+  <si>
+    <t>Bonfinópolis de Minas - MG</t>
+  </si>
+  <si>
+    <t>Araguari - MG</t>
+  </si>
+  <si>
+    <t>SORGO</t>
+  </si>
+  <si>
+    <t>165,00</t>
+  </si>
+  <si>
+    <t>Patos de Minas - MG</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>135,00</t>
+  </si>
+  <si>
+    <t>Janaúba - MG</t>
+  </si>
+  <si>
+    <t>Milho</t>
+  </si>
+  <si>
+    <t>Montes Claros - MG</t>
+  </si>
+  <si>
+    <t>Borda da Mata - MG</t>
+  </si>
+  <si>
+    <t>115,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO REPOM</t>
+  </si>
+  <si>
+    <t>Grajaú - MA</t>
+  </si>
+  <si>
+    <t>Cabeceiras - GO</t>
+  </si>
+  <si>
+    <t>Sorgo</t>
+  </si>
+  <si>
+    <t>150,00</t>
+  </si>
+  <si>
+    <t>Barro Alto - GO</t>
+  </si>
+  <si>
+    <t>BAUXITA</t>
+  </si>
+  <si>
+    <t>12.700,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM</t>
+  </si>
+  <si>
+    <t>Cuiabá - MT</t>
+  </si>
+  <si>
+    <t>9.930,00</t>
+  </si>
+  <si>
+    <t>17.750,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM / Só vamos carregar se aceitar carregar com os 5% (a partir de 48,5 )</t>
+  </si>
+  <si>
+    <t>Paracatu - MG</t>
+  </si>
+  <si>
+    <t>125,00</t>
+  </si>
+  <si>
+    <t>Goiânia - GO</t>
+  </si>
+  <si>
+    <t>CIMENTO</t>
+  </si>
+  <si>
+    <t>Pallet</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM</t>
+  </si>
+  <si>
+    <t>Anápolis - GO</t>
+  </si>
+  <si>
+    <t>Alfenas - MG</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Cubatão - SP</t>
+  </si>
+  <si>
+    <t>Truck</t>
+  </si>
+  <si>
+    <t>São José dos Campos - SP</t>
+  </si>
+  <si>
+    <t>Barueri - SP</t>
+  </si>
+  <si>
+    <t>Imperatriz - MA</t>
+  </si>
+  <si>
+    <t>Truck, Carreta LS</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Arame/MA, Buriticupu/MA, Carolina/MA, Cidelândia/MA, Estreito/MA, Formosa da Serra/MA, Grajaú/MA, Imperatriz/MA, Itinga do Maranhão /MA, Porto Franco/MA, Riachão/MA, São Pedro da Água Branca /MA, São Pedro dos Crentes/MA, Vila Nova dos Martírios/MA</t>
+  </si>
+  <si>
+    <t>Luís Eduardo Magalhães - BA</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: Cocos/BA, Serra Dourada/BA, São Félix do Coribe/BA, Tabocas do Brejo Velho/BA, Correntina/BA, Mansidão/BA, Formosa do Rio Preto/BA, Santa Rita de Cassia/BA, Barreiras/BA e Morpará/BA</t>
+  </si>
+  <si>
+    <t>Crateús - CE</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI. - POSSIVEIS DESTINOS DISPONIVEIS - Mombaça/CE, Poranga/CE, Pedra Branca/CE, Tauá/CE, Nova Russas/CE, Independência/CE e Tamboril/CE</t>
+  </si>
+  <si>
+    <t>Truck, Bitruck</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possiveis Destinos Disponiveis: Araruama/RJ, Campos dos Goytacazes/RJ, Itaperuna/RJ, Saquarema//RJ, Serra/ES</t>
+  </si>
+  <si>
+    <t>Volta Redonda - RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Paraty/RJ, Resende/RJ e Volta Redonda/RJ</t>
+  </si>
+  <si>
+    <t>São Gonçalo - RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Armação dos Búzios/RJ, Arraial do Cabo/RJ, Cabo Frio/RJ, Campos dos Goytacazes/RJ, Guapimirim/RJ, Itaboraí/RJ, Magé/RJ, Maricá/RJ, Niterói/RJ e São Gonçalo/RJ</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro - RJ</t>
+  </si>
+  <si>
+    <t>CIMENTO ENSACADO</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD SANTA CRUZ - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Duque de Caxias/RJ, Nova Iguaçu/RJ, Paraty/RJ, Petrópolis/RJ, Queimados/RJ e Rio de Janeiro/RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD PARADA DE LUCAS - Possiveis Destinos Disponiveis Duque de Caxias/RJ, Mangaratiba/RJ, Mesquita/RJ, Nova Iguaçu/RJ, Petrópolis/RJ e Rio de Janeiro/RJ</t>
+  </si>
+  <si>
+    <t>Vidal Ramos - SC</t>
+  </si>
+  <si>
+    <t>Blumenau - SC</t>
+  </si>
+  <si>
+    <t>Grade Baixa, Prancha</t>
+  </si>
+  <si>
+    <t>53,50</t>
+  </si>
+  <si>
+    <t>Buri - SP</t>
+  </si>
+  <si>
+    <t>116,00</t>
+  </si>
+  <si>
+    <t>120,00</t>
+  </si>
+  <si>
+    <t>Embu das Artes - SP</t>
+  </si>
+  <si>
+    <t>105,00</t>
+  </si>
+  <si>
+    <t>113,00</t>
+  </si>
+  <si>
+    <t>117,00</t>
+  </si>
+  <si>
+    <t>Regente Feijó - SP</t>
+  </si>
+  <si>
+    <t>Graneleiro, Sider</t>
+  </si>
+  <si>
+    <t>160,00</t>
+  </si>
+  <si>
+    <t>168,00</t>
+  </si>
+  <si>
+    <t>Ourinhos - SP</t>
+  </si>
+  <si>
+    <t>Graneleiro, Grade Baixa</t>
+  </si>
+  <si>
+    <t>129,00</t>
+  </si>
+  <si>
+    <t>134,00</t>
+  </si>
+  <si>
+    <t>Teresina - PI</t>
+  </si>
+  <si>
+    <t>Graneleiro, Grade Baixa, Prancha</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>DESTINOS DISPONIVEIS: No Extremo Sul do Estado do PI - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Campinas - SP</t>
+  </si>
+  <si>
+    <t>Bragança Paulista - SP</t>
+  </si>
+  <si>
+    <t>Toco, Truck, Bitruck</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI- VEICULOS TOCO APENAS 10 TON</t>
+  </si>
+  <si>
+    <t>Serra Negra - SP</t>
+  </si>
+  <si>
+    <t>Jundiaí - SP</t>
+  </si>
+  <si>
+    <t>Diadema - SP</t>
+  </si>
+  <si>
+    <t>Guarulhos - SP</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
+  </si>
+  <si>
+    <t>Saco</t>
+  </si>
+  <si>
+    <t>Petrolina - PE</t>
+  </si>
+  <si>
+    <t>Caruaru - PE</t>
+  </si>
+  <si>
+    <t>Truck, Bitruck, Carreta</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM / PEDÁGIO INCLUSO NO FRETE</t>
+  </si>
+  <si>
+    <t>Bitruck, Carreta LS</t>
+  </si>
+  <si>
+    <t>Corumbá - MS</t>
+  </si>
+  <si>
+    <t>Truck, Carreta</t>
+  </si>
+  <si>
+    <t>RODOTREM (48 Ton)</t>
+  </si>
+  <si>
+    <t>Feira de Santana - BA</t>
+  </si>
+  <si>
+    <t>Carreta, Bitrem 7 eixos, Rodotrem</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
+  </si>
+  <si>
+    <t>Itabuna - BA</t>
+  </si>
+  <si>
+    <t>Vitória da Conquista - BA</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER 07 PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>Goianira - GO</t>
+  </si>
+  <si>
+    <t>385,00</t>
+  </si>
+  <si>
+    <t>Acreúna - GO</t>
+  </si>
+  <si>
+    <t>Aparecida de Goiânia - GO</t>
+  </si>
+  <si>
+    <t>CARGA FRACIONADA (3 A 5 entregas) COM VAGA PARA FICAR FIXO NA UNIDADE COM DESTINOS AS REGIÕES DE: Anápolis/GO, Heitoraí/GO, Inhumas/GO, Itaberaí/GO, Jaraguá/GO e Leopoldo de Bulhões/GO - PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
     <t>São Luís - MA</t>
   </si>
   <si>
-    <t>Escória</t>
-  </si>
-  <si>
-    <t>Granel</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Rodotrem</t>
-  </si>
-  <si>
-    <t>Caçamba</t>
-  </si>
-  <si>
     <t>190,00</t>
   </si>
   <si>
-    <t>REPOM</t>
-  </si>
-  <si>
     <t>São Gonçalo do Amarante - CE</t>
   </si>
   <si>
     <t>só aceita rodocaçambas com lona fácil. Caso não tenham, o veículo não passa na vistoria dos guardas</t>
   </si>
   <si>
-    <t>Xambioá - TO</t>
-  </si>
-  <si>
-    <t>Urbano Santos - MA</t>
-  </si>
-  <si>
-    <t>Calcário</t>
-  </si>
-  <si>
-    <t>200,00</t>
-  </si>
-  <si>
-    <t>Santa Filomena - PI</t>
-  </si>
-  <si>
-    <t>calcário</t>
-  </si>
-  <si>
-    <t>175,00</t>
-  </si>
-  <si>
-    <t>Cajati - SP</t>
-  </si>
-  <si>
-    <t>Rio Branco do Sul - PR</t>
-  </si>
-  <si>
-    <t>Gesso</t>
-  </si>
-  <si>
-    <t>74,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO PAGBEM</t>
-  </si>
-  <si>
-    <t>Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>77,00</t>
-  </si>
-  <si>
-    <t>Carreta, Carreta LS, Bitrem 7 eixos</t>
-  </si>
-  <si>
-    <t>Itapeva - SP</t>
-  </si>
-  <si>
-    <t>Ipaussu - SP</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
-  </si>
-  <si>
-    <t>75,00</t>
-  </si>
-  <si>
-    <t>Laranjeiras - SE</t>
-  </si>
-  <si>
-    <t>Paulista - PE</t>
-  </si>
-  <si>
-    <t>Clinquer</t>
-  </si>
-  <si>
-    <t>185,00</t>
-  </si>
-  <si>
-    <t>Joinville - SC</t>
-  </si>
-  <si>
-    <t>Cascavel - PR</t>
-  </si>
-  <si>
-    <t>Tubos e Conexões</t>
-  </si>
-  <si>
-    <t>Outro</t>
-  </si>
-  <si>
-    <t>Truck</t>
-  </si>
-  <si>
-    <t>Sider</t>
-  </si>
-  <si>
-    <t>3.500,00</t>
-  </si>
-  <si>
-    <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>Carreta, Carreta LS, Vanderléia</t>
-  </si>
-  <si>
-    <t>4.800,00</t>
-  </si>
-  <si>
-    <t>Jucurutu - RN</t>
-  </si>
-  <si>
-    <t>Pitimbu - PB</t>
-  </si>
-  <si>
-    <t>Minério de Ferro</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>110,00</t>
-  </si>
-  <si>
-    <t>Baraúna - RN</t>
-  </si>
-  <si>
-    <t>Pacatuba - SE</t>
-  </si>
-  <si>
-    <t>Clínquer</t>
-  </si>
-  <si>
-    <t>Carreta LS, Vanderléia</t>
-  </si>
-  <si>
-    <t>240,00</t>
-  </si>
-  <si>
-    <t>Nossa Senhora do Socorro - SE</t>
-  </si>
-  <si>
-    <t>8.902,06</t>
-  </si>
-  <si>
-    <t>230,00</t>
-  </si>
-  <si>
-    <t>São João da Barra - RJ</t>
-  </si>
-  <si>
-    <t>Edealina - GO</t>
-  </si>
-  <si>
-    <t>coque</t>
-  </si>
-  <si>
-    <t>17.625,00</t>
-  </si>
-  <si>
-    <t>PAGBEM</t>
-  </si>
-  <si>
-    <t>Itaguaí - RJ</t>
-  </si>
-  <si>
-    <t>Votorantim - SP</t>
-  </si>
-  <si>
-    <t>107,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO REPOM /</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos</t>
-  </si>
-  <si>
-    <t>130,00</t>
-  </si>
-  <si>
-    <t>Salto de Pirapora - SP</t>
-  </si>
-  <si>
-    <t>Brasília - DF</t>
-  </si>
-  <si>
-    <t>325,00</t>
-  </si>
-  <si>
-    <t>295,00</t>
-  </si>
-  <si>
-    <t>Duque de Caxias - RJ</t>
-  </si>
-  <si>
-    <t>Cantagalo - RJ</t>
-  </si>
-  <si>
-    <t>106,00</t>
-  </si>
-  <si>
-    <t>Itaú de Minas - MG</t>
-  </si>
-  <si>
-    <t>260,00</t>
+    <t>Rio Claro - SP</t>
+  </si>
+  <si>
+    <t>5.700,00</t>
+  </si>
+  <si>
+    <t>5.500,00</t>
   </si>
   <si>
     <t>231,00</t>
   </si>
   <si>
-    <t>Castro - PR</t>
-  </si>
-  <si>
-    <t>Cajamar - SP</t>
-  </si>
-  <si>
-    <t>Carreta, Carreta LS, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>4.600,00</t>
-  </si>
-  <si>
-    <t>Ouricuri - PE</t>
-  </si>
-  <si>
-    <t>gesso</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Rodotrem</t>
-  </si>
-  <si>
-    <t>Grade Baixa</t>
-  </si>
-  <si>
-    <t>142,00</t>
-  </si>
-  <si>
-    <t>162,00</t>
-  </si>
-  <si>
-    <t>Trindade - PE</t>
-  </si>
-  <si>
-    <t>Gpisita</t>
-  </si>
-  <si>
-    <t>180,00</t>
-  </si>
-  <si>
-    <t>Vanderléia</t>
-  </si>
-  <si>
-    <t>Carreta LS</t>
-  </si>
-  <si>
-    <t>Carreta</t>
-  </si>
-  <si>
-    <t>Carreta toco 5 eixos</t>
-  </si>
-  <si>
-    <t>5.188,21</t>
-  </si>
-  <si>
-    <t>4.745,60</t>
-  </si>
-  <si>
-    <t>6.520,95</t>
-  </si>
-  <si>
-    <t>5.716,37</t>
-  </si>
-  <si>
-    <t>Belém - PA</t>
-  </si>
-  <si>
-    <t>Primavera - PA</t>
-  </si>
-  <si>
-    <t>Carvão</t>
-  </si>
-  <si>
-    <t>3.400,00</t>
-  </si>
-  <si>
-    <t>Pagbem</t>
-  </si>
-  <si>
-    <t>Barcarena - PA</t>
-  </si>
-  <si>
-    <t>Carvão Mineral</t>
-  </si>
-  <si>
-    <t>3.840,00</t>
-  </si>
-  <si>
-    <t>Aripuanã - MT</t>
-  </si>
-  <si>
-    <t>Juiz de Fora - MG</t>
-  </si>
-  <si>
-    <t>MINERIO</t>
-  </si>
-  <si>
-    <t>650,00</t>
-  </si>
-  <si>
-    <t>PASSAR NA GR,SIRENE DE RÉ,LONA FACIL,TECNIL,INCINOMETRO</t>
-  </si>
-  <si>
-    <t>Nobres - MT</t>
-  </si>
-  <si>
-    <t>Porto Velho - RO</t>
-  </si>
-  <si>
-    <t>Graneleiro, Caçamba</t>
-  </si>
-  <si>
-    <t>320,00</t>
-  </si>
-  <si>
-    <t>repom</t>
-  </si>
-  <si>
-    <t>Campo Grande - MS</t>
-  </si>
-  <si>
-    <t>pneu picado</t>
-  </si>
-  <si>
-    <t>305,00</t>
-  </si>
-  <si>
-    <t>PAGBEM/REPOM</t>
-  </si>
-  <si>
-    <t>Chapada Gaúcha - MG</t>
-  </si>
-  <si>
-    <t>Uberaba - MG</t>
-  </si>
-  <si>
-    <t>SOJA</t>
-  </si>
-  <si>
-    <t>Vanderléia, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>Carreta LS, Bitrem 7 eixos, Rodotrem</t>
-  </si>
-  <si>
-    <t>Unaí - MG</t>
-  </si>
-  <si>
-    <t>170,00</t>
-  </si>
-  <si>
-    <t>140,00</t>
-  </si>
-  <si>
-    <t>Bonfinópolis de Minas - MG</t>
-  </si>
-  <si>
-    <t>Araguari - MG</t>
-  </si>
-  <si>
-    <t>SORGO</t>
-  </si>
-  <si>
-    <t>165,00</t>
-  </si>
-  <si>
-    <t>Patos de Minas - MG</t>
-  </si>
-  <si>
-    <t>100,00</t>
-  </si>
-  <si>
-    <t>135,00</t>
-  </si>
-  <si>
-    <t>Janaúba - MG</t>
-  </si>
-  <si>
-    <t>Milho</t>
-  </si>
-  <si>
-    <t>Montes Claros - MG</t>
-  </si>
-  <si>
-    <t>Borda da Mata - MG</t>
-  </si>
-  <si>
-    <t>115,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO REPOM</t>
-  </si>
-  <si>
-    <t>Grajaú - MA</t>
-  </si>
-  <si>
-    <t>Goianira - GO</t>
-  </si>
-  <si>
-    <t>385,00</t>
-  </si>
-  <si>
-    <t>Acreúna - GO</t>
-  </si>
-  <si>
-    <t>Cabeceiras - GO</t>
-  </si>
-  <si>
-    <t>Sorgo</t>
-  </si>
-  <si>
-    <t>150,00</t>
-  </si>
-  <si>
-    <t>Barro Alto - GO</t>
-  </si>
-  <si>
-    <t>BAUXITA</t>
-  </si>
-  <si>
-    <t>12.700,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM</t>
-  </si>
-  <si>
-    <t>Cuiabá - MT</t>
-  </si>
-  <si>
-    <t>9.930,00</t>
-  </si>
-  <si>
-    <t>17.750,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM / Só vamos carregar se aceitar carregar com os 5% (a partir de 48,5 )</t>
-  </si>
-  <si>
-    <t>Paracatu - MG</t>
-  </si>
-  <si>
-    <t>125,00</t>
-  </si>
-  <si>
-    <t>Paranaguá - PR</t>
-  </si>
-  <si>
-    <t>Lençóis Paulista - SP</t>
-  </si>
-  <si>
-    <t>Fertilizantes</t>
-  </si>
-  <si>
-    <t>Graneleiro</t>
-  </si>
-  <si>
-    <t>Volumes em Bigbag</t>
-  </si>
-  <si>
-    <t>Tatuí - SP</t>
-  </si>
-  <si>
-    <t>Angatuba - SP</t>
-  </si>
-  <si>
-    <t>Cajuru - SP</t>
-  </si>
-  <si>
-    <t>Volumes em Bigbag / 40 Ton</t>
-  </si>
-  <si>
-    <t>Frutal - MG</t>
-  </si>
-  <si>
-    <t>Borebi - SP</t>
-  </si>
-  <si>
-    <t>Pardinho - SP</t>
-  </si>
-  <si>
     <t>Pinheiro Machado - RS</t>
   </si>
   <si>
-    <t>CIMENTO</t>
-  </si>
-  <si>
-    <t>Pallet</t>
-  </si>
-  <si>
-    <t>Truck, Bitruck</t>
-  </si>
-  <si>
     <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI.</t>
   </si>
   <si>
-    <t>Aparecida de Goiânia - GO</t>
-  </si>
-  <si>
     <t>Leopoldo de Bulhões - GO</t>
   </si>
   <si>
-    <t>CARGA FRACIONADA (3 A 5 entregas) COM VAGA PARA FICAR FIXO NA UNIDADE COM DESTINOS AS REGIÕES DE: Anápolis/GO, Heitoraí/GO, Inhumas/GO, Itaberaí/GO, Jaraguá/GO e Leopoldo de Bulhões/GO - PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
     <t>Jaraguá - GO</t>
   </si>
   <si>
@@ -621,241 +768,13 @@
   </si>
   <si>
     <t>Heitoraí - GO</t>
-  </si>
-  <si>
-    <t>Anápolis - GO</t>
-  </si>
-  <si>
-    <t>Goiânia - GO</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM</t>
-  </si>
-  <si>
-    <t>Alfenas - MG</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Cubatão - SP</t>
-  </si>
-  <si>
-    <t>São José dos Campos - SP</t>
-  </si>
-  <si>
-    <t>Barueri - SP</t>
-  </si>
-  <si>
-    <t>Luís Eduardo Magalhães - BA</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: Cocos/BA, Serra Dourada/BA, São Félix do Coribe/BA, Tabocas do Brejo Velho/BA, Correntina/BA, Mansidão/BA, Formosa do Rio Preto/BA, Santa Rita de Cassia/BA, Barreiras/BA e Morpará/BA</t>
-  </si>
-  <si>
-    <t>Crateús - CE</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI. - POSSIVEIS DESTINOS DISPONIVEIS - Mombaça/CE, Poranga/CE, Pedra Branca/CE, Tauá/CE, Nova Russas/CE, Independência/CE e Tamboril/CE</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possiveis Destinos Disponiveis: Araruama/RJ, Campos dos Goytacazes/RJ, Itaperuna/RJ, Saquarema//RJ, Serra/ES</t>
-  </si>
-  <si>
-    <t>Volta Redonda - RJ</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Paraty/RJ, Resende/RJ e Volta Redonda/RJ</t>
-  </si>
-  <si>
-    <t>São Gonçalo - RJ</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Armação dos Búzios/RJ, Arraial do Cabo/RJ, Cabo Frio/RJ, Campos dos Goytacazes/RJ, Guapimirim/RJ, Itaboraí/RJ, Magé/RJ, Maricá/RJ, Niterói/RJ e São Gonçalo/RJ</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro - RJ</t>
-  </si>
-  <si>
-    <t>CIMENTO ENSACADO</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD SANTA CRUZ - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Duque de Caxias/RJ, Nova Iguaçu/RJ, Paraty/RJ, Petrópolis/RJ, Queimados/RJ e Rio de Janeiro/RJ</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD PARADA DE LUCAS - Possiveis Destinos Disponiveis Duque de Caxias/RJ, Mangaratiba/RJ, Mesquita/RJ, Nova Iguaçu/RJ, Petrópolis/RJ e Rio de Janeiro/RJ</t>
-  </si>
-  <si>
-    <t>Vidal Ramos - SC</t>
-  </si>
-  <si>
-    <t>Blumenau - SC</t>
-  </si>
-  <si>
-    <t>Grade Baixa, Prancha</t>
-  </si>
-  <si>
-    <t>53,50</t>
-  </si>
-  <si>
-    <t>Buri - SP</t>
-  </si>
-  <si>
-    <t>116,00</t>
-  </si>
-  <si>
-    <t>120,00</t>
-  </si>
-  <si>
-    <t>Embu das Artes - SP</t>
-  </si>
-  <si>
-    <t>105,00</t>
-  </si>
-  <si>
-    <t>113,00</t>
-  </si>
-  <si>
-    <t>117,00</t>
-  </si>
-  <si>
-    <t>Regente Feijó - SP</t>
-  </si>
-  <si>
-    <t>Graneleiro, Sider</t>
-  </si>
-  <si>
-    <t>160,00</t>
-  </si>
-  <si>
-    <t>168,00</t>
-  </si>
-  <si>
-    <t>Ourinhos - SP</t>
-  </si>
-  <si>
-    <t>Graneleiro, Grade Baixa</t>
-  </si>
-  <si>
-    <t>129,00</t>
-  </si>
-  <si>
-    <t>134,00</t>
-  </si>
-  <si>
-    <t>Teresina - PI</t>
-  </si>
-  <si>
-    <t>Truck, Carreta LS</t>
-  </si>
-  <si>
-    <t>Graneleiro, Grade Baixa, Prancha</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>DESTINOS DISPONIVEIS: No Extremo Sul do Estado do PI - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Campinas - SP</t>
-  </si>
-  <si>
-    <t>Bragança Paulista - SP</t>
-  </si>
-  <si>
-    <t>Toco, Truck, Bitruck</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI- VEICULOS TOCO APENAS 10 TON</t>
-  </si>
-  <si>
-    <t>Serra Negra - SP</t>
-  </si>
-  <si>
-    <t>Jundiaí - SP</t>
-  </si>
-  <si>
-    <t>Diadema - SP</t>
-  </si>
-  <si>
-    <t>Guarulhos - SP</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
-  </si>
-  <si>
-    <t>Saco</t>
-  </si>
-  <si>
-    <t>Petrolina - PE</t>
-  </si>
-  <si>
-    <t>Caruaru - PE</t>
-  </si>
-  <si>
-    <t>Truck, Bitruck, Carreta</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM / PEDÁGIO INCLUSO NO FRETE</t>
-  </si>
-  <si>
-    <t>Bitruck, Carreta LS</t>
-  </si>
-  <si>
-    <t>Corumbá - MS</t>
-  </si>
-  <si>
-    <t>Truck, Carreta</t>
-  </si>
-  <si>
-    <t>RODOTREM (48 Ton)</t>
-  </si>
-  <si>
-    <t>Feira de Santana - BA</t>
-  </si>
-  <si>
-    <t>Carreta, Bitrem 7 eixos, Rodotrem</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
-  </si>
-  <si>
-    <t>Itabuna - BA</t>
-  </si>
-  <si>
-    <t>Vitória da Conquista - BA</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER 07 PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Carreta LS, Bitrem 7 eixos</t>
-  </si>
-  <si>
-    <t>Tubo</t>
-  </si>
-  <si>
-    <t>Querência - MT</t>
-  </si>
-  <si>
-    <t>São Simão - GO</t>
-  </si>
-  <si>
-    <t>Soja</t>
-  </si>
-  <si>
-    <t>Bitrem 9 eixos, Rodotrem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -870,11 +789,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -900,17 +814,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{B8ECB8C7-189A-4853-8704-7C158215864E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1241,15 +1153,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A090B303-E5A5-440F-8977-F555609CC44A}">
-  <dimension ref="A1:J147"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0629895-8555-4DE5-8A98-86473C65DDE6}">
+  <dimension ref="A1:J132"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="29.1796875" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="31.7265625" customWidth="1"/>
-    <col min="7" max="7" width="20.7265625" customWidth="1"/>
-    <col min="10" max="10" width="229.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="255.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1286,4070 +1203,3655 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>227</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>134</v>
-      </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>154</v>
+        <v>228</v>
       </c>
       <c r="J2" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>135</v>
-      </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>154</v>
+        <v>228</v>
       </c>
       <c r="J3" t="s">
-        <v>130</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
       </c>
       <c r="J4" t="s">
-        <v>188</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>188</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>186</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
       </c>
       <c r="J7" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="C8" t="s">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>183</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>95</v>
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>232</v>
       </c>
       <c r="J8" t="s">
-        <v>188</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>186</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>95</v>
+        <v>45</v>
+      </c>
+      <c r="H9" t="s">
+        <v>232</v>
       </c>
       <c r="J9" t="s">
-        <v>188</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="J10" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="J11" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
         <v>13</v>
       </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
         <v>38</v>
       </c>
-      <c r="G12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" t="s">
-        <v>63</v>
-      </c>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="J13" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" t="s">
+        <v>233</v>
+      </c>
+      <c r="J14" t="s">
         <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="J15" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>159</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
         <v>13</v>
       </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>162</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>163</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>164</v>
+        <v>55</v>
+      </c>
+      <c r="J17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>159</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="J18" t="s">
-        <v>166</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>182</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="G19" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H19" t="s">
+        <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>197</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
         <v>13</v>
       </c>
-      <c r="E20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="J20" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
         <v>13</v>
       </c>
-      <c r="E21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" t="s">
-        <v>135</v>
-      </c>
       <c r="G21" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="J21" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
         <v>13</v>
       </c>
-      <c r="E22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" t="s">
-        <v>134</v>
-      </c>
       <c r="G22" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>142</v>
+        <v>67</v>
+      </c>
+      <c r="I22">
+        <v>28000</v>
       </c>
       <c r="J22" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="G23" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>142</v>
+        <v>70</v>
+      </c>
+      <c r="I23">
+        <v>28000</v>
       </c>
       <c r="J23" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
         <v>13</v>
       </c>
-      <c r="E24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" t="s">
-        <v>134</v>
-      </c>
       <c r="G24" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>142</v>
+        <v>67</v>
+      </c>
+      <c r="I24">
+        <v>28000</v>
       </c>
       <c r="J24" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>168</v>
+        <v>70</v>
+      </c>
+      <c r="I25">
+        <v>28000</v>
+      </c>
+      <c r="J25" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>182</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H26" t="s">
+        <v>73</v>
       </c>
       <c r="J26" t="s">
-        <v>195</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>193</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>182</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H27" t="s">
+        <v>74</v>
       </c>
       <c r="J27" t="s">
-        <v>195</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>156</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="G29" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
         <v>13</v>
       </c>
-      <c r="E30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" t="s">
-        <v>15</v>
-      </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>234</v>
       </c>
       <c r="J30" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="J31" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>239</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>240</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H33" t="s">
+        <v>89</v>
+      </c>
+      <c r="I33">
+        <v>52</v>
       </c>
       <c r="J33" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>241</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H34" t="s">
+        <v>92</v>
       </c>
       <c r="J34" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="B35" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>241</v>
+        <v>28</v>
       </c>
       <c r="G35" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H35" t="s">
+        <v>92</v>
       </c>
       <c r="J35" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>239</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>241</v>
+        <v>69</v>
       </c>
       <c r="G36" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>92</v>
       </c>
       <c r="J36" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F37" t="s">
+        <v>93</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J37" t="s">
         <v>15</v>
-      </c>
-      <c r="G37" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" t="s">
-        <v>129</v>
-      </c>
-      <c r="J37" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>184</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H38" t="s">
+        <v>92</v>
       </c>
       <c r="J38" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s">
-        <v>250</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>251</v>
+        <v>95</v>
       </c>
       <c r="G39" t="s">
-        <v>216</v>
+        <v>14</v>
+      </c>
+      <c r="H39" t="s">
+        <v>92</v>
       </c>
       <c r="J39" t="s">
-        <v>237</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="G41" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="J41" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
         <v>13</v>
       </c>
-      <c r="E42" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" t="s">
-        <v>135</v>
-      </c>
       <c r="G42" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="J42" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>254</v>
+        <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>254</v>
+        <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>248</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G43" t="s">
-        <v>230</v>
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>100</v>
       </c>
       <c r="J43" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>254</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>254</v>
+        <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>248</v>
+        <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G44" t="s">
-        <v>230</v>
+        <v>14</v>
+      </c>
+      <c r="H44" t="s">
+        <v>100</v>
       </c>
       <c r="J44" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>254</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="D45" t="s">
-        <v>248</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>255</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s">
-        <v>230</v>
+        <v>14</v>
+      </c>
+      <c r="H45" t="s">
+        <v>97</v>
       </c>
       <c r="J45" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>203</v>
+        <v>102</v>
       </c>
       <c r="C46" t="s">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>104</v>
       </c>
       <c r="J46" t="s">
-        <v>204</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>198</v>
+        <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>198</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s">
-        <v>182</v>
+        <v>107</v>
       </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="G47" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H47" t="s">
+        <v>108</v>
       </c>
       <c r="J47" t="s">
-        <v>197</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="B48" t="s">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="C48" t="s">
-        <v>182</v>
+        <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>248</v>
+        <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>230</v>
+        <v>111</v>
+      </c>
+      <c r="H48" t="s">
+        <v>112</v>
       </c>
       <c r="J48" t="s">
-        <v>252</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B49" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="C49" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="D49" t="s">
-        <v>248</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>253</v>
+        <v>116</v>
       </c>
       <c r="G49" t="s">
-        <v>230</v>
+        <v>111</v>
+      </c>
+      <c r="H49" t="s">
+        <v>121</v>
       </c>
       <c r="J49" t="s">
-        <v>252</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>245</v>
+        <v>118</v>
       </c>
       <c r="B50" t="s">
-        <v>245</v>
+        <v>119</v>
       </c>
       <c r="C50" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>241</v>
+        <v>115</v>
       </c>
       <c r="G50" t="s">
-        <v>95</v>
+        <v>111</v>
+      </c>
+      <c r="H50" t="s">
+        <v>121</v>
       </c>
       <c r="J50" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="H51" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="J51" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="B52" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="D52" t="s">
-        <v>248</v>
+        <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>258</v>
+        <v>116</v>
       </c>
       <c r="G52" t="s">
-        <v>216</v>
+        <v>111</v>
+      </c>
+      <c r="H52" t="s">
+        <v>123</v>
       </c>
       <c r="J52" t="s">
-        <v>259</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="H53" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="J53" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="H54" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="J54" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="D55" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="H55" t="s">
-        <v>63</v>
-      </c>
-      <c r="I55">
-        <v>49</v>
+        <v>19</v>
+      </c>
+      <c r="J55" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>117</v>
       </c>
       <c r="B56" t="s">
-        <v>246</v>
+        <v>125</v>
       </c>
       <c r="C56" t="s">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="D56" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>241</v>
+        <v>116</v>
       </c>
       <c r="G56" t="s">
-        <v>216</v>
+        <v>111</v>
+      </c>
+      <c r="H56" t="s">
+        <v>19</v>
       </c>
       <c r="J56" t="s">
-        <v>247</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>260</v>
+        <v>118</v>
       </c>
       <c r="B57" t="s">
-        <v>261</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="G57" t="s">
-        <v>216</v>
+        <v>111</v>
+      </c>
+      <c r="H57" t="s">
+        <v>121</v>
       </c>
       <c r="J57" t="s">
-        <v>262</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>260</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>260</v>
+        <v>127</v>
       </c>
       <c r="C58" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="G58" t="s">
-        <v>216</v>
+        <v>111</v>
+      </c>
+      <c r="H58" t="s">
+        <v>121</v>
       </c>
       <c r="J58" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>260</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>260</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="D59" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>255</v>
+        <v>115</v>
       </c>
       <c r="G59" t="s">
-        <v>216</v>
+        <v>111</v>
+      </c>
+      <c r="H59" t="s">
+        <v>22</v>
       </c>
       <c r="J59" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="D60" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="G60" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="H60" t="s">
-        <v>74</v>
-      </c>
-      <c r="I60">
-        <v>28000</v>
+        <v>22</v>
       </c>
       <c r="J60" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="G61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H61" t="s">
-        <v>77</v>
-      </c>
-      <c r="I61">
-        <v>28000</v>
+        <v>129</v>
       </c>
       <c r="J61" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="G62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H62" t="s">
-        <v>74</v>
-      </c>
-      <c r="I62">
-        <v>28000</v>
+        <v>121</v>
       </c>
       <c r="J62" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C63" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D63" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" t="s">
         <v>13</v>
       </c>
-      <c r="E63" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" t="s">
-        <v>76</v>
-      </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H63" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="I63">
-        <v>28000</v>
-      </c>
-      <c r="J63" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>36</v>
+        <v>222</v>
       </c>
       <c r="B64" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="D64" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="G64" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H64" t="s">
-        <v>39</v>
+        <v>223</v>
       </c>
       <c r="J64" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="B65" t="s">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F65" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="G65" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H65" t="s">
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="J65" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>224</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C66" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F66" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="G66" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="J66" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>224</v>
       </c>
       <c r="B67" t="s">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="C67" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="D67" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F67" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="G67" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="H67" t="s">
+        <v>223</v>
       </c>
       <c r="J67" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="D68" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F68" t="s">
-        <v>48</v>
+        <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="H68" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="J68" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="D69" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F69" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="G69" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="H69" t="s">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="J69" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="D70" t="s">
-        <v>264</v>
+        <v>11</v>
       </c>
       <c r="E70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F70" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="G70" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H70" t="s">
-        <v>50</v>
-      </c>
-      <c r="I70">
-        <v>10</v>
+        <v>137</v>
+      </c>
+      <c r="J70" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="B71" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" t="s">
         <v>13</v>
       </c>
-      <c r="E71" t="s">
-        <v>14</v>
-      </c>
-      <c r="F71" t="s">
-        <v>57</v>
-      </c>
       <c r="G71" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H71" t="s">
-        <v>58</v>
-      </c>
-      <c r="J71" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="B72" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C72" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
         <v>13</v>
       </c>
-      <c r="E72" t="s">
-        <v>14</v>
-      </c>
-      <c r="F72" t="s">
-        <v>15</v>
-      </c>
       <c r="G72" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H72" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="J72" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="C73" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" t="s">
         <v>13</v>
       </c>
-      <c r="E73" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" t="s">
-        <v>15</v>
-      </c>
       <c r="G73" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H73" t="s">
-        <v>43</v>
-      </c>
-      <c r="J73" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>40</v>
+        <v>235</v>
       </c>
       <c r="B74" t="s">
-        <v>41</v>
+        <v>235</v>
       </c>
       <c r="C74" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="D74" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E74" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="G74" t="s">
-        <v>16</v>
-      </c>
-      <c r="H74" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="J74" t="s">
-        <v>18</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="B75" t="s">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="C75" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D75" t="s">
-        <v>248</v>
+        <v>147</v>
       </c>
       <c r="E75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="G75" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J75" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="B76" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="C76" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D76" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F76" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="G76" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J76" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="B77" t="s">
-        <v>123</v>
+        <v>239</v>
       </c>
       <c r="C77" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="D77" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E77" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G77" t="s">
-        <v>124</v>
-      </c>
-      <c r="H77" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="J77" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="B78" t="s">
-        <v>122</v>
+        <v>240</v>
       </c>
       <c r="C78" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D78" t="s">
-        <v>248</v>
+        <v>147</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F78" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G78" t="s">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="J78" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>225</v>
       </c>
       <c r="B79" t="s">
-        <v>41</v>
+        <v>241</v>
       </c>
       <c r="C79" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="D79" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F79" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G79" t="s">
-        <v>95</v>
-      </c>
-      <c r="H79" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="J79" t="s">
-        <v>18</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>92</v>
+        <v>225</v>
       </c>
       <c r="B80" t="s">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="C80" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="D80" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G80" t="s">
-        <v>16</v>
-      </c>
-      <c r="H80" t="s">
-        <v>97</v>
-      </c>
-      <c r="I80">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="J80" t="s">
-        <v>18</v>
+        <v>226</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C81" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D81" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="G81" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="J81" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="C82" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D82" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F82" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="G82" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="J82" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="B83" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="C83" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="G83" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="J83" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B84" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D84" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F84" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="G84" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="J84" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="B85" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="C85" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D85" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F85" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="G85" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="J85" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="C86" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D86" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E86" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F86" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="G86" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="J86" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B87" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C87" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F87" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="G87" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="J87" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B88" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C88" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D88" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F88" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="G88" t="s">
-        <v>124</v>
-      </c>
-      <c r="H88" t="s">
-        <v>144</v>
+        <v>87</v>
       </c>
       <c r="J88" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B89" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C89" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D89" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F89" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G89" t="s">
-        <v>124</v>
-      </c>
-      <c r="H89" t="s">
-        <v>144</v>
+        <v>87</v>
       </c>
       <c r="J89" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>249</v>
+        <v>76</v>
       </c>
       <c r="B90" t="s">
-        <v>249</v>
+        <v>76</v>
       </c>
       <c r="C90" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D90" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E90" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>241</v>
+        <v>163</v>
       </c>
       <c r="G90" t="s">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="J90" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="C91" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D91" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E91" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F91" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="G91" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J91" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>265</v>
+        <v>167</v>
       </c>
       <c r="B92" t="s">
-        <v>266</v>
+        <v>167</v>
       </c>
       <c r="C92" t="s">
-        <v>267</v>
+        <v>146</v>
       </c>
       <c r="D92" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E92" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F92" t="s">
-        <v>268</v>
+        <v>163</v>
       </c>
       <c r="G92" t="s">
-        <v>124</v>
+        <v>87</v>
+      </c>
+      <c r="J92" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="B93" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="C93" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D93" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="G93" t="s">
-        <v>95</v>
-      </c>
-      <c r="H93" t="s">
-        <v>219</v>
+        <v>87</v>
       </c>
       <c r="J93" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="B94" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="C94" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D94" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="G94" t="s">
-        <v>95</v>
-      </c>
-      <c r="H94" t="s">
-        <v>220</v>
+        <v>87</v>
       </c>
       <c r="J94" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="B95" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="C95" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D95" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F95" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G95" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="H95" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="J95" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B96" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="C96" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D96" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E96" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F96" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G96" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H96" t="s">
-        <v>223</v>
+        <v>178</v>
       </c>
       <c r="J96" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B97" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="C97" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D97" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E97" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F97" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G97" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H97" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="J97" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B98" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="C98" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D98" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E98" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G98" t="s">
-        <v>226</v>
+        <v>87</v>
       </c>
       <c r="H98" t="s">
-        <v>227</v>
+        <v>181</v>
+      </c>
+      <c r="J98" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B99" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="C99" t="s">
+        <v>146</v>
+      </c>
+      <c r="D99" t="s">
+        <v>147</v>
+      </c>
+      <c r="E99" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" t="s">
+        <v>28</v>
+      </c>
+      <c r="G99" t="s">
+        <v>87</v>
+      </c>
+      <c r="H99" t="s">
         <v>182</v>
       </c>
-      <c r="D99" t="s">
-        <v>183</v>
-      </c>
-      <c r="E99" t="s">
-        <v>14</v>
-      </c>
-      <c r="F99" t="s">
-        <v>15</v>
-      </c>
-      <c r="G99" t="s">
-        <v>216</v>
-      </c>
-      <c r="H99" t="s">
-        <v>227</v>
+      <c r="J99" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B100" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="C100" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D100" t="s">
+        <v>147</v>
+      </c>
+      <c r="E100" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" t="s">
+        <v>69</v>
+      </c>
+      <c r="G100" t="s">
+        <v>87</v>
+      </c>
+      <c r="H100" t="s">
         <v>183</v>
       </c>
-      <c r="E100" t="s">
-        <v>14</v>
-      </c>
-      <c r="F100" t="s">
-        <v>33</v>
-      </c>
-      <c r="G100" t="s">
-        <v>226</v>
-      </c>
-      <c r="H100" t="s">
-        <v>97</v>
+      <c r="J100" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B101" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="C101" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D101" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E101" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F101" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="H101" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B102" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="C102" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D102" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F102" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="H102" t="s">
-        <v>228</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B103" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="C103" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D103" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F103" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G103" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="H103" t="s">
-        <v>228</v>
+        <v>89</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B104" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="C104" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D104" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E104" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F104" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G104" t="s">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="H104" t="s">
-        <v>220</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B105" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="C105" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D105" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E105" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F105" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="G105" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="H105" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B106" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="C106" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D106" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E106" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F106" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G106" t="s">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="H106" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>210</v>
+        <v>24</v>
       </c>
       <c r="B107" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="C107" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="D107" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E107" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F107" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="G107" t="s">
-        <v>95</v>
-      </c>
-      <c r="J107" t="s">
-        <v>212</v>
+        <v>189</v>
+      </c>
+      <c r="H107" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>210</v>
+        <v>24</v>
       </c>
       <c r="B108" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="C108" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D108" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E108" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F108" t="s">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>95</v>
-      </c>
-      <c r="J108" t="s">
-        <v>213</v>
+        <v>189</v>
+      </c>
+      <c r="H108" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="B109" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="C109" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D109" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E109" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F109" t="s">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="G109" t="s">
-        <v>95</v>
-      </c>
-      <c r="J109" t="s">
-        <v>209</v>
+        <v>189</v>
+      </c>
+      <c r="H109" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="B110" t="s">
-        <v>11</v>
+        <v>192</v>
       </c>
       <c r="C110" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="D110" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E110" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F110" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="G110" t="s">
-        <v>16</v>
-      </c>
-      <c r="H110" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="J110" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
       <c r="B111" t="s">
-        <v>68</v>
+        <v>192</v>
       </c>
       <c r="C111" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="D111" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E111" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F111" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="G111" t="s">
-        <v>16</v>
-      </c>
-      <c r="H111" t="s">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="J111" t="s">
-        <v>71</v>
+        <v>195</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
       <c r="B112" t="s">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="C112" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="D112" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E112" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F112" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="G112" t="s">
-        <v>16</v>
-      </c>
-      <c r="H112" t="s">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="J112" t="s">
-        <v>71</v>
+        <v>196</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="B113" t="s">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="C113" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F113" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="G113" t="s">
-        <v>16</v>
-      </c>
-      <c r="H113" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J113" t="s">
-        <v>71</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="B114" t="s">
-        <v>85</v>
+        <v>201</v>
       </c>
       <c r="C114" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="D114" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E114" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F114" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
       <c r="G114" t="s">
-        <v>16</v>
-      </c>
-      <c r="H114" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J114" t="s">
-        <v>71</v>
+        <v>200</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="B115" t="s">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="C115" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="D115" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E115" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F115" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="G115" t="s">
-        <v>16</v>
-      </c>
-      <c r="H115" t="s">
         <v>87</v>
       </c>
       <c r="J115" t="s">
-        <v>71</v>
+        <v>200</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
+        <v>197</v>
+      </c>
+      <c r="B116" t="s">
+        <v>197</v>
+      </c>
+      <c r="C116" t="s">
+        <v>146</v>
+      </c>
+      <c r="D116" t="s">
+        <v>147</v>
+      </c>
+      <c r="E116" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" t="s">
         <v>199</v>
       </c>
-      <c r="B116" t="s">
-        <v>199</v>
-      </c>
-      <c r="C116" t="s">
-        <v>182</v>
-      </c>
-      <c r="D116" t="s">
-        <v>183</v>
-      </c>
-      <c r="E116" t="s">
-        <v>14</v>
-      </c>
-      <c r="F116" t="s">
-        <v>48</v>
-      </c>
       <c r="G116" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J116" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>10</v>
+        <v>203</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>203</v>
       </c>
       <c r="C117" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="D117" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E117" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F117" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="G117" t="s">
-        <v>16</v>
-      </c>
-      <c r="H117" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="J117" t="s">
-        <v>18</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="B118" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="C118" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D118" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E118" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F118" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="G118" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="J118" t="s">
-        <v>256</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>233</v>
+        <v>35</v>
       </c>
       <c r="B119" t="s">
-        <v>233</v>
+        <v>35</v>
       </c>
       <c r="C119" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D119" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="E119" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F119" t="s">
-        <v>234</v>
+        <v>30</v>
       </c>
       <c r="G119" t="s">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="J119" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B120" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="C120" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D120" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F120" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="G120" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="J120" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="B121" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="C121" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D121" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E121" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F121" t="s">
-        <v>94</v>
+        <v>209</v>
       </c>
       <c r="G121" t="s">
-        <v>235</v>
+        <v>175</v>
       </c>
       <c r="J121" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="C122" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D122" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="E122" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F122" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="G122" t="s">
-        <v>16</v>
-      </c>
-      <c r="H122" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="J122" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="B123" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="C123" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D123" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="E123" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F123" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="G123" t="s">
-        <v>16</v>
-      </c>
-      <c r="H123" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="J123" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B124" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="C124" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D124" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="E124" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F124" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G124" t="s">
-        <v>16</v>
-      </c>
-      <c r="H124" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="J124" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="B125" t="s">
-        <v>40</v>
+        <v>212</v>
       </c>
       <c r="C125" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D125" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="E125" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F125" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="G125" t="s">
-        <v>16</v>
-      </c>
-      <c r="H125" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="J125" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="B126" t="s">
-        <v>40</v>
+        <v>212</v>
       </c>
       <c r="C126" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D126" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="E126" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F126" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="G126" t="s">
-        <v>16</v>
-      </c>
-      <c r="H126" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="J126" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="B127" t="s">
-        <v>40</v>
+        <v>212</v>
       </c>
       <c r="C127" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D127" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="E127" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F127" t="s">
-        <v>103</v>
+        <v>213</v>
       </c>
       <c r="G127" t="s">
-        <v>16</v>
-      </c>
-      <c r="H127" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="J127" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="B128" t="s">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="C128" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D128" t="s">
+        <v>147</v>
+      </c>
+      <c r="E128" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" t="s">
         <v>13</v>
       </c>
-      <c r="E128" t="s">
-        <v>14</v>
-      </c>
-      <c r="F128" t="s">
-        <v>102</v>
-      </c>
       <c r="G128" t="s">
-        <v>16</v>
-      </c>
-      <c r="H128" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="J128" t="s">
-        <v>18</v>
+        <v>214</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>98</v>
+        <v>215</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>215</v>
       </c>
       <c r="C129" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D129" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="E129" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F129" t="s">
-        <v>103</v>
+        <v>216</v>
       </c>
       <c r="G129" t="s">
-        <v>16</v>
-      </c>
-      <c r="H129" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="J129" t="s">
-        <v>104</v>
+        <v>217</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="B130" t="s">
-        <v>10</v>
+        <v>219</v>
       </c>
       <c r="C130" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D130" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E130" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F130" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="G130" t="s">
-        <v>16</v>
-      </c>
-      <c r="H130" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="J130" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="B131" t="s">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="C131" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D131" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E131" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F131" t="s">
-        <v>33</v>
+        <v>221</v>
       </c>
       <c r="G131" t="s">
-        <v>16</v>
-      </c>
-      <c r="H131" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="J131" t="s">
-        <v>18</v>
+        <v>195</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="B132" t="s">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="C132" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D132" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E132" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F132" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="G132" t="s">
-        <v>16</v>
-      </c>
-      <c r="H132" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="J132" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>98</v>
-      </c>
-      <c r="B133" t="s">
-        <v>10</v>
-      </c>
-      <c r="C133" t="s">
-        <v>99</v>
-      </c>
-      <c r="D133" t="s">
-        <v>13</v>
-      </c>
-      <c r="E133" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" t="s">
-        <v>101</v>
-      </c>
-      <c r="G133" t="s">
-        <v>16</v>
-      </c>
-      <c r="H133" t="s">
-        <v>105</v>
-      </c>
-      <c r="J133" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>136</v>
-      </c>
-      <c r="B134" t="s">
-        <v>132</v>
-      </c>
-      <c r="C134" t="s">
-        <v>133</v>
-      </c>
-      <c r="D134" t="s">
-        <v>13</v>
-      </c>
-      <c r="E134" t="s">
-        <v>14</v>
-      </c>
-      <c r="F134" t="s">
-        <v>134</v>
-      </c>
-      <c r="G134" t="s">
-        <v>124</v>
-      </c>
-      <c r="H134" t="s">
-        <v>137</v>
-      </c>
-      <c r="J134" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>136</v>
-      </c>
-      <c r="B135" t="s">
-        <v>132</v>
-      </c>
-      <c r="C135" t="s">
-        <v>133</v>
-      </c>
-      <c r="D135" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" t="s">
-        <v>14</v>
-      </c>
-      <c r="F135" t="s">
-        <v>135</v>
-      </c>
-      <c r="G135" t="s">
-        <v>124</v>
-      </c>
-      <c r="H135" t="s">
-        <v>137</v>
-      </c>
-      <c r="J135" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>136</v>
-      </c>
-      <c r="B136" t="s">
-        <v>132</v>
-      </c>
-      <c r="C136" t="s">
-        <v>133</v>
-      </c>
-      <c r="D136" t="s">
-        <v>13</v>
-      </c>
-      <c r="E136" t="s">
-        <v>14</v>
-      </c>
-      <c r="F136" t="s">
-        <v>134</v>
-      </c>
-      <c r="G136" t="s">
-        <v>124</v>
-      </c>
-      <c r="H136" t="s">
-        <v>138</v>
-      </c>
-      <c r="J136" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>136</v>
-      </c>
-      <c r="B137" t="s">
-        <v>132</v>
-      </c>
-      <c r="C137" t="s">
-        <v>133</v>
-      </c>
-      <c r="D137" t="s">
-        <v>13</v>
-      </c>
-      <c r="E137" t="s">
-        <v>14</v>
-      </c>
-      <c r="F137" t="s">
-        <v>135</v>
-      </c>
-      <c r="G137" t="s">
-        <v>124</v>
-      </c>
-      <c r="H137" t="s">
-        <v>138</v>
-      </c>
-      <c r="J137" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>136</v>
-      </c>
-      <c r="B138" t="s">
-        <v>140</v>
-      </c>
-      <c r="C138" t="s">
-        <v>141</v>
-      </c>
-      <c r="D138" t="s">
-        <v>13</v>
-      </c>
-      <c r="E138" t="s">
-        <v>14</v>
-      </c>
-      <c r="F138" t="s">
-        <v>134</v>
-      </c>
-      <c r="G138" t="s">
-        <v>124</v>
-      </c>
-      <c r="H138" t="s">
-        <v>145</v>
-      </c>
-      <c r="J138" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>136</v>
-      </c>
-      <c r="B139" t="s">
-        <v>140</v>
-      </c>
-      <c r="C139" t="s">
-        <v>141</v>
-      </c>
-      <c r="D139" t="s">
-        <v>13</v>
-      </c>
-      <c r="E139" t="s">
-        <v>14</v>
-      </c>
-      <c r="F139" t="s">
-        <v>135</v>
-      </c>
-      <c r="G139" t="s">
-        <v>124</v>
-      </c>
-      <c r="H139" t="s">
-        <v>145</v>
-      </c>
-      <c r="J139" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>136</v>
-      </c>
-      <c r="B140" t="s">
-        <v>146</v>
-      </c>
-      <c r="C140" t="s">
-        <v>147</v>
-      </c>
-      <c r="D140" t="s">
-        <v>13</v>
-      </c>
-      <c r="E140" t="s">
-        <v>14</v>
-      </c>
-      <c r="F140" t="s">
-        <v>134</v>
-      </c>
-      <c r="G140" t="s">
-        <v>124</v>
-      </c>
-      <c r="H140" t="s">
-        <v>24</v>
-      </c>
-      <c r="J140" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>136</v>
-      </c>
-      <c r="B141" t="s">
-        <v>146</v>
-      </c>
-      <c r="C141" t="s">
-        <v>147</v>
-      </c>
-      <c r="D141" t="s">
-        <v>13</v>
-      </c>
-      <c r="E141" t="s">
-        <v>14</v>
-      </c>
-      <c r="F141" t="s">
-        <v>135</v>
-      </c>
-      <c r="G141" t="s">
-        <v>124</v>
-      </c>
-      <c r="H141" t="s">
-        <v>24</v>
-      </c>
-      <c r="J141" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>136</v>
-      </c>
-      <c r="B142" t="s">
-        <v>148</v>
-      </c>
-      <c r="C142" t="s">
-        <v>141</v>
-      </c>
-      <c r="D142" t="s">
-        <v>13</v>
-      </c>
-      <c r="E142" t="s">
-        <v>14</v>
-      </c>
-      <c r="F142" t="s">
-        <v>134</v>
-      </c>
-      <c r="G142" t="s">
-        <v>124</v>
-      </c>
-      <c r="H142" t="s">
-        <v>27</v>
-      </c>
-      <c r="J142" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>136</v>
-      </c>
-      <c r="B143" t="s">
-        <v>148</v>
-      </c>
-      <c r="C143" t="s">
-        <v>141</v>
-      </c>
-      <c r="D143" t="s">
-        <v>13</v>
-      </c>
-      <c r="E143" t="s">
-        <v>14</v>
-      </c>
-      <c r="F143" t="s">
-        <v>135</v>
-      </c>
-      <c r="G143" t="s">
-        <v>124</v>
-      </c>
-      <c r="H143" t="s">
-        <v>27</v>
-      </c>
-      <c r="J143" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>214</v>
-      </c>
-      <c r="B144" t="s">
-        <v>215</v>
-      </c>
-      <c r="C144" t="s">
-        <v>182</v>
-      </c>
-      <c r="D144" t="s">
-        <v>183</v>
-      </c>
-      <c r="E144" t="s">
-        <v>14</v>
-      </c>
-      <c r="F144" t="s">
-        <v>57</v>
-      </c>
-      <c r="G144" t="s">
-        <v>216</v>
-      </c>
-      <c r="H144" t="s">
-        <v>217</v>
-      </c>
-      <c r="J144" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>206</v>
-      </c>
-      <c r="B145" t="s">
-        <v>206</v>
-      </c>
-      <c r="C145" t="s">
-        <v>182</v>
-      </c>
-      <c r="D145" t="s">
-        <v>183</v>
-      </c>
-      <c r="E145" t="s">
-        <v>14</v>
-      </c>
-      <c r="F145" t="s">
-        <v>184</v>
-      </c>
-      <c r="G145" t="s">
-        <v>95</v>
-      </c>
-      <c r="J145" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>21</v>
-      </c>
-      <c r="B146" t="s">
-        <v>22</v>
-      </c>
-      <c r="C146" t="s">
-        <v>23</v>
-      </c>
-      <c r="D146" t="s">
-        <v>13</v>
-      </c>
-      <c r="E146" t="s">
-        <v>14</v>
-      </c>
-      <c r="F146" t="s">
-        <v>15</v>
-      </c>
-      <c r="G146" t="s">
-        <v>16</v>
-      </c>
-      <c r="H146" t="s">
-        <v>24</v>
-      </c>
-      <c r="J146" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>21</v>
-      </c>
-      <c r="B147" t="s">
-        <v>25</v>
-      </c>
-      <c r="C147" t="s">
-        <v>26</v>
-      </c>
-      <c r="D147" t="s">
-        <v>13</v>
-      </c>
-      <c r="E147" t="s">
-        <v>14</v>
-      </c>
-      <c r="F147" t="s">
-        <v>15</v>
-      </c>
-      <c r="G147" t="s">
-        <v>16</v>
-      </c>
-      <c r="H147" t="s">
-        <v>27</v>
-      </c>
-      <c r="J147" t="s">
-        <v>18</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J147" xr:uid="{A090B303-E5A5-440F-8977-F555609CC44A}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J147">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:J132" xr:uid="{E0629895-8555-4DE5-8A98-86473C65DDE6}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PamelaSilvaTeixeira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D9E989-B6B4-4810-9BCA-7DB56618D5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99634FBC-7984-4B33-B47B-37E51D138D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F9C8F682-8F69-48C0-A164-B472E5744D19}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="259">
   <si>
     <t>Origem</t>
   </si>
@@ -140,15 +140,9 @@
     <t>Itapeva - SP</t>
   </si>
   <si>
-    <t>Ipaussu - SP</t>
-  </si>
-  <si>
     <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
   </si>
   <si>
-    <t>75,00</t>
-  </si>
-  <si>
     <t>Laranjeiras - SE</t>
   </si>
   <si>
@@ -167,9 +161,6 @@
     <t>Joinville - SC</t>
   </si>
   <si>
-    <t>Cascavel - PR</t>
-  </si>
-  <si>
     <t>Tubos e Conexões</t>
   </si>
   <si>
@@ -353,24 +344,9 @@
     <t>Primavera - PA</t>
   </si>
   <si>
-    <t>Carvão</t>
-  </si>
-  <si>
-    <t>3.400,00</t>
-  </si>
-  <si>
-    <t>Pagbem</t>
-  </si>
-  <si>
     <t>Barcarena - PA</t>
   </si>
   <si>
-    <t>Carvão Mineral</t>
-  </si>
-  <si>
-    <t>3.840,00</t>
-  </si>
-  <si>
     <t>Nobres - MT</t>
   </si>
   <si>
@@ -380,12 +356,6 @@
     <t>Graneleiro, Caçamba</t>
   </si>
   <si>
-    <t>320,00</t>
-  </si>
-  <si>
-    <t>repom</t>
-  </si>
-  <si>
     <t>PAGBEM/REPOM</t>
   </si>
   <si>
@@ -410,12 +380,6 @@
     <t>165,00</t>
   </si>
   <si>
-    <t>Patos de Minas - MG</t>
-  </si>
-  <si>
-    <t>100,00</t>
-  </si>
-  <si>
     <t>135,00</t>
   </si>
   <si>
@@ -440,15 +404,6 @@
     <t>Grajaú - MA</t>
   </si>
   <si>
-    <t>Cabeceiras - GO</t>
-  </si>
-  <si>
-    <t>Sorgo</t>
-  </si>
-  <si>
-    <t>150,00</t>
-  </si>
-  <si>
     <t>Barro Alto - GO</t>
   </si>
   <si>
@@ -464,18 +419,6 @@
     <t>Cuiabá - MT</t>
   </si>
   <si>
-    <t>9.930,00</t>
-  </si>
-  <si>
-    <t>17.750,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM / Só vamos carregar se aceitar carregar com os 5% (a partir de 48,5 )</t>
-  </si>
-  <si>
-    <t>Paracatu - MG</t>
-  </si>
-  <si>
     <t>125,00</t>
   </si>
   <si>
@@ -686,39 +629,15 @@
     <t>Truck, Carreta</t>
   </si>
   <si>
-    <t>RODOTREM (48 Ton)</t>
-  </si>
-  <si>
     <t>Feira de Santana - BA</t>
   </si>
   <si>
-    <t>Carreta, Bitrem 7 eixos, Rodotrem</t>
-  </si>
-  <si>
     <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
   </si>
   <si>
     <t>Itabuna - BA</t>
   </si>
   <si>
-    <t>Vitória da Conquista - BA</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER 07 PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Carreta LS, Bitrem 7 eixos</t>
-  </si>
-  <si>
-    <t>Goianira - GO</t>
-  </si>
-  <si>
-    <t>385,00</t>
-  </si>
-  <si>
-    <t>Acreúna - GO</t>
-  </si>
-  <si>
     <t>Aparecida de Goiânia - GO</t>
   </si>
   <si>
@@ -743,9 +662,6 @@
     <t>5.700,00</t>
   </si>
   <si>
-    <t>5.500,00</t>
-  </si>
-  <si>
     <t>231,00</t>
   </si>
   <si>
@@ -768,6 +684,141 @@
   </si>
   <si>
     <t>Heitoraí - GO</t>
+  </si>
+  <si>
+    <t>Bento de Abreu - SP</t>
+  </si>
+  <si>
+    <t>140,00</t>
+  </si>
+  <si>
+    <t>Valparaíso - SP</t>
+  </si>
+  <si>
+    <t>Araçatuba - SP</t>
+  </si>
+  <si>
+    <t>Balsas - MA</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO REPOM / PAGBEM</t>
+  </si>
+  <si>
+    <t>CLINQUER</t>
+  </si>
+  <si>
+    <t>310,00</t>
+  </si>
+  <si>
+    <t>Confresa - MT</t>
+  </si>
+  <si>
+    <t>Colinas do Tocantins - TO</t>
+  </si>
+  <si>
+    <t>ARM AGRICOLA</t>
+  </si>
+  <si>
+    <t>Silo</t>
+  </si>
+  <si>
+    <t>PARA MOTORISTAS CATIVOS OU QUE DESEJAM FICAR NA REGIÃO. ROTAS COM DESTINO PARA OS ESTADOS DE GO OU MS</t>
+  </si>
+  <si>
+    <t>Pirenópolis - GO</t>
+  </si>
+  <si>
+    <t>Poços de Caldas - MG</t>
+  </si>
+  <si>
+    <t>Sider, Baú</t>
+  </si>
+  <si>
+    <t>50,00</t>
+  </si>
+  <si>
+    <t>clínquer</t>
+  </si>
+  <si>
+    <t>Ipiranga do Norte - MT</t>
+  </si>
+  <si>
+    <t>Rondonópolis - MT</t>
+  </si>
+  <si>
+    <t>Porto Alegre do Norte - MT</t>
+  </si>
+  <si>
+    <t>Água Azul do Norte - PA</t>
+  </si>
+  <si>
+    <t>Dom Aquino - MT</t>
+  </si>
+  <si>
+    <t>Primavera do Leste - MT</t>
+  </si>
+  <si>
+    <t>Sinop - MT</t>
+  </si>
+  <si>
+    <t>São Miguel do Araguaia - GO</t>
+  </si>
+  <si>
+    <t>Jussara - GO</t>
+  </si>
+  <si>
+    <t>Goianésia - GO</t>
+  </si>
+  <si>
+    <t>Tabaporã - MT</t>
+  </si>
+  <si>
+    <t>Itanhangá - MT</t>
+  </si>
+  <si>
+    <t>Nova Ubiratã - MT</t>
+  </si>
+  <si>
+    <t>Itaituba - PA</t>
+  </si>
+  <si>
+    <t>Sorriso - MT</t>
+  </si>
+  <si>
+    <t>Campos de Júlio - MT</t>
+  </si>
+  <si>
+    <t>Sapezal - MT</t>
+  </si>
+  <si>
+    <t>Nova Mutum - MT</t>
+  </si>
+  <si>
+    <t>Barra do Bugres - MT</t>
+  </si>
+  <si>
+    <t>Tangará da Serra - MT</t>
+  </si>
+  <si>
+    <t>Cocalinho - MT</t>
+  </si>
+  <si>
+    <t>Alto Garças - MT</t>
+  </si>
+  <si>
+    <t>Chapada dos Guimarães - MT</t>
+  </si>
+  <si>
+    <t>Pedra Preta - MT</t>
+  </si>
+  <si>
+    <t>Itiquira - MT</t>
+  </si>
+  <si>
+    <t>5.100,00</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI.</t>
   </si>
 </sst>
 </file>
@@ -1154,10 +1205,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0629895-8555-4DE5-8A98-86473C65DDE6}">
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6328125" bestFit="1" customWidth="1"/>
@@ -1203,13 +1254,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1224,7 +1275,7 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -1232,13 +1283,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>229</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1253,21 +1304,21 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>228</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>230</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1282,7 +1333,7 @@
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>215</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
@@ -1290,10 +1341,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -1311,7 +1362,7 @@
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -1319,13 +1370,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>217</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -1340,10 +1391,10 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -1363,13 +1414,13 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J7" t="s">
         <v>27</v>
@@ -1377,16 +1428,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -1395,53 +1446,53 @@
         <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>231</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1450,27 +1501,27 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J10" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1479,13 +1530,13 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
@@ -1493,28 +1544,28 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>205</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -1522,28 +1573,28 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>205</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
@@ -1551,57 +1602,57 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>233</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
         <v>47</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" t="s">
-        <v>50</v>
       </c>
       <c r="J15" t="s">
         <v>27</v>
@@ -1609,13 +1660,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1624,13 +1675,13 @@
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J16" t="s">
         <v>27</v>
@@ -1638,28 +1689,28 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
         <v>52</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
-        <v>55</v>
       </c>
       <c r="J17" t="s">
         <v>27</v>
@@ -1667,13 +1718,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1682,13 +1733,13 @@
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J18" t="s">
         <v>27</v>
@@ -1696,13 +1747,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1711,13 +1762,13 @@
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J19" t="s">
         <v>27</v>
@@ -1725,13 +1776,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1746,21 +1797,21 @@
         <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J20" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1775,30 +1826,33 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="I21">
+        <v>28000</v>
       </c>
       <c r="J21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
         <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1810,59 +1864,59 @@
         <v>28000</v>
       </c>
       <c r="J22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" t="s">
         <v>64</v>
-      </c>
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" t="s">
-        <v>70</v>
       </c>
       <c r="I23">
         <v>28000</v>
       </c>
       <c r="J23" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
         <v>66</v>
-      </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1874,18 +1928,18 @@
         <v>28000</v>
       </c>
       <c r="J24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1894,7 +1948,7 @@
         <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
@@ -1902,22 +1956,19 @@
       <c r="H25" t="s">
         <v>70</v>
       </c>
-      <c r="I25">
-        <v>28000</v>
-      </c>
       <c r="J25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -1926,27 +1977,27 @@
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -1955,7 +2006,7 @@
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
@@ -1964,47 +2015,47 @@
         <v>74</v>
       </c>
       <c r="J27" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
         <v>75</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" t="s">
         <v>76</v>
       </c>
-      <c r="C28" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" t="s">
-        <v>77</v>
-      </c>
       <c r="J28" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -2013,71 +2064,71 @@
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="J29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s">
         <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="H30" t="s">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="J30" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
@@ -2085,13 +2136,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2100,13 +2151,16 @@
         <v>12</v>
       </c>
       <c r="F32" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" t="s">
         <v>86</v>
       </c>
-      <c r="G32" t="s">
-        <v>87</v>
-      </c>
-      <c r="H32" t="s">
-        <v>88</v>
+      <c r="I32">
+        <v>52</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
@@ -2114,13 +2168,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2129,7 +2183,7 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
         <v>14</v>
@@ -2137,22 +2191,19 @@
       <c r="H33" t="s">
         <v>89</v>
       </c>
-      <c r="I33">
-        <v>52</v>
-      </c>
       <c r="J33" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -2161,13 +2212,13 @@
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
@@ -2175,13 +2226,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -2190,13 +2241,13 @@
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
@@ -2204,28 +2255,28 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
         <v>90</v>
       </c>
-      <c r="B36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" t="s">
-        <v>69</v>
-      </c>
       <c r="G36" t="s">
         <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
@@ -2233,28 +2284,28 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
         <v>91</v>
       </c>
-      <c r="D37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" t="s">
-        <v>93</v>
-      </c>
       <c r="G37" t="s">
         <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
@@ -2262,13 +2313,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -2277,56 +2328,56 @@
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G38" t="s">
         <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
         <v>91</v>
       </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s">
-        <v>95</v>
-      </c>
       <c r="G39" t="s">
         <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J39" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -2335,27 +2386,27 @@
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G40" t="s">
         <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J40" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2364,27 +2415,27 @@
         <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="G41" t="s">
         <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J41" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -2393,13 +2444,13 @@
         <v>12</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G42" t="s">
         <v>14</v>
       </c>
       <c r="H42" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J42" t="s">
         <v>15</v>
@@ -2407,13 +2458,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -2422,13 +2473,13 @@
         <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="G43" t="s">
         <v>14</v>
       </c>
       <c r="H43" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J43" t="s">
         <v>15</v>
@@ -2436,13 +2487,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -2451,13 +2502,13 @@
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s">
         <v>14</v>
       </c>
       <c r="H44" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J44" t="s">
         <v>15</v>
@@ -2465,42 +2516,42 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
         <v>90</v>
       </c>
-      <c r="B45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" t="s">
-        <v>93</v>
-      </c>
       <c r="G45" t="s">
         <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>97</v>
+        <v>230</v>
       </c>
       <c r="J45" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>231</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -2509,27 +2560,27 @@
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="G46" t="s">
         <v>14</v>
       </c>
       <c r="H46" t="s">
+        <v>230</v>
+      </c>
+      <c r="J46" t="s">
         <v>104</v>
-      </c>
-      <c r="J46" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>218</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -2544,21 +2595,21 @@
         <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="J47" t="s">
-        <v>105</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -2570,24 +2621,21 @@
         <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>112</v>
-      </c>
-      <c r="J48" t="s">
-        <v>113</v>
+        <v>221</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -2596,27 +2644,27 @@
         <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="G49" t="s">
+        <v>103</v>
+      </c>
+      <c r="H49" t="s">
         <v>111</v>
       </c>
-      <c r="H49" t="s">
-        <v>121</v>
-      </c>
       <c r="J49" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2625,27 +2673,27 @@
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G50" t="s">
+        <v>103</v>
+      </c>
+      <c r="H50" t="s">
         <v>111</v>
       </c>
-      <c r="H50" t="s">
-        <v>121</v>
-      </c>
       <c r="J50" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C51" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -2654,27 +2702,27 @@
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G51" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H51" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="J51" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B52" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2683,27 +2731,27 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="G52" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H52" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="J52" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B53" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -2712,27 +2760,27 @@
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G53" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H53" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="J53" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -2741,27 +2789,27 @@
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="G54" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H54" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="J54" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -2770,27 +2818,27 @@
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G55" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H55" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J55" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C56" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2799,85 +2847,85 @@
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="G56" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H56" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J56" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>91</v>
+      </c>
+      <c r="G57" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>117</v>
+      </c>
+      <c r="J57" t="s">
         <v>118</v>
-      </c>
-      <c r="B57" t="s">
-        <v>127</v>
-      </c>
-      <c r="C57" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" t="s">
-        <v>12</v>
-      </c>
-      <c r="F57" t="s">
-        <v>116</v>
-      </c>
-      <c r="G57" t="s">
-        <v>111</v>
-      </c>
-      <c r="H57" t="s">
-        <v>121</v>
-      </c>
-      <c r="J57" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E58" t="s">
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>121</v>
-      </c>
-      <c r="J58" t="s">
-        <v>114</v>
+        <v>52</v>
+      </c>
+      <c r="I58">
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="C59" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -2886,27 +2934,27 @@
         <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="G59" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="J59" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>202</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>200</v>
       </c>
       <c r="C60" t="s">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -2915,27 +2963,27 @@
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="H60" t="s">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="J60" t="s">
-        <v>114</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="B61" t="s">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="C61" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -2944,27 +2992,21 @@
         <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="G61" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" t="s">
-        <v>129</v>
-      </c>
-      <c r="J61" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>235</v>
       </c>
       <c r="C62" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -2973,56 +3015,44 @@
         <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="G62" t="s">
         <v>14</v>
-      </c>
-      <c r="H62" t="s">
-        <v>121</v>
-      </c>
-      <c r="J62" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="B63" t="s">
-        <v>101</v>
+        <v>237</v>
       </c>
       <c r="C63" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="D63" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E63" t="s">
         <v>12</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="G63" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" t="s">
-        <v>55</v>
-      </c>
-      <c r="I63">
-        <v>49</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>239</v>
       </c>
       <c r="C64" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -3031,28 +3061,22 @@
         <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="G64" t="s">
         <v>14</v>
       </c>
-      <c r="H64" t="s">
-        <v>223</v>
-      </c>
-      <c r="J64" t="s">
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65" t="s">
+        <v>240</v>
+      </c>
+      <c r="C65" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>222</v>
-      </c>
-      <c r="B65" t="s">
-        <v>59</v>
-      </c>
-      <c r="C65" t="s">
-        <v>120</v>
-      </c>
       <c r="D65" t="s">
         <v>11</v>
       </c>
@@ -3060,28 +3084,22 @@
         <v>12</v>
       </c>
       <c r="F65" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="G65" t="s">
         <v>14</v>
       </c>
-      <c r="H65" t="s">
-        <v>223</v>
-      </c>
-      <c r="J65" t="s">
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>238</v>
+      </c>
+      <c r="B66" t="s">
+        <v>241</v>
+      </c>
+      <c r="C66" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>224</v>
-      </c>
-      <c r="B66" t="s">
-        <v>59</v>
-      </c>
-      <c r="C66" t="s">
-        <v>120</v>
-      </c>
       <c r="D66" t="s">
         <v>11</v>
       </c>
@@ -3089,28 +3107,22 @@
         <v>12</v>
       </c>
       <c r="F66" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="G66" t="s">
         <v>14</v>
       </c>
-      <c r="H66" t="s">
-        <v>223</v>
-      </c>
-      <c r="J66" t="s">
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>242</v>
+      </c>
+      <c r="B67" t="s">
+        <v>238</v>
+      </c>
+      <c r="C67" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>224</v>
-      </c>
-      <c r="B67" t="s">
-        <v>59</v>
-      </c>
-      <c r="C67" t="s">
-        <v>120</v>
-      </c>
       <c r="D67" t="s">
         <v>11</v>
       </c>
@@ -3118,28 +3130,22 @@
         <v>12</v>
       </c>
       <c r="F67" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="G67" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" t="s">
-        <v>223</v>
-      </c>
-      <c r="J67" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>243</v>
+      </c>
+      <c r="B68" t="s">
+        <v>238</v>
+      </c>
+      <c r="C68" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>132</v>
-      </c>
-      <c r="B68" t="s">
-        <v>119</v>
-      </c>
-      <c r="C68" t="s">
-        <v>133</v>
-      </c>
       <c r="D68" t="s">
         <v>11</v>
       </c>
@@ -3147,28 +3153,22 @@
         <v>12</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G68" t="s">
-        <v>111</v>
-      </c>
-      <c r="H68" t="s">
-        <v>134</v>
-      </c>
-      <c r="J68" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>244</v>
+      </c>
+      <c r="B69" t="s">
+        <v>238</v>
+      </c>
+      <c r="C69" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>132</v>
-      </c>
-      <c r="B69" t="s">
-        <v>119</v>
-      </c>
-      <c r="C69" t="s">
-        <v>133</v>
-      </c>
       <c r="D69" t="s">
         <v>11</v>
       </c>
@@ -3176,28 +3176,22 @@
         <v>12</v>
       </c>
       <c r="F69" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="G69" t="s">
-        <v>111</v>
-      </c>
-      <c r="H69" t="s">
-        <v>134</v>
-      </c>
-      <c r="J69" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>244</v>
+      </c>
+      <c r="B70" t="s">
+        <v>245</v>
+      </c>
+      <c r="C70" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>135</v>
-      </c>
-      <c r="B70" t="s">
-        <v>65</v>
-      </c>
-      <c r="C70" t="s">
-        <v>136</v>
-      </c>
       <c r="D70" t="s">
         <v>11</v>
       </c>
@@ -3205,27 +3199,21 @@
         <v>12</v>
       </c>
       <c r="F70" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G70" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" t="s">
-        <v>137</v>
-      </c>
-      <c r="J70" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>246</v>
       </c>
       <c r="B71" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="C71" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -3234,24 +3222,21 @@
         <v>12</v>
       </c>
       <c r="F71" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G71" t="s">
         <v>14</v>
       </c>
-      <c r="H71" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>135</v>
+        <v>247</v>
       </c>
       <c r="B72" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="C72" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -3263,24 +3248,18 @@
         <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>14</v>
-      </c>
-      <c r="H72" t="s">
-        <v>141</v>
-      </c>
-      <c r="J72" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>248</v>
       </c>
       <c r="B73" t="s">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="C73" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -3292,730 +3271,685 @@
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>14</v>
-      </c>
-      <c r="H73" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B74" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C74" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D74" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E74" t="s">
         <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>163</v>
+        <v>13</v>
       </c>
       <c r="G74" t="s">
-        <v>87</v>
-      </c>
-      <c r="J74" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C75" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E75" t="s">
         <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="G75" t="s">
-        <v>87</v>
-      </c>
-      <c r="J75" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C76" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E76" t="s">
         <v>12</v>
       </c>
       <c r="F76" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="G76" t="s">
-        <v>87</v>
-      </c>
-      <c r="J76" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B77" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C77" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D77" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E77" t="s">
         <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="G77" t="s">
-        <v>87</v>
-      </c>
-      <c r="J77" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B78" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="C78" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E78" t="s">
         <v>12</v>
       </c>
       <c r="F78" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>87</v>
-      </c>
-      <c r="J78" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B79" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="C79" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D79" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E79" t="s">
         <v>12</v>
       </c>
       <c r="F79" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="G79" t="s">
-        <v>87</v>
-      </c>
-      <c r="J79" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B80" t="s">
-        <v>149</v>
+        <v>256</v>
       </c>
       <c r="C80" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D80" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E80" t="s">
         <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="G80" t="s">
-        <v>87</v>
-      </c>
-      <c r="J80" t="s">
-        <v>226</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>72</v>
+        <v>249</v>
       </c>
       <c r="B81" t="s">
-        <v>145</v>
+        <v>233</v>
       </c>
       <c r="C81" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D81" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E81" t="s">
         <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="G81" t="s">
-        <v>87</v>
-      </c>
-      <c r="J81" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="B82" t="s">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D82" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E82" t="s">
         <v>12</v>
       </c>
       <c r="F82" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>87</v>
-      </c>
-      <c r="J82" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="B83" t="s">
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="C83" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D83" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="E83" t="s">
         <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="J83" t="s">
-        <v>151</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D84" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E84" t="s">
         <v>12</v>
       </c>
       <c r="F84" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="G84" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J84" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="B85" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="C85" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D85" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E85" t="s">
         <v>12</v>
       </c>
       <c r="F85" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="G85" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="J85" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="C86" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D86" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E86" t="s">
         <v>12</v>
       </c>
       <c r="F86" t="s">
-        <v>69</v>
+        <v>180</v>
       </c>
       <c r="G86" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J86" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="B87" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="C87" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D87" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E87" t="s">
         <v>12</v>
       </c>
       <c r="F87" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="G87" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J87" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="B88" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="C88" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D88" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E88" t="s">
         <v>12</v>
       </c>
       <c r="F88" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="G88" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J88" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="B89" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C89" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D89" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E89" t="s">
         <v>12</v>
       </c>
       <c r="F89" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="G89" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J89" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="B90" t="s">
-        <v>76</v>
+        <v>183</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D90" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E90" t="s">
         <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="G90" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J90" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B91" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D91" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E91" t="s">
         <v>12</v>
       </c>
       <c r="F91" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="G91" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J91" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="B92" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D92" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E92" t="s">
         <v>12</v>
       </c>
       <c r="F92" t="s">
-        <v>163</v>
+        <v>66</v>
       </c>
       <c r="G92" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J92" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="D93" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="E93" t="s">
         <v>12</v>
       </c>
       <c r="F93" t="s">
-        <v>163</v>
+        <v>30</v>
       </c>
       <c r="G93" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J93" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="B94" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="C94" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D94" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E94" t="s">
         <v>12</v>
       </c>
       <c r="F94" t="s">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="G94" t="s">
-        <v>87</v>
+        <v>156</v>
+      </c>
+      <c r="H94" t="s">
+        <v>157</v>
       </c>
       <c r="J94" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="B95" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C95" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D95" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E95" t="s">
         <v>12</v>
       </c>
       <c r="F95" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="G95" t="s">
-        <v>175</v>
-      </c>
-      <c r="H95" t="s">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="J95" t="s">
-        <v>151</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>24</v>
+        <v>146</v>
       </c>
       <c r="B96" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D96" t="s">
+        <v>128</v>
+      </c>
+      <c r="E96" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" t="s">
+        <v>144</v>
+      </c>
+      <c r="G96" t="s">
+        <v>84</v>
+      </c>
+      <c r="J96" t="s">
         <v>147</v>
-      </c>
-      <c r="E96" t="s">
-        <v>12</v>
-      </c>
-      <c r="F96" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" t="s">
-        <v>87</v>
-      </c>
-      <c r="H96" t="s">
-        <v>178</v>
-      </c>
-      <c r="J96" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="B97" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="C97" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D97" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E97" t="s">
         <v>12</v>
       </c>
       <c r="F97" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="G97" t="s">
-        <v>87</v>
-      </c>
-      <c r="H97" t="s">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="J97" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="B98" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C98" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D98" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E98" t="s">
         <v>12</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="G98" t="s">
-        <v>87</v>
-      </c>
-      <c r="H98" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="J98" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="B99" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C99" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D99" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E99" t="s">
         <v>12</v>
       </c>
       <c r="F99" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="G99" t="s">
-        <v>87</v>
-      </c>
-      <c r="H99" t="s">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="J99" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="B100" t="s">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="C100" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D100" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E100" t="s">
         <v>12</v>
       </c>
       <c r="F100" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="G100" t="s">
-        <v>87</v>
-      </c>
-      <c r="H100" t="s">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="J100" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.35">
@@ -4023,13 +3957,13 @@
         <v>24</v>
       </c>
       <c r="B101" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C101" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D101" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E101" t="s">
         <v>12</v>
@@ -4038,10 +3972,13 @@
         <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="H101" t="s">
-        <v>186</v>
+        <v>159</v>
+      </c>
+      <c r="J101" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
@@ -4049,25 +3986,28 @@
         <v>24</v>
       </c>
       <c r="B102" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C102" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D102" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E102" t="s">
         <v>12</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="G102" t="s">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="H102" t="s">
-        <v>186</v>
+        <v>160</v>
+      </c>
+      <c r="J102" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,25 +4015,28 @@
         <v>24</v>
       </c>
       <c r="B103" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="C103" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D103" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E103" t="s">
         <v>12</v>
       </c>
       <c r="F103" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="H103" t="s">
-        <v>89</v>
+        <v>162</v>
+      </c>
+      <c r="J103" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.35">
@@ -4101,13 +4044,13 @@
         <v>24</v>
       </c>
       <c r="B104" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="C104" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D104" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E104" t="s">
         <v>12</v>
@@ -4116,10 +4059,13 @@
         <v>28</v>
       </c>
       <c r="G104" t="s">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="H104" t="s">
-        <v>89</v>
+        <v>163</v>
+      </c>
+      <c r="J104" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.35">
@@ -4127,25 +4073,28 @@
         <v>24</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="C105" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D105" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E105" t="s">
         <v>12</v>
       </c>
       <c r="F105" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G105" t="s">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="H105" t="s">
-        <v>187</v>
+        <v>164</v>
+      </c>
+      <c r="J105" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.35">
@@ -4153,25 +4102,25 @@
         <v>24</v>
       </c>
       <c r="B106" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C106" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D106" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E106" t="s">
         <v>12</v>
       </c>
       <c r="F106" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H106" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
@@ -4179,13 +4128,13 @@
         <v>24</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C107" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D107" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E107" t="s">
         <v>12</v>
@@ -4194,10 +4143,10 @@
         <v>13</v>
       </c>
       <c r="G107" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="H107" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.35">
@@ -4205,13 +4154,13 @@
         <v>24</v>
       </c>
       <c r="B108" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C108" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D108" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E108" t="s">
         <v>12</v>
@@ -4220,10 +4169,10 @@
         <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="H108" t="s">
-        <v>190</v>
+        <v>86</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.35">
@@ -4231,627 +4180,968 @@
         <v>24</v>
       </c>
       <c r="B109" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C109" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D109" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E109" t="s">
         <v>12</v>
       </c>
       <c r="F109" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="H109" t="s">
-        <v>191</v>
+        <v>86</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="B110" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D110" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E110" t="s">
         <v>12</v>
       </c>
       <c r="F110" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="G110" t="s">
-        <v>193</v>
-      </c>
-      <c r="J110" t="s">
-        <v>194</v>
+        <v>166</v>
+      </c>
+      <c r="H110" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="B111" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D111" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E111" t="s">
         <v>12</v>
       </c>
       <c r="F111" t="s">
-        <v>163</v>
+        <v>66</v>
       </c>
       <c r="G111" t="s">
-        <v>175</v>
-      </c>
-      <c r="J111" t="s">
-        <v>195</v>
+        <v>156</v>
+      </c>
+      <c r="H111" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="B112" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D112" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E112" t="s">
         <v>12</v>
       </c>
       <c r="F112" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="G112" t="s">
-        <v>193</v>
-      </c>
-      <c r="J112" t="s">
-        <v>196</v>
+        <v>170</v>
+      </c>
+      <c r="H112" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>197</v>
+        <v>24</v>
       </c>
       <c r="B113" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D113" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E113" t="s">
         <v>12</v>
       </c>
       <c r="F113" t="s">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="G113" t="s">
-        <v>87</v>
-      </c>
-      <c r="J113" t="s">
-        <v>200</v>
+        <v>170</v>
+      </c>
+      <c r="H113" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>197</v>
+        <v>24</v>
       </c>
       <c r="B114" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="C114" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D114" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E114" t="s">
         <v>12</v>
       </c>
       <c r="F114" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="G114" t="s">
-        <v>87</v>
-      </c>
-      <c r="J114" t="s">
-        <v>200</v>
+        <v>170</v>
+      </c>
+      <c r="H114" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="B115" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="C115" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D115" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E115" t="s">
         <v>12</v>
       </c>
       <c r="F115" t="s">
-        <v>199</v>
+        <v>138</v>
       </c>
       <c r="G115" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="J115" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="B116" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D116" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E116" t="s">
         <v>12</v>
       </c>
       <c r="F116" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
       <c r="G116" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="J116" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="C117" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D117" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E117" t="s">
         <v>12</v>
       </c>
       <c r="F117" t="s">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="G117" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="J117" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="B118" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C118" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D118" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E118" t="s">
         <v>12</v>
       </c>
       <c r="F118" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="G118" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J118" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="B119" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="C119" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D119" t="s">
-        <v>206</v>
+        <v>128</v>
       </c>
       <c r="E119" t="s">
         <v>12</v>
       </c>
       <c r="F119" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="G119" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="J119" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="B120" t="s">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="C120" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D120" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="E120" t="s">
         <v>12</v>
       </c>
       <c r="F120" t="s">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="G120" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="J120" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>208</v>
+        <v>124</v>
       </c>
       <c r="B121" t="s">
-        <v>208</v>
+        <v>124</v>
       </c>
       <c r="C121" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D121" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="E121" t="s">
         <v>12</v>
       </c>
       <c r="F121" t="s">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="G121" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J121" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B122" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C122" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D122" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="E122" t="s">
         <v>12</v>
       </c>
       <c r="F122" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="G122" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="J122" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="B123" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="C123" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D123" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="E123" t="s">
         <v>12</v>
       </c>
       <c r="F123" t="s">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="G123" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="J123" t="s">
-        <v>210</v>
+        <v>132</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="B124" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="C124" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D124" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="E124" t="s">
         <v>12</v>
       </c>
       <c r="F124" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="G124" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="J124" t="s">
-        <v>210</v>
+        <v>132</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="B125" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="C125" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D125" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="E125" t="s">
         <v>12</v>
       </c>
       <c r="F125" t="s">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="G125" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="J125" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="B126" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C126" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D126" t="s">
-        <v>206</v>
+        <v>128</v>
       </c>
       <c r="E126" t="s">
         <v>12</v>
       </c>
       <c r="F126" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="G126" t="s">
-        <v>189</v>
+        <v>84</v>
       </c>
       <c r="J126" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="B127" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D127" t="s">
-        <v>206</v>
+        <v>128</v>
       </c>
       <c r="E127" t="s">
         <v>12</v>
       </c>
       <c r="F127" t="s">
-        <v>213</v>
+        <v>91</v>
       </c>
       <c r="G127" t="s">
-        <v>189</v>
+        <v>84</v>
       </c>
       <c r="J127" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="B128" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="C128" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D128" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E128" t="s">
         <v>12</v>
       </c>
       <c r="F128" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="G128" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J128" t="s">
-        <v>214</v>
+        <v>139</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="B129" t="s">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="C129" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D129" t="s">
-        <v>206</v>
+        <v>40</v>
       </c>
       <c r="E129" t="s">
         <v>12</v>
       </c>
       <c r="F129" t="s">
-        <v>216</v>
+        <v>37</v>
       </c>
       <c r="G129" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="J129" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="B130" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C130" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D130" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E130" t="s">
         <v>12</v>
       </c>
       <c r="F130" t="s">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="G130" t="s">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="J130" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="B131" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C131" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E131" t="s">
         <v>12</v>
       </c>
       <c r="F131" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="G131" t="s">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="J131" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="B132" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C132" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D132" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E132" t="s">
         <v>12</v>
       </c>
       <c r="F132" t="s">
+        <v>92</v>
+      </c>
+      <c r="G132" t="s">
+        <v>84</v>
+      </c>
+      <c r="J132" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>198</v>
+      </c>
+      <c r="B133" t="s">
+        <v>212</v>
+      </c>
+      <c r="C133" t="s">
+        <v>127</v>
+      </c>
+      <c r="D133" t="s">
+        <v>128</v>
+      </c>
+      <c r="E133" t="s">
+        <v>12</v>
+      </c>
+      <c r="F133" t="s">
+        <v>92</v>
+      </c>
+      <c r="G133" t="s">
+        <v>84</v>
+      </c>
+      <c r="J133" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>198</v>
+      </c>
+      <c r="B134" t="s">
         <v>213</v>
       </c>
-      <c r="G132" t="s">
-        <v>175</v>
-      </c>
-      <c r="J132" t="s">
+      <c r="C134" t="s">
+        <v>127</v>
+      </c>
+      <c r="D134" t="s">
+        <v>128</v>
+      </c>
+      <c r="E134" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" t="s">
+        <v>92</v>
+      </c>
+      <c r="G134" t="s">
+        <v>84</v>
+      </c>
+      <c r="J134" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>198</v>
+      </c>
+      <c r="B135" t="s">
+        <v>130</v>
+      </c>
+      <c r="C135" t="s">
+        <v>127</v>
+      </c>
+      <c r="D135" t="s">
+        <v>128</v>
+      </c>
+      <c r="E135" t="s">
+        <v>12</v>
+      </c>
+      <c r="F135" t="s">
+        <v>92</v>
+      </c>
+      <c r="G135" t="s">
+        <v>84</v>
+      </c>
+      <c r="J135" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>69</v>
+      </c>
+      <c r="B136" t="s">
+        <v>227</v>
+      </c>
+      <c r="C136" t="s">
+        <v>127</v>
+      </c>
+      <c r="D136" t="s">
+        <v>128</v>
+      </c>
+      <c r="E136" t="s">
+        <v>12</v>
+      </c>
+      <c r="F136" t="s">
+        <v>46</v>
+      </c>
+      <c r="G136" t="s">
+        <v>84</v>
+      </c>
+      <c r="J136" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>69</v>
+      </c>
+      <c r="B137" t="s">
+        <v>126</v>
+      </c>
+      <c r="C137" t="s">
+        <v>127</v>
+      </c>
+      <c r="D137" t="s">
+        <v>128</v>
+      </c>
+      <c r="E137" t="s">
+        <v>12</v>
+      </c>
+      <c r="F137" t="s">
+        <v>46</v>
+      </c>
+      <c r="G137" t="s">
+        <v>84</v>
+      </c>
+      <c r="J137" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>69</v>
+      </c>
+      <c r="B138" t="s">
+        <v>130</v>
+      </c>
+      <c r="C138" t="s">
+        <v>127</v>
+      </c>
+      <c r="D138" t="s">
+        <v>128</v>
+      </c>
+      <c r="E138" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" t="s">
+        <v>46</v>
+      </c>
+      <c r="G138" t="s">
+        <v>84</v>
+      </c>
+      <c r="J138" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>10</v>
+      </c>
+      <c r="B139" t="s">
+        <v>173</v>
+      </c>
+      <c r="C139" t="s">
+        <v>127</v>
+      </c>
+      <c r="D139" t="s">
+        <v>128</v>
+      </c>
+      <c r="E139" t="s">
+        <v>12</v>
+      </c>
+      <c r="F139" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" t="s">
+        <v>84</v>
+      </c>
+      <c r="H139" t="s">
+        <v>257</v>
+      </c>
+      <c r="J139" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>142</v>
+      </c>
+      <c r="B140" t="s">
+        <v>142</v>
+      </c>
+      <c r="C140" t="s">
+        <v>127</v>
+      </c>
+      <c r="D140" t="s">
+        <v>128</v>
+      </c>
+      <c r="E140" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" t="s">
+        <v>134</v>
+      </c>
+      <c r="G140" t="s">
+        <v>84</v>
+      </c>
+      <c r="J140" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>140</v>
+      </c>
+      <c r="C141" t="s">
+        <v>127</v>
+      </c>
+      <c r="D141" t="s">
+        <v>128</v>
+      </c>
+      <c r="E141" t="s">
+        <v>12</v>
+      </c>
+      <c r="F141" t="s">
+        <v>30</v>
+      </c>
+      <c r="G141" t="s">
+        <v>84</v>
+      </c>
+      <c r="J141" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>197</v>
+      </c>
+      <c r="B142" t="s">
+        <v>197</v>
+      </c>
+      <c r="C142" t="s">
+        <v>127</v>
+      </c>
+      <c r="D142" t="s">
+        <v>128</v>
+      </c>
+      <c r="E142" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" t="s">
+        <v>37</v>
+      </c>
+      <c r="G142" t="s">
+        <v>156</v>
+      </c>
+      <c r="J142" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>197</v>
+      </c>
+      <c r="B143" t="s">
+        <v>197</v>
+      </c>
+      <c r="C143" t="s">
+        <v>127</v>
+      </c>
+      <c r="D143" t="s">
+        <v>128</v>
+      </c>
+      <c r="E143" t="s">
+        <v>12</v>
+      </c>
+      <c r="F143" t="s">
+        <v>190</v>
+      </c>
+      <c r="G143" t="s">
+        <v>156</v>
+      </c>
+      <c r="J143" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
         <v>195</v>
       </c>
+      <c r="B144" t="s">
+        <v>195</v>
+      </c>
+      <c r="C144" t="s">
+        <v>127</v>
+      </c>
+      <c r="D144" t="s">
+        <v>187</v>
+      </c>
+      <c r="E144" t="s">
+        <v>12</v>
+      </c>
+      <c r="F144" t="s">
+        <v>83</v>
+      </c>
+      <c r="G144" t="s">
+        <v>156</v>
+      </c>
+      <c r="J144" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>195</v>
+      </c>
+      <c r="B145" t="s">
+        <v>195</v>
+      </c>
+      <c r="C145" t="s">
+        <v>127</v>
+      </c>
+      <c r="D145" t="s">
+        <v>187</v>
+      </c>
+      <c r="E145" t="s">
+        <v>12</v>
+      </c>
+      <c r="F145" t="s">
+        <v>79</v>
+      </c>
+      <c r="G145" t="s">
+        <v>156</v>
+      </c>
+      <c r="J145" t="s">
+        <v>196</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J132" xr:uid="{E0629895-8555-4DE5-8A98-86473C65DDE6}"/>
+  <autoFilter ref="A1:J145" xr:uid="{E0629895-8555-4DE5-8A98-86473C65DDE6}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/scripts/cargas.xlsx
+++ b/scripts/cargas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PamelaSilvaTeixeira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99634FBC-7984-4B33-B47B-37E51D138D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8E1916-BBF2-489A-8DEB-0BDA959002BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F9C8F682-8F69-48C0-A164-B472E5744D19}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$130</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="253">
   <si>
     <t>Origem</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Calcário</t>
   </si>
   <si>
-    <t>200,00</t>
-  </si>
-  <si>
     <t>Santa Filomena - PI</t>
   </si>
   <si>
@@ -113,712 +110,697 @@
     <t>175,00</t>
   </si>
   <si>
+    <t>Rio Branco do Sul - PR</t>
+  </si>
+  <si>
+    <t>Gesso</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM</t>
+  </si>
+  <si>
+    <t>Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>Itapeva - SP</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
+  </si>
+  <si>
+    <t>Laranjeiras - SE</t>
+  </si>
+  <si>
+    <t>Paulista - PE</t>
+  </si>
+  <si>
+    <t>Clinquer</t>
+  </si>
+  <si>
+    <t>185,00</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Joinville - SC</t>
+  </si>
+  <si>
+    <t>Tubos e Conexões</t>
+  </si>
+  <si>
+    <t>Outro</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Vanderléia</t>
+  </si>
+  <si>
+    <t>Jucurutu - RN</t>
+  </si>
+  <si>
+    <t>Pitimbu - PB</t>
+  </si>
+  <si>
+    <t>Minério de Ferro</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>110,00</t>
+  </si>
+  <si>
+    <t>Carreta LS, Vanderléia</t>
+  </si>
+  <si>
+    <t>240,00</t>
+  </si>
+  <si>
+    <t>São João da Barra - RJ</t>
+  </si>
+  <si>
+    <t>Edealina - GO</t>
+  </si>
+  <si>
+    <t>coque</t>
+  </si>
+  <si>
+    <t>PAGBEM</t>
+  </si>
+  <si>
+    <t>Itaguaí - RJ</t>
+  </si>
+  <si>
+    <t>Votorantim - SP</t>
+  </si>
+  <si>
+    <t>Escória</t>
+  </si>
+  <si>
+    <t>107,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO REPOM /</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos</t>
+  </si>
+  <si>
+    <t>130,00</t>
+  </si>
+  <si>
+    <t>Salto de Pirapora - SP</t>
+  </si>
+  <si>
+    <t>Brasília - DF</t>
+  </si>
+  <si>
+    <t>325,00</t>
+  </si>
+  <si>
+    <t>295,00</t>
+  </si>
+  <si>
+    <t>Duque de Caxias - RJ</t>
+  </si>
+  <si>
+    <t>Cantagalo - RJ</t>
+  </si>
+  <si>
+    <t>106,00</t>
+  </si>
+  <si>
+    <t>Itaú de Minas - MG</t>
+  </si>
+  <si>
+    <t>260,00</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Ouricuri - PE</t>
+  </si>
+  <si>
+    <t>gesso</t>
+  </si>
+  <si>
+    <t>Bitrem 7 eixos, Rodotrem</t>
+  </si>
+  <si>
+    <t>Grade Baixa</t>
+  </si>
+  <si>
+    <t>142,00</t>
+  </si>
+  <si>
+    <t>162,00</t>
+  </si>
+  <si>
+    <t>Trindade - PE</t>
+  </si>
+  <si>
+    <t>Gpisita</t>
+  </si>
+  <si>
+    <t>180,00</t>
+  </si>
+  <si>
+    <t>Vanderléia</t>
+  </si>
+  <si>
+    <t>Carreta LS</t>
+  </si>
+  <si>
+    <t>Carreta</t>
+  </si>
+  <si>
+    <t>Carreta toco 5 eixos</t>
+  </si>
+  <si>
+    <t>5.188,21</t>
+  </si>
+  <si>
+    <t>4.745,60</t>
+  </si>
+  <si>
+    <t>6.520,95</t>
+  </si>
+  <si>
+    <t>5.716,37</t>
+  </si>
+  <si>
+    <t>Belém - PA</t>
+  </si>
+  <si>
+    <t>Primavera - PA</t>
+  </si>
+  <si>
+    <t>Nobres - MT</t>
+  </si>
+  <si>
+    <t>Porto Velho - RO</t>
+  </si>
+  <si>
+    <t>Graneleiro, Caçamba</t>
+  </si>
+  <si>
+    <t>PAGBEM/REPOM</t>
+  </si>
+  <si>
+    <t>Vanderléia, Carreta 4º eixo</t>
+  </si>
+  <si>
+    <t>Carreta LS, Bitrem 7 eixos, Rodotrem</t>
+  </si>
+  <si>
+    <t>Unaí - MG</t>
+  </si>
+  <si>
+    <t>Bonfinópolis de Minas - MG</t>
+  </si>
+  <si>
+    <t>Araguari - MG</t>
+  </si>
+  <si>
+    <t>SORGO</t>
+  </si>
+  <si>
+    <t>165,00</t>
+  </si>
+  <si>
+    <t>135,00</t>
+  </si>
+  <si>
+    <t>Montes Claros - MG</t>
+  </si>
+  <si>
+    <t>Grajaú - MA</t>
+  </si>
+  <si>
+    <t>Barro Alto - GO</t>
+  </si>
+  <si>
+    <t>BAUXITA</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM</t>
+  </si>
+  <si>
+    <t>Cuiabá - MT</t>
+  </si>
+  <si>
+    <t>125,00</t>
+  </si>
+  <si>
+    <t>Goiânia - GO</t>
+  </si>
+  <si>
+    <t>CIMENTO</t>
+  </si>
+  <si>
+    <t>Pallet</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM</t>
+  </si>
+  <si>
+    <t>Anápolis - GO</t>
+  </si>
+  <si>
+    <t>Alfenas - MG</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Cubatão - SP</t>
+  </si>
+  <si>
+    <t>Truck</t>
+  </si>
+  <si>
+    <t>São José dos Campos - SP</t>
+  </si>
+  <si>
+    <t>Barueri - SP</t>
+  </si>
+  <si>
+    <t>Imperatriz - MA</t>
+  </si>
+  <si>
+    <t>Truck, Carreta LS</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Arame/MA, Buriticupu/MA, Carolina/MA, Cidelândia/MA, Estreito/MA, Formosa da Serra/MA, Grajaú/MA, Imperatriz/MA, Itinga do Maranhão /MA, Porto Franco/MA, Riachão/MA, São Pedro da Água Branca /MA, São Pedro dos Crentes/MA, Vila Nova dos Martírios/MA</t>
+  </si>
+  <si>
+    <t>Luís Eduardo Magalhães - BA</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: Cocos/BA, Serra Dourada/BA, São Félix do Coribe/BA, Tabocas do Brejo Velho/BA, Correntina/BA, Mansidão/BA, Formosa do Rio Preto/BA, Santa Rita de Cassia/BA, Barreiras/BA e Morpará/BA</t>
+  </si>
+  <si>
+    <t>Crateús - CE</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI. - POSSIVEIS DESTINOS DISPONIVEIS - Mombaça/CE, Poranga/CE, Pedra Branca/CE, Tauá/CE, Nova Russas/CE, Independência/CE e Tamboril/CE</t>
+  </si>
+  <si>
+    <t>Truck, Bitruck</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possiveis Destinos Disponiveis: Araruama/RJ, Campos dos Goytacazes/RJ, Itaperuna/RJ, Saquarema//RJ, Serra/ES</t>
+  </si>
+  <si>
+    <t>Volta Redonda - RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Paraty/RJ, Resende/RJ e Volta Redonda/RJ</t>
+  </si>
+  <si>
+    <t>São Gonçalo - RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Armação dos Búzios/RJ, Arraial do Cabo/RJ, Cabo Frio/RJ, Campos dos Goytacazes/RJ, Guapimirim/RJ, Itaboraí/RJ, Magé/RJ, Maricá/RJ, Niterói/RJ e São Gonçalo/RJ</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro - RJ</t>
+  </si>
+  <si>
+    <t>CIMENTO ENSACADO</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD SANTA CRUZ - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Duque de Caxias/RJ, Nova Iguaçu/RJ, Paraty/RJ, Petrópolis/RJ, Queimados/RJ e Rio de Janeiro/RJ</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD PARADA DE LUCAS - Possiveis Destinos Disponiveis Duque de Caxias/RJ, Mangaratiba/RJ, Mesquita/RJ, Nova Iguaçu/RJ, Petrópolis/RJ e Rio de Janeiro/RJ</t>
+  </si>
+  <si>
+    <t>Vidal Ramos - SC</t>
+  </si>
+  <si>
+    <t>Blumenau - SC</t>
+  </si>
+  <si>
+    <t>Grade Baixa, Prancha</t>
+  </si>
+  <si>
+    <t>53,50</t>
+  </si>
+  <si>
+    <t>Buri - SP</t>
+  </si>
+  <si>
+    <t>116,00</t>
+  </si>
+  <si>
+    <t>120,00</t>
+  </si>
+  <si>
+    <t>Embu das Artes - SP</t>
+  </si>
+  <si>
+    <t>105,00</t>
+  </si>
+  <si>
+    <t>113,00</t>
+  </si>
+  <si>
+    <t>117,00</t>
+  </si>
+  <si>
+    <t>Regente Feijó - SP</t>
+  </si>
+  <si>
+    <t>Graneleiro, Sider</t>
+  </si>
+  <si>
+    <t>160,00</t>
+  </si>
+  <si>
+    <t>168,00</t>
+  </si>
+  <si>
+    <t>Ourinhos - SP</t>
+  </si>
+  <si>
+    <t>Graneleiro, Grade Baixa</t>
+  </si>
+  <si>
+    <t>129,00</t>
+  </si>
+  <si>
+    <t>134,00</t>
+  </si>
+  <si>
+    <t>Teresina - PI</t>
+  </si>
+  <si>
+    <t>Graneleiro, Grade Baixa, Prancha</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>DESTINOS DISPONIVEIS: No Extremo Sul do Estado do PI - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>Campinas - SP</t>
+  </si>
+  <si>
+    <t>Bragança Paulista - SP</t>
+  </si>
+  <si>
+    <t>Toco, Truck, Bitruck</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI- VEICULOS TOCO APENAS 10 TON</t>
+  </si>
+  <si>
+    <t>Serra Negra - SP</t>
+  </si>
+  <si>
+    <t>Jundiaí - SP</t>
+  </si>
+  <si>
+    <t>Diadema - SP</t>
+  </si>
+  <si>
+    <t>Guarulhos - SP</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
+  </si>
+  <si>
+    <t>Saco</t>
+  </si>
+  <si>
+    <t>Petrolina - PE</t>
+  </si>
+  <si>
+    <t>Caruaru - PE</t>
+  </si>
+  <si>
+    <t>Truck, Bitruck, Carreta</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM / PEDÁGIO INCLUSO NO FRETE</t>
+  </si>
+  <si>
+    <t>Bitruck, Carreta LS</t>
+  </si>
+  <si>
+    <t>Corumbá - MS</t>
+  </si>
+  <si>
+    <t>Truck, Carreta</t>
+  </si>
+  <si>
+    <t>Feira de Santana - BA</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
+  </si>
+  <si>
+    <t>Itabuna - BA</t>
+  </si>
+  <si>
+    <t>Aparecida de Goiânia - GO</t>
+  </si>
+  <si>
+    <t>CARGA FRACIONADA (3 A 5 entregas) COM VAGA PARA FICAR FIXO NA UNIDADE COM DESTINOS AS REGIÕES DE: Anápolis/GO, Heitoraí/GO, Inhumas/GO, Itaberaí/GO, Jaraguá/GO e Leopoldo de Bulhões/GO - PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
+  </si>
+  <si>
+    <t>São Luís - MA</t>
+  </si>
+  <si>
+    <t>190,00</t>
+  </si>
+  <si>
+    <t>São Gonçalo do Amarante - CE</t>
+  </si>
+  <si>
+    <t>só aceita rodocaçambas com lona fácil. Caso não tenham, o veículo não passa na vistoria dos guardas</t>
+  </si>
+  <si>
+    <t>Rio Claro - SP</t>
+  </si>
+  <si>
+    <t>5.700,00</t>
+  </si>
+  <si>
+    <t>231,00</t>
+  </si>
+  <si>
+    <t>Pinheiro Machado - RS</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI.</t>
+  </si>
+  <si>
+    <t>Leopoldo de Bulhões - GO</t>
+  </si>
+  <si>
+    <t>Jaraguá - GO</t>
+  </si>
+  <si>
+    <t>Itaberaí - GO</t>
+  </si>
+  <si>
+    <t>Inhumas - GO</t>
+  </si>
+  <si>
+    <t>Heitoraí - GO</t>
+  </si>
+  <si>
+    <t>Balsas - MA</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO REPOM / PAGBEM</t>
+  </si>
+  <si>
+    <t>CLINQUER</t>
+  </si>
+  <si>
+    <t>310,00</t>
+  </si>
+  <si>
+    <t>Silo</t>
+  </si>
+  <si>
+    <t>PARA MOTORISTAS CATIVOS OU QUE DESEJAM FICAR NA REGIÃO. ROTAS COM DESTINO PARA OS ESTADOS DE GO OU MS</t>
+  </si>
+  <si>
+    <t>Pirenópolis - GO</t>
+  </si>
+  <si>
+    <t>Poços de Caldas - MG</t>
+  </si>
+  <si>
+    <t>Sider, Baú</t>
+  </si>
+  <si>
+    <t>5.100,00</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI.</t>
+  </si>
+  <si>
+    <t>17.155,00</t>
+  </si>
+  <si>
+    <t>10.450,00</t>
+  </si>
+  <si>
+    <t>Bitrem 9 eixos, Rodotrem</t>
+  </si>
+  <si>
+    <t>13.440,00</t>
+  </si>
+  <si>
+    <t>215,00</t>
+  </si>
+  <si>
+    <t>Juara - MT</t>
+  </si>
+  <si>
+    <t>Feliz Natal - MT</t>
+  </si>
+  <si>
+    <t>Porto Alegre do Norte - MT</t>
+  </si>
+  <si>
+    <t>Vera - MT</t>
+  </si>
+  <si>
+    <t>Tabaporã - MT</t>
+  </si>
+  <si>
+    <t>Itanhangá - MT</t>
+  </si>
+  <si>
+    <t>Confresa - MT</t>
+  </si>
+  <si>
     <t>Cajati - SP</t>
   </si>
   <si>
-    <t>Rio Branco do Sul - PR</t>
-  </si>
-  <si>
-    <t>Gesso</t>
-  </si>
-  <si>
-    <t>74,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO PAGBEM</t>
-  </si>
-  <si>
-    <t>Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>77,00</t>
-  </si>
-  <si>
-    <t>Carreta, Carreta LS, Bitrem 7 eixos</t>
-  </si>
-  <si>
-    <t>Itapeva - SP</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Carreta 4º eixo, Rodotrem</t>
-  </si>
-  <si>
-    <t>Laranjeiras - SE</t>
-  </si>
-  <si>
-    <t>Paulista - PE</t>
-  </si>
-  <si>
-    <t>Clinquer</t>
-  </si>
-  <si>
-    <t>185,00</t>
-  </si>
-  <si>
-    <t>Carreta LS, Bitrem 7 eixos, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>Joinville - SC</t>
-  </si>
-  <si>
-    <t>Tubos e Conexões</t>
-  </si>
-  <si>
-    <t>Outro</t>
-  </si>
-  <si>
-    <t>Carreta, Carreta LS, Vanderléia</t>
+    <t>Sorocaba - SP</t>
+  </si>
+  <si>
+    <t>Itápolis - SP</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>Aripuanã - MT</t>
+  </si>
+  <si>
+    <t>Juiz de Fora - MG</t>
+  </si>
+  <si>
+    <t>MINERIO</t>
+  </si>
+  <si>
+    <t>650,00</t>
+  </si>
+  <si>
+    <t>repom</t>
+  </si>
+  <si>
+    <t>17.750,00</t>
+  </si>
+  <si>
+    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM / Só vamos carregar se aceitar carregar com os 5% (a partir de 48,5 )</t>
+  </si>
+  <si>
+    <t>Cascavel - PR</t>
+  </si>
+  <si>
+    <t>Tubo</t>
+  </si>
+  <si>
+    <t>Carreta, Carreta LS, Vanderléia, Carreta 4º eixo</t>
   </si>
   <si>
     <t>Sider</t>
   </si>
   <si>
-    <t>Jucurutu - RN</t>
-  </si>
-  <si>
-    <t>Pitimbu - PB</t>
-  </si>
-  <si>
-    <t>Minério de Ferro</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>110,00</t>
-  </si>
-  <si>
-    <t>Baraúna - RN</t>
-  </si>
-  <si>
-    <t>Pacatuba - SE</t>
-  </si>
-  <si>
-    <t>Clínquer</t>
-  </si>
-  <si>
-    <t>Carreta LS, Vanderléia</t>
-  </si>
-  <si>
-    <t>240,00</t>
-  </si>
-  <si>
-    <t>Nossa Senhora do Socorro - SE</t>
-  </si>
-  <si>
-    <t>8.902,06</t>
-  </si>
-  <si>
-    <t>230,00</t>
-  </si>
-  <si>
-    <t>São João da Barra - RJ</t>
-  </si>
-  <si>
-    <t>Edealina - GO</t>
-  </si>
-  <si>
-    <t>coque</t>
-  </si>
-  <si>
-    <t>17.625,00</t>
-  </si>
-  <si>
-    <t>PAGBEM</t>
-  </si>
-  <si>
-    <t>Itaguaí - RJ</t>
-  </si>
-  <si>
-    <t>Votorantim - SP</t>
-  </si>
-  <si>
-    <t>Escória</t>
-  </si>
-  <si>
-    <t>107,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO REPOM /</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos</t>
-  </si>
-  <si>
-    <t>130,00</t>
-  </si>
-  <si>
-    <t>Salto de Pirapora - SP</t>
-  </si>
-  <si>
-    <t>Brasília - DF</t>
-  </si>
-  <si>
-    <t>325,00</t>
-  </si>
-  <si>
-    <t>295,00</t>
-  </si>
-  <si>
-    <t>Duque de Caxias - RJ</t>
-  </si>
-  <si>
-    <t>Cantagalo - RJ</t>
-  </si>
-  <si>
-    <t>106,00</t>
-  </si>
-  <si>
-    <t>Itaú de Minas - MG</t>
-  </si>
-  <si>
-    <t>260,00</t>
-  </si>
-  <si>
-    <t>Castro - PR</t>
-  </si>
-  <si>
-    <t>Cajamar - SP</t>
-  </si>
-  <si>
-    <t>Carreta, Carreta LS, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>4.600,00</t>
-  </si>
-  <si>
-    <t>Ouricuri - PE</t>
-  </si>
-  <si>
-    <t>gesso</t>
-  </si>
-  <si>
-    <t>Bitrem 7 eixos, Rodotrem</t>
-  </si>
-  <si>
-    <t>Grade Baixa</t>
-  </si>
-  <si>
-    <t>142,00</t>
-  </si>
-  <si>
-    <t>162,00</t>
-  </si>
-  <si>
-    <t>Trindade - PE</t>
-  </si>
-  <si>
-    <t>Gpisita</t>
-  </si>
-  <si>
-    <t>180,00</t>
-  </si>
-  <si>
-    <t>Vanderléia</t>
-  </si>
-  <si>
-    <t>Carreta LS</t>
-  </si>
-  <si>
-    <t>Carreta</t>
-  </si>
-  <si>
-    <t>Carreta toco 5 eixos</t>
-  </si>
-  <si>
-    <t>5.188,21</t>
-  </si>
-  <si>
-    <t>4.745,60</t>
-  </si>
-  <si>
-    <t>6.520,95</t>
-  </si>
-  <si>
-    <t>5.716,37</t>
-  </si>
-  <si>
-    <t>Belém - PA</t>
-  </si>
-  <si>
-    <t>Primavera - PA</t>
-  </si>
-  <si>
-    <t>Barcarena - PA</t>
-  </si>
-  <si>
-    <t>Nobres - MT</t>
-  </si>
-  <si>
-    <t>Porto Velho - RO</t>
-  </si>
-  <si>
-    <t>Graneleiro, Caçamba</t>
-  </si>
-  <si>
-    <t>PAGBEM/REPOM</t>
-  </si>
-  <si>
-    <t>Vanderléia, Carreta 4º eixo</t>
-  </si>
-  <si>
-    <t>Carreta LS, Bitrem 7 eixos, Rodotrem</t>
-  </si>
-  <si>
-    <t>Unaí - MG</t>
-  </si>
-  <si>
-    <t>Bonfinópolis de Minas - MG</t>
-  </si>
-  <si>
-    <t>Araguari - MG</t>
-  </si>
-  <si>
-    <t>SORGO</t>
-  </si>
-  <si>
-    <t>165,00</t>
-  </si>
-  <si>
-    <t>135,00</t>
-  </si>
-  <si>
-    <t>Janaúba - MG</t>
+    <t>Pimenteiras do Oeste - RO</t>
+  </si>
+  <si>
+    <t>250,00</t>
+  </si>
+  <si>
+    <t>Patos de Minas - MG</t>
+  </si>
+  <si>
+    <t>Poço Fundo - MG</t>
+  </si>
+  <si>
+    <t>Sider, Grade Baixa</t>
+  </si>
+  <si>
+    <t>Caratinga - MG</t>
+  </si>
+  <si>
+    <t>335,00</t>
+  </si>
+  <si>
+    <t>Imbituba - SC</t>
+  </si>
+  <si>
+    <t>COQUE</t>
+  </si>
+  <si>
+    <t>Grossos - RN</t>
+  </si>
+  <si>
+    <t>Gesso de Salina</t>
+  </si>
+  <si>
+    <t>128,00</t>
+  </si>
+  <si>
+    <t>Porto dos Gaúchos - MT</t>
+  </si>
+  <si>
+    <t>Sinop - MT</t>
   </si>
   <si>
     <t>Milho</t>
   </si>
   <si>
-    <t>Montes Claros - MG</t>
-  </si>
-  <si>
-    <t>Borda da Mata - MG</t>
-  </si>
-  <si>
-    <t>115,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO REPOM</t>
-  </si>
-  <si>
-    <t>Grajaú - MA</t>
-  </si>
-  <si>
-    <t>Barro Alto - GO</t>
-  </si>
-  <si>
-    <t>BAUXITA</t>
-  </si>
-  <si>
-    <t>12.700,00</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO PAGBEM ou REPOM</t>
-  </si>
-  <si>
-    <t>Cuiabá - MT</t>
-  </si>
-  <si>
-    <t>125,00</t>
-  </si>
-  <si>
-    <t>Goiânia - GO</t>
-  </si>
-  <si>
-    <t>CIMENTO</t>
-  </si>
-  <si>
-    <t>Pallet</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM</t>
-  </si>
-  <si>
-    <t>Anápolis - GO</t>
-  </si>
-  <si>
-    <t>Alfenas - MG</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Cubatão - SP</t>
-  </si>
-  <si>
-    <t>Truck</t>
-  </si>
-  <si>
-    <t>São José dos Campos - SP</t>
-  </si>
-  <si>
-    <t>Barueri - SP</t>
-  </si>
-  <si>
-    <t>Imperatriz - MA</t>
-  </si>
-  <si>
-    <t>Truck, Carreta LS</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Arame/MA, Buriticupu/MA, Carolina/MA, Cidelândia/MA, Estreito/MA, Formosa da Serra/MA, Grajaú/MA, Imperatriz/MA, Itinga do Maranhão /MA, Porto Franco/MA, Riachão/MA, São Pedro da Água Branca /MA, São Pedro dos Crentes/MA, Vila Nova dos Martírios/MA</t>
-  </si>
-  <si>
-    <t>Luís Eduardo Magalhães - BA</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: Cocos/BA, Serra Dourada/BA, São Félix do Coribe/BA, Tabocas do Brejo Velho/BA, Correntina/BA, Mansidão/BA, Formosa do Rio Preto/BA, Santa Rita de Cassia/BA, Barreiras/BA e Morpará/BA</t>
-  </si>
-  <si>
-    <t>Crateús - CE</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI. - POSSIVEIS DESTINOS DISPONIVEIS - Mombaça/CE, Poranga/CE, Pedra Branca/CE, Tauá/CE, Nova Russas/CE, Independência/CE e Tamboril/CE</t>
-  </si>
-  <si>
-    <t>Truck, Bitruck</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. Possiveis Destinos Disponiveis: Araruama/RJ, Campos dos Goytacazes/RJ, Itaperuna/RJ, Saquarema//RJ, Serra/ES</t>
-  </si>
-  <si>
-    <t>Volta Redonda - RJ</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Paraty/RJ, Resende/RJ e Volta Redonda/RJ</t>
-  </si>
-  <si>
-    <t>São Gonçalo - RJ</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. - Possiveis Destinos Disponiveis: Armação dos Búzios/RJ, Arraial do Cabo/RJ, Cabo Frio/RJ, Campos dos Goytacazes/RJ, Guapimirim/RJ, Itaboraí/RJ, Magé/RJ, Maricá/RJ, Niterói/RJ e São Gonçalo/RJ</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro - RJ</t>
-  </si>
-  <si>
-    <t>CIMENTO ENSACADO</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD SANTA CRUZ - Possiveis Destinos Disponiveis: Angra dos Reis/RJ, Duque de Caxias/RJ, Nova Iguaçu/RJ, Paraty/RJ, Petrópolis/RJ, Queimados/RJ e Rio de Janeiro/RJ</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI. CD PARADA DE LUCAS - Possiveis Destinos Disponiveis Duque de Caxias/RJ, Mangaratiba/RJ, Mesquita/RJ, Nova Iguaçu/RJ, Petrópolis/RJ e Rio de Janeiro/RJ</t>
-  </si>
-  <si>
-    <t>Vidal Ramos - SC</t>
-  </si>
-  <si>
-    <t>Blumenau - SC</t>
-  </si>
-  <si>
-    <t>Grade Baixa, Prancha</t>
-  </si>
-  <si>
-    <t>53,50</t>
-  </si>
-  <si>
-    <t>Buri - SP</t>
-  </si>
-  <si>
-    <t>116,00</t>
-  </si>
-  <si>
-    <t>120,00</t>
-  </si>
-  <si>
-    <t>Embu das Artes - SP</t>
-  </si>
-  <si>
-    <t>105,00</t>
-  </si>
-  <si>
-    <t>113,00</t>
-  </si>
-  <si>
-    <t>117,00</t>
-  </si>
-  <si>
-    <t>Regente Feijó - SP</t>
-  </si>
-  <si>
-    <t>Graneleiro, Sider</t>
-  </si>
-  <si>
-    <t>160,00</t>
-  </si>
-  <si>
-    <t>168,00</t>
-  </si>
-  <si>
-    <t>Ourinhos - SP</t>
-  </si>
-  <si>
-    <t>Graneleiro, Grade Baixa</t>
-  </si>
-  <si>
-    <t>129,00</t>
-  </si>
-  <si>
-    <t>134,00</t>
-  </si>
-  <si>
-    <t>Teresina - PI</t>
-  </si>
-  <si>
-    <t>Graneleiro, Grade Baixa, Prancha</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - DESTINOS DISPONIVEIS: CASTELO DO PIAUI/PI, SÃO MIGUEL DO TAPUI/PI, PARNAIBA/PI, BARRAS/PI, CAJUEIRO DA PRAIA/PI, SÃO JOÃO DA FRONTEIRA/PI, ILHA GRANDE/PI, COCAL/PI, LAGOA ALEGRE/PI, MIGUEL ALVES/PI, ALTOS/PI, SÃO JOÃO DA SERRA/PI, CAMPO MAIOR/PI, BENEDITINOS/PI, LUZILANDIA/PI, MADEIRO/PI, MATIAS OLIMPIO/PI, TUTOIA/MA.</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>DESTINOS DISPONIVEIS: No Extremo Sul do Estado do PI - PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>Campinas - SP</t>
-  </si>
-  <si>
-    <t>Bragança Paulista - SP</t>
-  </si>
-  <si>
-    <t>Toco, Truck, Bitruck</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI- VEICULOS TOCO APENAS 10 TON</t>
-  </si>
-  <si>
-    <t>Serra Negra - SP</t>
-  </si>
-  <si>
-    <t>Jundiaí - SP</t>
-  </si>
-  <si>
-    <t>Diadema - SP</t>
-  </si>
-  <si>
-    <t>Guarulhos - SP</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI - POSSIVEIS DESTINOS DISPONIVEIS: Guarulhos/SP, São Paulo/SP (Zona Leste), Região do Alto Tietê/SP</t>
-  </si>
-  <si>
-    <t>Saco</t>
-  </si>
-  <si>
-    <t>Petrolina - PE</t>
-  </si>
-  <si>
-    <t>Caruaru - PE</t>
-  </si>
-  <si>
-    <t>Truck, Bitruck, Carreta</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI / VALOR PAGO NO CARTÃO REPOM / PEDÁGIO INCLUSO NO FRETE</t>
-  </si>
-  <si>
-    <t>Bitruck, Carreta LS</t>
-  </si>
-  <si>
-    <t>Corumbá - MS</t>
-  </si>
-  <si>
-    <t>Truck, Carreta</t>
-  </si>
-  <si>
-    <t>Feira de Santana - BA</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI / DESTINOS DISPONIVEIS: TANHACU, CHAPADA, BRUMADO, JAGUAQUARA - JACOBINA</t>
-  </si>
-  <si>
-    <t>Itabuna - BA</t>
-  </si>
-  <si>
-    <t>Aparecida de Goiânia - GO</t>
-  </si>
-  <si>
-    <t>CARGA FRACIONADA (3 A 5 entregas) COM VAGA PARA FICAR FIXO NA UNIDADE COM DESTINOS AS REGIÕES DE: Anápolis/GO, Heitoraí/GO, Inhumas/GO, Itaberaí/GO, Jaraguá/GO e Leopoldo de Bulhões/GO - PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI</t>
-  </si>
-  <si>
-    <t>São Luís - MA</t>
-  </si>
-  <si>
-    <t>190,00</t>
-  </si>
-  <si>
-    <t>São Gonçalo do Amarante - CE</t>
-  </si>
-  <si>
-    <t>só aceita rodocaçambas com lona fácil. Caso não tenham, o veículo não passa na vistoria dos guardas</t>
-  </si>
-  <si>
-    <t>Rio Claro - SP</t>
-  </si>
-  <si>
-    <t>5.700,00</t>
-  </si>
-  <si>
-    <t>231,00</t>
-  </si>
-  <si>
-    <t>Pinheiro Machado - RS</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO CHAPA (AJUDANTE) E TER PALLETS, CINTA, LONA E EPI.</t>
-  </si>
-  <si>
-    <t>Leopoldo de Bulhões - GO</t>
-  </si>
-  <si>
-    <t>Jaraguá - GO</t>
-  </si>
-  <si>
-    <t>Itaberaí - GO</t>
-  </si>
-  <si>
-    <t>Inhumas - GO</t>
-  </si>
-  <si>
-    <t>Heitoraí - GO</t>
-  </si>
-  <si>
-    <t>Bento de Abreu - SP</t>
-  </si>
-  <si>
-    <t>140,00</t>
-  </si>
-  <si>
-    <t>Valparaíso - SP</t>
-  </si>
-  <si>
-    <t>Araçatuba - SP</t>
-  </si>
-  <si>
-    <t>Balsas - MA</t>
-  </si>
-  <si>
-    <t>VALOR PAGO NO CARTÃO REPOM / PAGBEM</t>
-  </si>
-  <si>
-    <t>CLINQUER</t>
-  </si>
-  <si>
-    <t>310,00</t>
-  </si>
-  <si>
-    <t>Confresa - MT</t>
+    <t>Campos de Júlio - MT</t>
+  </si>
+  <si>
+    <t>Rondonópolis - MT</t>
+  </si>
+  <si>
+    <t>Água Azul do Norte - PA</t>
+  </si>
+  <si>
+    <t>Sorriso - MT</t>
   </si>
   <si>
     <t>Colinas do Tocantins - TO</t>
   </si>
   <si>
-    <t>ARM AGRICOLA</t>
-  </si>
-  <si>
-    <t>Silo</t>
-  </si>
-  <si>
-    <t>PARA MOTORISTAS CATIVOS OU QUE DESEJAM FICAR NA REGIÃO. ROTAS COM DESTINO PARA OS ESTADOS DE GO OU MS</t>
-  </si>
-  <si>
-    <t>Pirenópolis - GO</t>
-  </si>
-  <si>
-    <t>Poços de Caldas - MG</t>
-  </si>
-  <si>
-    <t>Sider, Baú</t>
-  </si>
-  <si>
-    <t>50,00</t>
-  </si>
-  <si>
-    <t>clínquer</t>
-  </si>
-  <si>
-    <t>Ipiranga do Norte - MT</t>
-  </si>
-  <si>
-    <t>Rondonópolis - MT</t>
-  </si>
-  <si>
-    <t>Porto Alegre do Norte - MT</t>
-  </si>
-  <si>
-    <t>Água Azul do Norte - PA</t>
-  </si>
-  <si>
-    <t>Dom Aquino - MT</t>
-  </si>
-  <si>
-    <t>Primavera do Leste - MT</t>
-  </si>
-  <si>
-    <t>Sinop - MT</t>
-  </si>
-  <si>
-    <t>São Miguel do Araguaia - GO</t>
-  </si>
-  <si>
-    <t>Jussara - GO</t>
-  </si>
-  <si>
-    <t>Goianésia - GO</t>
-  </si>
-  <si>
-    <t>Tabaporã - MT</t>
-  </si>
-  <si>
-    <t>Itanhangá - MT</t>
-  </si>
-  <si>
-    <t>Nova Ubiratã - MT</t>
-  </si>
-  <si>
-    <t>Itaituba - PA</t>
-  </si>
-  <si>
-    <t>Sorriso - MT</t>
-  </si>
-  <si>
-    <t>Campos de Júlio - MT</t>
-  </si>
-  <si>
-    <t>Sapezal - MT</t>
-  </si>
-  <si>
-    <t>Nova Mutum - MT</t>
-  </si>
-  <si>
-    <t>Barra do Bugres - MT</t>
-  </si>
-  <si>
-    <t>Tangará da Serra - MT</t>
-  </si>
-  <si>
-    <t>Cocalinho - MT</t>
-  </si>
-  <si>
-    <t>Alto Garças - MT</t>
-  </si>
-  <si>
-    <t>Chapada dos Guimarães - MT</t>
-  </si>
-  <si>
-    <t>Pedra Preta - MT</t>
-  </si>
-  <si>
-    <t>Itiquira - MT</t>
-  </si>
-  <si>
-    <t>5.100,00</t>
-  </si>
-  <si>
-    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI.</t>
+    <t>Santarém - PA</t>
+  </si>
+  <si>
+    <t>Truck, Carreta, Carreta LS</t>
+  </si>
+  <si>
+    <t>PARA CARREGAMENTO, NECESSÁRIO TER PALLETS, CINTA, LONA E EPI - Possiveis Destinos Disponíveis: BELTERÁ/PA , Placas/PA e Santarém/PA</t>
   </si>
 </sst>
 </file>
@@ -1205,18 +1187,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0629895-8555-4DE5-8A98-86473C65DDE6}">
-  <dimension ref="A1:J145"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="75.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="255.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1254,42 +1236,39 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
+        <v>229</v>
+      </c>
+      <c r="I2">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1304,21 +1283,21 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>231</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>232</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1327,27 +1306,27 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s">
-        <v>215</v>
+        <v>103</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>232</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1356,27 +1335,27 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -1385,13 +1364,13 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="H6" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
@@ -1399,13 +1378,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -1420,21 +1399,21 @@
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>207</v>
       </c>
       <c r="J7" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1443,27 +1422,27 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>235</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -1472,27 +1451,27 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>236</v>
       </c>
       <c r="J9" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1501,27 +1480,27 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1530,42 +1509,42 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="G12" t="s">
-        <v>229</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -1573,28 +1552,28 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>204</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>229</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>205</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
@@ -1602,13 +1581,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1617,27 +1596,27 @@
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
         <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1646,85 +1625,82 @@
         <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
       </c>
-      <c r="H15" t="s">
-        <v>47</v>
-      </c>
       <c r="J15" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="J16" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="J17" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>239</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1733,27 +1709,27 @@
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>205</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="J18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1762,27 +1738,27 @@
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="J19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1797,21 +1773,21 @@
         <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="J20" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1826,24 +1802,21 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>64</v>
-      </c>
-      <c r="I21">
-        <v>28000</v>
+        <v>203</v>
       </c>
       <c r="J21" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1852,30 +1825,30 @@
         <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="I22">
         <v>28000</v>
       </c>
       <c r="J22" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1884,30 +1857,30 @@
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G23" t="s">
         <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I23">
         <v>28000</v>
       </c>
       <c r="J23" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -1916,30 +1889,30 @@
         <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="I24">
         <v>28000</v>
       </c>
       <c r="J24" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
         <v>56</v>
       </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1948,27 +1921,30 @@
         <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>55</v>
+      </c>
+      <c r="I25">
+        <v>28000</v>
       </c>
       <c r="J25" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -1977,27 +1953,27 @@
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="J26" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -2006,27 +1982,27 @@
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="J27" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -2035,27 +2011,27 @@
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="J28" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -2064,56 +2040,56 @@
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>206</v>
+        <v>64</v>
       </c>
       <c r="J29" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2122,13 +2098,13 @@
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G31" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H31" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
@@ -2136,13 +2112,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2151,13 +2127,13 @@
         <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
       </c>
       <c r="H32" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="I32">
         <v>52</v>
@@ -2168,13 +2144,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2189,7 +2165,7 @@
         <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
@@ -2197,13 +2173,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -2212,13 +2188,13 @@
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
@@ -2226,13 +2202,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -2241,13 +2217,13 @@
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
@@ -2255,13 +2231,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -2270,13 +2246,13 @@
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s">
         <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
@@ -2284,13 +2260,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -2299,13 +2275,13 @@
         <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s">
         <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
@@ -2313,13 +2289,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -2328,27 +2304,27 @@
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s">
         <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="J38" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -2357,13 +2333,13 @@
         <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s">
         <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="J39" t="s">
         <v>15</v>
@@ -2371,13 +2347,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -2386,27 +2362,27 @@
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s">
         <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J40" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2421,7 +2397,7 @@
         <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="J41" t="s">
         <v>15</v>
@@ -2429,13 +2405,13 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -2444,13 +2420,13 @@
         <v>12</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G42" t="s">
         <v>14</v>
       </c>
       <c r="H42" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s">
         <v>15</v>
@@ -2458,13 +2434,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -2473,13 +2449,13 @@
         <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G43" t="s">
         <v>14</v>
       </c>
       <c r="H43" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="J43" t="s">
         <v>15</v>
@@ -2487,13 +2463,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -2502,13 +2478,13 @@
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s">
         <v>14</v>
       </c>
       <c r="H44" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="J44" t="s">
         <v>15</v>
@@ -2516,13 +2492,13 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -2531,27 +2507,27 @@
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="G45" t="s">
         <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="J45" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="C46" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -2560,27 +2536,27 @@
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="G46" t="s">
         <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="J46" t="s">
-        <v>104</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -2595,21 +2571,18 @@
         <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>160</v>
-      </c>
-      <c r="J47" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>220</v>
+        <v>94</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -2618,24 +2591,27 @@
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s">
-        <v>221</v>
+        <v>95</v>
+      </c>
+      <c r="J48" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -2644,27 +2620,27 @@
         <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="J49" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2673,27 +2649,27 @@
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="J50" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -2702,27 +2678,27 @@
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="J51" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2731,27 +2707,27 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="G52" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -2760,56 +2736,56 @@
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E54" t="s">
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
-      </c>
-      <c r="J54" t="s">
-        <v>104</v>
+        <v>44</v>
+      </c>
+      <c r="I54">
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -2818,27 +2794,27 @@
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="H55" t="s">
-        <v>22</v>
+        <v>224</v>
       </c>
       <c r="J55" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2847,27 +2823,27 @@
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="G56" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="J56" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2876,56 +2852,56 @@
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>91</v>
+        <v>205</v>
       </c>
       <c r="G57" t="s">
         <v>14</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="J57" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E58" t="s">
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="G58" t="s">
         <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>52</v>
-      </c>
-      <c r="I58">
-        <v>49</v>
+        <v>179</v>
+      </c>
+      <c r="J58" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>242</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>243</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>244</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -2934,27 +2910,21 @@
         <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="G59" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" t="s">
-        <v>122</v>
-      </c>
-      <c r="J59" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="B60" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="C60" t="s">
-        <v>63</v>
+        <v>244</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -2963,27 +2933,21 @@
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="G60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" t="s">
-        <v>201</v>
-      </c>
-      <c r="J60" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="B61" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -2992,21 +2956,21 @@
         <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="B62" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C62" t="s">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -3015,21 +2979,21 @@
         <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="G62" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C63" t="s">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -3038,1129 +3002,1174 @@
         <v>12</v>
       </c>
       <c r="F63" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C64" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s">
+        <v>90</v>
+      </c>
+      <c r="G64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>212</v>
+      </c>
+      <c r="B65" t="s">
+        <v>243</v>
+      </c>
+      <c r="C65" t="s">
+        <v>244</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>213</v>
+      </c>
+      <c r="B66" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" t="s">
+        <v>244</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" t="s">
+        <v>90</v>
+      </c>
+      <c r="G66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>214</v>
+      </c>
+      <c r="B67" t="s">
+        <v>249</v>
+      </c>
+      <c r="C67" t="s">
+        <v>244</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>250</v>
+      </c>
+      <c r="B68" t="s">
+        <v>250</v>
+      </c>
+      <c r="C68" t="s">
+        <v>105</v>
+      </c>
+      <c r="D68" t="s">
+        <v>106</v>
+      </c>
+      <c r="E68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" t="s">
+        <v>251</v>
+      </c>
+      <c r="G68" t="s">
+        <v>69</v>
+      </c>
+      <c r="J68" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>113</v>
+      </c>
+      <c r="B69" t="s">
+        <v>113</v>
+      </c>
+      <c r="C69" t="s">
+        <v>105</v>
+      </c>
+      <c r="D69" t="s">
+        <v>106</v>
+      </c>
+      <c r="E69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" t="s">
+        <v>112</v>
+      </c>
+      <c r="G69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J69" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>163</v>
+      </c>
+      <c r="B70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C70" t="s">
+        <v>105</v>
+      </c>
+      <c r="D70" t="s">
+        <v>106</v>
+      </c>
+      <c r="E70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" t="s">
+        <v>158</v>
+      </c>
+      <c r="G70" t="s">
+        <v>134</v>
+      </c>
+      <c r="J70" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>162</v>
+      </c>
+      <c r="B71" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" t="s">
+        <v>105</v>
+      </c>
+      <c r="D71" t="s">
+        <v>106</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" t="s">
+        <v>158</v>
+      </c>
+      <c r="G71" t="s">
+        <v>69</v>
+      </c>
+      <c r="J71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>111</v>
+      </c>
+      <c r="B72" t="s">
+        <v>111</v>
+      </c>
+      <c r="C72" t="s">
+        <v>105</v>
+      </c>
+      <c r="D72" t="s">
+        <v>106</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
+        <v>112</v>
+      </c>
+      <c r="G72" t="s">
+        <v>69</v>
+      </c>
+      <c r="J72" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>156</v>
+      </c>
+      <c r="B73" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" t="s">
+        <v>106</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" t="s">
+        <v>112</v>
+      </c>
+      <c r="G73" t="s">
+        <v>69</v>
+      </c>
+      <c r="J73" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>156</v>
+      </c>
+      <c r="B74" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" t="s">
+        <v>105</v>
+      </c>
+      <c r="D74" t="s">
+        <v>106</v>
+      </c>
+      <c r="E74" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" t="s">
+        <v>112</v>
+      </c>
+      <c r="G74" t="s">
+        <v>69</v>
+      </c>
+      <c r="J74" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>156</v>
+      </c>
+      <c r="B75" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" t="s">
+        <v>105</v>
+      </c>
+      <c r="D75" t="s">
+        <v>106</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" t="s">
+        <v>112</v>
+      </c>
+      <c r="G75" t="s">
+        <v>69</v>
+      </c>
+      <c r="J75" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>156</v>
+      </c>
+      <c r="B76" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" t="s">
+        <v>105</v>
+      </c>
+      <c r="D76" t="s">
+        <v>106</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s">
+        <v>112</v>
+      </c>
+      <c r="G76" t="s">
+        <v>69</v>
+      </c>
+      <c r="J76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>114</v>
       </c>
-      <c r="D64" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" t="s">
-        <v>32</v>
-      </c>
-      <c r="G64" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>238</v>
-      </c>
-      <c r="B65" t="s">
-        <v>240</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="B77" t="s">
         <v>114</v>
       </c>
-      <c r="D65" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" t="s">
-        <v>32</v>
-      </c>
-      <c r="G65" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>238</v>
-      </c>
-      <c r="B66" t="s">
-        <v>241</v>
-      </c>
-      <c r="C66" t="s">
-        <v>114</v>
-      </c>
-      <c r="D66" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" t="s">
-        <v>32</v>
-      </c>
-      <c r="G66" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>242</v>
-      </c>
-      <c r="B67" t="s">
-        <v>238</v>
-      </c>
-      <c r="C67" t="s">
-        <v>114</v>
-      </c>
-      <c r="D67" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" t="s">
-        <v>32</v>
-      </c>
-      <c r="G67" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>243</v>
-      </c>
-      <c r="B68" t="s">
-        <v>238</v>
-      </c>
-      <c r="C68" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" t="s">
-        <v>106</v>
-      </c>
-      <c r="G68" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>244</v>
-      </c>
-      <c r="B69" t="s">
-        <v>238</v>
-      </c>
-      <c r="C69" t="s">
-        <v>114</v>
-      </c>
-      <c r="D69" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" t="s">
-        <v>32</v>
-      </c>
-      <c r="G69" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>244</v>
-      </c>
-      <c r="B70" t="s">
-        <v>245</v>
-      </c>
-      <c r="C70" t="s">
-        <v>114</v>
-      </c>
-      <c r="D70" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" t="s">
-        <v>32</v>
-      </c>
-      <c r="G70" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>246</v>
-      </c>
-      <c r="B71" t="s">
-        <v>245</v>
-      </c>
-      <c r="C71" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" t="s">
-        <v>12</v>
-      </c>
-      <c r="F71" t="s">
-        <v>32</v>
-      </c>
-      <c r="G71" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>247</v>
-      </c>
-      <c r="B72" t="s">
-        <v>233</v>
-      </c>
-      <c r="C72" t="s">
-        <v>114</v>
-      </c>
-      <c r="D72" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>248</v>
-      </c>
-      <c r="B73" t="s">
-        <v>233</v>
-      </c>
-      <c r="C73" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>249</v>
-      </c>
-      <c r="B74" t="s">
-        <v>250</v>
-      </c>
-      <c r="C74" t="s">
-        <v>114</v>
-      </c>
-      <c r="D74" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>249</v>
-      </c>
-      <c r="B75" t="s">
-        <v>251</v>
-      </c>
-      <c r="C75" t="s">
-        <v>114</v>
-      </c>
-      <c r="D75" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>249</v>
-      </c>
-      <c r="B76" t="s">
-        <v>252</v>
-      </c>
-      <c r="C76" t="s">
-        <v>114</v>
-      </c>
-      <c r="D76" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>249</v>
-      </c>
-      <c r="B77" t="s">
-        <v>253</v>
-      </c>
       <c r="C77" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D77" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E77" t="s">
         <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G77" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="J77" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>249</v>
+        <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>254</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D78" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="E78" t="s">
         <v>12</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="J78" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>249</v>
+        <v>132</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D79" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E79" t="s">
         <v>12</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G79" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+      <c r="H79" t="s">
+        <v>135</v>
+      </c>
+      <c r="J79" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="B80" t="s">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="C80" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D80" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E80" t="s">
         <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="G80" t="s">
-        <v>14</v>
+        <v>69</v>
+      </c>
+      <c r="J80" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>249</v>
+        <v>124</v>
       </c>
       <c r="B81" t="s">
-        <v>233</v>
+        <v>124</v>
       </c>
       <c r="C81" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D81" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E81" t="s">
         <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="G81" t="s">
-        <v>14</v>
+        <v>69</v>
+      </c>
+      <c r="J81" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>222</v>
+        <v>126</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D82" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E82" t="s">
         <v>12</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="G82" t="s">
-        <v>103</v>
+        <v>69</v>
+      </c>
+      <c r="J82" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>222</v>
+        <v>128</v>
       </c>
       <c r="B83" t="s">
-        <v>223</v>
+        <v>128</v>
       </c>
       <c r="C83" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E83" t="s">
         <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="G83" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="J83" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B84" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C84" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E84" t="s">
         <v>12</v>
       </c>
       <c r="F84" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="G84" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="J84" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>185</v>
+        <v>61</v>
       </c>
       <c r="B85" t="s">
-        <v>185</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E85" t="s">
         <v>12</v>
       </c>
       <c r="F85" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="G85" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="J85" t="s">
-        <v>186</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="B86" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="C86" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E86" t="s">
         <v>12</v>
       </c>
       <c r="F86" t="s">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="H86" t="s">
+        <v>137</v>
       </c>
       <c r="J86" t="s">
-        <v>176</v>
+        <v>110</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>133</v>
+        <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C87" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E87" t="s">
         <v>12</v>
       </c>
       <c r="F87" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="G87" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="H87" t="s">
+        <v>138</v>
       </c>
       <c r="J87" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="C88" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D88" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E88" t="s">
         <v>12</v>
       </c>
       <c r="F88" t="s">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="G88" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="H88" t="s">
+        <v>140</v>
       </c>
       <c r="J88" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="C89" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D89" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E89" t="s">
         <v>12</v>
       </c>
       <c r="F89" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="G89" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="H89" t="s">
+        <v>141</v>
       </c>
       <c r="J89" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="C90" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D90" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E90" t="s">
         <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="G90" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="H90" t="s">
+        <v>142</v>
       </c>
       <c r="J90" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="B91" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="C91" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E91" t="s">
         <v>12</v>
       </c>
       <c r="F91" t="s">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="G91" t="s">
-        <v>84</v>
-      </c>
-      <c r="J91" t="s">
-        <v>181</v>
+        <v>144</v>
+      </c>
+      <c r="H91" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="B92" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C92" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D92" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E92" t="s">
         <v>12</v>
       </c>
       <c r="F92" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>84</v>
-      </c>
-      <c r="J92" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="H92" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D93" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="E93" t="s">
         <v>12</v>
       </c>
       <c r="F93" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G93" t="s">
-        <v>84</v>
-      </c>
-      <c r="J93" t="s">
-        <v>176</v>
+        <v>144</v>
+      </c>
+      <c r="H93" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="B94" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C94" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D94" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E94" t="s">
         <v>12</v>
       </c>
       <c r="F94" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G94" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="H94" t="s">
-        <v>157</v>
-      </c>
-      <c r="J94" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="B95" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="C95" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D95" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E95" t="s">
         <v>12</v>
       </c>
       <c r="F95" t="s">
+        <v>54</v>
+      </c>
+      <c r="G95" t="s">
         <v>144</v>
       </c>
-      <c r="G95" t="s">
-        <v>84</v>
-      </c>
-      <c r="J95" t="s">
-        <v>208</v>
+      <c r="H95" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" t="s">
+        <v>143</v>
+      </c>
+      <c r="C96" t="s">
+        <v>105</v>
+      </c>
+      <c r="D96" t="s">
+        <v>106</v>
+      </c>
+      <c r="E96" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" t="s">
+        <v>54</v>
+      </c>
+      <c r="G96" t="s">
+        <v>134</v>
+      </c>
+      <c r="H96" t="s">
         <v>146</v>
-      </c>
-      <c r="B96" t="s">
-        <v>146</v>
-      </c>
-      <c r="C96" t="s">
-        <v>127</v>
-      </c>
-      <c r="D96" t="s">
-        <v>128</v>
-      </c>
-      <c r="E96" t="s">
-        <v>12</v>
-      </c>
-      <c r="F96" t="s">
-        <v>144</v>
-      </c>
-      <c r="G96" t="s">
-        <v>84</v>
-      </c>
-      <c r="J96" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" t="s">
+        <v>147</v>
+      </c>
+      <c r="C97" t="s">
+        <v>105</v>
+      </c>
+      <c r="D97" t="s">
+        <v>106</v>
+      </c>
+      <c r="E97" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" t="s">
         <v>148</v>
       </c>
-      <c r="B97" t="s">
-        <v>148</v>
-      </c>
-      <c r="C97" t="s">
-        <v>127</v>
-      </c>
-      <c r="D97" t="s">
-        <v>128</v>
-      </c>
-      <c r="E97" t="s">
-        <v>12</v>
-      </c>
-      <c r="F97" t="s">
-        <v>144</v>
-      </c>
-      <c r="G97" t="s">
-        <v>84</v>
-      </c>
-      <c r="J97" t="s">
-        <v>149</v>
+      <c r="H97" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C98" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="D98" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E98" t="s">
         <v>12</v>
       </c>
       <c r="F98" t="s">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="G98" t="s">
-        <v>84</v>
-      </c>
-      <c r="J98" t="s">
-        <v>152</v>
+        <v>148</v>
+      </c>
+      <c r="H98" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" t="s">
+        <v>147</v>
+      </c>
+      <c r="C99" t="s">
+        <v>105</v>
+      </c>
+      <c r="D99" t="s">
+        <v>106</v>
+      </c>
+      <c r="E99" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" t="s">
+        <v>54</v>
+      </c>
+      <c r="G99" t="s">
+        <v>148</v>
+      </c>
+      <c r="H99" t="s">
         <v>150</v>
-      </c>
-      <c r="B99" t="s">
-        <v>150</v>
-      </c>
-      <c r="C99" t="s">
-        <v>127</v>
-      </c>
-      <c r="D99" t="s">
-        <v>128</v>
-      </c>
-      <c r="E99" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" t="s">
-        <v>144</v>
-      </c>
-      <c r="G99" t="s">
-        <v>84</v>
-      </c>
-      <c r="J99" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="B100" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="C100" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D100" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E100" t="s">
         <v>12</v>
       </c>
       <c r="F100" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="G100" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="J100" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="B101" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C101" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D101" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E101" t="s">
         <v>12</v>
       </c>
       <c r="F101" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="G101" t="s">
-        <v>84</v>
-      </c>
-      <c r="H101" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="J101" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="B102" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C102" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D102" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E102" t="s">
         <v>12</v>
       </c>
       <c r="F102" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G102" t="s">
-        <v>84</v>
-      </c>
-      <c r="H102" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="J102" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="B103" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C103" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D103" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E103" t="s">
         <v>12</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="G103" t="s">
-        <v>84</v>
-      </c>
-      <c r="H103" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="J103" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="B104" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C104" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D104" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E104" t="s">
         <v>12</v>
       </c>
       <c r="F104" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="G104" t="s">
-        <v>84</v>
-      </c>
-      <c r="H104" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="J104" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="B105" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D105" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="E105" t="s">
         <v>12</v>
       </c>
       <c r="F105" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G105" t="s">
-        <v>84</v>
-      </c>
-      <c r="H105" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J105" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="B106" t="s">
+        <v>102</v>
+      </c>
+      <c r="C106" t="s">
+        <v>105</v>
+      </c>
+      <c r="D106" t="s">
         <v>165</v>
       </c>
-      <c r="C106" t="s">
-        <v>127</v>
-      </c>
-      <c r="D106" t="s">
-        <v>128</v>
-      </c>
       <c r="E106" t="s">
         <v>12</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="G106" t="s">
-        <v>166</v>
-      </c>
-      <c r="H106" t="s">
-        <v>167</v>
+        <v>148</v>
+      </c>
+      <c r="J106" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="B107" t="s">
+        <v>102</v>
+      </c>
+      <c r="C107" t="s">
+        <v>105</v>
+      </c>
+      <c r="D107" t="s">
         <v>165</v>
       </c>
-      <c r="C107" t="s">
-        <v>127</v>
-      </c>
-      <c r="D107" t="s">
-        <v>128</v>
-      </c>
       <c r="E107" t="s">
         <v>12</v>
       </c>
       <c r="F107" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="G107" t="s">
-        <v>156</v>
-      </c>
-      <c r="H107" t="s">
-        <v>167</v>
+        <v>148</v>
+      </c>
+      <c r="J107" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="B108" t="s">
+        <v>171</v>
+      </c>
+      <c r="C108" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" t="s">
         <v>165</v>
-      </c>
-      <c r="C108" t="s">
-        <v>127</v>
-      </c>
-      <c r="D108" t="s">
-        <v>128</v>
       </c>
       <c r="E108" t="s">
         <v>12</v>
@@ -4169,241 +4178,241 @@
         <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>166</v>
-      </c>
-      <c r="H108" t="s">
-        <v>86</v>
+        <v>148</v>
+      </c>
+      <c r="J108" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="B109" t="s">
+        <v>171</v>
+      </c>
+      <c r="C109" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" t="s">
         <v>165</v>
       </c>
-      <c r="C109" t="s">
-        <v>127</v>
-      </c>
-      <c r="D109" t="s">
-        <v>128</v>
-      </c>
       <c r="E109" t="s">
         <v>12</v>
       </c>
       <c r="F109" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G109" t="s">
-        <v>156</v>
-      </c>
-      <c r="H109" t="s">
-        <v>86</v>
+        <v>148</v>
+      </c>
+      <c r="J109" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="B110" t="s">
+        <v>171</v>
+      </c>
+      <c r="C110" t="s">
+        <v>105</v>
+      </c>
+      <c r="D110" t="s">
         <v>165</v>
       </c>
-      <c r="C110" t="s">
-        <v>127</v>
-      </c>
-      <c r="D110" t="s">
-        <v>128</v>
-      </c>
       <c r="E110" t="s">
         <v>12</v>
       </c>
       <c r="F110" t="s">
-        <v>66</v>
+        <v>172</v>
       </c>
       <c r="G110" t="s">
-        <v>166</v>
-      </c>
-      <c r="H110" t="s">
-        <v>168</v>
+        <v>148</v>
+      </c>
+      <c r="J110" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="B111" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="C111" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D111" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E111" t="s">
         <v>12</v>
       </c>
       <c r="F111" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G111" t="s">
-        <v>156</v>
-      </c>
-      <c r="H111" t="s">
-        <v>168</v>
+        <v>69</v>
+      </c>
+      <c r="J111" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="B112" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="C112" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D112" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E112" t="s">
         <v>12</v>
       </c>
       <c r="F112" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="G112" t="s">
-        <v>170</v>
-      </c>
-      <c r="H112" t="s">
-        <v>160</v>
+        <v>69</v>
+      </c>
+      <c r="J112" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="B113" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="C113" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D113" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E113" t="s">
         <v>12</v>
       </c>
       <c r="F113" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G113" t="s">
-        <v>170</v>
-      </c>
-      <c r="H113" t="s">
-        <v>171</v>
+        <v>69</v>
+      </c>
+      <c r="J113" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B114" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D114" t="s">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="E114" t="s">
         <v>12</v>
       </c>
       <c r="F114" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="G114" t="s">
-        <v>170</v>
-      </c>
-      <c r="H114" t="s">
-        <v>172</v>
+        <v>196</v>
+      </c>
+      <c r="J114" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B115" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C115" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D115" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E115" t="s">
         <v>12</v>
       </c>
       <c r="F115" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="G115" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="J115" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B116" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="C116" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D116" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E116" t="s">
         <v>12</v>
       </c>
       <c r="F116" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="G116" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="J116" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B117" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="C117" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D117" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E117" t="s">
         <v>12</v>
       </c>
       <c r="F117" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G117" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="J117" t="s">
         <v>177</v>
@@ -4411,737 +4420,347 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B118" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C118" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D118" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E118" t="s">
         <v>12</v>
       </c>
       <c r="F118" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="G118" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="J118" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B119" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C119" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D119" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E119" t="s">
         <v>12</v>
       </c>
       <c r="F119" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="G119" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="J119" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="B120" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C120" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D120" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="E120" t="s">
         <v>12</v>
       </c>
       <c r="F120" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G120" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="J120" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="B121" t="s">
-        <v>124</v>
+        <v>198</v>
       </c>
       <c r="C121" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D121" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="E121" t="s">
         <v>12</v>
       </c>
       <c r="F121" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="G121" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="J121" t="s">
-        <v>191</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="B122" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C122" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D122" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="E122" t="s">
         <v>12</v>
       </c>
       <c r="F122" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="G122" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="J122" t="s">
-        <v>191</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>193</v>
+        <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="C123" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D123" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="E123" t="s">
         <v>12</v>
       </c>
       <c r="F123" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G123" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="J123" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="B124" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="C124" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D124" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="E124" t="s">
         <v>12</v>
       </c>
       <c r="F124" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="G124" t="s">
-        <v>170</v>
+        <v>69</v>
+      </c>
+      <c r="H124" t="s">
+        <v>201</v>
       </c>
       <c r="J124" t="s">
-        <v>132</v>
+        <v>202</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="B125" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="C125" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D125" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="E125" t="s">
         <v>12</v>
       </c>
       <c r="F125" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="G125" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="J125" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="B126" t="s">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="C126" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D126" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E126" t="s">
         <v>12</v>
       </c>
       <c r="F126" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="G126" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="J126" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="C127" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D127" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E127" t="s">
         <v>12</v>
       </c>
       <c r="F127" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="G127" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="J127" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="C128" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D128" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E128" t="s">
         <v>12</v>
       </c>
       <c r="F128" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="G128" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="J128" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="B129" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="C129" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D129" t="s">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="E129" t="s">
         <v>12</v>
       </c>
       <c r="F129" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="G129" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="J129" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="B130" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="C130" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D130" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="E130" t="s">
         <v>12</v>
       </c>
       <c r="F130" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="G130" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="J130" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>198</v>
-      </c>
-      <c r="B131" t="s">
-        <v>210</v>
-      </c>
-      <c r="C131" t="s">
-        <v>127</v>
-      </c>
-      <c r="D131" t="s">
-        <v>128</v>
-      </c>
-      <c r="E131" t="s">
-        <v>12</v>
-      </c>
-      <c r="F131" t="s">
-        <v>92</v>
-      </c>
-      <c r="G131" t="s">
-        <v>84</v>
-      </c>
-      <c r="J131" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>198</v>
-      </c>
-      <c r="B132" t="s">
-        <v>211</v>
-      </c>
-      <c r="C132" t="s">
-        <v>127</v>
-      </c>
-      <c r="D132" t="s">
-        <v>128</v>
-      </c>
-      <c r="E132" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" t="s">
-        <v>92</v>
-      </c>
-      <c r="G132" t="s">
-        <v>84</v>
-      </c>
-      <c r="J132" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>198</v>
-      </c>
-      <c r="B133" t="s">
-        <v>212</v>
-      </c>
-      <c r="C133" t="s">
-        <v>127</v>
-      </c>
-      <c r="D133" t="s">
-        <v>128</v>
-      </c>
-      <c r="E133" t="s">
-        <v>12</v>
-      </c>
-      <c r="F133" t="s">
-        <v>92</v>
-      </c>
-      <c r="G133" t="s">
-        <v>84</v>
-      </c>
-      <c r="J133" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>198</v>
-      </c>
-      <c r="B134" t="s">
-        <v>213</v>
-      </c>
-      <c r="C134" t="s">
-        <v>127</v>
-      </c>
-      <c r="D134" t="s">
-        <v>128</v>
-      </c>
-      <c r="E134" t="s">
-        <v>12</v>
-      </c>
-      <c r="F134" t="s">
-        <v>92</v>
-      </c>
-      <c r="G134" t="s">
-        <v>84</v>
-      </c>
-      <c r="J134" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>198</v>
-      </c>
-      <c r="B135" t="s">
-        <v>130</v>
-      </c>
-      <c r="C135" t="s">
-        <v>127</v>
-      </c>
-      <c r="D135" t="s">
-        <v>128</v>
-      </c>
-      <c r="E135" t="s">
-        <v>12</v>
-      </c>
-      <c r="F135" t="s">
-        <v>92</v>
-      </c>
-      <c r="G135" t="s">
-        <v>84</v>
-      </c>
-      <c r="J135" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>69</v>
-      </c>
-      <c r="B136" t="s">
-        <v>227</v>
-      </c>
-      <c r="C136" t="s">
-        <v>127</v>
-      </c>
-      <c r="D136" t="s">
-        <v>128</v>
-      </c>
-      <c r="E136" t="s">
-        <v>12</v>
-      </c>
-      <c r="F136" t="s">
-        <v>46</v>
-      </c>
-      <c r="G136" t="s">
-        <v>84</v>
-      </c>
-      <c r="J136" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>69</v>
-      </c>
-      <c r="B137" t="s">
-        <v>126</v>
-      </c>
-      <c r="C137" t="s">
-        <v>127</v>
-      </c>
-      <c r="D137" t="s">
-        <v>128</v>
-      </c>
-      <c r="E137" t="s">
-        <v>12</v>
-      </c>
-      <c r="F137" t="s">
-        <v>46</v>
-      </c>
-      <c r="G137" t="s">
-        <v>84</v>
-      </c>
-      <c r="J137" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>69</v>
-      </c>
-      <c r="B138" t="s">
-        <v>130</v>
-      </c>
-      <c r="C138" t="s">
-        <v>127</v>
-      </c>
-      <c r="D138" t="s">
-        <v>128</v>
-      </c>
-      <c r="E138" t="s">
-        <v>12</v>
-      </c>
-      <c r="F138" t="s">
-        <v>46</v>
-      </c>
-      <c r="G138" t="s">
-        <v>84</v>
-      </c>
-      <c r="J138" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>10</v>
-      </c>
-      <c r="B139" t="s">
-        <v>173</v>
-      </c>
-      <c r="C139" t="s">
-        <v>127</v>
-      </c>
-      <c r="D139" t="s">
-        <v>128</v>
-      </c>
-      <c r="E139" t="s">
-        <v>12</v>
-      </c>
-      <c r="F139" t="s">
-        <v>13</v>
-      </c>
-      <c r="G139" t="s">
-        <v>84</v>
-      </c>
-      <c r="H139" t="s">
-        <v>257</v>
-      </c>
-      <c r="J139" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>142</v>
-      </c>
-      <c r="B140" t="s">
-        <v>142</v>
-      </c>
-      <c r="C140" t="s">
-        <v>127</v>
-      </c>
-      <c r="D140" t="s">
-        <v>128</v>
-      </c>
-      <c r="E140" t="s">
-        <v>12</v>
-      </c>
-      <c r="F140" t="s">
-        <v>134</v>
-      </c>
-      <c r="G140" t="s">
-        <v>84</v>
-      </c>
-      <c r="J140" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>140</v>
-      </c>
-      <c r="B141" t="s">
-        <v>140</v>
-      </c>
-      <c r="C141" t="s">
-        <v>127</v>
-      </c>
-      <c r="D141" t="s">
-        <v>128</v>
-      </c>
-      <c r="E141" t="s">
-        <v>12</v>
-      </c>
-      <c r="F141" t="s">
-        <v>30</v>
-      </c>
-      <c r="G141" t="s">
-        <v>84</v>
-      </c>
-      <c r="J141" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>197</v>
-      </c>
-      <c r="B142" t="s">
-        <v>197</v>
-      </c>
-      <c r="C142" t="s">
-        <v>127</v>
-      </c>
-      <c r="D142" t="s">
-        <v>128</v>
-      </c>
-      <c r="E142" t="s">
-        <v>12</v>
-      </c>
-      <c r="F142" t="s">
-        <v>37</v>
-      </c>
-      <c r="G142" t="s">
-        <v>156</v>
-      </c>
-      <c r="J142" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>197</v>
-      </c>
-      <c r="B143" t="s">
-        <v>197</v>
-      </c>
-      <c r="C143" t="s">
-        <v>127</v>
-      </c>
-      <c r="D143" t="s">
-        <v>128</v>
-      </c>
-      <c r="E143" t="s">
-        <v>12</v>
-      </c>
-      <c r="F143" t="s">
-        <v>190</v>
-      </c>
-      <c r="G143" t="s">
-        <v>156</v>
-      </c>
-      <c r="J143" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>195</v>
-      </c>
-      <c r="B144" t="s">
-        <v>195</v>
-      </c>
-      <c r="C144" t="s">
-        <v>127</v>
-      </c>
-      <c r="D144" t="s">
-        <v>187</v>
-      </c>
-      <c r="E144" t="s">
-        <v>12</v>
-      </c>
-      <c r="F144" t="s">
-        <v>83</v>
-      </c>
-      <c r="G144" t="s">
-        <v>156</v>
-      </c>
-      <c r="J144" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>195</v>
-      </c>
-      <c r="B145" t="s">
-        <v>195</v>
-      </c>
-      <c r="C145" t="s">
-        <v>127</v>
-      </c>
-      <c r="D145" t="s">
-        <v>187</v>
-      </c>
-      <c r="E145" t="s">
-        <v>12</v>
-      </c>
-      <c r="F145" t="s">
-        <v>79</v>
-      </c>
-      <c r="G145" t="s">
-        <v>156</v>
-      </c>
-      <c r="J145" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J145" xr:uid="{E0629895-8555-4DE5-8A98-86473C65DDE6}"/>
+  <autoFilter ref="A1:J130" xr:uid="{E0629895-8555-4DE5-8A98-86473C65DDE6}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>